--- a/AAII_Financials/Quarterly/KRG_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/KRG_QTR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Quarterly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Quarterly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,12 +17,12 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="154" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="156" uniqueCount="92">
   <si>
     <t>KRG</t>
   </si>
@@ -656,416 +656,428 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AF102"/>
+  <dimension ref="A5:AG102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:33" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E7" s="2">
         <v>45199</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45107</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45016</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44926</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44834</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44742</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44651</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44561</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44469</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44377</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44286</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44196</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44104</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44012</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>43921</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>43830</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43738</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43646</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43555</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43465</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43373</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43281</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43190</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43100</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43008</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>42916</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>42825</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>42735</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>200300</v>
+      </c>
+      <c r="E8" s="3">
         <v>207200</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>208800</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>206800</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>204700</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>200300</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>202600</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>194400</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>163000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>71500</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>69500</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>69400</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>68400</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>65100</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>63300</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>69900</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>75200</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>74900</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>81500</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>83500</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>86900</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>85700</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>91700</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>89800</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>88900</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>87100</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>92600</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>90100</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>88900</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>89100</v>
       </c>
     </row>
-    <row r="9" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>47900</v>
+      </c>
+      <c r="E9" s="3">
         <v>54100</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>53900</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>54500</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>53800</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>51200</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>54000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>52800</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>47500</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>19100</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>18800</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>19700</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>19900</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>19700</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>17600</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>19700</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>20600</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>20700</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>21400</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>21600</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>23200</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>23300</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>23000</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>23200</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>23500</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>22700</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>23400</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>23300</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>23000</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>22600</v>
       </c>
     </row>
-    <row r="10" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>152400</v>
+      </c>
+      <c r="E10" s="3">
         <v>153100</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>154900</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>152300</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>150900</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>149100</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>148600</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>141600</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>115500</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>52400</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>50700</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>49700</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>48500</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>45400</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>45700</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>50200</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>54600</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>54200</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>60100</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>61900</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>63700</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>62400</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>68700</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>66600</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>65400</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>64400</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>69200</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>66800</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>65900</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>66500</v>
       </c>
     </row>
-    <row r="11" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1098,8 +1110,9 @@
       <c r="AD11" s="3"/>
       <c r="AE11" s="3"/>
       <c r="AF11" s="3"/>
-    </row>
-    <row r="12" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG11" s="3"/>
+    </row>
+    <row r="12" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1190,8 +1203,11 @@
       <c r="AF12" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG12" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1282,47 +1298,50 @@
       <c r="AF13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>0</v>
+      </c>
+      <c r="E14" s="3">
         <v>500</v>
       </c>
-      <c r="E14" s="3">
-        <v>0</v>
-      </c>
       <c r="F14" s="3">
         <v>0</v>
       </c>
       <c r="G14" s="3">
+        <v>0</v>
+      </c>
+      <c r="H14" s="3">
         <v>-100</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>100</v>
       </c>
-      <c r="I14" s="3">
-        <v>0</v>
-      </c>
       <c r="J14" s="3">
+        <v>0</v>
+      </c>
+      <c r="K14" s="3">
         <v>900</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>76600</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>9200</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>800</v>
       </c>
-      <c r="N14" s="3" t="s">
+      <c r="O14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O14" s="3">
-        <v>0</v>
-      </c>
       <c r="P14" s="3">
         <v>0</v>
       </c>
@@ -1333,32 +1352,32 @@
         <v>0</v>
       </c>
       <c r="S14" s="3">
+        <v>0</v>
+      </c>
+      <c r="T14" s="3">
         <v>2000</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>15600</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>27700</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>4100</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>31500</v>
       </c>
-      <c r="X14" s="3">
-        <v>0</v>
-      </c>
       <c r="Y14" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z14" s="3">
         <v>14800</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AA14" s="3">
         <v>24100</v>
       </c>
-      <c r="AA14" s="3">
-        <v>0</v>
-      </c>
       <c r="AB14" s="3">
         <v>0</v>
       </c>
@@ -1366,108 +1385,114 @@
         <v>0</v>
       </c>
       <c r="AD14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE14" s="3">
         <v>7400</v>
       </c>
-      <c r="AE14" s="3">
+      <c r="AF14" s="3">
         <v>2800</v>
       </c>
-      <c r="AF14" s="3" t="s">
+      <c r="AG14" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="15" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>102900</v>
+      </c>
+      <c r="E15" s="3">
         <v>105900</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>109500</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>108100</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>112700</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>115800</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>119800</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>121500</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>109800</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>30200</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>29800</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>30600</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>31800</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>34000</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>31400</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>31500</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>30800</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>32000</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>34700</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>34600</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>36300</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>36900</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="Z15" s="3">
         <v>40500</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AA15" s="3">
         <v>38600</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AB15" s="3">
         <v>40800</v>
       </c>
-      <c r="AB15" s="3">
+      <c r="AC15" s="3">
         <v>42800</v>
       </c>
-      <c r="AC15" s="3">
+      <c r="AD15" s="3">
         <v>42700</v>
       </c>
-      <c r="AD15" s="3">
+      <c r="AE15" s="3">
         <v>45800</v>
       </c>
-      <c r="AE15" s="3">
+      <c r="AF15" s="3">
         <v>42900</v>
       </c>
-      <c r="AF15" s="3">
+      <c r="AG15" s="3">
         <v>45500</v>
       </c>
     </row>
-    <row r="16" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:33" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1497,192 +1522,199 @@
       <c r="AD16" s="3"/>
       <c r="AE16" s="3"/>
       <c r="AF16" s="3"/>
-    </row>
-    <row r="17" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG16" s="3"/>
+    </row>
+    <row r="17" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>165000</v>
+      </c>
+      <c r="E17" s="3">
         <v>180400</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>149500</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>176000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>179400</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>182000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>163600</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>185400</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>240600</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>65500</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>57400</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>31400</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>62700</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>56900</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>54900</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>57100</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>47000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>80700</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>66700</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>60500</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>92500</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>65000</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>83800</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>91800</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>54400</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>70900</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>71600</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>82000</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>71300</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>73200</v>
       </c>
     </row>
-    <row r="18" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>35300</v>
+      </c>
+      <c r="E18" s="3">
         <v>26800</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>59400</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>30800</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>25300</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>18300</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>39000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>9000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-77600</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>6000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>12100</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>38000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>5700</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>8200</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>8400</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>12800</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>28200</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-5800</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>14800</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>23000</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>-5600</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>20700</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>7900</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>-2000</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>34500</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>16200</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>21000</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>8100</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>17600</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>15900</v>
       </c>
     </row>
-    <row r="19" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1715,55 +1747,56 @@
       <c r="AD19" s="3"/>
       <c r="AE19" s="3"/>
       <c r="AF19" s="3"/>
-    </row>
-    <row r="20" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG19" s="3"/>
+    </row>
+    <row r="20" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>300</v>
+      </c>
+      <c r="E20" s="3">
         <v>1000</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>300</v>
-      </c>
-      <c r="F20" s="3">
-        <v>400</v>
       </c>
       <c r="G20" s="3">
         <v>400</v>
       </c>
       <c r="H20" s="3">
+        <v>400</v>
+      </c>
+      <c r="I20" s="3">
         <v>100</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-200</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-100</v>
-      </c>
-      <c r="K20" s="3">
-        <v>100</v>
       </c>
       <c r="L20" s="3">
         <v>100</v>
       </c>
       <c r="M20" s="3">
+        <v>100</v>
+      </c>
+      <c r="N20" s="3">
         <v>300</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-200</v>
       </c>
-      <c r="O20" s="3">
-        <v>0</v>
-      </c>
       <c r="P20" s="3">
         <v>0</v>
       </c>
       <c r="Q20" s="3">
+        <v>0</v>
+      </c>
+      <c r="R20" s="3">
         <v>400</v>
-      </c>
-      <c r="R20" s="3">
-        <v>-100</v>
       </c>
       <c r="S20" s="3">
         <v>-100</v>
@@ -1772,212 +1805,218 @@
         <v>-100</v>
       </c>
       <c r="U20" s="3">
-        <v>-200</v>
+        <v>-100</v>
       </c>
       <c r="V20" s="3">
         <v>-200</v>
       </c>
       <c r="W20" s="3">
+        <v>-200</v>
+      </c>
+      <c r="X20" s="3">
         <v>-8300</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-300</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>7700</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>300</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>-15200</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>-100</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>6300</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>8700</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>4000</v>
       </c>
-      <c r="AF20" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG20" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>139500</v>
+      </c>
+      <c r="E21" s="3">
         <v>134600</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>170000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>140200</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>139500</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>135000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>158200</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>132200</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>33100</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>37000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>42900</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>69000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>38000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>42600</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>40700</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>44800</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>59500</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>26800</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>50200</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>58100</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>24100</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>57900</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>57000</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>37500</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>60600</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>59600</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>70700</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>63200</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>65300</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>63500</v>
       </c>
     </row>
-    <row r="22" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>27200</v>
+      </c>
+      <c r="E22" s="3">
         <v>25500</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>27200</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>25400</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>26800</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>26200</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>25700</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>25500</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>23100</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>12900</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>12300</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>12200</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>12300</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>12600</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>13300</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>12300</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>12400</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>14300</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>16100</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>16500</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>17600</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>16100</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>16700</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>16300</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>16500</v>
-      </c>
-      <c r="AB22" s="3">
-        <v>16400</v>
       </c>
       <c r="AC22" s="3">
         <v>16400</v>
@@ -1986,134 +2025,140 @@
         <v>16400</v>
       </c>
       <c r="AE22" s="3">
+        <v>16400</v>
+      </c>
+      <c r="AF22" s="3">
         <v>17600</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>17100</v>
       </c>
     </row>
-    <row r="23" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>8400</v>
+      </c>
+      <c r="E23" s="3">
         <v>2300</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>32400</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>5800</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-1100</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-7900</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>13100</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-16600</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-100500</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-6700</v>
       </c>
-      <c r="M23" s="3">
-        <v>0</v>
-      </c>
       <c r="N23" s="3">
+        <v>0</v>
+      </c>
+      <c r="O23" s="3">
         <v>25600</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-6600</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-4400</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-4600</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>400</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>15700</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-20100</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-1500</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>6300</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-31600</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>4300</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-1100</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>-18000</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>2800</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>-200</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>10900</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>400</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>4000</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>-1200</v>
       </c>
     </row>
-    <row r="24" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>400</v>
+      </c>
+      <c r="E24" s="3">
         <v>100</v>
       </c>
-      <c r="E24" s="3">
-        <v>0</v>
-      </c>
       <c r="F24" s="3">
         <v>0</v>
       </c>
       <c r="G24" s="3">
+        <v>0</v>
+      </c>
+      <c r="H24" s="3">
         <v>300</v>
       </c>
-      <c r="H24" s="3">
-        <v>0</v>
-      </c>
       <c r="I24" s="3">
+        <v>0</v>
+      </c>
+      <c r="J24" s="3">
         <v>-200</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>-100</v>
       </c>
-      <c r="K24" s="3">
-        <v>0</v>
-      </c>
       <c r="L24" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="M24" s="3">
         <v>-100</v>
@@ -2122,7 +2167,7 @@
         <v>-100</v>
       </c>
       <c r="O24" s="3">
-        <v>-200</v>
+        <v>-100</v>
       </c>
       <c r="P24" s="3">
         <v>-200</v>
@@ -2131,16 +2176,16 @@
         <v>-200</v>
       </c>
       <c r="R24" s="3">
-        <v>-100</v>
+        <v>-200</v>
       </c>
       <c r="S24" s="3">
         <v>-100</v>
       </c>
       <c r="T24" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="U24" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="V24" s="3">
         <v>-100</v>
@@ -2149,7 +2194,7 @@
         <v>-100</v>
       </c>
       <c r="X24" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="Y24" s="3">
         <v>0</v>
@@ -2170,13 +2215,16 @@
         <v>0</v>
       </c>
       <c r="AE24" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF24" s="3">
         <v>100</v>
       </c>
-      <c r="AF24" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2267,192 +2315,201 @@
       <c r="AF25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>8000</v>
+      </c>
+      <c r="E26" s="3">
         <v>2200</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>32400</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>5800</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-1400</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-7900</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>13300</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-16500</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-100500</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-6600</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>100</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>25700</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-6400</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-4200</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-4400</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>500</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>15800</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-20100</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-1500</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>6400</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-31400</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>4300</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-1100</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>-18000</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>2800</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>-200</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>10900</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>400</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>3900</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>-1300</v>
       </c>
     </row>
-    <row r="27" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>8000</v>
+      </c>
+      <c r="E27" s="3">
         <v>2100</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>32100</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>5400</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-1100</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-7800</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>13100</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-16800</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-98200</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-7000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-200</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>24600</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-6800</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-4600</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-4800</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-100</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>15300</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-19700</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-1800</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>5700</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-31200</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>3900</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-1400</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>-17900</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>2300</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>-600</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>10200</v>
       </c>
-      <c r="AD27" s="3">
-        <v>0</v>
-      </c>
       <c r="AE27" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF27" s="3">
         <v>3400</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>-1700</v>
       </c>
     </row>
-    <row r="28" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2543,8 +2600,11 @@
       <c r="AF28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2617,8 +2677,8 @@
       <c r="Z29" s="3">
         <v>0</v>
       </c>
-      <c r="AA29" s="3" t="s">
-        <v>8</v>
+      <c r="AA29" s="3">
+        <v>0</v>
       </c>
       <c r="AB29" s="3" t="s">
         <v>8</v>
@@ -2629,14 +2689,17 @@
       <c r="AD29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AE29" s="3">
-        <v>0</v>
-      </c>
-      <c r="AF29" s="3" t="s">
+      <c r="AE29" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="30" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AF29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG29" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="30" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2727,8 +2790,11 @@
       <c r="AF30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2819,55 +2885,58 @@
       <c r="AF31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-300</v>
+      </c>
+      <c r="E32" s="3">
         <v>-1000</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-300</v>
-      </c>
-      <c r="F32" s="3">
-        <v>-400</v>
       </c>
       <c r="G32" s="3">
         <v>-400</v>
       </c>
       <c r="H32" s="3">
+        <v>-400</v>
+      </c>
+      <c r="I32" s="3">
         <v>-100</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>200</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>100</v>
-      </c>
-      <c r="K32" s="3">
-        <v>-100</v>
       </c>
       <c r="L32" s="3">
         <v>-100</v>
       </c>
       <c r="M32" s="3">
+        <v>-100</v>
+      </c>
+      <c r="N32" s="3">
         <v>-300</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>200</v>
       </c>
-      <c r="O32" s="3">
-        <v>0</v>
-      </c>
       <c r="P32" s="3">
         <v>0</v>
       </c>
       <c r="Q32" s="3">
+        <v>0</v>
+      </c>
+      <c r="R32" s="3">
         <v>-400</v>
-      </c>
-      <c r="R32" s="3">
-        <v>100</v>
       </c>
       <c r="S32" s="3">
         <v>100</v>
@@ -2876,135 +2945,141 @@
         <v>100</v>
       </c>
       <c r="U32" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="V32" s="3">
         <v>200</v>
       </c>
       <c r="W32" s="3">
+        <v>200</v>
+      </c>
+      <c r="X32" s="3">
         <v>8300</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>300</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-7700</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-300</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>15200</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>100</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>-6300</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>-8700</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>-4000</v>
       </c>
-      <c r="AF32" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="33" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG32" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>8000</v>
+      </c>
+      <c r="E33" s="3">
         <v>2100</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>32100</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>5400</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-1100</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-7800</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>13100</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-16800</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-98200</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-7000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-200</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>24600</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-6800</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-4600</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-4800</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-100</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>15300</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-19700</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-1800</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>5700</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-31200</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>3900</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-1400</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-17900</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>2300</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>-600</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>10200</v>
       </c>
-      <c r="AD33" s="3">
-        <v>0</v>
-      </c>
       <c r="AE33" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF33" s="3">
         <v>3400</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>-1700</v>
       </c>
     </row>
-    <row r="34" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3095,197 +3170,206 @@
       <c r="AF34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>8000</v>
+      </c>
+      <c r="E35" s="3">
         <v>2100</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>32100</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>5400</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-1100</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-7800</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>13100</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-16800</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-98200</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-7000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-200</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>24600</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-6800</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-4600</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-4800</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-100</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>15300</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-19700</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-1800</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>5700</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-31200</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>3900</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-1400</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-17900</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>2300</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>-600</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>10200</v>
       </c>
-      <c r="AD35" s="3">
-        <v>0</v>
-      </c>
       <c r="AE35" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF35" s="3">
         <v>3400</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>-1700</v>
       </c>
     </row>
-    <row r="37" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:33" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E38" s="2">
         <v>45199</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45107</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45016</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44926</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44834</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44742</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44651</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44561</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44469</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44377</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44286</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44196</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44104</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44012</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>43921</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>43830</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43738</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43646</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43555</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43465</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43373</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43281</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43190</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43100</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43008</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>42916</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>42825</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>42735</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3318,8 +3402,9 @@
       <c r="AD39" s="3"/>
       <c r="AE39" s="3"/>
       <c r="AF39" s="3"/>
-    </row>
-    <row r="40" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG39" s="3"/>
+    </row>
+    <row r="40" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3352,100 +3437,104 @@
       <c r="AD40" s="3"/>
       <c r="AE40" s="3"/>
       <c r="AF40" s="3"/>
-    </row>
-    <row r="41" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG40" s="3"/>
+    </row>
+    <row r="41" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>36400</v>
+      </c>
+      <c r="E41" s="3">
         <v>52300</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>129300</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>43700</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>115800</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>88400</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>90800</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>74300</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>93200</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>99500</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>89900</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>228800</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>43600</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>129300</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>230000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>343900</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>31300</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>40400</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>35800</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>28400</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>35400</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>30700</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>32400</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>28800</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>24100</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>32500</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>27600</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>22600</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>19900</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>28800</v>
       </c>
     </row>
-    <row r="42" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3536,100 +3625,106 @@
       <c r="AF42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>113300</v>
+      </c>
+      <c r="E43" s="3">
         <v>113100</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>109600</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>103500</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>101300</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>86600</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>76900</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>69100</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>68400</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>45900</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>46700</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>49100</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>57200</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>57100</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>61600</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>49900</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>55300</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>50000</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>52000</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>55400</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>58100</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>57100</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>53100</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>57200</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>58300</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>53300</v>
-      </c>
-      <c r="AC43" s="3">
-        <v>52300</v>
       </c>
       <c r="AD43" s="3">
         <v>52300</v>
       </c>
       <c r="AE43" s="3">
+        <v>52300</v>
+      </c>
+      <c r="AF43" s="3">
         <v>53100</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>50400</v>
       </c>
     </row>
-    <row r="44" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3720,100 +3815,106 @@
       <c r="AF44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>117800</v>
+      </c>
+      <c r="E45" s="3">
         <v>134600</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>130500</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>117400</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>127000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>142800</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>106000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>96300</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>84800</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>39200</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>39500</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>42900</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>13000</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>39300</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>38200</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>36300</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>7500</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>10100</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>10300</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>14100</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>12800</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>17400</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>14200</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>20300</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>16400</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>12800</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>10200</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>12800</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>9700</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>10800</v>
       </c>
     </row>
-    <row r="46" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
@@ -3904,79 +4005,82 @@
       <c r="AF46" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="47" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG46" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>9100</v>
+      </c>
+      <c r="E47" s="3">
         <v>10200</v>
-      </c>
-      <c r="E47" s="3">
-        <v>10300</v>
       </c>
       <c r="F47" s="3">
         <v>10300</v>
       </c>
       <c r="G47" s="3">
+        <v>10300</v>
+      </c>
+      <c r="H47" s="3">
         <v>10400</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>10600</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>10400</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>136800</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>136900</v>
-      </c>
-      <c r="L47" s="3">
-        <v>138000</v>
       </c>
       <c r="M47" s="3">
         <v>138000</v>
       </c>
       <c r="N47" s="3">
+        <v>138000</v>
+      </c>
+      <c r="O47" s="3">
         <v>13000</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>12800</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>13100</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>13200</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>12100</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>12600</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>12900</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>12700</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>13300</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>13500</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>13800</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>13900</v>
-      </c>
-      <c r="Z47" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AA47" s="3" t="s">
         <v>8</v>
@@ -3996,100 +4100,106 @@
       <c r="AF47" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="48" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG47" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="48" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>6358300</v>
+      </c>
+      <c r="E48" s="3">
         <v>6397300</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>6426100</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>6508700</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>6571400</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>6621600</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>6617800</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>6676800</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>6707500</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>2308000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>2343700</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>2358900</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>2415900</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>2347400</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>2380500</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>2404000</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>2447400</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>2514100</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>2716800</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>2911300</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>2941200</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>3051700</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>3076800</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>3194200</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>3293300</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>3320300</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>3331800</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>3399700</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>3435400</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>3458300</v>
       </c>
     </row>
-    <row r="49" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -4157,31 +4267,34 @@
         <v>0</v>
       </c>
       <c r="Y49" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z49" s="3">
         <v>32300</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>39000</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>44000</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>47900</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>53000</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>59300</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>65500</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>70000</v>
       </c>
     </row>
-    <row r="50" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4272,8 +4385,11 @@
       <c r="AF50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4364,100 +4480,106 @@
       <c r="AF51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>309200</v>
+      </c>
+      <c r="E52" s="3">
         <v>345000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>359400</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>413200</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>416000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>450000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>483000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>520300</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>548600</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>78400</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>61400</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>62600</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>66100</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>71900</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>88300</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>91300</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>94600</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>86300</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>108700</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>180800</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>111100</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>115100</v>
-      </c>
-      <c r="Y52" s="3">
-        <v>79400</v>
       </c>
       <c r="Z52" s="3">
         <v>79400</v>
       </c>
       <c r="AA52" s="3">
+        <v>79400</v>
+      </c>
+      <c r="AB52" s="3">
         <v>76400</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>76600</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>75400</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>76700</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>72800</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>72700</v>
       </c>
     </row>
-    <row r="53" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4548,100 +4670,106 @@
       <c r="AF53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>6944100</v>
+      </c>
+      <c r="E54" s="3">
         <v>7052500</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>7165100</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>7196900</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>7342000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>7399900</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>7384900</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>7573700</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>7639600</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>2708900</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>2719200</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>2755300</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>2608500</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>2658100</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>2811800</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>2937400</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>2648900</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>2713900</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>2936300</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>3203200</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>3172000</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>3285900</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>3302200</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>3418900</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>3512500</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>3543400</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>3550300</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>3623500</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>3656400</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>3690900</v>
       </c>
     </row>
-    <row r="55" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4674,8 +4802,9 @@
       <c r="AD55" s="3"/>
       <c r="AE55" s="3"/>
       <c r="AF55" s="3"/>
-    </row>
-    <row r="56" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG55" s="3"/>
+    </row>
+    <row r="56" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4708,100 +4837,104 @@
       <c r="AD56" s="3"/>
       <c r="AE56" s="3"/>
       <c r="AF56" s="3"/>
-    </row>
-    <row r="57" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG56" s="3"/>
+    </row>
+    <row r="57" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>198100</v>
+      </c>
+      <c r="E57" s="3">
         <v>198500</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>178200</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>160100</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>207800</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>152000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>133800</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>124200</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>185000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>85700</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>74400</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>72100</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>77500</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>88600</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>85700</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>109400</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>69800</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>77500</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>66600</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>61900</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>85900</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>98500</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>101200</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>102900</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>78500</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>101600</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>88500</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>88800</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>80700</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>93400</v>
       </c>
     </row>
-    <row r="58" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -4892,70 +5025,73 @@
       <c r="AF58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>78200</v>
+      </c>
+      <c r="E59" s="3">
         <v>82000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>79600</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>68900</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>79300</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>78100</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>76000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>79200</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>70200</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>26200</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>26300</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>26400</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>26500</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>26600</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>26800</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>26900</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>27000</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>27100</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>27200</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>27300</v>
-      </c>
-      <c r="W59" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="X59" s="3" t="s">
         <v>8</v>
@@ -4966,8 +5102,8 @@
       <c r="Z59" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AA59" s="3">
-        <v>0</v>
+      <c r="AA59" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AB59" s="3">
         <v>0</v>
@@ -4984,8 +5120,11 @@
       <c r="AF59" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="60" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG59" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
@@ -5076,100 +5215,106 @@
       <c r="AF60" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="61" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG60" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>2829200</v>
+      </c>
+      <c r="E61" s="3">
         <v>2868800</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>2938000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>2972600</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>3010300</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>3012900</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>3001200</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>3179100</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>3150800</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>1289000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>1289400</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>1315200</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>1170800</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>1196100</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>1346300</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>1446500</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>1146600</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>1198600</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>1376600</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>1602600</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>1543300</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>1578300</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>1565400</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>1650500</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>1699200</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>1681700</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>1675100</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>1726900</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>1731100</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>1732300</v>
       </c>
     </row>
-    <row r="62" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -5194,8 +5339,8 @@
       <c r="J62" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K62" s="3">
-        <v>0</v>
+      <c r="K62" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="L62" s="3">
         <v>0</v>
@@ -5224,14 +5369,14 @@
       <c r="T62" s="3">
         <v>0</v>
       </c>
-      <c r="U62" s="3" t="s">
+      <c r="U62" s="3">
+        <v>0</v>
+      </c>
+      <c r="V62" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>2400</v>
-      </c>
-      <c r="W62" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="X62" s="3" t="s">
         <v>8</v>
@@ -5242,8 +5387,8 @@
       <c r="Z62" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AA62" s="3">
-        <v>0</v>
+      <c r="AA62" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AB62" s="3">
         <v>0</v>
@@ -5260,8 +5405,11 @@
       <c r="AF62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5352,8 +5500,11 @@
       <c r="AF63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5444,8 +5595,11 @@
       <c r="AF64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5536,100 +5690,106 @@
       <c r="AF65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>3375900</v>
+      </c>
+      <c r="E66" s="3">
         <v>3417200</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>3472300</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>3490900</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>3575500</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>3527100</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>3493700</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>3675100</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>3717500</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>1510000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>1505700</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>1523500</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>1377900</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>1416000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>1563600</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>1684600</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>1359800</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>1411700</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>1583700</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>1816400</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>1759300</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>1807700</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>1802800</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>1893900</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>1947100</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>1958500</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>1940600</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>2004000</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>2012800</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>2046500</v>
       </c>
     </row>
-    <row r="67" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5662,8 +5822,9 @@
       <c r="AD67" s="3"/>
       <c r="AE67" s="3"/>
       <c r="AF67" s="3"/>
-    </row>
-    <row r="68" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG67" s="3"/>
+    </row>
+    <row r="68" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5754,8 +5915,11 @@
       <c r="AF68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5846,8 +6010,11 @@
       <c r="AF69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5938,8 +6105,11 @@
       <c r="AF70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6030,100 +6200,106 @@
       <c r="AF71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-1373100</v>
+      </c>
+      <c r="E72" s="3">
         <v>-1326200</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-1275600</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-1255000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-1207800</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-1105800</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-1052000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-1021300</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-962900</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-849500</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-827300</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-812700</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-824300</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-810800</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-801800</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-797000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-770000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-758600</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-712200</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-683700</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-662700</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-604900</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>-582200</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>-554300</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>-509800</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>-485600</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>-459700</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>-444600</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>-419300</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>-397400</v>
       </c>
     </row>
-    <row r="73" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6214,8 +6390,11 @@
       <c r="AF73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6306,8 +6485,11 @@
       <c r="AF74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6398,100 +6580,106 @@
       <c r="AF75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>3568100</v>
+      </c>
+      <c r="E76" s="3">
         <v>3635300</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>3692800</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>3706000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>3766500</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>3872800</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>3891100</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>3898600</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>3922000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>1198800</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>1213500</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>1231900</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>1230700</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>1242100</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>1248200</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>1252800</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>1289000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>1302200</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>1352700</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>1386800</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>1412700</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>1478200</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>1499400</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>1525000</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>1565400</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>1584900</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>1609700</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>1619500</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>1643600</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>1644400</v>
       </c>
     </row>
-    <row r="77" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6582,197 +6770,206 @@
       <c r="AF77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:33" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E80" s="2">
         <v>45199</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45107</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45016</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44926</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44834</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44742</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44651</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44561</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44469</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44377</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44286</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44196</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44104</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44012</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>43921</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>43830</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43738</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43646</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43555</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43465</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43373</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43281</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43190</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43100</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43008</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>42916</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>42825</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>42735</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>8000</v>
+      </c>
+      <c r="E81" s="3">
         <v>2100</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>32100</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>5400</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-1100</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-7800</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>13100</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-16800</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-98200</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-7000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-200</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>24600</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-6800</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-4600</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-4800</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-100</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>15300</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-19700</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-1800</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>5700</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-31200</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>3900</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-1400</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-17900</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>2300</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>-600</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>10200</v>
       </c>
-      <c r="AD81" s="3">
-        <v>0</v>
-      </c>
       <c r="AE81" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF81" s="3">
         <v>3400</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>-1700</v>
       </c>
     </row>
-    <row r="82" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6805,100 +7002,104 @@
       <c r="AD82" s="3"/>
       <c r="AE82" s="3"/>
       <c r="AF82" s="3"/>
-    </row>
-    <row r="83" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG82" s="3"/>
+    </row>
+    <row r="83" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>103800</v>
+      </c>
+      <c r="E83" s="3">
         <v>106800</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>110400</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>109000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>113700</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>116600</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>119300</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>123300</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>110600</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>30800</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>30500</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>31200</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>32300</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>34400</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>32000</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>32100</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>31400</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>32600</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>35600</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>35300</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>38000</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>37500</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>41300</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>39200</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>41400</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>43500</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>43400</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>46400</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>43700</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>47700</v>
       </c>
     </row>
-    <row r="84" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6989,8 +7190,11 @@
       <c r="AF84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7081,8 +7285,11 @@
       <c r="AF85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7173,8 +7380,11 @@
       <c r="AF86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7265,8 +7475,11 @@
       <c r="AF87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7357,100 +7570,106 @@
       <c r="AF88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>103500</v>
+      </c>
+      <c r="E89" s="3">
         <v>110800</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>116800</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>63600</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>116900</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>108100</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>104700</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>49600</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-3500</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>36400</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>36100</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>31300</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>9800</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>35900</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>28000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>21900</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>31800</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>36500</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>37300</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>32300</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>35400</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>37000</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>45800</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>36300</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>30800</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>42700</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>44900</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>36200</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>34200</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>39800</v>
       </c>
     </row>
-    <row r="90" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7483,100 +7702,104 @@
       <c r="AD90" s="3"/>
       <c r="AE90" s="3"/>
       <c r="AF90" s="3"/>
-    </row>
-    <row r="91" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG90" s="3"/>
+    </row>
+    <row r="91" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-43900</v>
+      </c>
+      <c r="E91" s="3">
         <v>-30900</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-28600</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-39100</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-52000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-47800</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-35000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-23800</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-20400</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-15700</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-13300</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-7900</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-7600</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-8200</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-9200</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-13200</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-15700</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-12400</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-13700</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-11500</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-12000</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-12700</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-16500</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-18100</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-10800</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-24800</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-11200</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-47700</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-26000</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-24100</v>
       </c>
     </row>
-    <row r="92" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7667,8 +7890,11 @@
       <c r="AF92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7759,100 +7985,106 @@
       <c r="AF93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-26200</v>
+      </c>
+      <c r="E94" s="3">
         <v>-63500</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>49500</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-41500</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-31500</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-82300</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>130800</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-62200</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>18000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-9600</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-133300</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>33900</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-64900</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>4700</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-13500</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-7100</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>52800</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>166900</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>226600</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-29700</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>44700</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-14500</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>71800</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>46400</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-23200</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-16500</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>38100</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>1400</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-15600</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-22200</v>
       </c>
     </row>
-    <row r="95" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -7885,8 +8117,9 @@
       <c r="AD95" s="3"/>
       <c r="AE95" s="3"/>
       <c r="AF95" s="3"/>
-    </row>
-    <row r="96" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG95" s="3"/>
+    </row>
+    <row r="96" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -7894,49 +8127,49 @@
         <v>-52700</v>
       </c>
       <c r="E96" s="3">
-        <v>-52600</v>
+        <v>-52700</v>
       </c>
       <c r="F96" s="3">
         <v>-52600</v>
       </c>
       <c r="G96" s="3">
+        <v>-52600</v>
+      </c>
+      <c r="H96" s="3">
         <v>-48200</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>-46000</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>-43800</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>-41600</v>
-      </c>
-      <c r="K96" s="3">
-        <v>-15200</v>
       </c>
       <c r="L96" s="3">
         <v>-15200</v>
       </c>
       <c r="M96" s="3">
+        <v>-15200</v>
+      </c>
+      <c r="N96" s="3">
         <v>-14400</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>-13000</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>-6700</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>-4400</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="R96" s="3">
         <v>-26700</v>
       </c>
-      <c r="R96" s="3">
+      <c r="S96" s="3">
         <v>-300</v>
-      </c>
-      <c r="S96" s="3">
-        <v>-26700</v>
       </c>
       <c r="T96" s="3">
         <v>-26700</v>
@@ -7945,10 +8178,10 @@
         <v>-26700</v>
       </c>
       <c r="V96" s="3">
+        <v>-26700</v>
+      </c>
+      <c r="W96" s="3">
         <v>-53300</v>
-      </c>
-      <c r="W96" s="3">
-        <v>-26600</v>
       </c>
       <c r="X96" s="3">
         <v>-26600</v>
@@ -7957,10 +8190,10 @@
         <v>-26600</v>
       </c>
       <c r="Z96" s="3">
+        <v>-26600</v>
+      </c>
+      <c r="AA96" s="3">
         <v>-26500</v>
-      </c>
-      <c r="AA96" s="3">
-        <v>-25300</v>
       </c>
       <c r="AB96" s="3">
         <v>-25300</v>
@@ -7972,13 +8205,16 @@
         <v>-25300</v>
       </c>
       <c r="AE96" s="3">
-        <v>-24000</v>
+        <v>-25300</v>
       </c>
       <c r="AF96" s="3">
         <v>-24000</v>
       </c>
-    </row>
-    <row r="97" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG96" s="3">
+        <v>-24000</v>
+      </c>
+    </row>
+    <row r="97" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8069,8 +8305,11 @@
       <c r="AF97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8161,8 +8400,11 @@
       <c r="AF98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8253,100 +8495,106 @@
       <c r="AF99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-94100</v>
+      </c>
+      <c r="E100" s="3">
         <v>-123900</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-84100</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-91400</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-59900</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-28400</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-218600</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-5600</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-18000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-17100</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-41200</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>120800</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-35600</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-155100</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-128300</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>298000</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-81800</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-212900</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-256400</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>3800</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-75600</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-24800</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-112800</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-76300</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-16800</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-19700</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-78700</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-34200</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-27600</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-26600</v>
       </c>
     </row>
-    <row r="101" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -8437,96 +8685,102 @@
       <c r="AF101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-16900</v>
+      </c>
+      <c r="E102" s="3">
         <v>-76600</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>82300</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-69300</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>25500</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-2600</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>17000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-18200</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-3400</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>9700</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-138500</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>185900</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-90700</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-114500</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-113800</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>312800</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>2800</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-9500</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>7600</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>6400</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>4500</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-2300</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>4800</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>6400</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-8400</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>4800</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>4400</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>3300</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>-8900</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>-9100</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/KRG_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/KRG_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="156" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="159" uniqueCount="92">
   <si>
     <t>KRG</t>
   </si>
@@ -656,428 +656,441 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AG102"/>
+  <dimension ref="A5:AH102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:34" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E7" s="2">
         <v>45291</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45199</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45107</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45016</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44926</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44834</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44742</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44651</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44561</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44469</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44377</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44286</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44196</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44104</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44012</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>43921</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43830</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43738</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43646</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43555</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43465</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43373</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43281</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43190</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43100</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43008</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>42916</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>42825</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>42735</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>207400</v>
+      </c>
+      <c r="E8" s="3">
         <v>200300</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>207200</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>208800</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>206800</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>204700</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>200300</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>202600</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>194400</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>163000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>71500</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>69500</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>69400</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>68400</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>65100</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>63300</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>69900</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>75200</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>74900</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>81500</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>83500</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>86900</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>85700</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>91700</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>89800</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>88900</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>87100</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>92600</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>90100</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>88900</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>89100</v>
       </c>
     </row>
-    <row r="9" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>54600</v>
+      </c>
+      <c r="E9" s="3">
         <v>47900</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>54100</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>53900</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>54500</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>53800</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>51200</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>54000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>52800</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>47500</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>19100</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>18800</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>19700</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>19900</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>19700</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>17600</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>19700</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>20600</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>20700</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>21400</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>21600</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>23200</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>23300</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>23000</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>23200</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>23500</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>22700</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>23400</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>23300</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>23000</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>22600</v>
       </c>
     </row>
-    <row r="10" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>152800</v>
+      </c>
+      <c r="E10" s="3">
         <v>152400</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>153100</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>154900</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>152300</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>150900</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>149100</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>148600</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>141600</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>115500</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>52400</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>50700</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>49700</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>48500</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>45400</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>45700</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>50200</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>54600</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>54200</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>60100</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>61900</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>63700</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>62400</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>68700</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>66600</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>65400</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>64400</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>69200</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>66800</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>65900</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>66500</v>
       </c>
     </row>
-    <row r="11" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1111,8 +1124,9 @@
       <c r="AE11" s="3"/>
       <c r="AF11" s="3"/>
       <c r="AG11" s="3"/>
-    </row>
-    <row r="12" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH11" s="3"/>
+    </row>
+    <row r="12" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1206,8 +1220,11 @@
       <c r="AG12" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH12" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1301,50 +1318,53 @@
       <c r="AG13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3">
-        <v>0</v>
+      <c r="D14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="E14" s="3">
+        <v>0</v>
+      </c>
+      <c r="F14" s="3">
         <v>500</v>
       </c>
-      <c r="F14" s="3">
-        <v>0</v>
-      </c>
       <c r="G14" s="3">
         <v>0</v>
       </c>
       <c r="H14" s="3">
+        <v>0</v>
+      </c>
+      <c r="I14" s="3">
         <v>-100</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>100</v>
       </c>
-      <c r="J14" s="3">
-        <v>0</v>
-      </c>
       <c r="K14" s="3">
+        <v>0</v>
+      </c>
+      <c r="L14" s="3">
         <v>900</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>76600</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>9200</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>800</v>
       </c>
-      <c r="O14" s="3" t="s">
+      <c r="P14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P14" s="3">
-        <v>0</v>
-      </c>
       <c r="Q14" s="3">
         <v>0</v>
       </c>
@@ -1355,32 +1375,32 @@
         <v>0</v>
       </c>
       <c r="T14" s="3">
+        <v>0</v>
+      </c>
+      <c r="U14" s="3">
         <v>2000</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>15600</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>27700</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>4100</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Y14" s="3">
         <v>31500</v>
       </c>
-      <c r="Y14" s="3">
-        <v>0</v>
-      </c>
       <c r="Z14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA14" s="3">
         <v>14800</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AB14" s="3">
         <v>24100</v>
       </c>
-      <c r="AB14" s="3">
-        <v>0</v>
-      </c>
       <c r="AC14" s="3">
         <v>0</v>
       </c>
@@ -1388,111 +1408,117 @@
         <v>0</v>
       </c>
       <c r="AE14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF14" s="3">
         <v>7400</v>
       </c>
-      <c r="AF14" s="3">
+      <c r="AG14" s="3">
         <v>2800</v>
       </c>
-      <c r="AG14" s="3" t="s">
+      <c r="AH14" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="15" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>100400</v>
+      </c>
+      <c r="E15" s="3">
         <v>102900</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>105900</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>109500</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>108100</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>112700</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>115800</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>119800</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>121500</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>109800</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>30200</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>29800</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>30600</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>31800</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>34000</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>31400</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>31500</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>30800</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>32000</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>34700</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>34600</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>36300</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="Z15" s="3">
         <v>36900</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AA15" s="3">
         <v>40500</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AB15" s="3">
         <v>38600</v>
       </c>
-      <c r="AB15" s="3">
+      <c r="AC15" s="3">
         <v>40800</v>
       </c>
-      <c r="AC15" s="3">
+      <c r="AD15" s="3">
         <v>42800</v>
       </c>
-      <c r="AD15" s="3">
+      <c r="AE15" s="3">
         <v>42700</v>
       </c>
-      <c r="AE15" s="3">
+      <c r="AF15" s="3">
         <v>45800</v>
       </c>
-      <c r="AF15" s="3">
+      <c r="AG15" s="3">
         <v>42900</v>
       </c>
-      <c r="AG15" s="3">
+      <c r="AH15" s="3">
         <v>45500</v>
       </c>
     </row>
-    <row r="16" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:34" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1523,198 +1549,205 @@
       <c r="AE16" s="3"/>
       <c r="AF16" s="3"/>
       <c r="AG16" s="3"/>
-    </row>
-    <row r="17" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH16" s="3"/>
+    </row>
+    <row r="17" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>168000</v>
+      </c>
+      <c r="E17" s="3">
         <v>165000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>180400</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>149500</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>176000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>179400</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>182000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>163600</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>185400</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>240600</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>65500</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>57400</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>31400</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>62700</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>56900</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>54900</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>57100</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>47000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>80700</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>66700</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>60500</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>92500</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>65000</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>83800</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>91800</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>54400</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>70900</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>71600</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>82000</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>71300</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>73200</v>
       </c>
     </row>
-    <row r="18" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>39400</v>
+      </c>
+      <c r="E18" s="3">
         <v>35300</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>26800</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>59400</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>30800</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>25300</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>18300</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>39000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>9000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-77600</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>6000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>12100</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>38000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>5700</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>8200</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>8400</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>12800</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>28200</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-5800</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>14800</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>23000</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>-5600</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>20700</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>7900</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>-2000</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>34500</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>16200</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>21000</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>8100</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>17600</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>15900</v>
       </c>
     </row>
-    <row r="19" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1748,58 +1781,59 @@
       <c r="AE19" s="3"/>
       <c r="AF19" s="3"/>
       <c r="AG19" s="3"/>
-    </row>
-    <row r="20" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH19" s="3"/>
+    </row>
+    <row r="20" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>6000</v>
+      </c>
+      <c r="E20" s="3">
         <v>300</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>1000</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>300</v>
-      </c>
-      <c r="G20" s="3">
-        <v>400</v>
       </c>
       <c r="H20" s="3">
         <v>400</v>
       </c>
       <c r="I20" s="3">
+        <v>400</v>
+      </c>
+      <c r="J20" s="3">
         <v>100</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-200</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-100</v>
-      </c>
-      <c r="L20" s="3">
-        <v>100</v>
       </c>
       <c r="M20" s="3">
         <v>100</v>
       </c>
       <c r="N20" s="3">
+        <v>100</v>
+      </c>
+      <c r="O20" s="3">
         <v>300</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-200</v>
       </c>
-      <c r="P20" s="3">
-        <v>0</v>
-      </c>
       <c r="Q20" s="3">
         <v>0</v>
       </c>
       <c r="R20" s="3">
+        <v>0</v>
+      </c>
+      <c r="S20" s="3">
         <v>400</v>
-      </c>
-      <c r="S20" s="3">
-        <v>-100</v>
       </c>
       <c r="T20" s="3">
         <v>-100</v>
@@ -1808,218 +1842,224 @@
         <v>-100</v>
       </c>
       <c r="V20" s="3">
-        <v>-200</v>
+        <v>-100</v>
       </c>
       <c r="W20" s="3">
         <v>-200</v>
       </c>
       <c r="X20" s="3">
+        <v>-200</v>
+      </c>
+      <c r="Y20" s="3">
         <v>-8300</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>-300</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>7700</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>300</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>-15200</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>-100</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>6300</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>8700</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>4000</v>
       </c>
-      <c r="AG20" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH20" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>146700</v>
+      </c>
+      <c r="E21" s="3">
         <v>139500</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>134600</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>170000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>140200</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>139500</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>135000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>158200</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>132200</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>33100</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>37000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>42900</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>69000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>38000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>42600</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>40700</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>44800</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>59500</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>26800</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>50200</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>58100</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>24100</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>57900</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>57000</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>37500</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>60600</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>59600</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>70700</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>63200</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>65300</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>63500</v>
       </c>
     </row>
-    <row r="22" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>30400</v>
+      </c>
+      <c r="E22" s="3">
         <v>27200</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>25500</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>27200</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>25400</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>26800</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>26200</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>25700</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>25500</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>23100</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>12900</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>12300</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>12200</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>12300</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>12600</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>13300</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>12300</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>12400</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>14300</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>16100</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>16500</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>17600</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>16100</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>16700</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>16300</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>16500</v>
-      </c>
-      <c r="AC22" s="3">
-        <v>16400</v>
       </c>
       <c r="AD22" s="3">
         <v>16400</v>
@@ -2028,140 +2068,146 @@
         <v>16400</v>
       </c>
       <c r="AF22" s="3">
+        <v>16400</v>
+      </c>
+      <c r="AG22" s="3">
         <v>17600</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AH22" s="3">
         <v>17100</v>
       </c>
     </row>
-    <row r="23" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>15000</v>
+      </c>
+      <c r="E23" s="3">
         <v>8400</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>2300</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>32400</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>5800</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-1100</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-7900</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>13100</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-16600</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-100500</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-6700</v>
       </c>
-      <c r="N23" s="3">
-        <v>0</v>
-      </c>
       <c r="O23" s="3">
+        <v>0</v>
+      </c>
+      <c r="P23" s="3">
         <v>25600</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-6600</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-4400</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-4600</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>400</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>15700</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-20100</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-1500</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>6300</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-31600</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>4300</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>-1100</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>-18000</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>2800</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>-200</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>10900</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>400</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>4000</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>-1200</v>
       </c>
     </row>
-    <row r="24" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>200</v>
+      </c>
+      <c r="E24" s="3">
         <v>400</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>100</v>
       </c>
-      <c r="F24" s="3">
-        <v>0</v>
-      </c>
       <c r="G24" s="3">
         <v>0</v>
       </c>
       <c r="H24" s="3">
+        <v>0</v>
+      </c>
+      <c r="I24" s="3">
         <v>300</v>
       </c>
-      <c r="I24" s="3">
-        <v>0</v>
-      </c>
       <c r="J24" s="3">
+        <v>0</v>
+      </c>
+      <c r="K24" s="3">
         <v>-200</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>-100</v>
       </c>
-      <c r="L24" s="3">
-        <v>0</v>
-      </c>
       <c r="M24" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="N24" s="3">
         <v>-100</v>
@@ -2170,7 +2216,7 @@
         <v>-100</v>
       </c>
       <c r="P24" s="3">
-        <v>-200</v>
+        <v>-100</v>
       </c>
       <c r="Q24" s="3">
         <v>-200</v>
@@ -2179,16 +2225,16 @@
         <v>-200</v>
       </c>
       <c r="S24" s="3">
-        <v>-100</v>
+        <v>-200</v>
       </c>
       <c r="T24" s="3">
         <v>-100</v>
       </c>
       <c r="U24" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="V24" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="W24" s="3">
         <v>-100</v>
@@ -2197,7 +2243,7 @@
         <v>-100</v>
       </c>
       <c r="Y24" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="Z24" s="3">
         <v>0</v>
@@ -2218,13 +2264,16 @@
         <v>0</v>
       </c>
       <c r="AF24" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG24" s="3">
         <v>100</v>
       </c>
-      <c r="AG24" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2318,198 +2367,207 @@
       <c r="AG25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>14900</v>
+      </c>
+      <c r="E26" s="3">
         <v>8000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>2200</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>32400</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>5800</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-1400</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-7900</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>13300</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-16500</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-100500</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-6600</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>100</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>25700</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-6400</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-4200</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-4400</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>500</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>15800</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-20100</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-1500</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>6400</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-31400</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>4300</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>-1100</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>-18000</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>2800</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>-200</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>10900</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>400</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>3900</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>-1300</v>
       </c>
     </row>
-    <row r="27" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>14200</v>
+      </c>
+      <c r="E27" s="3">
         <v>8000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>2100</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>32100</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>5400</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-1100</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-7800</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>13100</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-16800</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-98200</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-7000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-200</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>24600</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-6800</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-4600</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-4800</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-100</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>15300</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-19700</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-1800</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>5700</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-31200</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>3900</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>-1400</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>-17900</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>2300</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>-600</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>10200</v>
       </c>
-      <c r="AE27" s="3">
-        <v>0</v>
-      </c>
       <c r="AF27" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG27" s="3">
         <v>3400</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>-1700</v>
       </c>
     </row>
-    <row r="28" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2603,8 +2661,11 @@
       <c r="AG28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2680,8 +2741,8 @@
       <c r="AA29" s="3">
         <v>0</v>
       </c>
-      <c r="AB29" s="3" t="s">
-        <v>8</v>
+      <c r="AB29" s="3">
+        <v>0</v>
       </c>
       <c r="AC29" s="3" t="s">
         <v>8</v>
@@ -2692,14 +2753,17 @@
       <c r="AE29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AF29" s="3">
-        <v>0</v>
-      </c>
-      <c r="AG29" s="3" t="s">
+      <c r="AF29" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="30" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AG29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH29" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="30" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2793,8 +2857,11 @@
       <c r="AG30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2888,58 +2955,61 @@
       <c r="AG31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-6000</v>
+      </c>
+      <c r="E32" s="3">
         <v>-300</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-1000</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-300</v>
-      </c>
-      <c r="G32" s="3">
-        <v>-400</v>
       </c>
       <c r="H32" s="3">
         <v>-400</v>
       </c>
       <c r="I32" s="3">
+        <v>-400</v>
+      </c>
+      <c r="J32" s="3">
         <v>-100</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>200</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>100</v>
-      </c>
-      <c r="L32" s="3">
-        <v>-100</v>
       </c>
       <c r="M32" s="3">
         <v>-100</v>
       </c>
       <c r="N32" s="3">
+        <v>-100</v>
+      </c>
+      <c r="O32" s="3">
         <v>-300</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>200</v>
       </c>
-      <c r="P32" s="3">
-        <v>0</v>
-      </c>
       <c r="Q32" s="3">
         <v>0</v>
       </c>
       <c r="R32" s="3">
+        <v>0</v>
+      </c>
+      <c r="S32" s="3">
         <v>-400</v>
-      </c>
-      <c r="S32" s="3">
-        <v>100</v>
       </c>
       <c r="T32" s="3">
         <v>100</v>
@@ -2948,138 +3018,144 @@
         <v>100</v>
       </c>
       <c r="V32" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="W32" s="3">
         <v>200</v>
       </c>
       <c r="X32" s="3">
+        <v>200</v>
+      </c>
+      <c r="Y32" s="3">
         <v>8300</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>300</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-7700</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>-300</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>15200</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>100</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>-6300</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>-8700</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>-4000</v>
       </c>
-      <c r="AG32" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="33" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH32" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>14200</v>
+      </c>
+      <c r="E33" s="3">
         <v>8000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>2100</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>32100</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>5400</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-1100</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-7800</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>13100</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-16800</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-98200</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-7000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-200</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>24600</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-6800</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-4600</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-4800</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-100</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>15300</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-19700</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-1800</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>5700</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-31200</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>3900</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-1400</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>-17900</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>2300</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>-600</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>10200</v>
       </c>
-      <c r="AE33" s="3">
-        <v>0</v>
-      </c>
       <c r="AF33" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG33" s="3">
         <v>3400</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>-1700</v>
       </c>
     </row>
-    <row r="34" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3173,203 +3249,212 @@
       <c r="AG34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>14200</v>
+      </c>
+      <c r="E35" s="3">
         <v>8000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>2100</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>32100</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>5400</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-1100</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-7800</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>13100</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-16800</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-98200</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-7000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-200</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>24600</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-6800</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-4600</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-4800</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-100</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>15300</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-19700</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-1800</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>5700</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-31200</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>3900</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-1400</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>-17900</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>2300</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>-600</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>10200</v>
       </c>
-      <c r="AE35" s="3">
-        <v>0</v>
-      </c>
       <c r="AF35" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG35" s="3">
         <v>3400</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>-1700</v>
       </c>
     </row>
-    <row r="37" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:34" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E38" s="2">
         <v>45291</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45199</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45107</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45016</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44926</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44834</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44742</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44651</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44561</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44469</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44377</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44286</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44196</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44104</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44012</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>43921</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43830</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43738</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43646</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43555</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43465</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43373</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43281</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43190</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43100</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43008</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>42916</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>42825</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>42735</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3403,8 +3488,9 @@
       <c r="AE39" s="3"/>
       <c r="AF39" s="3"/>
       <c r="AG39" s="3"/>
-    </row>
-    <row r="40" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH39" s="3"/>
+    </row>
+    <row r="40" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3438,103 +3524,107 @@
       <c r="AE40" s="3"/>
       <c r="AF40" s="3"/>
       <c r="AG40" s="3"/>
-    </row>
-    <row r="41" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH40" s="3"/>
+    </row>
+    <row r="41" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>83600</v>
+      </c>
+      <c r="E41" s="3">
         <v>36400</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>52300</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>129300</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>43700</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>115800</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>88400</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>90800</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>74300</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>93200</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>99500</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>89900</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>228800</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>43600</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>129300</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>230000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>343900</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>31300</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>40400</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>35800</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>28400</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>35400</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>30700</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>32400</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>28800</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>24100</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>32500</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>27600</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>22600</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>19900</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>28800</v>
       </c>
     </row>
-    <row r="42" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3628,103 +3718,109 @@
       <c r="AG42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>118100</v>
+      </c>
+      <c r="E43" s="3">
         <v>113300</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>113100</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>109600</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>103500</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>101300</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>86600</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>76900</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>69100</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>68400</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>45900</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>46700</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>49100</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>57200</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>57100</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>61600</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>49900</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>55300</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>50000</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>52000</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>55400</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>58100</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>57100</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>53100</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>57200</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>58300</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>53300</v>
-      </c>
-      <c r="AD43" s="3">
-        <v>52300</v>
       </c>
       <c r="AE43" s="3">
         <v>52300</v>
       </c>
       <c r="AF43" s="3">
+        <v>52300</v>
+      </c>
+      <c r="AG43" s="3">
         <v>53100</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>50400</v>
       </c>
     </row>
-    <row r="44" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3818,103 +3914,109 @@
       <c r="AG44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>131800</v>
+      </c>
+      <c r="E45" s="3">
         <v>117800</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>134600</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>130500</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>117400</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>127000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>142800</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>106000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>96300</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>84800</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>39200</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>39500</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>42900</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>13000</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>39300</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>38200</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>36300</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>7500</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>10100</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>10300</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>14100</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>12800</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>17400</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>14200</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>20300</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>16400</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>12800</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>10200</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>12800</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>9700</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>10800</v>
       </c>
     </row>
-    <row r="46" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
@@ -4008,82 +4110,85 @@
       <c r="AG46" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="47" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH46" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>274600</v>
+      </c>
+      <c r="E47" s="3">
         <v>9100</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>10200</v>
-      </c>
-      <c r="F47" s="3">
-        <v>10300</v>
       </c>
       <c r="G47" s="3">
         <v>10300</v>
       </c>
       <c r="H47" s="3">
+        <v>10300</v>
+      </c>
+      <c r="I47" s="3">
         <v>10400</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>10600</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>10400</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>136800</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>136900</v>
-      </c>
-      <c r="M47" s="3">
-        <v>138000</v>
       </c>
       <c r="N47" s="3">
         <v>138000</v>
       </c>
       <c r="O47" s="3">
+        <v>138000</v>
+      </c>
+      <c r="P47" s="3">
         <v>13000</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>12800</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>13100</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>13200</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>12100</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>12600</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>12900</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>12700</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>13300</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>13500</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>13800</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>13900</v>
-      </c>
-      <c r="AA47" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AB47" s="3" t="s">
         <v>8</v>
@@ -4103,103 +4208,109 @@
       <c r="AG47" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="48" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH47" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="48" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>6305700</v>
+      </c>
+      <c r="E48" s="3">
         <v>6358300</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>6397300</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>6426100</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>6508700</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>6571400</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>6621600</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>6617800</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>6676800</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>6707500</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>2308000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>2343700</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>2358900</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>2415900</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>2347400</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>2380500</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>2404000</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>2447400</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>2514100</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>2716800</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>2911300</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>2941200</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>3051700</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>3076800</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>3194200</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>3293300</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>3320300</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>3331800</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>3399700</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>3435400</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>3458300</v>
       </c>
     </row>
-    <row r="49" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -4270,31 +4381,34 @@
         <v>0</v>
       </c>
       <c r="Z49" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA49" s="3">
         <v>32300</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>39000</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>44000</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>47900</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>53000</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>59300</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>65500</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>70000</v>
       </c>
     </row>
-    <row r="50" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4388,8 +4502,11 @@
       <c r="AG50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4483,103 +4600,109 @@
       <c r="AG51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>290800</v>
+      </c>
+      <c r="E52" s="3">
         <v>309200</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>345000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>359400</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>413200</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>416000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>450000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>483000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>520300</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>548600</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>78400</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>61400</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>62600</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>66100</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>71900</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>88300</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>91300</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>94600</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>86300</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>108700</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>180800</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>111100</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>115100</v>
-      </c>
-      <c r="Z52" s="3">
-        <v>79400</v>
       </c>
       <c r="AA52" s="3">
         <v>79400</v>
       </c>
       <c r="AB52" s="3">
+        <v>79400</v>
+      </c>
+      <c r="AC52" s="3">
         <v>76400</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>76600</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>75400</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>76700</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>72800</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>72700</v>
       </c>
     </row>
-    <row r="53" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4673,103 +4796,109 @@
       <c r="AG53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>7204500</v>
+      </c>
+      <c r="E54" s="3">
         <v>6944100</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>7052500</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>7165100</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>7196900</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>7342000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>7399900</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>7384900</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>7573700</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>7639600</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>2708900</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>2719200</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>2755300</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>2608500</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>2658100</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>2811800</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>2937400</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>2648900</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>2713900</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>2936300</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>3203200</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>3172000</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>3285900</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>3302200</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>3418900</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>3512500</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>3543400</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>3550300</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>3623500</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>3656400</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>3690900</v>
       </c>
     </row>
-    <row r="55" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4803,8 +4932,9 @@
       <c r="AE55" s="3"/>
       <c r="AF55" s="3"/>
       <c r="AG55" s="3"/>
-    </row>
-    <row r="56" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH55" s="3"/>
+    </row>
+    <row r="56" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4838,103 +4968,107 @@
       <c r="AE56" s="3"/>
       <c r="AF56" s="3"/>
       <c r="AG56" s="3"/>
-    </row>
-    <row r="57" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH56" s="3"/>
+    </row>
+    <row r="57" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>171600</v>
+      </c>
+      <c r="E57" s="3">
         <v>198100</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>198500</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>178200</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>160100</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>207800</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>152000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>133800</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>124200</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>185000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>85700</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>74400</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>72100</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>77500</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>88600</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>85700</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>109400</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>69800</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>77500</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>66600</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>61900</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>85900</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>98500</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>101200</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>102900</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>78500</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>101600</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>88500</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>88800</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>80700</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>93400</v>
       </c>
     </row>
-    <row r="58" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -5028,73 +5162,76 @@
       <c r="AG58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>78400</v>
+      </c>
+      <c r="E59" s="3">
         <v>78200</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>82000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>79600</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>68900</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>79300</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>78100</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>76000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>79200</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>70200</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>26200</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>26300</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>26400</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>26500</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>26600</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>26800</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>26900</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>27000</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>27100</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>27200</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>27300</v>
-      </c>
-      <c r="X59" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="Y59" s="3" t="s">
         <v>8</v>
@@ -5105,8 +5242,8 @@
       <c r="AA59" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AB59" s="3">
-        <v>0</v>
+      <c r="AB59" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AC59" s="3">
         <v>0</v>
@@ -5123,8 +5260,11 @@
       <c r="AG59" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="60" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH59" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
@@ -5218,103 +5358,109 @@
       <c r="AG60" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="61" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH60" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>3167500</v>
+      </c>
+      <c r="E61" s="3">
         <v>2829200</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>2868800</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>2938000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>2972600</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>3010300</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>3012900</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>3001200</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>3179100</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>3150800</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>1289000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>1289400</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>1315200</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>1170800</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>1196100</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>1346300</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>1446500</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>1146600</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>1198600</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>1376600</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>1602600</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>1543300</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>1578300</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>1565400</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>1650500</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>1699200</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>1681700</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>1675100</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>1726900</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>1731100</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>1732300</v>
       </c>
     </row>
-    <row r="62" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -5342,8 +5488,8 @@
       <c r="K62" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L62" s="3">
-        <v>0</v>
+      <c r="L62" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="M62" s="3">
         <v>0</v>
@@ -5372,14 +5518,14 @@
       <c r="U62" s="3">
         <v>0</v>
       </c>
-      <c r="V62" s="3" t="s">
+      <c r="V62" s="3">
+        <v>0</v>
+      </c>
+      <c r="W62" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>2400</v>
-      </c>
-      <c r="X62" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="Y62" s="3" t="s">
         <v>8</v>
@@ -5390,8 +5536,8 @@
       <c r="AA62" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AB62" s="3">
-        <v>0</v>
+      <c r="AB62" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AC62" s="3">
         <v>0</v>
@@ -5408,8 +5554,11 @@
       <c r="AG62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5503,8 +5652,11 @@
       <c r="AG63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5598,8 +5750,11 @@
       <c r="AG64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5693,103 +5848,109 @@
       <c r="AG65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>3673700</v>
+      </c>
+      <c r="E66" s="3">
         <v>3375900</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>3417200</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>3472300</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>3490900</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>3575500</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>3527100</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>3493700</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>3675100</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>3717500</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>1510000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>1505700</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>1523500</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>1377900</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>1416000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>1563600</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>1684600</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>1359800</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>1411700</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>1583700</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>1816400</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>1759300</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>1807700</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>1802800</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>1893900</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>1947100</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>1958500</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>1940600</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>2004000</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>2012800</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>2046500</v>
       </c>
     </row>
-    <row r="67" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5823,8 +5984,9 @@
       <c r="AE67" s="3"/>
       <c r="AF67" s="3"/>
       <c r="AG67" s="3"/>
-    </row>
-    <row r="68" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH67" s="3"/>
+    </row>
+    <row r="68" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5918,8 +6080,11 @@
       <c r="AG68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6013,8 +6178,11 @@
       <c r="AG69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6108,8 +6276,11 @@
       <c r="AG70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6203,103 +6374,109 @@
       <c r="AG71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-1413800</v>
+      </c>
+      <c r="E72" s="3">
         <v>-1373100</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-1326200</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-1275600</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-1255000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-1207800</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-1105800</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-1052000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-1021300</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-962900</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-849500</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-827300</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-812700</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-824300</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-810800</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-801800</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-797000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-770000</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-758600</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-712200</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-683700</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-662700</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>-604900</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>-582200</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>-554300</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>-509800</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>-485600</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>-459700</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>-444600</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>-419300</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>-397400</v>
       </c>
     </row>
-    <row r="73" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6393,8 +6570,11 @@
       <c r="AG73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6488,8 +6668,11 @@
       <c r="AG74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6583,103 +6766,109 @@
       <c r="AG75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>3530800</v>
+      </c>
+      <c r="E76" s="3">
         <v>3568100</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>3635300</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>3692800</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>3706000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>3766500</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>3872800</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>3891100</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>3898600</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>3922000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>1198800</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>1213500</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>1231900</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>1230700</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>1242100</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>1248200</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>1252800</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>1289000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>1302200</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>1352700</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>1386800</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>1412700</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>1478200</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>1499400</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>1525000</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>1565400</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>1584900</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>1609700</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>1619500</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>1643600</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>1644400</v>
       </c>
     </row>
-    <row r="77" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6773,203 +6962,212 @@
       <c r="AG77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:34" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E80" s="2">
         <v>45291</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45199</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45107</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45016</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44926</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44834</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44742</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44651</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44561</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44469</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44377</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44286</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44196</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44104</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44012</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>43921</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43830</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43738</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43646</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43555</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43465</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43373</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43281</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43190</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43100</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43008</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>42916</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>42825</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>42735</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>14200</v>
+      </c>
+      <c r="E81" s="3">
         <v>8000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>2100</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>32100</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>5400</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-1100</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-7800</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>13100</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-16800</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-98200</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-7000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-200</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>24600</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-6800</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-4600</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-4800</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-100</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>15300</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-19700</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-1800</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>5700</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-31200</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>3900</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-1400</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>-17900</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>2300</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>-600</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>10200</v>
       </c>
-      <c r="AE81" s="3">
-        <v>0</v>
-      </c>
       <c r="AF81" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG81" s="3">
         <v>3400</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>-1700</v>
       </c>
     </row>
-    <row r="82" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7003,103 +7201,107 @@
       <c r="AE82" s="3"/>
       <c r="AF82" s="3"/>
       <c r="AG82" s="3"/>
-    </row>
-    <row r="83" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH82" s="3"/>
+    </row>
+    <row r="83" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>101300</v>
+      </c>
+      <c r="E83" s="3">
         <v>103800</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>106800</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>110400</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>109000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>113700</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>116600</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>119300</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>123300</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>110600</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>30800</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>30500</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>31200</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>32300</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>34400</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>32000</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>32100</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>31400</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>32600</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>35600</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>35300</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>38000</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>37500</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>41300</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>39200</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>41400</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>43500</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>43400</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>46400</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>43700</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>47700</v>
       </c>
     </row>
-    <row r="84" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7193,8 +7395,11 @@
       <c r="AG84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7288,8 +7493,11 @@
       <c r="AG85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7383,8 +7591,11 @@
       <c r="AG86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7478,8 +7689,11 @@
       <c r="AG87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7573,103 +7787,109 @@
       <c r="AG88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>53600</v>
+      </c>
+      <c r="E89" s="3">
         <v>103500</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>110800</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>116800</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>63600</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>116900</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>108100</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>104700</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>49600</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-3500</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>36400</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>36100</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>31300</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>9800</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>35900</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>28000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>21900</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>31800</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>36500</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>37300</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>32300</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>35400</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>37000</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>45800</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>36300</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>30800</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>42700</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>44900</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>36200</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>34200</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>39800</v>
       </c>
     </row>
-    <row r="90" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7703,103 +7923,107 @@
       <c r="AE90" s="3"/>
       <c r="AF90" s="3"/>
       <c r="AG90" s="3"/>
-    </row>
-    <row r="91" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH90" s="3"/>
+    </row>
+    <row r="91" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-28200</v>
+      </c>
+      <c r="E91" s="3">
         <v>-43900</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-30900</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-28600</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-39100</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-52000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-47800</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-35000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-23800</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-20400</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-15700</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-13300</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-7900</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-7600</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-8200</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-9200</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-13200</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-15700</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-12400</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-13700</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-11500</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-12000</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-12700</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-16500</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-18100</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-10800</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-24800</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-11200</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-47700</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-26000</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-24100</v>
       </c>
     </row>
-    <row r="92" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7893,8 +8117,11 @@
       <c r="AG92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7988,103 +8215,109 @@
       <c r="AG93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-289300</v>
+      </c>
+      <c r="E94" s="3">
         <v>-26200</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-63500</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>49500</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-41500</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-31500</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-82300</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>130800</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-62200</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>18000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-9600</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-133300</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>33900</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-64900</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>4700</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-13500</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-7100</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>52800</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>166900</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>226600</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-29700</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>44700</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-14500</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>71800</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>46400</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-23200</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-16500</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>38100</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>1400</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-15600</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-22200</v>
       </c>
     </row>
-    <row r="95" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8118,61 +8351,62 @@
       <c r="AE95" s="3"/>
       <c r="AF95" s="3"/>
       <c r="AG95" s="3"/>
-    </row>
-    <row r="96" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH95" s="3"/>
+    </row>
+    <row r="96" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>-52700</v>
+        <v>-54900</v>
       </c>
       <c r="E96" s="3">
         <v>-52700</v>
       </c>
       <c r="F96" s="3">
-        <v>-52600</v>
+        <v>-52700</v>
       </c>
       <c r="G96" s="3">
         <v>-52600</v>
       </c>
       <c r="H96" s="3">
+        <v>-52600</v>
+      </c>
+      <c r="I96" s="3">
         <v>-48200</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>-46000</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>-43800</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>-41600</v>
-      </c>
-      <c r="L96" s="3">
-        <v>-15200</v>
       </c>
       <c r="M96" s="3">
         <v>-15200</v>
       </c>
       <c r="N96" s="3">
+        <v>-15200</v>
+      </c>
+      <c r="O96" s="3">
         <v>-14400</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>-13000</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>-6700</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="R96" s="3">
         <v>-4400</v>
       </c>
-      <c r="R96" s="3">
+      <c r="S96" s="3">
         <v>-26700</v>
       </c>
-      <c r="S96" s="3">
+      <c r="T96" s="3">
         <v>-300</v>
-      </c>
-      <c r="T96" s="3">
-        <v>-26700</v>
       </c>
       <c r="U96" s="3">
         <v>-26700</v>
@@ -8181,10 +8415,10 @@
         <v>-26700</v>
       </c>
       <c r="W96" s="3">
+        <v>-26700</v>
+      </c>
+      <c r="X96" s="3">
         <v>-53300</v>
-      </c>
-      <c r="X96" s="3">
-        <v>-26600</v>
       </c>
       <c r="Y96" s="3">
         <v>-26600</v>
@@ -8193,10 +8427,10 @@
         <v>-26600</v>
       </c>
       <c r="AA96" s="3">
+        <v>-26600</v>
+      </c>
+      <c r="AB96" s="3">
         <v>-26500</v>
-      </c>
-      <c r="AB96" s="3">
-        <v>-25300</v>
       </c>
       <c r="AC96" s="3">
         <v>-25300</v>
@@ -8208,13 +8442,16 @@
         <v>-25300</v>
       </c>
       <c r="AF96" s="3">
-        <v>-24000</v>
+        <v>-25300</v>
       </c>
       <c r="AG96" s="3">
         <v>-24000</v>
       </c>
-    </row>
-    <row r="97" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH96" s="3">
+        <v>-24000</v>
+      </c>
+    </row>
+    <row r="97" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8308,8 +8545,11 @@
       <c r="AG97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8403,8 +8643,11 @@
       <c r="AG98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8498,103 +8741,109 @@
       <c r="AG99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>283300</v>
+      </c>
+      <c r="E100" s="3">
         <v>-94100</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-123900</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-84100</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-91400</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-59900</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-28400</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-218600</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-5600</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-18000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-17100</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-41200</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>120800</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-35600</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-155100</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-128300</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>298000</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-81800</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-212900</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-256400</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>3800</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-75600</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-24800</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-112800</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-76300</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-16800</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-19700</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-78700</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-34200</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-27600</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-26600</v>
       </c>
     </row>
-    <row r="101" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -8688,99 +8937,105 @@
       <c r="AG101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>47500</v>
+      </c>
+      <c r="E102" s="3">
         <v>-16900</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-76600</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>82300</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-69300</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>25500</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-2600</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>17000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-18200</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-3400</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>9700</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-138500</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>185900</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-90700</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-114500</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-113800</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>312800</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>2800</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-9500</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>7600</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>6400</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>4500</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-2300</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>4800</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>6400</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-8400</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>4800</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>4400</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>3300</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>-8900</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>-9100</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/KRG_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/KRG_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="159" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="168" uniqueCount="92">
   <si>
     <t>KRG</t>
   </si>
@@ -656,441 +656,454 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AH102"/>
+  <dimension ref="A5:AI102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="35" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:35" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E7" s="2">
         <v>45382</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45291</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45199</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45107</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45016</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44926</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44834</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44742</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44651</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44561</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44469</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44377</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44286</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44196</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44104</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44012</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43921</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43830</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43738</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43646</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43555</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43465</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43373</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43281</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43190</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43100</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43008</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>42916</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>42825</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>42735</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>212400</v>
+      </c>
+      <c r="E8" s="3">
         <v>207400</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>200300</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>207200</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>208800</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>206800</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>204700</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>200300</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>202600</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>194400</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>163000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>71500</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>69500</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>69400</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>68400</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>65100</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>63300</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>69900</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>75200</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>74900</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>81500</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>83500</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>86900</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>85700</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>91700</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>89800</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>88900</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>87100</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>92600</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>90100</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>88900</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>89100</v>
       </c>
     </row>
-    <row r="9" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>55100</v>
+      </c>
+      <c r="E9" s="3">
         <v>54600</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>47900</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>54100</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>53900</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>54500</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>53800</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>51200</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>54000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>52800</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>47500</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>19100</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>18800</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>19700</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>19900</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>19700</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>17600</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>19700</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>20600</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>20700</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>21400</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>21600</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>23200</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>23300</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>23000</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>23200</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>23500</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>22700</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>23400</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>23300</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>23000</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>22600</v>
       </c>
     </row>
-    <row r="10" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>157300</v>
+      </c>
+      <c r="E10" s="3">
         <v>152800</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>152400</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>153100</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>154900</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>152300</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>150900</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>149100</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>148600</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>141600</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>115500</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>52400</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>50700</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>49700</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>48500</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>45400</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>45700</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>50200</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>54600</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>54200</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>60100</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>61900</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>63700</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>62400</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>68700</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>66600</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>65400</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>64400</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>69200</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>66800</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>65900</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>66500</v>
       </c>
     </row>
-    <row r="11" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1125,8 +1138,9 @@
       <c r="AF11" s="3"/>
       <c r="AG11" s="3"/>
       <c r="AH11" s="3"/>
-    </row>
-    <row r="12" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI11" s="3"/>
+    </row>
+    <row r="12" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1223,8 +1237,11 @@
       <c r="AH12" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI12" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1321,53 +1338,56 @@
       <c r="AH13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3" t="s">
+      <c r="D14" s="3">
+        <v>66200</v>
+      </c>
+      <c r="E14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E14" s="3">
-        <v>0</v>
-      </c>
       <c r="F14" s="3">
+        <v>0</v>
+      </c>
+      <c r="G14" s="3">
         <v>500</v>
       </c>
-      <c r="G14" s="3">
-        <v>0</v>
-      </c>
       <c r="H14" s="3">
         <v>0</v>
       </c>
       <c r="I14" s="3">
+        <v>0</v>
+      </c>
+      <c r="J14" s="3">
         <v>-100</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>100</v>
       </c>
-      <c r="K14" s="3">
-        <v>0</v>
-      </c>
       <c r="L14" s="3">
+        <v>0</v>
+      </c>
+      <c r="M14" s="3">
         <v>900</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>76600</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>9200</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>800</v>
       </c>
-      <c r="P14" s="3" t="s">
+      <c r="Q14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q14" s="3">
-        <v>0</v>
-      </c>
       <c r="R14" s="3">
         <v>0</v>
       </c>
@@ -1378,32 +1398,32 @@
         <v>0</v>
       </c>
       <c r="U14" s="3">
+        <v>0</v>
+      </c>
+      <c r="V14" s="3">
         <v>2000</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>15600</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>27700</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Y14" s="3">
         <v>4100</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="Z14" s="3">
         <v>31500</v>
       </c>
-      <c r="Z14" s="3">
-        <v>0</v>
-      </c>
       <c r="AA14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB14" s="3">
         <v>14800</v>
       </c>
-      <c r="AB14" s="3">
+      <c r="AC14" s="3">
         <v>24100</v>
       </c>
-      <c r="AC14" s="3">
-        <v>0</v>
-      </c>
       <c r="AD14" s="3">
         <v>0</v>
       </c>
@@ -1411,114 +1431,120 @@
         <v>0</v>
       </c>
       <c r="AF14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG14" s="3">
         <v>7400</v>
       </c>
-      <c r="AG14" s="3">
+      <c r="AH14" s="3">
         <v>2800</v>
       </c>
-      <c r="AH14" s="3" t="s">
+      <c r="AI14" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="15" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>99300</v>
+      </c>
+      <c r="E15" s="3">
         <v>100400</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>102900</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>105900</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>109500</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>108100</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>112700</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>115800</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>119800</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>121500</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>109800</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>30200</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>29800</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>30600</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>31800</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>34000</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>31400</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>31500</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>30800</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>32000</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>34700</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>34600</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="Z15" s="3">
         <v>36300</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AA15" s="3">
         <v>36900</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AB15" s="3">
         <v>40500</v>
       </c>
-      <c r="AB15" s="3">
+      <c r="AC15" s="3">
         <v>38600</v>
       </c>
-      <c r="AC15" s="3">
+      <c r="AD15" s="3">
         <v>40800</v>
       </c>
-      <c r="AD15" s="3">
+      <c r="AE15" s="3">
         <v>42800</v>
       </c>
-      <c r="AE15" s="3">
+      <c r="AF15" s="3">
         <v>42700</v>
       </c>
-      <c r="AF15" s="3">
+      <c r="AG15" s="3">
         <v>45800</v>
       </c>
-      <c r="AG15" s="3">
+      <c r="AH15" s="3">
         <v>42900</v>
       </c>
-      <c r="AH15" s="3">
+      <c r="AI15" s="3">
         <v>45500</v>
       </c>
     </row>
-    <row r="16" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:35" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1550,204 +1576,211 @@
       <c r="AF16" s="3"/>
       <c r="AG16" s="3"/>
       <c r="AH16" s="3"/>
-    </row>
-    <row r="17" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI16" s="3"/>
+    </row>
+    <row r="17" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>234700</v>
+      </c>
+      <c r="E17" s="3">
         <v>168000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>165000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>180400</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>149500</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>176000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>179400</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>182000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>163600</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>185400</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>240600</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>65500</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>57400</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>31400</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>62700</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>56900</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>54900</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>57100</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>47000</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>80700</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>66700</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>60500</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>92500</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>65000</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>83800</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>91800</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>54400</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>70900</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>71600</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>82000</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>71300</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>73200</v>
       </c>
     </row>
-    <row r="18" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-22300</v>
+      </c>
+      <c r="E18" s="3">
         <v>39400</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>35300</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>26800</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>59400</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>30800</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>25300</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>18300</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>39000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>9000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-77600</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>6000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>12100</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>38000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>5700</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>8200</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>8400</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>12800</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>28200</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-5800</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>14800</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>23000</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>-5600</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>20700</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>7900</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>-2000</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>34500</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>16200</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>21000</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>8100</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>17600</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>15900</v>
       </c>
     </row>
-    <row r="19" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1782,61 +1815,62 @@
       <c r="AF19" s="3"/>
       <c r="AG19" s="3"/>
       <c r="AH19" s="3"/>
-    </row>
-    <row r="20" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI19" s="3"/>
+    </row>
+    <row r="20" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>4300</v>
+      </c>
+      <c r="E20" s="3">
         <v>6000</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>300</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>1000</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>300</v>
-      </c>
-      <c r="H20" s="3">
-        <v>400</v>
       </c>
       <c r="I20" s="3">
         <v>400</v>
       </c>
       <c r="J20" s="3">
+        <v>400</v>
+      </c>
+      <c r="K20" s="3">
         <v>100</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-200</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-100</v>
-      </c>
-      <c r="M20" s="3">
-        <v>100</v>
       </c>
       <c r="N20" s="3">
         <v>100</v>
       </c>
       <c r="O20" s="3">
+        <v>100</v>
+      </c>
+      <c r="P20" s="3">
         <v>300</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-200</v>
       </c>
-      <c r="Q20" s="3">
-        <v>0</v>
-      </c>
       <c r="R20" s="3">
         <v>0</v>
       </c>
       <c r="S20" s="3">
+        <v>0</v>
+      </c>
+      <c r="T20" s="3">
         <v>400</v>
-      </c>
-      <c r="T20" s="3">
-        <v>-100</v>
       </c>
       <c r="U20" s="3">
         <v>-100</v>
@@ -1845,224 +1879,230 @@
         <v>-100</v>
       </c>
       <c r="W20" s="3">
-        <v>-200</v>
+        <v>-100</v>
       </c>
       <c r="X20" s="3">
         <v>-200</v>
       </c>
       <c r="Y20" s="3">
+        <v>-200</v>
+      </c>
+      <c r="Z20" s="3">
         <v>-8300</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>-300</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>7700</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>300</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>-15200</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>-100</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>6300</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>8700</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>4000</v>
       </c>
-      <c r="AH20" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI20" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>82300</v>
+      </c>
+      <c r="E21" s="3">
         <v>146700</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>139500</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>134600</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>170000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>140200</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>139500</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>135000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>158200</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>132200</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>33100</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>37000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>42900</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>69000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>38000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>42600</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>40700</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>44800</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>59500</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>26800</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>50200</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>58100</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>24100</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>57900</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>57000</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>37500</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>60600</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>59600</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>70700</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>63200</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>65300</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>63500</v>
       </c>
     </row>
-    <row r="22" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>31000</v>
+      </c>
+      <c r="E22" s="3">
         <v>30400</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>27200</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>25500</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>27200</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>25400</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>26800</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>26200</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>25700</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>25500</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>23100</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>12900</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>12300</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>12200</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>12300</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>12600</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>13300</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>12300</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>12400</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>14300</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>16100</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>16500</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>17600</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>16100</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>16700</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>16300</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>16500</v>
-      </c>
-      <c r="AD22" s="3">
-        <v>16400</v>
       </c>
       <c r="AE22" s="3">
         <v>16400</v>
@@ -2071,146 +2111,152 @@
         <v>16400</v>
       </c>
       <c r="AG22" s="3">
+        <v>16400</v>
+      </c>
+      <c r="AH22" s="3">
         <v>17600</v>
       </c>
-      <c r="AH22" s="3">
+      <c r="AI22" s="3">
         <v>17100</v>
       </c>
     </row>
-    <row r="23" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-49000</v>
+      </c>
+      <c r="E23" s="3">
         <v>15000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>8400</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>2300</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>32400</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>5800</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-1100</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-7900</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>13100</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-16600</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-100500</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-6700</v>
       </c>
-      <c r="O23" s="3">
-        <v>0</v>
-      </c>
       <c r="P23" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q23" s="3">
         <v>25600</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-6600</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-4400</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-4600</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>400</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>15700</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-20100</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-1500</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>6300</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-31600</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>4300</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>-1100</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>-18000</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>2800</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>-200</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>10900</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>400</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>4000</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>-1200</v>
       </c>
     </row>
-    <row r="24" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>100</v>
+      </c>
+      <c r="E24" s="3">
         <v>200</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>400</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>100</v>
       </c>
-      <c r="G24" s="3">
-        <v>0</v>
-      </c>
       <c r="H24" s="3">
         <v>0</v>
       </c>
       <c r="I24" s="3">
+        <v>0</v>
+      </c>
+      <c r="J24" s="3">
         <v>300</v>
       </c>
-      <c r="J24" s="3">
-        <v>0</v>
-      </c>
       <c r="K24" s="3">
+        <v>0</v>
+      </c>
+      <c r="L24" s="3">
         <v>-200</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>-100</v>
       </c>
-      <c r="M24" s="3">
-        <v>0</v>
-      </c>
       <c r="N24" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="O24" s="3">
         <v>-100</v>
@@ -2219,7 +2265,7 @@
         <v>-100</v>
       </c>
       <c r="Q24" s="3">
-        <v>-200</v>
+        <v>-100</v>
       </c>
       <c r="R24" s="3">
         <v>-200</v>
@@ -2228,16 +2274,16 @@
         <v>-200</v>
       </c>
       <c r="T24" s="3">
-        <v>-100</v>
+        <v>-200</v>
       </c>
       <c r="U24" s="3">
         <v>-100</v>
       </c>
       <c r="V24" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="W24" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="X24" s="3">
         <v>-100</v>
@@ -2246,7 +2292,7 @@
         <v>-100</v>
       </c>
       <c r="Z24" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="AA24" s="3">
         <v>0</v>
@@ -2267,13 +2313,16 @@
         <v>0</v>
       </c>
       <c r="AG24" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH24" s="3">
         <v>100</v>
       </c>
-      <c r="AH24" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2370,204 +2419,213 @@
       <c r="AH25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-49100</v>
+      </c>
+      <c r="E26" s="3">
         <v>14900</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>8000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>2200</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>32400</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>5800</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-1400</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-7900</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>13300</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-16500</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-100500</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-6600</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>100</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>25700</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-6400</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-4200</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-4400</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>500</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>15800</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-20100</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-1500</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>6400</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-31400</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>4300</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>-1100</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>-18000</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>2800</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>-200</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>10900</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>400</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>3900</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>-1300</v>
       </c>
     </row>
-    <row r="27" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-48600</v>
+      </c>
+      <c r="E27" s="3">
         <v>14200</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>8000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>2100</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>32100</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>5400</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-1100</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-7800</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>13100</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-16800</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-98200</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-7000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-200</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>24600</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-6800</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-4600</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-4800</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-100</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>15300</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-19700</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-1800</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>5700</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-31200</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>3900</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>-1400</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>-17900</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>2300</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>-600</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>10200</v>
       </c>
-      <c r="AF27" s="3">
-        <v>0</v>
-      </c>
       <c r="AG27" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH27" s="3">
         <v>3400</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>-1700</v>
       </c>
     </row>
-    <row r="28" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2664,8 +2722,11 @@
       <c r="AH28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2744,8 +2805,8 @@
       <c r="AB29" s="3">
         <v>0</v>
       </c>
-      <c r="AC29" s="3" t="s">
-        <v>8</v>
+      <c r="AC29" s="3">
+        <v>0</v>
       </c>
       <c r="AD29" s="3" t="s">
         <v>8</v>
@@ -2756,14 +2817,17 @@
       <c r="AF29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AG29" s="3">
-        <v>0</v>
-      </c>
-      <c r="AH29" s="3" t="s">
+      <c r="AG29" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="30" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AH29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI29" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="30" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2860,8 +2924,11 @@
       <c r="AH30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2958,61 +3025,64 @@
       <c r="AH31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-4300</v>
+      </c>
+      <c r="E32" s="3">
         <v>-6000</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-300</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-1000</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-300</v>
-      </c>
-      <c r="H32" s="3">
-        <v>-400</v>
       </c>
       <c r="I32" s="3">
         <v>-400</v>
       </c>
       <c r="J32" s="3">
+        <v>-400</v>
+      </c>
+      <c r="K32" s="3">
         <v>-100</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>200</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>100</v>
-      </c>
-      <c r="M32" s="3">
-        <v>-100</v>
       </c>
       <c r="N32" s="3">
         <v>-100</v>
       </c>
       <c r="O32" s="3">
+        <v>-100</v>
+      </c>
+      <c r="P32" s="3">
         <v>-300</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>200</v>
       </c>
-      <c r="Q32" s="3">
-        <v>0</v>
-      </c>
       <c r="R32" s="3">
         <v>0</v>
       </c>
       <c r="S32" s="3">
+        <v>0</v>
+      </c>
+      <c r="T32" s="3">
         <v>-400</v>
-      </c>
-      <c r="T32" s="3">
-        <v>100</v>
       </c>
       <c r="U32" s="3">
         <v>100</v>
@@ -3021,141 +3091,147 @@
         <v>100</v>
       </c>
       <c r="W32" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="X32" s="3">
         <v>200</v>
       </c>
       <c r="Y32" s="3">
+        <v>200</v>
+      </c>
+      <c r="Z32" s="3">
         <v>8300</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>300</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>-7700</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>-300</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>15200</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>100</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>-6300</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>-8700</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>-4000</v>
       </c>
-      <c r="AH32" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="33" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI32" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-48600</v>
+      </c>
+      <c r="E33" s="3">
         <v>14200</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>8000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>2100</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>32100</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>5400</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-1100</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-7800</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>13100</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-16800</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-98200</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-7000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-200</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>24600</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-6800</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-4600</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-4800</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-100</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>15300</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-19700</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-1800</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>5700</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-31200</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>3900</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>-1400</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>-17900</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>2300</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>-600</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>10200</v>
       </c>
-      <c r="AF33" s="3">
-        <v>0</v>
-      </c>
       <c r="AG33" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH33" s="3">
         <v>3400</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>-1700</v>
       </c>
     </row>
-    <row r="34" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3252,209 +3328,218 @@
       <c r="AH34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-48600</v>
+      </c>
+      <c r="E35" s="3">
         <v>14200</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>8000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>2100</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>32100</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>5400</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-1100</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-7800</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>13100</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-16800</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-98200</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-7000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-200</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>24600</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-6800</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-4600</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-4800</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-100</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>15300</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-19700</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-1800</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>5700</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-31200</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>3900</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>-1400</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>-17900</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>2300</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>-600</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>10200</v>
       </c>
-      <c r="AF35" s="3">
-        <v>0</v>
-      </c>
       <c r="AG35" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH35" s="3">
         <v>3400</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>-1700</v>
       </c>
     </row>
-    <row r="37" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:35" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E38" s="2">
         <v>45382</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45291</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45199</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45107</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45016</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44926</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44834</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44742</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44651</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44561</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44469</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44377</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44286</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44196</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44104</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44012</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43921</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43830</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43738</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43646</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43555</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43465</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43373</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43281</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43190</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43100</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43008</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>42916</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>42825</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>42735</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3489,8 +3574,9 @@
       <c r="AF39" s="3"/>
       <c r="AG39" s="3"/>
       <c r="AH39" s="3"/>
-    </row>
-    <row r="40" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI39" s="3"/>
+    </row>
+    <row r="40" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3525,106 +3611,110 @@
       <c r="AF40" s="3"/>
       <c r="AG40" s="3"/>
       <c r="AH40" s="3"/>
-    </row>
-    <row r="41" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI40" s="3"/>
+    </row>
+    <row r="41" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>153800</v>
+      </c>
+      <c r="E41" s="3">
         <v>83600</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>36400</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>52300</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>129300</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>43700</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>115800</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>88400</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>90800</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>74300</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>93200</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>99500</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>89900</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>228800</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>43600</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>129300</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>230000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>343900</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>31300</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>40400</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>35800</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>28400</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>35400</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>30700</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>32400</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>28800</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>24100</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>32500</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>27600</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>22600</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>19900</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>28800</v>
       </c>
     </row>
-    <row r="42" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3721,106 +3811,112 @@
       <c r="AH42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>120000</v>
+      </c>
+      <c r="E43" s="3">
         <v>118100</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>113300</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>113100</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>109600</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>103500</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>101300</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>86600</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>76900</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>69100</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>68400</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>45900</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>46700</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>49100</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>57200</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>57100</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>61600</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>49900</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>55300</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>50000</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>52000</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>55400</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>58100</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>57100</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>53100</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>57200</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>58300</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>53300</v>
-      </c>
-      <c r="AE43" s="3">
-        <v>52300</v>
       </c>
       <c r="AF43" s="3">
         <v>52300</v>
       </c>
       <c r="AG43" s="3">
+        <v>52300</v>
+      </c>
+      <c r="AH43" s="3">
         <v>53100</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>50400</v>
       </c>
     </row>
-    <row r="44" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3917,106 +4013,112 @@
       <c r="AH44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>114200</v>
+      </c>
+      <c r="E45" s="3">
         <v>131800</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>117800</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>134600</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>130500</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>117400</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>127000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>142800</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>106000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>96300</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>84800</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>39200</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>39500</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>42900</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>13000</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>39300</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>38200</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>36300</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>7500</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>10100</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>10300</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>14100</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>12800</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>17400</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>14200</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>20300</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>16400</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>12800</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>10200</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>12800</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>9700</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>10800</v>
       </c>
     </row>
-    <row r="46" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
@@ -4113,85 +4215,88 @@
       <c r="AH46" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="47" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI46" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>130000</v>
+      </c>
+      <c r="E47" s="3">
         <v>274600</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>9100</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>10200</v>
-      </c>
-      <c r="G47" s="3">
-        <v>10300</v>
       </c>
       <c r="H47" s="3">
         <v>10300</v>
       </c>
       <c r="I47" s="3">
+        <v>10300</v>
+      </c>
+      <c r="J47" s="3">
         <v>10400</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>10600</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>10400</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>136800</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>136900</v>
-      </c>
-      <c r="N47" s="3">
-        <v>138000</v>
       </c>
       <c r="O47" s="3">
         <v>138000</v>
       </c>
       <c r="P47" s="3">
+        <v>138000</v>
+      </c>
+      <c r="Q47" s="3">
         <v>13000</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>12800</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>13100</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>13200</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>12100</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>12600</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>12900</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>12700</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>13300</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>13500</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>13800</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>13900</v>
-      </c>
-      <c r="AB47" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AC47" s="3" t="s">
         <v>8</v>
@@ -4211,129 +4316,135 @@
       <c r="AH47" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="48" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI47" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="48" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>6098600</v>
+      </c>
+      <c r="E48" s="3">
         <v>6305700</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>6358300</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>6397300</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>6426100</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>6508700</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>6571400</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>6621600</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>6617800</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>6676800</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>6707500</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>2308000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>2343700</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>2358900</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>2415900</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>2347400</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>2380500</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>2404000</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>2447400</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>2514100</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>2716800</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>2911300</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>2941200</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>3051700</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>3076800</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>3194200</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>3293300</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>3320300</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>3331800</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>3399700</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>3435400</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>3458300</v>
       </c>
     </row>
-    <row r="49" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>0</v>
+        <v>389200</v>
       </c>
       <c r="E49" s="3">
-        <v>0</v>
+        <v>405500</v>
       </c>
       <c r="F49" s="3">
-        <v>0</v>
-      </c>
-      <c r="G49" s="3">
-        <v>0</v>
-      </c>
-      <c r="H49" s="3">
-        <v>0</v>
-      </c>
-      <c r="I49" s="3">
-        <v>0</v>
-      </c>
-      <c r="J49" s="3">
-        <v>0</v>
+        <v>433800</v>
+      </c>
+      <c r="G49" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H49" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I49" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J49" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K49" s="3">
         <v>0</v>
@@ -4384,31 +4495,34 @@
         <v>0</v>
       </c>
       <c r="AA49" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB49" s="3">
         <v>32300</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>39000</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>44000</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>47900</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>53000</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>59300</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>65500</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>70000</v>
       </c>
     </row>
-    <row r="50" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4505,8 +4619,11 @@
       <c r="AH50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4603,106 +4720,112 @@
       <c r="AH51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="D52" s="3">
-        <v>290800</v>
-      </c>
-      <c r="E52" s="3">
-        <v>309200</v>
-      </c>
-      <c r="F52" s="3">
+      <c r="D52" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E52" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F52" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G52" s="3">
         <v>345000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>359400</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>413200</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>416000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>450000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>483000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>520300</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>548600</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>78400</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>61400</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>62600</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>66100</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>71900</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>88300</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>91300</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>94600</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>86300</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>108700</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>180800</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>111100</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>115100</v>
-      </c>
-      <c r="AA52" s="3">
-        <v>79400</v>
       </c>
       <c r="AB52" s="3">
         <v>79400</v>
       </c>
       <c r="AC52" s="3">
+        <v>79400</v>
+      </c>
+      <c r="AD52" s="3">
         <v>76400</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>76600</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>75400</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>76700</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>72800</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>72700</v>
       </c>
     </row>
-    <row r="53" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4799,106 +4922,112 @@
       <c r="AH53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>6958900</v>
+      </c>
+      <c r="E54" s="3">
         <v>7204500</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>6944100</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>7052500</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>7165100</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>7196900</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>7342000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>7399900</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>7384900</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>7573700</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>7639600</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>2708900</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>2719200</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>2755300</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>2608500</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>2658100</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>2811800</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>2937400</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>2648900</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>2713900</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>2936300</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>3203200</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>3172000</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>3285900</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>3302200</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>3418900</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>3512500</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>3543400</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>3550300</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>3623500</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>3656400</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>3690900</v>
       </c>
     </row>
-    <row r="55" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4933,8 +5062,9 @@
       <c r="AF55" s="3"/>
       <c r="AG55" s="3"/>
       <c r="AH55" s="3"/>
-    </row>
-    <row r="56" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI55" s="3"/>
+    </row>
+    <row r="56" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4969,106 +5099,110 @@
       <c r="AF56" s="3"/>
       <c r="AG56" s="3"/>
       <c r="AH56" s="3"/>
-    </row>
-    <row r="57" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI56" s="3"/>
+    </row>
+    <row r="57" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>189700</v>
+      </c>
+      <c r="E57" s="3">
         <v>171600</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>198100</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>198500</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>178200</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>160100</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>207800</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>152000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>133800</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>124200</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>185000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>85700</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>74400</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>72100</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>77500</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>88600</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>85700</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>109400</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>69800</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>77500</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>66600</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>61900</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>85900</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>98500</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>101200</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>102900</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>78500</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>101600</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>88500</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>88800</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>80700</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>93400</v>
       </c>
     </row>
-    <row r="58" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -5165,76 +5299,79 @@
       <c r="AH58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>80300</v>
+      </c>
+      <c r="E59" s="3">
         <v>78400</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>78200</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>82000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>79600</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>68900</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>79300</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>78100</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>76000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>79200</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>70200</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>26200</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>26300</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>26400</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>26500</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>26600</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>26800</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>26900</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>27000</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>27100</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>27200</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>27300</v>
-      </c>
-      <c r="Y59" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="Z59" s="3" t="s">
         <v>8</v>
@@ -5245,8 +5382,8 @@
       <c r="AB59" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AC59" s="3">
-        <v>0</v>
+      <c r="AC59" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AD59" s="3">
         <v>0</v>
@@ -5263,8 +5400,11 @@
       <c r="AH59" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="60" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI59" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
@@ -5361,106 +5501,112 @@
       <c r="AH60" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="61" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI60" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>3015600</v>
+      </c>
+      <c r="E61" s="3">
         <v>3167500</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>2829200</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>2868800</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>2938000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>2972600</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>3010300</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>3012900</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>3001200</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>3179100</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>3150800</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>1289000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>1289400</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>1315200</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>1170800</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>1196100</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>1346300</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>1446500</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>1146600</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>1198600</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>1376600</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>1602600</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>1543300</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>1578300</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>1565400</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>1650500</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>1699200</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>1681700</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>1675100</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>1726900</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>1731100</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>1732300</v>
       </c>
     </row>
-    <row r="62" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -5491,8 +5637,8 @@
       <c r="L62" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M62" s="3">
-        <v>0</v>
+      <c r="M62" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="N62" s="3">
         <v>0</v>
@@ -5521,14 +5667,14 @@
       <c r="V62" s="3">
         <v>0</v>
       </c>
-      <c r="W62" s="3" t="s">
+      <c r="W62" s="3">
+        <v>0</v>
+      </c>
+      <c r="X62" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>2400</v>
-      </c>
-      <c r="Y62" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="Z62" s="3" t="s">
         <v>8</v>
@@ -5539,8 +5685,8 @@
       <c r="AB62" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AC62" s="3">
-        <v>0</v>
+      <c r="AC62" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AD62" s="3">
         <v>0</v>
@@ -5557,8 +5703,11 @@
       <c r="AH62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5655,8 +5804,11 @@
       <c r="AH63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5753,8 +5905,11 @@
       <c r="AH64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5851,106 +6006,112 @@
       <c r="AH65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>3537300</v>
+      </c>
+      <c r="E66" s="3">
         <v>3673700</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>3375900</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>3417200</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>3472300</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>3490900</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>3575500</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>3527100</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>3493700</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>3675100</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>3717500</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>1510000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>1505700</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>1523500</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>1377900</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>1416000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>1563600</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>1684600</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>1359800</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>1411700</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>1583700</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>1816400</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>1759300</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>1807700</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>1802800</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>1893900</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>1947100</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>1958500</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>1940600</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>2004000</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>2012800</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>2046500</v>
       </c>
     </row>
-    <row r="67" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5985,8 +6146,9 @@
       <c r="AF67" s="3"/>
       <c r="AG67" s="3"/>
       <c r="AH67" s="3"/>
-    </row>
-    <row r="68" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI67" s="3"/>
+    </row>
+    <row r="68" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6083,8 +6245,11 @@
       <c r="AH68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6181,8 +6346,11 @@
       <c r="AH69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6279,8 +6447,11 @@
       <c r="AH70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6377,106 +6548,112 @@
       <c r="AH71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-1517400</v>
+      </c>
+      <c r="E72" s="3">
         <v>-1413800</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-1373100</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-1326200</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-1275600</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-1255000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-1207800</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-1105800</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-1052000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-1021300</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-962900</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-849500</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-827300</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-812700</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-824300</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-810800</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-801800</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-797000</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-770000</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-758600</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-712200</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-683700</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>-662700</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>-604900</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>-582200</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>-554300</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>-509800</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>-485600</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>-459700</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>-444600</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>-419300</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>-397400</v>
       </c>
     </row>
-    <row r="73" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6573,8 +6750,11 @@
       <c r="AH73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6671,8 +6851,11 @@
       <c r="AH74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6769,106 +6952,112 @@
       <c r="AH75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>3421600</v>
+      </c>
+      <c r="E76" s="3">
         <v>3530800</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>3568100</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>3635300</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>3692800</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>3706000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>3766500</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>3872800</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>3891100</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>3898600</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>3922000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>1198800</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>1213500</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>1231900</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>1230700</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>1242100</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>1248200</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>1252800</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>1289000</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>1302200</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>1352700</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>1386800</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>1412700</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>1478200</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>1499400</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>1525000</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>1565400</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>1584900</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>1609700</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>1619500</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>1643600</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>1644400</v>
       </c>
     </row>
-    <row r="77" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6965,209 +7154,218 @@
       <c r="AH77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:35" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E80" s="2">
         <v>45382</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45291</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45199</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45107</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45016</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44926</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44834</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44742</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44651</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44561</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44469</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44377</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44286</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44196</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44104</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44012</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43921</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43830</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43738</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43646</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43555</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43465</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43373</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43281</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43190</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43100</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43008</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>42916</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>42825</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>42735</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-48600</v>
+      </c>
+      <c r="E81" s="3">
         <v>14200</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>8000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>2100</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>32100</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>5400</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-1100</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-7800</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>13100</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-16800</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-98200</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-7000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-200</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>24600</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-6800</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-4600</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-4800</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-100</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>15300</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-19700</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-1800</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>5700</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-31200</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>3900</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>-1400</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>-17900</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>2300</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>-600</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>10200</v>
       </c>
-      <c r="AF81" s="3">
-        <v>0</v>
-      </c>
       <c r="AG81" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH81" s="3">
         <v>3400</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>-1700</v>
       </c>
     </row>
-    <row r="82" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7202,106 +7400,110 @@
       <c r="AF82" s="3"/>
       <c r="AG82" s="3"/>
       <c r="AH82" s="3"/>
-    </row>
-    <row r="83" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI82" s="3"/>
+    </row>
+    <row r="83" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>100300</v>
+      </c>
+      <c r="E83" s="3">
         <v>101300</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>103800</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>106800</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>110400</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>109000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>113700</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>116600</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>119300</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>123300</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>110600</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>30800</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>30500</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>31200</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>32300</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>34400</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>32000</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>32100</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>31400</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>32600</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>35600</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>35300</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>38000</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>37500</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>41300</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>39200</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>41400</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>43500</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>43400</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>46400</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>43700</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>47700</v>
       </c>
     </row>
-    <row r="84" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7398,8 +7600,11 @@
       <c r="AH84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7496,8 +7701,11 @@
       <c r="AH85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7594,8 +7802,11 @@
       <c r="AH86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7692,8 +7903,11 @@
       <c r="AH87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7790,106 +8004,112 @@
       <c r="AH88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>142100</v>
+      </c>
+      <c r="E89" s="3">
         <v>53600</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>103500</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>110800</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>116800</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>63600</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>116900</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>108100</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>104700</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>49600</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-3500</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>36400</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>36100</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>31300</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>9800</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>35900</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>28000</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>21900</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>31800</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>36500</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>37300</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>32300</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>35400</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>37000</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>45800</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>36300</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>30800</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>42700</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>44900</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>36200</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>34200</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>39800</v>
       </c>
     </row>
-    <row r="90" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7924,106 +8144,110 @@
       <c r="AF90" s="3"/>
       <c r="AG90" s="3"/>
       <c r="AH90" s="3"/>
-    </row>
-    <row r="91" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI90" s="3"/>
+    </row>
+    <row r="91" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-38900</v>
+      </c>
+      <c r="E91" s="3">
         <v>-28200</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-43900</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-30900</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-28600</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-39100</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-52000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-47800</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-35000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-23800</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-20400</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-15700</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-13300</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-7900</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-7600</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-8200</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-9200</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-13200</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-15700</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-12400</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-13700</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-11500</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-12000</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-12700</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-16500</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-18100</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-10800</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-24800</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-11200</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-47700</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-26000</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-24100</v>
       </c>
     </row>
-    <row r="92" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8120,8 +8344,11 @@
       <c r="AH92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8218,106 +8445,112 @@
       <c r="AH93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>134700</v>
+      </c>
+      <c r="E94" s="3">
         <v>-289300</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-26200</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-63500</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>49500</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-41500</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-31500</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-82300</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>130800</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-62200</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>18000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-9600</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-133300</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>33900</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-64900</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>4700</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-13500</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-7100</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>52800</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>166900</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>226600</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-29700</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>44700</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-14500</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>71800</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>46400</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-23200</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-16500</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>38100</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>1400</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-15600</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-22200</v>
       </c>
     </row>
-    <row r="95" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8352,8 +8585,9 @@
       <c r="AF95" s="3"/>
       <c r="AG95" s="3"/>
       <c r="AH95" s="3"/>
-    </row>
-    <row r="96" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI95" s="3"/>
+    </row>
+    <row r="96" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -8361,55 +8595,55 @@
         <v>-54900</v>
       </c>
       <c r="E96" s="3">
-        <v>-52700</v>
+        <v>-54900</v>
       </c>
       <c r="F96" s="3">
         <v>-52700</v>
       </c>
       <c r="G96" s="3">
-        <v>-52600</v>
+        <v>-52700</v>
       </c>
       <c r="H96" s="3">
         <v>-52600</v>
       </c>
       <c r="I96" s="3">
+        <v>-52600</v>
+      </c>
+      <c r="J96" s="3">
         <v>-48200</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>-46000</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>-43800</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>-41600</v>
-      </c>
-      <c r="M96" s="3">
-        <v>-15200</v>
       </c>
       <c r="N96" s="3">
         <v>-15200</v>
       </c>
       <c r="O96" s="3">
+        <v>-15200</v>
+      </c>
+      <c r="P96" s="3">
         <v>-14400</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>-13000</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="R96" s="3">
         <v>-6700</v>
       </c>
-      <c r="R96" s="3">
+      <c r="S96" s="3">
         <v>-4400</v>
       </c>
-      <c r="S96" s="3">
+      <c r="T96" s="3">
         <v>-26700</v>
       </c>
-      <c r="T96" s="3">
+      <c r="U96" s="3">
         <v>-300</v>
-      </c>
-      <c r="U96" s="3">
-        <v>-26700</v>
       </c>
       <c r="V96" s="3">
         <v>-26700</v>
@@ -8418,10 +8652,10 @@
         <v>-26700</v>
       </c>
       <c r="X96" s="3">
+        <v>-26700</v>
+      </c>
+      <c r="Y96" s="3">
         <v>-53300</v>
-      </c>
-      <c r="Y96" s="3">
-        <v>-26600</v>
       </c>
       <c r="Z96" s="3">
         <v>-26600</v>
@@ -8430,10 +8664,10 @@
         <v>-26600</v>
       </c>
       <c r="AB96" s="3">
+        <v>-26600</v>
+      </c>
+      <c r="AC96" s="3">
         <v>-26500</v>
-      </c>
-      <c r="AC96" s="3">
-        <v>-25300</v>
       </c>
       <c r="AD96" s="3">
         <v>-25300</v>
@@ -8445,13 +8679,16 @@
         <v>-25300</v>
       </c>
       <c r="AG96" s="3">
-        <v>-24000</v>
+        <v>-25300</v>
       </c>
       <c r="AH96" s="3">
         <v>-24000</v>
       </c>
-    </row>
-    <row r="97" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI96" s="3">
+        <v>-24000</v>
+      </c>
+    </row>
+    <row r="97" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8548,8 +8785,11 @@
       <c r="AH97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8646,8 +8886,11 @@
       <c r="AH98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8744,106 +8987,112 @@
       <c r="AH99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-206800</v>
+      </c>
+      <c r="E100" s="3">
         <v>283300</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-94100</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-123900</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-84100</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-91400</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-59900</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-28400</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-218600</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-5600</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-18000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-17100</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-41200</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>120800</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-35600</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-155100</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-128300</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>298000</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-81800</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-212900</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-256400</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>3800</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-75600</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-24800</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-112800</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-76300</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-16800</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-19700</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-78700</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-34200</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-27600</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>-26600</v>
       </c>
     </row>
-    <row r="101" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -8940,102 +9189,108 @@
       <c r="AH101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>70000</v>
+      </c>
+      <c r="E102" s="3">
         <v>47500</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-16900</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-76600</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>82300</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-69300</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>25500</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-2600</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>17000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-18200</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-3400</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>9700</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-138500</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>185900</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-90700</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-114500</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-113800</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>312800</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>2800</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-9500</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>7600</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>6400</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>4500</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-2300</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>4800</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>6400</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-8400</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>4800</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>4400</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>3300</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>-8900</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>-9100</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/KRG_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/KRG_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="168" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="178" uniqueCount="92">
   <si>
     <t>KRG</t>
   </si>
@@ -656,454 +656,467 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AI102"/>
+  <dimension ref="A5:AJ102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="35" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="36" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:36" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E7" s="2">
         <v>45473</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45382</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45291</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45199</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45107</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45016</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44926</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44834</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44742</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44651</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44561</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44469</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44377</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44286</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44196</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44104</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44012</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43921</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43830</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43738</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43646</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43555</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43465</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43373</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43281</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43190</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43100</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43008</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>42916</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>42825</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>42735</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>207300</v>
+      </c>
+      <c r="E8" s="3">
         <v>212400</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>207400</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>200300</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>207200</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>208800</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>206800</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>204700</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>200300</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>202600</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>194400</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>163000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>71500</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>69500</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>69400</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>68400</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>65100</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>63300</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>69900</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>75200</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>74900</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>81500</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>83500</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>86900</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>85700</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>91700</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>89800</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>88900</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>87100</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>92600</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>90100</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>88900</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>89100</v>
       </c>
     </row>
-    <row r="9" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>53000</v>
+      </c>
+      <c r="E9" s="3">
         <v>55100</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>54600</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>47900</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>54100</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>53900</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>54500</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>53800</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>51200</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>54000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>52800</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>47500</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>19100</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>18800</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>19700</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>19900</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>19700</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>17600</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>19700</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>20600</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>20700</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>21400</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>21600</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>23200</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>23300</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>23000</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>23200</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>23500</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>22700</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>23400</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>23300</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>23000</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>22600</v>
       </c>
     </row>
-    <row r="10" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>157300</v>
+        <v>154300</v>
       </c>
       <c r="E10" s="3">
+        <v>157400</v>
+      </c>
+      <c r="F10" s="3">
         <v>152800</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>152400</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>153100</v>
       </c>
-      <c r="H10" s="3">
-        <v>154900</v>
-      </c>
       <c r="I10" s="3">
+        <v>154800</v>
+      </c>
+      <c r="J10" s="3">
         <v>152300</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>150900</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>149100</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>148600</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>141600</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>115500</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>52400</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>50700</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>49700</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>48500</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>45400</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>45700</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>50200</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>54600</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>54200</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>60100</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>61900</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>63700</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>62400</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>68700</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>66600</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>65400</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>64400</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>69200</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>66800</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>65900</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>66500</v>
       </c>
     </row>
-    <row r="11" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1139,8 +1152,9 @@
       <c r="AG11" s="3"/>
       <c r="AH11" s="3"/>
       <c r="AI11" s="3"/>
+      <c r="AJ11" s="3"/>
     </row>
-    <row r="12" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1240,8 +1254,11 @@
       <c r="AI12" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AJ12" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="13" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1341,210 +1358,219 @@
       <c r="AI13" s="3">
         <v>0</v>
       </c>
+      <c r="AJ13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>66200</v>
-      </c>
-      <c r="E14" s="3" t="s">
+        <v>-5000</v>
+      </c>
+      <c r="E14" s="3">
+        <v>63100</v>
+      </c>
+      <c r="F14" s="3">
+        <v>-5700</v>
+      </c>
+      <c r="G14" s="3">
+        <v>-500</v>
+      </c>
+      <c r="H14" s="3">
+        <v>5500</v>
+      </c>
+      <c r="I14" s="3">
+        <v>-28700</v>
+      </c>
+      <c r="J14" s="3">
+        <v>-400</v>
+      </c>
+      <c r="K14" s="3">
+        <v>-100</v>
+      </c>
+      <c r="L14" s="3">
+        <v>100</v>
+      </c>
+      <c r="M14" s="3">
+        <v>0</v>
+      </c>
+      <c r="N14" s="3">
+        <v>900</v>
+      </c>
+      <c r="O14" s="3">
+        <v>76600</v>
+      </c>
+      <c r="P14" s="3">
+        <v>9200</v>
+      </c>
+      <c r="Q14" s="3">
+        <v>800</v>
+      </c>
+      <c r="R14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="F14" s="3">
-        <v>0</v>
-      </c>
-      <c r="G14" s="3">
-        <v>500</v>
-      </c>
-      <c r="H14" s="3">
-        <v>0</v>
-      </c>
-      <c r="I14" s="3">
-        <v>0</v>
-      </c>
-      <c r="J14" s="3">
-        <v>-100</v>
-      </c>
-      <c r="K14" s="3">
-        <v>100</v>
-      </c>
-      <c r="L14" s="3">
-        <v>0</v>
-      </c>
-      <c r="M14" s="3">
-        <v>900</v>
-      </c>
-      <c r="N14" s="3">
-        <v>76600</v>
-      </c>
-      <c r="O14" s="3">
-        <v>9200</v>
-      </c>
-      <c r="P14" s="3">
-        <v>800</v>
-      </c>
-      <c r="Q14" s="3" t="s">
+      <c r="S14" s="3">
+        <v>0</v>
+      </c>
+      <c r="T14" s="3">
+        <v>0</v>
+      </c>
+      <c r="U14" s="3">
+        <v>0</v>
+      </c>
+      <c r="V14" s="3">
+        <v>0</v>
+      </c>
+      <c r="W14" s="3">
+        <v>2000</v>
+      </c>
+      <c r="X14" s="3">
+        <v>15600</v>
+      </c>
+      <c r="Y14" s="3">
+        <v>27700</v>
+      </c>
+      <c r="Z14" s="3">
+        <v>4100</v>
+      </c>
+      <c r="AA14" s="3">
+        <v>31500</v>
+      </c>
+      <c r="AB14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC14" s="3">
+        <v>14800</v>
+      </c>
+      <c r="AD14" s="3">
+        <v>24100</v>
+      </c>
+      <c r="AE14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH14" s="3">
+        <v>7400</v>
+      </c>
+      <c r="AI14" s="3">
+        <v>2800</v>
+      </c>
+      <c r="AJ14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="R14" s="3">
-        <v>0</v>
-      </c>
-      <c r="S14" s="3">
-        <v>0</v>
-      </c>
-      <c r="T14" s="3">
-        <v>0</v>
-      </c>
-      <c r="U14" s="3">
-        <v>0</v>
-      </c>
-      <c r="V14" s="3">
-        <v>2000</v>
-      </c>
-      <c r="W14" s="3">
-        <v>15600</v>
-      </c>
-      <c r="X14" s="3">
-        <v>27700</v>
-      </c>
-      <c r="Y14" s="3">
-        <v>4100</v>
-      </c>
-      <c r="Z14" s="3">
-        <v>31500</v>
-      </c>
-      <c r="AA14" s="3">
-        <v>0</v>
-      </c>
-      <c r="AB14" s="3">
-        <v>14800</v>
-      </c>
-      <c r="AC14" s="3">
-        <v>24100</v>
-      </c>
-      <c r="AD14" s="3">
-        <v>0</v>
-      </c>
-      <c r="AE14" s="3">
-        <v>0</v>
-      </c>
-      <c r="AF14" s="3">
-        <v>0</v>
-      </c>
-      <c r="AG14" s="3">
-        <v>7400</v>
-      </c>
-      <c r="AH14" s="3">
-        <v>2800</v>
-      </c>
-      <c r="AI14" s="3" t="s">
-        <v>8</v>
-      </c>
     </row>
-    <row r="15" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>96700</v>
+      </c>
+      <c r="E15" s="3">
         <v>99300</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>100400</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>102900</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>105900</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>109500</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>108100</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>112700</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>115800</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>119800</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>121500</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>109800</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>30200</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>29800</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>30600</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>31800</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>34000</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>31400</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>31500</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>30800</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>32000</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>34700</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="Z15" s="3">
         <v>34600</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AA15" s="3">
         <v>36300</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AB15" s="3">
         <v>36900</v>
       </c>
-      <c r="AB15" s="3">
+      <c r="AC15" s="3">
         <v>40500</v>
       </c>
-      <c r="AC15" s="3">
+      <c r="AD15" s="3">
         <v>38600</v>
       </c>
-      <c r="AD15" s="3">
+      <c r="AE15" s="3">
         <v>40800</v>
       </c>
-      <c r="AE15" s="3">
+      <c r="AF15" s="3">
         <v>42800</v>
       </c>
-      <c r="AF15" s="3">
+      <c r="AG15" s="3">
         <v>42700</v>
       </c>
-      <c r="AG15" s="3">
+      <c r="AH15" s="3">
         <v>45800</v>
       </c>
-      <c r="AH15" s="3">
+      <c r="AI15" s="3">
         <v>42900</v>
       </c>
-      <c r="AI15" s="3">
+      <c r="AJ15" s="3">
         <v>45500</v>
       </c>
     </row>
-    <row r="16" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:36" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1577,210 +1603,217 @@
       <c r="AG16" s="3"/>
       <c r="AH16" s="3"/>
       <c r="AI16" s="3"/>
+      <c r="AJ16" s="3"/>
     </row>
-    <row r="17" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>234700</v>
+        <v>162900</v>
       </c>
       <c r="E17" s="3">
-        <v>168000</v>
+        <v>167300</v>
       </c>
       <c r="F17" s="3">
-        <v>165000</v>
+        <v>167800</v>
       </c>
       <c r="G17" s="3">
-        <v>180400</v>
+        <v>165100</v>
       </c>
       <c r="H17" s="3">
-        <v>149500</v>
+        <v>173900</v>
       </c>
       <c r="I17" s="3">
+        <v>177900</v>
+      </c>
+      <c r="J17" s="3">
         <v>176000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>179400</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>182000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>163600</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>185400</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>240600</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>65500</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>57400</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>31400</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>62700</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>56900</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>54900</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>57100</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>47000</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>80700</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>66700</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>60500</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>92500</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>65000</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>83800</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>91800</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>54400</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>70900</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>71600</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>82000</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>71300</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>73200</v>
       </c>
     </row>
-    <row r="18" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>-22300</v>
+        <v>44400</v>
       </c>
       <c r="E18" s="3">
-        <v>39400</v>
+        <v>45100</v>
       </c>
       <c r="F18" s="3">
-        <v>35300</v>
+        <v>39700</v>
       </c>
       <c r="G18" s="3">
-        <v>26800</v>
+        <v>35200</v>
       </c>
       <c r="H18" s="3">
-        <v>59400</v>
+        <v>33300</v>
       </c>
       <c r="I18" s="3">
+        <v>30900</v>
+      </c>
+      <c r="J18" s="3">
         <v>30800</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>25300</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>18300</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>39000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>9000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-77600</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>6000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>12100</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>38000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>5700</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>8200</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>8400</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>12800</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>28200</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>-5800</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>14800</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>23000</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>-5600</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>20700</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>7900</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>-2000</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>34500</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>16200</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>21000</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>8100</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>17600</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>15900</v>
       </c>
     </row>
-    <row r="19" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1816,64 +1849,65 @@
       <c r="AG19" s="3"/>
       <c r="AH19" s="3"/>
       <c r="AI19" s="3"/>
+      <c r="AJ19" s="3"/>
     </row>
-    <row r="20" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>4300</v>
+        <v>600</v>
       </c>
       <c r="E20" s="3">
-        <v>6000</v>
+        <v>200</v>
       </c>
       <c r="F20" s="3">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="G20" s="3">
-        <v>1000</v>
+        <v>-200</v>
       </c>
       <c r="H20" s="3">
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="I20" s="3">
+        <v>-100</v>
+      </c>
+      <c r="J20" s="3">
+        <v>200</v>
+      </c>
+      <c r="K20" s="3">
         <v>400</v>
       </c>
-      <c r="J20" s="3">
-        <v>400</v>
-      </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>100</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-200</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-100</v>
-      </c>
-      <c r="N20" s="3">
-        <v>100</v>
       </c>
       <c r="O20" s="3">
         <v>100</v>
       </c>
       <c r="P20" s="3">
+        <v>100</v>
+      </c>
+      <c r="Q20" s="3">
         <v>300</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-200</v>
       </c>
-      <c r="R20" s="3">
-        <v>0</v>
-      </c>
       <c r="S20" s="3">
         <v>0</v>
       </c>
       <c r="T20" s="3">
+        <v>0</v>
+      </c>
+      <c r="U20" s="3">
         <v>400</v>
-      </c>
-      <c r="U20" s="3">
-        <v>-100</v>
       </c>
       <c r="V20" s="3">
         <v>-100</v>
@@ -1882,230 +1916,236 @@
         <v>-100</v>
       </c>
       <c r="X20" s="3">
-        <v>-200</v>
+        <v>-100</v>
       </c>
       <c r="Y20" s="3">
         <v>-200</v>
       </c>
       <c r="Z20" s="3">
+        <v>-200</v>
+      </c>
+      <c r="AA20" s="3">
         <v>-8300</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>-300</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>7700</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>300</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>-15200</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>-100</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>6300</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>8700</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>4000</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>82300</v>
+        <v>140400</v>
       </c>
       <c r="E21" s="3">
-        <v>146700</v>
+        <v>144200</v>
       </c>
       <c r="F21" s="3">
+        <v>139600</v>
+      </c>
+      <c r="G21" s="3">
+        <v>138300</v>
+      </c>
+      <c r="H21" s="3">
+        <v>139200</v>
+      </c>
+      <c r="I21" s="3">
+        <v>140400</v>
+      </c>
+      <c r="J21" s="3">
+        <v>138600</v>
+      </c>
+      <c r="K21" s="3">
         <v>139500</v>
       </c>
-      <c r="G21" s="3">
-        <v>134600</v>
-      </c>
-      <c r="H21" s="3">
-        <v>170000</v>
-      </c>
-      <c r="I21" s="3">
-        <v>140200</v>
-      </c>
-      <c r="J21" s="3">
-        <v>139500</v>
-      </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>135000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>158200</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>132200</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>33100</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>37000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>42900</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>69000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>38000</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>42600</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>40700</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>44800</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>59500</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>26800</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>50200</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>58100</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>24100</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>57900</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>57000</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>37500</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>60600</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>59600</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>70700</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>63200</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>65300</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>63500</v>
       </c>
     </row>
-    <row r="22" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>31600</v>
+      </c>
+      <c r="E22" s="3">
         <v>31000</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>30400</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>27200</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>25500</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>27200</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>25400</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>26800</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>26200</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>25700</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>25500</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>23100</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>12900</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>12300</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>12200</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>12300</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>12600</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>13300</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>12300</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>12400</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>14300</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>16100</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>16500</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>17600</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>16100</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>16700</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>16300</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>16500</v>
-      </c>
-      <c r="AE22" s="3">
-        <v>16400</v>
       </c>
       <c r="AF22" s="3">
         <v>16400</v>
@@ -2114,152 +2154,158 @@
         <v>16400</v>
       </c>
       <c r="AH22" s="3">
+        <v>16400</v>
+      </c>
+      <c r="AI22" s="3">
         <v>17600</v>
       </c>
-      <c r="AI22" s="3">
+      <c r="AJ22" s="3">
         <v>17100</v>
       </c>
     </row>
-    <row r="23" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>-49000</v>
+        <v>17100</v>
       </c>
       <c r="E23" s="3">
-        <v>15000</v>
+        <v>-49200</v>
       </c>
       <c r="F23" s="3">
-        <v>8400</v>
+        <v>14600</v>
       </c>
       <c r="G23" s="3">
-        <v>2300</v>
+        <v>8600</v>
       </c>
       <c r="H23" s="3">
-        <v>32400</v>
+        <v>2200</v>
       </c>
       <c r="I23" s="3">
-        <v>5800</v>
+        <v>32500</v>
       </c>
       <c r="J23" s="3">
+        <v>5500</v>
+      </c>
+      <c r="K23" s="3">
         <v>-1100</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-7900</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>13100</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-16600</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-100500</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-6700</v>
       </c>
-      <c r="P23" s="3">
-        <v>0</v>
-      </c>
       <c r="Q23" s="3">
+        <v>0</v>
+      </c>
+      <c r="R23" s="3">
         <v>25600</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-6600</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-4400</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-4600</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>400</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>15700</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-20100</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-1500</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>6300</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>-31600</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>4300</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>-1100</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>-18000</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>2800</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>-200</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>10900</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>400</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>4000</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>-1200</v>
       </c>
     </row>
-    <row r="24" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>0</v>
+      </c>
+      <c r="E24" s="3">
         <v>100</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>200</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>400</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>100</v>
       </c>
-      <c r="H24" s="3">
-        <v>0</v>
-      </c>
       <c r="I24" s="3">
         <v>0</v>
       </c>
       <c r="J24" s="3">
+        <v>0</v>
+      </c>
+      <c r="K24" s="3">
         <v>300</v>
       </c>
-      <c r="K24" s="3">
-        <v>0</v>
-      </c>
       <c r="L24" s="3">
+        <v>0</v>
+      </c>
+      <c r="M24" s="3">
         <v>-200</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>-100</v>
       </c>
-      <c r="N24" s="3">
-        <v>0</v>
-      </c>
       <c r="O24" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="P24" s="3">
         <v>-100</v>
@@ -2268,7 +2314,7 @@
         <v>-100</v>
       </c>
       <c r="R24" s="3">
-        <v>-200</v>
+        <v>-100</v>
       </c>
       <c r="S24" s="3">
         <v>-200</v>
@@ -2277,16 +2323,16 @@
         <v>-200</v>
       </c>
       <c r="U24" s="3">
-        <v>-100</v>
+        <v>-200</v>
       </c>
       <c r="V24" s="3">
         <v>-100</v>
       </c>
       <c r="W24" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="X24" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="Y24" s="3">
         <v>-100</v>
@@ -2295,7 +2341,7 @@
         <v>-100</v>
       </c>
       <c r="AA24" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="AB24" s="3">
         <v>0</v>
@@ -2316,13 +2362,16 @@
         <v>0</v>
       </c>
       <c r="AH24" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI24" s="3">
         <v>100</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2422,210 +2471,219 @@
       <c r="AI25" s="3">
         <v>0</v>
       </c>
+      <c r="AJ25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>-49100</v>
+        <v>17100</v>
       </c>
       <c r="E26" s="3">
-        <v>14900</v>
+        <v>-49300</v>
       </c>
       <c r="F26" s="3">
-        <v>8000</v>
+        <v>14400</v>
       </c>
       <c r="G26" s="3">
+        <v>8200</v>
+      </c>
+      <c r="H26" s="3">
         <v>2200</v>
       </c>
-      <c r="H26" s="3">
-        <v>32400</v>
-      </c>
       <c r="I26" s="3">
-        <v>5800</v>
+        <v>32500</v>
       </c>
       <c r="J26" s="3">
+        <v>5600</v>
+      </c>
+      <c r="K26" s="3">
         <v>-1400</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-7900</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>13300</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-16500</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-100500</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-6600</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>100</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>25700</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-6400</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-4200</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-4400</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>500</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>15800</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-20100</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-1500</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>6400</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>-31400</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>4300</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>-1100</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>-18000</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>2800</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>-200</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>10900</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>400</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>3900</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>-1300</v>
       </c>
     </row>
-    <row r="27" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>16700</v>
+      </c>
+      <c r="E27" s="3">
         <v>-48600</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>14200</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>8000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>2100</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>32100</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>5400</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-1100</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-7800</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>13100</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-16800</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-98200</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-7000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-200</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>24600</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-6800</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-4600</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-4800</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-100</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>15300</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-19700</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-1800</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>5700</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>-31200</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>3900</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>-1400</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>-17900</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>2300</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>-600</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>10200</v>
       </c>
-      <c r="AG27" s="3">
-        <v>0</v>
-      </c>
       <c r="AH27" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI27" s="3">
         <v>3400</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>-1700</v>
       </c>
     </row>
-    <row r="28" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2725,8 +2783,11 @@
       <c r="AI28" s="3">
         <v>0</v>
       </c>
+      <c r="AJ28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2808,8 +2869,8 @@
       <c r="AC29" s="3">
         <v>0</v>
       </c>
-      <c r="AD29" s="3" t="s">
-        <v>8</v>
+      <c r="AD29" s="3">
+        <v>0</v>
       </c>
       <c r="AE29" s="3" t="s">
         <v>8</v>
@@ -2820,14 +2881,17 @@
       <c r="AG29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AH29" s="3">
-        <v>0</v>
-      </c>
-      <c r="AI29" s="3" t="s">
+      <c r="AH29" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AI29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ29" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="30" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2927,8 +2991,11 @@
       <c r="AI30" s="3">
         <v>0</v>
       </c>
+      <c r="AJ30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3028,64 +3095,67 @@
       <c r="AI31" s="3">
         <v>0</v>
       </c>
+      <c r="AJ31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-4300</v>
+        <v>-600</v>
       </c>
       <c r="E32" s="3">
-        <v>-6000</v>
+        <v>-200</v>
       </c>
       <c r="F32" s="3">
-        <v>-300</v>
+        <v>-400</v>
       </c>
       <c r="G32" s="3">
-        <v>-1000</v>
+        <v>200</v>
       </c>
       <c r="H32" s="3">
-        <v>-300</v>
+        <v>0</v>
       </c>
       <c r="I32" s="3">
+        <v>100</v>
+      </c>
+      <c r="J32" s="3">
+        <v>-200</v>
+      </c>
+      <c r="K32" s="3">
         <v>-400</v>
       </c>
-      <c r="J32" s="3">
-        <v>-400</v>
-      </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-100</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>200</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>100</v>
-      </c>
-      <c r="N32" s="3">
-        <v>-100</v>
       </c>
       <c r="O32" s="3">
         <v>-100</v>
       </c>
       <c r="P32" s="3">
+        <v>-100</v>
+      </c>
+      <c r="Q32" s="3">
         <v>-300</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>200</v>
       </c>
-      <c r="R32" s="3">
-        <v>0</v>
-      </c>
       <c r="S32" s="3">
         <v>0</v>
       </c>
       <c r="T32" s="3">
+        <v>0</v>
+      </c>
+      <c r="U32" s="3">
         <v>-400</v>
-      </c>
-      <c r="U32" s="3">
-        <v>100</v>
       </c>
       <c r="V32" s="3">
         <v>100</v>
@@ -3094,144 +3164,150 @@
         <v>100</v>
       </c>
       <c r="X32" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="Y32" s="3">
         <v>200</v>
       </c>
       <c r="Z32" s="3">
+        <v>200</v>
+      </c>
+      <c r="AA32" s="3">
         <v>8300</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>300</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>-7700</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>-300</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>15200</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>100</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>-6300</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>-8700</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>-4000</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>16700</v>
+      </c>
+      <c r="E33" s="3">
         <v>-48600</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>14200</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>8000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>2100</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>32100</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>5400</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-1100</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-7800</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>13100</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-16800</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-98200</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-7000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-200</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>24600</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-6800</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-4600</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-4800</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-100</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>15300</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-19700</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-1800</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>5700</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-31200</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>3900</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>-1400</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>-17900</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>2300</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>-600</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>10200</v>
       </c>
-      <c r="AG33" s="3">
-        <v>0</v>
-      </c>
       <c r="AH33" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI33" s="3">
         <v>3400</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>-1700</v>
       </c>
     </row>
-    <row r="34" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3331,215 +3407,224 @@
       <c r="AI34" s="3">
         <v>0</v>
       </c>
+      <c r="AJ34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>16700</v>
+      </c>
+      <c r="E35" s="3">
         <v>-48600</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>14200</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>8000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>2100</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>32100</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>5400</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-1100</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-7800</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>13100</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-16800</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-98200</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-7000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-200</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>24600</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-6800</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-4600</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-4800</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-100</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>15300</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-19700</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-1800</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>5700</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-31200</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>3900</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>-1400</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>-17900</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>2300</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>-600</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>10200</v>
       </c>
-      <c r="AG35" s="3">
-        <v>0</v>
-      </c>
       <c r="AH35" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI35" s="3">
         <v>3400</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>-1700</v>
       </c>
     </row>
-    <row r="37" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:36" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E38" s="2">
         <v>45473</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45382</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45291</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45199</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45107</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45016</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44926</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44834</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44742</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44651</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44561</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44469</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44377</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44286</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44196</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44104</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44012</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43921</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43830</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43738</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43646</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43555</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43465</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43373</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43281</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43190</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43100</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43008</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>42916</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>42825</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>42735</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3575,8 +3660,9 @@
       <c r="AG39" s="3"/>
       <c r="AH39" s="3"/>
       <c r="AI39" s="3"/>
+      <c r="AJ39" s="3"/>
     </row>
-    <row r="40" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3612,132 +3698,136 @@
       <c r="AG40" s="3"/>
       <c r="AH40" s="3"/>
       <c r="AI40" s="3"/>
+      <c r="AJ40" s="3"/>
     </row>
-    <row r="41" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>117500</v>
+      </c>
+      <c r="E41" s="3">
         <v>153800</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>83600</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>36400</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>52300</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>129300</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>43700</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>115800</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>88400</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>90800</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>74300</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>93200</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>99500</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>89900</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>228800</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>43600</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>129300</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>230000</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>343900</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>31300</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>40400</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>35800</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>28400</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>35400</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>30700</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>32400</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>28800</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>24100</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>32500</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>27600</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>22600</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>19900</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>28800</v>
       </c>
     </row>
-    <row r="42" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>0</v>
+        <v>10200</v>
       </c>
       <c r="E42" s="3">
-        <v>0</v>
+        <v>21800</v>
       </c>
       <c r="F42" s="3">
-        <v>0</v>
+        <v>25300</v>
       </c>
       <c r="G42" s="3">
-        <v>0</v>
+        <v>23100</v>
       </c>
       <c r="H42" s="3">
-        <v>0</v>
+        <v>37200</v>
       </c>
       <c r="I42" s="3">
-        <v>0</v>
+        <v>37000</v>
       </c>
       <c r="J42" s="3">
-        <v>0</v>
+        <v>26700</v>
       </c>
       <c r="K42" s="3">
         <v>0</v>
@@ -3814,132 +3904,138 @@
       <c r="AI42" s="3">
         <v>0</v>
       </c>
+      <c r="AJ42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>113800</v>
+      </c>
+      <c r="E43" s="3">
         <v>120000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>118100</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>113300</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>113100</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>109600</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>103500</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>101300</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>86600</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>76900</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>69100</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>68400</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>45900</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>46700</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>49100</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>57200</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>57100</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>61600</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>49900</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>55300</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>50000</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>52000</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>55400</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>58100</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>57100</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>53100</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>57200</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>58300</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>53300</v>
-      </c>
-      <c r="AF43" s="3">
-        <v>52300</v>
       </c>
       <c r="AG43" s="3">
         <v>52300</v>
       </c>
       <c r="AH43" s="3">
+        <v>52300</v>
+      </c>
+      <c r="AI43" s="3">
         <v>53100</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>50400</v>
       </c>
     </row>
-    <row r="44" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D44" s="3">
-        <v>0</v>
-      </c>
-      <c r="E44" s="3">
-        <v>0</v>
-      </c>
-      <c r="F44" s="3">
-        <v>0</v>
-      </c>
-      <c r="G44" s="3">
-        <v>0</v>
-      </c>
-      <c r="H44" s="3">
-        <v>0</v>
-      </c>
-      <c r="I44" s="3">
-        <v>0</v>
-      </c>
-      <c r="J44" s="3">
-        <v>0</v>
+      <c r="D44" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E44" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F44" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G44" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H44" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I44" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J44" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K44" s="3">
         <v>0</v>
@@ -4016,132 +4112,138 @@
       <c r="AI44" s="3">
         <v>0</v>
       </c>
+      <c r="AJ44" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="45" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>114200</v>
+        <v>520700</v>
       </c>
       <c r="E45" s="3">
-        <v>131800</v>
+        <v>285900</v>
       </c>
       <c r="F45" s="3">
-        <v>117800</v>
+        <v>371500</v>
       </c>
       <c r="G45" s="3">
-        <v>134600</v>
+        <v>94800</v>
       </c>
       <c r="H45" s="3">
-        <v>130500</v>
+        <v>111800</v>
       </c>
       <c r="I45" s="3">
-        <v>117400</v>
+        <v>93500</v>
       </c>
       <c r="J45" s="3">
+        <v>113500</v>
+      </c>
+      <c r="K45" s="3">
         <v>127000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>142800</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>106000</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>96300</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>84800</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>39200</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>39500</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>42900</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>13000</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>39300</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>38200</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>36300</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>7500</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>10100</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>10300</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>14100</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>12800</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>17400</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>14200</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>20300</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>16400</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>12800</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>10200</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>12800</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>9700</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AJ45" s="3">
         <v>10800</v>
       </c>
     </row>
-    <row r="46" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>0</v>
+        <v>767800</v>
       </c>
       <c r="E46" s="3">
-        <v>0</v>
+        <v>586500</v>
       </c>
       <c r="F46" s="3">
-        <v>0</v>
+        <v>603800</v>
       </c>
       <c r="G46" s="3">
-        <v>0</v>
+        <v>272600</v>
       </c>
       <c r="H46" s="3">
-        <v>0</v>
+        <v>320300</v>
       </c>
       <c r="I46" s="3">
-        <v>0</v>
+        <v>375000</v>
       </c>
       <c r="J46" s="3">
-        <v>0</v>
+        <v>296300</v>
       </c>
       <c r="K46" s="3">
         <v>0</v>
@@ -4218,88 +4320,91 @@
       <c r="AI46" s="3">
         <v>0</v>
       </c>
+      <c r="AJ46" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="47" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>130000</v>
+        <v>18800</v>
       </c>
       <c r="E47" s="3">
-        <v>274600</v>
+        <v>10000</v>
       </c>
       <c r="F47" s="3">
+        <v>9600</v>
+      </c>
+      <c r="G47" s="3">
         <v>9100</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>10200</v>
-      </c>
-      <c r="H47" s="3">
-        <v>10300</v>
       </c>
       <c r="I47" s="3">
         <v>10300</v>
       </c>
       <c r="J47" s="3">
+        <v>10300</v>
+      </c>
+      <c r="K47" s="3">
         <v>10400</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>10600</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>10400</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>136800</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>136900</v>
-      </c>
-      <c r="O47" s="3">
-        <v>138000</v>
       </c>
       <c r="P47" s="3">
         <v>138000</v>
       </c>
       <c r="Q47" s="3">
+        <v>138000</v>
+      </c>
+      <c r="R47" s="3">
         <v>13000</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>12800</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>13100</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>13200</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>12100</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>12600</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>12900</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>12700</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>13300</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>13500</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>13800</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>13900</v>
-      </c>
-      <c r="AC47" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AD47" s="3" t="s">
         <v>8</v>
@@ -4319,136 +4424,142 @@
       <c r="AI47" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AJ47" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="48" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>6091000</v>
+      </c>
+      <c r="E48" s="3">
         <v>6098600</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>6305700</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>6358300</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>6397300</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>6426100</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>6508700</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>6571400</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>6621600</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>6617800</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>6676800</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>6707500</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>2308000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>2343700</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>2358900</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>2415900</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>2347400</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>2380500</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>2404000</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>2447400</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>2514100</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>2716800</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>2911300</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>2941200</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>3051700</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>3076800</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>3194200</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>3293300</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>3320300</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>3331800</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>3399700</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>3435400</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>3458300</v>
       </c>
     </row>
-    <row r="49" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>389200</v>
+        <v>0</v>
       </c>
       <c r="E49" s="3">
-        <v>405500</v>
+        <v>0</v>
       </c>
       <c r="F49" s="3">
-        <v>433800</v>
-      </c>
-      <c r="G49" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="G49" s="3">
+        <v>0</v>
+      </c>
+      <c r="H49" s="3">
+        <v>0</v>
+      </c>
+      <c r="I49" s="3">
+        <v>0</v>
+      </c>
+      <c r="J49" s="3">
+        <v>0</v>
+      </c>
+      <c r="K49" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="H49" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="I49" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="J49" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="K49" s="3">
-        <v>0</v>
-      </c>
       <c r="L49" s="3">
         <v>0</v>
       </c>
@@ -4498,31 +4609,34 @@
         <v>0</v>
       </c>
       <c r="AB49" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC49" s="3">
         <v>32300</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>39000</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>44000</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>47900</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>53000</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>59300</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>65500</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>70000</v>
       </c>
     </row>
-    <row r="50" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4622,8 +4736,11 @@
       <c r="AI50" s="3">
         <v>0</v>
       </c>
+      <c r="AJ50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4723,8 +4840,11 @@
       <c r="AI51" s="3">
         <v>0</v>
       </c>
+      <c r="AJ51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -4737,95 +4857,98 @@
       <c r="F52" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="G52" s="3">
-        <v>345000</v>
-      </c>
-      <c r="H52" s="3">
-        <v>359400</v>
-      </c>
-      <c r="I52" s="3">
-        <v>413200</v>
-      </c>
-      <c r="J52" s="3">
+      <c r="G52" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H52" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I52" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J52" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K52" s="3">
         <v>416000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>450000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>483000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>520300</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>548600</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>78400</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>61400</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>62600</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>66100</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>71900</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>88300</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>91300</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>94600</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>86300</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>108700</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>180800</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>111100</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>115100</v>
-      </c>
-      <c r="AB52" s="3">
-        <v>79400</v>
       </c>
       <c r="AC52" s="3">
         <v>79400</v>
       </c>
       <c r="AD52" s="3">
+        <v>79400</v>
+      </c>
+      <c r="AE52" s="3">
         <v>76400</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>76600</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>75400</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>76700</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>72800</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>72700</v>
       </c>
     </row>
-    <row r="53" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4925,109 +5048,115 @@
       <c r="AI53" s="3">
         <v>0</v>
       </c>
+      <c r="AJ53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>7129700</v>
+      </c>
+      <c r="E54" s="3">
         <v>6958900</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>7204500</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>6944100</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>7052500</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>7165100</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>7196900</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>7342000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>7399900</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>7384900</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>7573700</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>7639600</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>2708900</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>2719200</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>2755300</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>2608500</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>2658100</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>2811800</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>2937400</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>2648900</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>2713900</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>2936300</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>3203200</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>3172000</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>3285900</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>3302200</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>3418900</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>3512500</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>3543400</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>3550300</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>3623500</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>3656400</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>3690900</v>
       </c>
     </row>
-    <row r="55" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5063,8 +5192,9 @@
       <c r="AG55" s="3"/>
       <c r="AH55" s="3"/>
       <c r="AI55" s="3"/>
+      <c r="AJ55" s="3"/>
     </row>
-    <row r="56" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5100,132 +5230,136 @@
       <c r="AG56" s="3"/>
       <c r="AH56" s="3"/>
       <c r="AI56" s="3"/>
+      <c r="AJ56" s="3"/>
     </row>
-    <row r="57" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>189700</v>
+        <v>184000</v>
       </c>
       <c r="E57" s="3">
-        <v>171600</v>
+        <v>181800</v>
       </c>
       <c r="F57" s="3">
-        <v>198100</v>
+        <v>162400</v>
       </c>
       <c r="G57" s="3">
-        <v>198500</v>
+        <v>188000</v>
       </c>
       <c r="H57" s="3">
-        <v>178200</v>
+        <v>185700</v>
       </c>
       <c r="I57" s="3">
-        <v>160100</v>
+        <v>164800</v>
       </c>
       <c r="J57" s="3">
+        <v>148100</v>
+      </c>
+      <c r="K57" s="3">
         <v>207800</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>152000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>133800</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>124200</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>185000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>85700</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>74400</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>72100</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>77500</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>88600</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>85700</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>109400</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>69800</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>77500</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>66600</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>61900</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>85900</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>98500</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>101200</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>102900</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>78500</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>101600</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>88500</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>88800</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>80700</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>93400</v>
       </c>
     </row>
-    <row r="58" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>0</v>
+        <v>1300</v>
       </c>
       <c r="E58" s="3">
-        <v>0</v>
+        <v>122600</v>
       </c>
       <c r="F58" s="3">
-        <v>0</v>
+        <v>273500</v>
       </c>
       <c r="G58" s="3">
-        <v>0</v>
+        <v>5100</v>
       </c>
       <c r="H58" s="3">
-        <v>0</v>
+        <v>1300</v>
       </c>
       <c r="I58" s="3">
-        <v>0</v>
+        <v>124200</v>
       </c>
       <c r="J58" s="3">
-        <v>0</v>
+        <v>125100</v>
       </c>
       <c r="K58" s="3">
         <v>0</v>
@@ -5302,79 +5436,82 @@
       <c r="AI58" s="3">
         <v>0</v>
       </c>
+      <c r="AJ58" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="59" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>80300</v>
+        <v>3800</v>
       </c>
       <c r="E59" s="3">
-        <v>78400</v>
-      </c>
-      <c r="F59" s="3">
-        <v>78200</v>
+        <v>3900</v>
+      </c>
+      <c r="F59" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="G59" s="3">
-        <v>82000</v>
+        <v>19300</v>
       </c>
       <c r="H59" s="3">
-        <v>79600</v>
+        <v>168000</v>
       </c>
       <c r="I59" s="3">
-        <v>68900</v>
+        <v>11400</v>
       </c>
       <c r="J59" s="3">
+        <v>14600</v>
+      </c>
+      <c r="K59" s="3">
         <v>79300</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>78100</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>76000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>79200</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>70200</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>26200</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>26300</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>26400</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>26500</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>26600</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>26800</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>26900</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>27000</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>27100</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>27200</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>27300</v>
-      </c>
-      <c r="Z59" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AA59" s="3" t="s">
         <v>8</v>
@@ -5385,8 +5522,8 @@
       <c r="AC59" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AD59" s="3">
-        <v>0</v>
+      <c r="AD59" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AE59" s="3">
         <v>0</v>
@@ -5403,31 +5540,34 @@
       <c r="AI59" s="3">
         <v>0</v>
       </c>
+      <c r="AJ59" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="60" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>0</v>
+        <v>189100</v>
       </c>
       <c r="E60" s="3">
-        <v>0</v>
+        <v>308300</v>
       </c>
       <c r="F60" s="3">
-        <v>0</v>
+        <v>435900</v>
       </c>
       <c r="G60" s="3">
-        <v>0</v>
+        <v>212400</v>
       </c>
       <c r="H60" s="3">
-        <v>0</v>
+        <v>354900</v>
       </c>
       <c r="I60" s="3">
-        <v>0</v>
+        <v>300400</v>
       </c>
       <c r="J60" s="3">
-        <v>0</v>
+        <v>287800</v>
       </c>
       <c r="K60" s="3">
         <v>0</v>
@@ -5504,132 +5644,138 @@
       <c r="AI60" s="3">
         <v>0</v>
       </c>
+      <c r="AJ60" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="61" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>3015600</v>
+        <v>3311100</v>
       </c>
       <c r="E61" s="3">
-        <v>3167500</v>
+        <v>2969000</v>
       </c>
       <c r="F61" s="3">
-        <v>2829200</v>
+        <v>2971700</v>
       </c>
       <c r="G61" s="3">
-        <v>2868800</v>
+        <v>2903100</v>
       </c>
       <c r="H61" s="3">
-        <v>2938000</v>
+        <v>2949700</v>
       </c>
       <c r="I61" s="3">
-        <v>2972600</v>
+        <v>2895300</v>
       </c>
       <c r="J61" s="3">
+        <v>2927500</v>
+      </c>
+      <c r="K61" s="3">
         <v>3010300</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>3012900</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>3001200</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>3179100</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>3150800</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>1289000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>1289400</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>1315200</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>1170800</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>1196100</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>1346300</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>1446500</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>1146600</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>1198600</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>1376600</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>1602600</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>1543300</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>1578300</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>1565400</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>1650500</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>1699200</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>1681700</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>1675100</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>1726900</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>1731100</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>1732300</v>
       </c>
     </row>
-    <row r="62" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="D62" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E62" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F62" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="G62" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="H62" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="I62" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="J62" s="3" t="s">
-        <v>8</v>
+      <c r="D62" s="3">
+        <v>151900</v>
+      </c>
+      <c r="E62" s="3">
+        <v>154400</v>
+      </c>
+      <c r="F62" s="3">
+        <v>164400</v>
+      </c>
+      <c r="G62" s="3">
+        <v>149300</v>
+      </c>
+      <c r="H62" s="3">
+        <v>12000</v>
+      </c>
+      <c r="I62" s="3">
+        <v>176500</v>
+      </c>
+      <c r="J62" s="3">
+        <v>182900</v>
       </c>
       <c r="K62" s="3" t="s">
         <v>8</v>
@@ -5640,8 +5786,8 @@
       <c r="M62" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="N62" s="3">
-        <v>0</v>
+      <c r="N62" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="O62" s="3">
         <v>0</v>
@@ -5670,14 +5816,14 @@
       <c r="W62" s="3">
         <v>0</v>
       </c>
-      <c r="X62" s="3" t="s">
+      <c r="X62" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y62" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>2400</v>
-      </c>
-      <c r="Z62" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AA62" s="3" t="s">
         <v>8</v>
@@ -5688,8 +5834,8 @@
       <c r="AC62" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AD62" s="3">
-        <v>0</v>
+      <c r="AD62" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AE62" s="3">
         <v>0</v>
@@ -5706,8 +5852,11 @@
       <c r="AI62" s="3">
         <v>0</v>
       </c>
+      <c r="AJ62" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="63" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5807,8 +5956,11 @@
       <c r="AI63" s="3">
         <v>0</v>
       </c>
+      <c r="AJ63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5908,8 +6060,11 @@
       <c r="AI64" s="3">
         <v>0</v>
       </c>
+      <c r="AJ64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6009,109 +6164,115 @@
       <c r="AI65" s="3">
         <v>0</v>
       </c>
+      <c r="AJ65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>3537300</v>
+        <v>3681500</v>
       </c>
       <c r="E66" s="3">
-        <v>3673700</v>
+        <v>3459300</v>
       </c>
       <c r="F66" s="3">
-        <v>3375900</v>
+        <v>3598100</v>
       </c>
       <c r="G66" s="3">
-        <v>3417200</v>
+        <v>3300200</v>
       </c>
       <c r="H66" s="3">
-        <v>3472300</v>
+        <v>3347800</v>
       </c>
       <c r="I66" s="3">
-        <v>3490900</v>
+        <v>3405900</v>
       </c>
       <c r="J66" s="3">
+        <v>3428400</v>
+      </c>
+      <c r="K66" s="3">
         <v>3575500</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>3527100</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>3493700</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>3675100</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>3717500</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>1510000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>1505700</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>1523500</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>1377900</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>1416000</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>1563600</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>1684600</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>1359800</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>1411700</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>1583700</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>1816400</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>1759300</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>1807700</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>1802800</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>1893900</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>1947100</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>1958500</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>1940600</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>2004000</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>2012800</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>2046500</v>
       </c>
     </row>
-    <row r="67" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6147,8 +6308,9 @@
       <c r="AG67" s="3"/>
       <c r="AH67" s="3"/>
       <c r="AI67" s="3"/>
+      <c r="AJ67" s="3"/>
     </row>
-    <row r="68" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6248,8 +6410,11 @@
       <c r="AI68" s="3">
         <v>0</v>
       </c>
+      <c r="AJ68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6349,8 +6514,11 @@
       <c r="AI69" s="3">
         <v>0</v>
       </c>
+      <c r="AJ69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6450,8 +6618,11 @@
       <c r="AI70" s="3">
         <v>0</v>
       </c>
+      <c r="AJ70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6551,109 +6722,115 @@
       <c r="AI71" s="3">
         <v>0</v>
       </c>
+      <c r="AJ71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-1557800</v>
+      </c>
+      <c r="E72" s="3">
         <v>-1517400</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-1413800</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-1373100</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-1326200</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-1275600</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-1255000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-1207800</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-1105800</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-1052000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-1021300</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-962900</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-849500</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-827300</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-812700</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-824300</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-810800</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-801800</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-797000</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-770000</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-758600</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-712200</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>-683700</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>-662700</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>-604900</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>-582200</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>-554300</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>-509800</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>-485600</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>-459700</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>-444600</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>-419300</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>-397400</v>
       </c>
     </row>
-    <row r="73" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6753,8 +6930,11 @@
       <c r="AI73" s="3">
         <v>0</v>
       </c>
+      <c r="AJ73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6854,8 +7034,11 @@
       <c r="AI74" s="3">
         <v>0</v>
       </c>
+      <c r="AJ74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6955,109 +7138,115 @@
       <c r="AI75" s="3">
         <v>0</v>
       </c>
+      <c r="AJ75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>3349400</v>
+      </c>
+      <c r="E76" s="3">
         <v>3421600</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>3530800</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>3568100</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>3635300</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>3692800</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>3706000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>3766500</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>3872800</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>3891100</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>3898600</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>3922000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>1198800</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>1213500</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>1231900</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>1230700</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>1242100</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>1248200</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>1252800</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>1289000</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>1302200</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>1352700</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>1386800</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>1412700</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>1478200</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>1499400</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>1525000</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>1565400</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>1584900</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>1609700</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>1619500</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>1643600</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>1644400</v>
       </c>
     </row>
-    <row r="77" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7157,215 +7346,224 @@
       <c r="AI77" s="3">
         <v>0</v>
       </c>
+      <c r="AJ77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:36" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E80" s="2">
         <v>45473</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45382</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45291</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45199</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45107</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45016</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44926</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44834</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44742</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44651</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44561</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44469</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44377</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44286</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44196</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44104</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44012</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43921</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43830</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43738</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43646</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43555</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43465</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43373</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43281</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43190</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43100</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43008</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>42916</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>42825</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>42735</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>16700</v>
+      </c>
+      <c r="E81" s="3">
         <v>-48600</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>14200</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>8000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>2100</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>32100</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>5400</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-1100</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-7800</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>13100</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-16800</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-98200</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-7000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-200</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>24600</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-6800</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-4600</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-4800</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-100</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>15300</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-19700</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-1800</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>5700</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-31200</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>3900</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>-1400</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>-17900</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>2300</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>-600</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>10200</v>
       </c>
-      <c r="AG81" s="3">
-        <v>0</v>
-      </c>
       <c r="AH81" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI81" s="3">
         <v>3400</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>-1700</v>
       </c>
     </row>
-    <row r="82" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7401,109 +7599,113 @@
       <c r="AG82" s="3"/>
       <c r="AH82" s="3"/>
       <c r="AI82" s="3"/>
+      <c r="AJ82" s="3"/>
     </row>
-    <row r="83" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>100300</v>
+        <v>75900</v>
       </c>
       <c r="E83" s="3">
-        <v>101300</v>
+        <v>77700</v>
       </c>
       <c r="F83" s="3">
-        <v>103800</v>
+        <v>79600</v>
       </c>
       <c r="G83" s="3">
-        <v>106800</v>
+        <v>78000</v>
       </c>
       <c r="H83" s="3">
-        <v>110400</v>
+        <v>79200</v>
       </c>
       <c r="I83" s="3">
-        <v>109000</v>
+        <v>78300</v>
       </c>
       <c r="J83" s="3">
+        <v>79800</v>
+      </c>
+      <c r="K83" s="3">
         <v>113700</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>116600</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>119300</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>123300</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>110600</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>30800</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>30500</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>31200</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>32300</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>34400</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>32000</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>32100</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>31400</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>32600</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>35600</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>35300</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>38000</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>37500</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>41300</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>39200</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>41400</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>43500</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>43400</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>46400</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>43700</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>47700</v>
       </c>
     </row>
-    <row r="84" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7603,8 +7805,11 @@
       <c r="AI84" s="3">
         <v>0</v>
       </c>
+      <c r="AJ84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7704,8 +7909,11 @@
       <c r="AI85" s="3">
         <v>0</v>
       </c>
+      <c r="AJ85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7805,8 +8013,11 @@
       <c r="AI86" s="3">
         <v>0</v>
       </c>
+      <c r="AJ86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7906,8 +8117,11 @@
       <c r="AI87" s="3">
         <v>0</v>
       </c>
+      <c r="AJ87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8007,109 +8221,115 @@
       <c r="AI88" s="3">
         <v>0</v>
       </c>
+      <c r="AJ88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>112400</v>
+      </c>
+      <c r="E89" s="3">
         <v>142100</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>53600</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>103500</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>110800</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>116800</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>63600</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>116900</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>108100</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>104700</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>49600</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-3500</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>36400</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>36100</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>31300</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>9800</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>35900</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>28000</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>21900</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>31800</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>36500</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>37300</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>32300</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>35400</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>37000</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>45800</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>36300</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>30800</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>42700</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>44900</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>36200</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>34200</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>39800</v>
       </c>
     </row>
-    <row r="90" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -8145,109 +8365,113 @@
       <c r="AG90" s="3"/>
       <c r="AH90" s="3"/>
       <c r="AI90" s="3"/>
+      <c r="AJ90" s="3"/>
     </row>
-    <row r="91" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-34800</v>
+      </c>
+      <c r="E91" s="3">
         <v>-38900</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-28200</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-43900</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-30900</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-28600</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-39100</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-52000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-47800</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-35000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-23800</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-20400</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-15700</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-13300</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-7900</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-7600</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-8200</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-9200</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-13200</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-15700</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-12400</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-13700</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-11500</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-12000</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-12700</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-16500</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-18100</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-10800</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-24800</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-11200</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-47700</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-26000</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-24100</v>
       </c>
     </row>
-    <row r="92" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8347,8 +8571,11 @@
       <c r="AI92" s="3">
         <v>0</v>
       </c>
+      <c r="AJ92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8448,109 +8675,115 @@
       <c r="AI93" s="3">
         <v>0</v>
       </c>
+      <c r="AJ93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-314900</v>
+      </c>
+      <c r="E94" s="3">
         <v>134700</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-289300</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-26200</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-63500</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>49500</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-41500</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-31500</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-82300</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>130800</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-62200</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>18000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-9600</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-133300</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>33900</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-64900</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>4700</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-13500</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-7100</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>52800</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>166900</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>226600</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-29700</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>44700</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-14500</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>71800</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>46400</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-23200</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-16500</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>38100</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>1400</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-15600</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-22200</v>
       </c>
     </row>
-    <row r="95" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8586,67 +8819,68 @@
       <c r="AG95" s="3"/>
       <c r="AH95" s="3"/>
       <c r="AI95" s="3"/>
+      <c r="AJ95" s="3"/>
     </row>
-    <row r="96" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>-54900</v>
+        <v>54900</v>
       </c>
       <c r="E96" s="3">
-        <v>-54900</v>
+        <v>54900</v>
       </c>
       <c r="F96" s="3">
-        <v>-52700</v>
+        <v>54900</v>
       </c>
       <c r="G96" s="3">
-        <v>-52700</v>
+        <v>52700</v>
       </c>
       <c r="H96" s="3">
-        <v>-52600</v>
+        <v>52700</v>
       </c>
       <c r="I96" s="3">
-        <v>-52600</v>
+        <v>52600</v>
       </c>
       <c r="J96" s="3">
+        <v>52600</v>
+      </c>
+      <c r="K96" s="3">
         <v>-48200</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>-46000</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>-43800</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>-41600</v>
-      </c>
-      <c r="N96" s="3">
-        <v>-15200</v>
       </c>
       <c r="O96" s="3">
         <v>-15200</v>
       </c>
       <c r="P96" s="3">
+        <v>-15200</v>
+      </c>
+      <c r="Q96" s="3">
         <v>-14400</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="R96" s="3">
         <v>-13000</v>
       </c>
-      <c r="R96" s="3">
+      <c r="S96" s="3">
         <v>-6700</v>
       </c>
-      <c r="S96" s="3">
+      <c r="T96" s="3">
         <v>-4400</v>
       </c>
-      <c r="T96" s="3">
+      <c r="U96" s="3">
         <v>-26700</v>
       </c>
-      <c r="U96" s="3">
+      <c r="V96" s="3">
         <v>-300</v>
-      </c>
-      <c r="V96" s="3">
-        <v>-26700</v>
       </c>
       <c r="W96" s="3">
         <v>-26700</v>
@@ -8655,10 +8889,10 @@
         <v>-26700</v>
       </c>
       <c r="Y96" s="3">
+        <v>-26700</v>
+      </c>
+      <c r="Z96" s="3">
         <v>-53300</v>
-      </c>
-      <c r="Z96" s="3">
-        <v>-26600</v>
       </c>
       <c r="AA96" s="3">
         <v>-26600</v>
@@ -8667,10 +8901,10 @@
         <v>-26600</v>
       </c>
       <c r="AC96" s="3">
+        <v>-26600</v>
+      </c>
+      <c r="AD96" s="3">
         <v>-26500</v>
-      </c>
-      <c r="AD96" s="3">
-        <v>-25300</v>
       </c>
       <c r="AE96" s="3">
         <v>-25300</v>
@@ -8682,13 +8916,16 @@
         <v>-25300</v>
       </c>
       <c r="AH96" s="3">
-        <v>-24000</v>
+        <v>-25300</v>
       </c>
       <c r="AI96" s="3">
         <v>-24000</v>
       </c>
+      <c r="AJ96" s="3">
+        <v>-24000</v>
+      </c>
     </row>
-    <row r="97" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8788,8 +9025,11 @@
       <c r="AI97" s="3">
         <v>0</v>
       </c>
+      <c r="AJ97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8889,8 +9129,11 @@
       <c r="AI98" s="3">
         <v>0</v>
       </c>
+      <c r="AJ98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8990,132 +9233,138 @@
       <c r="AI99" s="3">
         <v>0</v>
       </c>
+      <c r="AJ99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>166800</v>
+      </c>
+      <c r="E100" s="3">
         <v>-206800</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>283300</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-94100</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-123900</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-84100</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-91400</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-59900</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-28400</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-218600</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-5600</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-18000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-17100</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-41200</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>120800</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-35600</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-155100</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-128300</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>298000</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-81800</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-212900</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-256400</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>3800</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-75600</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-24800</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-112800</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-76300</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-16800</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-19700</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-78700</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-34200</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>-27600</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>-26600</v>
       </c>
     </row>
-    <row r="101" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="D101" s="3">
-        <v>0</v>
-      </c>
-      <c r="E101" s="3">
-        <v>0</v>
-      </c>
-      <c r="F101" s="3">
-        <v>0</v>
-      </c>
-      <c r="G101" s="3">
-        <v>0</v>
-      </c>
-      <c r="H101" s="3">
-        <v>0</v>
-      </c>
-      <c r="I101" s="3">
-        <v>0</v>
-      </c>
-      <c r="J101" s="3">
-        <v>0</v>
+      <c r="D101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J101" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K101" s="3">
         <v>0</v>
@@ -9192,105 +9441,111 @@
       <c r="AI101" s="3">
         <v>0</v>
       </c>
+      <c r="AJ101" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="102" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-35700</v>
+      </c>
+      <c r="E102" s="3">
         <v>70000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>47500</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-16900</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-76600</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>82300</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-69300</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>25500</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-2600</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>17000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-18200</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-3400</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>9700</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-138500</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>185900</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-90700</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-114500</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-113800</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>312800</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>2800</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-9500</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>7600</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>6400</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>4500</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-2300</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>4800</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>6400</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>-8400</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>4800</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>4400</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>3300</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>-8900</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>-9100</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/KRG_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/KRG_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="178" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="183" uniqueCount="92">
   <si>
     <t>KRG</t>
   </si>
@@ -656,467 +656,479 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AJ102"/>
+  <dimension ref="A5:AK102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="36" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="37" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:37" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E7" s="2">
         <v>45565</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45473</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45382</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45291</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45199</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45107</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45016</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44926</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44834</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44742</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44651</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44561</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44469</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44377</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44286</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44196</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44104</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44012</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43921</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43830</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43738</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43646</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43555</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43465</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43373</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43281</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43190</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43100</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43008</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>42916</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>42825</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>42735</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>214700</v>
+      </c>
+      <c r="E8" s="3">
         <v>207300</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>212400</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>207400</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>200300</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>207200</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>208800</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>206800</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>204700</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>200300</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>202600</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>194400</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>163000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>71500</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>69500</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>69400</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>68400</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>65100</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>63300</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>69900</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>75200</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>74900</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>81500</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>83500</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>86900</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>85700</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>91700</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>89800</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>88900</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>87100</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>92600</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>90100</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>88900</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>89100</v>
       </c>
     </row>
-    <row r="9" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>54800</v>
+      </c>
+      <c r="E9" s="3">
         <v>53000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>55100</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>54600</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>47900</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>54100</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>53900</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>54500</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>53800</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>51200</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>54000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>52800</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>47500</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>19100</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>18800</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>19700</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>19900</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>19700</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>17600</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>19700</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>20600</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>20700</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>21400</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>21600</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>23200</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>23300</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>23000</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>23200</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>23500</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>22700</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>23400</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>23300</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>23000</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AK9" s="3">
         <v>22600</v>
       </c>
     </row>
-    <row r="10" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>159900</v>
+      </c>
+      <c r="E10" s="3">
         <v>154300</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>157400</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>152800</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>152400</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>153100</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>154800</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>152300</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>150900</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>149100</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>148600</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>141600</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>115500</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>52400</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>50700</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>49700</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>48500</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>45400</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>45700</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>50200</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>54600</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>54200</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>60100</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>61900</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>63700</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>62400</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>68700</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>66600</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>65400</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>64400</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>69200</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>66800</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>65900</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AK10" s="3">
         <v>66500</v>
       </c>
     </row>
-    <row r="11" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1153,8 +1165,9 @@
       <c r="AH11" s="3"/>
       <c r="AI11" s="3"/>
       <c r="AJ11" s="3"/>
+      <c r="AK11" s="3"/>
     </row>
-    <row r="12" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1257,8 +1270,11 @@
       <c r="AJ12" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AK12" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="13" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1361,59 +1377,62 @@
       <c r="AJ13" s="3">
         <v>0</v>
       </c>
+      <c r="AK13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>-5400</v>
+      </c>
+      <c r="E14" s="3">
         <v>-5000</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>63100</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>-5700</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>-500</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>5500</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>-28700</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>-400</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>-100</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>100</v>
       </c>
-      <c r="M14" s="3">
-        <v>0</v>
-      </c>
       <c r="N14" s="3">
+        <v>0</v>
+      </c>
+      <c r="O14" s="3">
         <v>900</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>76600</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>9200</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>800</v>
       </c>
-      <c r="R14" s="3" t="s">
+      <c r="S14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="S14" s="3">
-        <v>0</v>
-      </c>
       <c r="T14" s="3">
         <v>0</v>
       </c>
@@ -1424,32 +1443,32 @@
         <v>0</v>
       </c>
       <c r="W14" s="3">
+        <v>0</v>
+      </c>
+      <c r="X14" s="3">
         <v>2000</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Y14" s="3">
         <v>15600</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="Z14" s="3">
         <v>27700</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AA14" s="3">
         <v>4100</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AB14" s="3">
         <v>31500</v>
       </c>
-      <c r="AB14" s="3">
-        <v>0</v>
-      </c>
       <c r="AC14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD14" s="3">
         <v>14800</v>
       </c>
-      <c r="AD14" s="3">
+      <c r="AE14" s="3">
         <v>24100</v>
       </c>
-      <c r="AE14" s="3">
-        <v>0</v>
-      </c>
       <c r="AF14" s="3">
         <v>0</v>
       </c>
@@ -1457,120 +1476,126 @@
         <v>0</v>
       </c>
       <c r="AH14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI14" s="3">
         <v>7400</v>
       </c>
-      <c r="AI14" s="3">
+      <c r="AJ14" s="3">
         <v>2800</v>
       </c>
-      <c r="AJ14" s="3" t="s">
+      <c r="AK14" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="15" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>97000</v>
+      </c>
+      <c r="E15" s="3">
         <v>96700</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>99300</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>100400</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>102900</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>105900</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>109500</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>108100</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>112700</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>115800</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>119800</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>121500</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>109800</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>30200</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>29800</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>30600</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>31800</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>34000</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>31400</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>31500</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>30800</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>32000</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="Z15" s="3">
         <v>34700</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AA15" s="3">
         <v>34600</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AB15" s="3">
         <v>36300</v>
       </c>
-      <c r="AB15" s="3">
+      <c r="AC15" s="3">
         <v>36900</v>
       </c>
-      <c r="AC15" s="3">
+      <c r="AD15" s="3">
         <v>40500</v>
       </c>
-      <c r="AD15" s="3">
+      <c r="AE15" s="3">
         <v>38600</v>
       </c>
-      <c r="AE15" s="3">
+      <c r="AF15" s="3">
         <v>40800</v>
       </c>
-      <c r="AF15" s="3">
+      <c r="AG15" s="3">
         <v>42800</v>
       </c>
-      <c r="AG15" s="3">
+      <c r="AH15" s="3">
         <v>42700</v>
       </c>
-      <c r="AH15" s="3">
+      <c r="AI15" s="3">
         <v>45800</v>
       </c>
-      <c r="AI15" s="3">
+      <c r="AJ15" s="3">
         <v>42900</v>
       </c>
-      <c r="AJ15" s="3">
+      <c r="AK15" s="3">
         <v>45500</v>
       </c>
     </row>
-    <row r="16" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:37" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1604,216 +1629,223 @@
       <c r="AH16" s="3"/>
       <c r="AI16" s="3"/>
       <c r="AJ16" s="3"/>
+      <c r="AK16" s="3"/>
     </row>
-    <row r="17" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>165400</v>
+      </c>
+      <c r="E17" s="3">
         <v>162900</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>167300</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>167800</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>165100</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>173900</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>177900</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>176000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>179400</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>182000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>163600</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>185400</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>240600</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>65500</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>57400</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>31400</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>62700</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>56900</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>54900</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>57100</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>47000</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>80700</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>66700</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>60500</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>92500</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>65000</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>83800</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>91800</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>54400</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>70900</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>71600</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>82000</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>71300</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>73200</v>
       </c>
     </row>
-    <row r="18" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>49300</v>
+      </c>
+      <c r="E18" s="3">
         <v>44400</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>45100</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>39700</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>35200</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>33300</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>30900</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>30800</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>25300</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>18300</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>39000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>9000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-77600</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>6000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>12100</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>38000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>5700</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>8200</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>8400</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>12800</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>28200</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>-5800</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>14800</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>23000</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>-5600</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>20700</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>7900</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>-2000</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>34500</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>16200</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>21000</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>8100</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>17600</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>15900</v>
       </c>
     </row>
-    <row r="19" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1850,67 +1882,68 @@
       <c r="AH19" s="3"/>
       <c r="AI19" s="3"/>
       <c r="AJ19" s="3"/>
+      <c r="AK19" s="3"/>
     </row>
-    <row r="20" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>0</v>
+      </c>
+      <c r="E20" s="3">
         <v>600</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>200</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>400</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-200</v>
       </c>
-      <c r="H20" s="3">
-        <v>0</v>
-      </c>
       <c r="I20" s="3">
+        <v>0</v>
+      </c>
+      <c r="J20" s="3">
         <v>-100</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>200</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>400</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>100</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-200</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-100</v>
-      </c>
-      <c r="O20" s="3">
-        <v>100</v>
       </c>
       <c r="P20" s="3">
         <v>100</v>
       </c>
       <c r="Q20" s="3">
+        <v>100</v>
+      </c>
+      <c r="R20" s="3">
         <v>300</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-200</v>
       </c>
-      <c r="S20" s="3">
-        <v>0</v>
-      </c>
       <c r="T20" s="3">
         <v>0</v>
       </c>
       <c r="U20" s="3">
+        <v>0</v>
+      </c>
+      <c r="V20" s="3">
         <v>400</v>
-      </c>
-      <c r="V20" s="3">
-        <v>-100</v>
       </c>
       <c r="W20" s="3">
         <v>-100</v>
@@ -1919,236 +1952,242 @@
         <v>-100</v>
       </c>
       <c r="Y20" s="3">
-        <v>-200</v>
+        <v>-100</v>
       </c>
       <c r="Z20" s="3">
         <v>-200</v>
       </c>
       <c r="AA20" s="3">
+        <v>-200</v>
+      </c>
+      <c r="AB20" s="3">
         <v>-8300</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>-300</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>7700</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>300</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>-15200</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>-100</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>6300</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>8700</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>4000</v>
       </c>
-      <c r="AJ20" s="3">
+      <c r="AK20" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>146400</v>
+      </c>
+      <c r="E21" s="3">
         <v>140400</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>144200</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>139600</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>138300</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>139200</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>140400</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>138600</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>139500</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>135000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>158200</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>132200</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>33100</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>37000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>42900</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>69000</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>38000</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>42600</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>40700</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>44800</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>59500</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>26800</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>50200</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>58100</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>24100</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>57900</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>57000</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>37500</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>60600</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>59600</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>70700</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>63200</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>65300</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>63500</v>
       </c>
     </row>
-    <row r="22" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>32700</v>
+      </c>
+      <c r="E22" s="3">
         <v>31600</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>31000</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>30400</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>27200</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>25500</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>27200</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>25400</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>26800</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>26200</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>25700</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>25500</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>23100</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>12900</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>12300</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>12200</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>12300</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>12600</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>13300</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>12300</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>12400</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>14300</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>16100</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>16500</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>17600</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>16100</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>16700</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>16300</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>16500</v>
-      </c>
-      <c r="AF22" s="3">
-        <v>16400</v>
       </c>
       <c r="AG22" s="3">
         <v>16400</v>
@@ -2157,158 +2196,164 @@
         <v>16400</v>
       </c>
       <c r="AI22" s="3">
+        <v>16400</v>
+      </c>
+      <c r="AJ22" s="3">
         <v>17600</v>
       </c>
-      <c r="AJ22" s="3">
+      <c r="AK22" s="3">
         <v>17100</v>
       </c>
     </row>
-    <row r="23" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>22000</v>
+      </c>
+      <c r="E23" s="3">
         <v>17100</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-49200</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>14600</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>8600</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>2200</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>32500</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>5500</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-1100</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-7900</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>13100</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-16600</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-100500</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-6700</v>
       </c>
-      <c r="Q23" s="3">
-        <v>0</v>
-      </c>
       <c r="R23" s="3">
+        <v>0</v>
+      </c>
+      <c r="S23" s="3">
         <v>25600</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-6600</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-4400</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-4600</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>400</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>15700</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-20100</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-1500</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>6300</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>-31600</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>4300</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>-1100</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>-18000</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>2800</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>-200</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>10900</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>400</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>4000</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>-1200</v>
       </c>
     </row>
-    <row r="24" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>0</v>
+        <v>-200</v>
       </c>
       <c r="E24" s="3">
+        <v>0</v>
+      </c>
+      <c r="F24" s="3">
         <v>100</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>200</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>400</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>100</v>
       </c>
-      <c r="I24" s="3">
-        <v>0</v>
-      </c>
       <c r="J24" s="3">
         <v>0</v>
       </c>
       <c r="K24" s="3">
+        <v>0</v>
+      </c>
+      <c r="L24" s="3">
         <v>300</v>
       </c>
-      <c r="L24" s="3">
-        <v>0</v>
-      </c>
       <c r="M24" s="3">
+        <v>0</v>
+      </c>
+      <c r="N24" s="3">
         <v>-200</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>-100</v>
       </c>
-      <c r="O24" s="3">
-        <v>0</v>
-      </c>
       <c r="P24" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="Q24" s="3">
         <v>-100</v>
@@ -2317,7 +2362,7 @@
         <v>-100</v>
       </c>
       <c r="S24" s="3">
-        <v>-200</v>
+        <v>-100</v>
       </c>
       <c r="T24" s="3">
         <v>-200</v>
@@ -2326,16 +2371,16 @@
         <v>-200</v>
       </c>
       <c r="V24" s="3">
-        <v>-100</v>
+        <v>-200</v>
       </c>
       <c r="W24" s="3">
         <v>-100</v>
       </c>
       <c r="X24" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="Y24" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="Z24" s="3">
         <v>-100</v>
@@ -2344,7 +2389,7 @@
         <v>-100</v>
       </c>
       <c r="AB24" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="AC24" s="3">
         <v>0</v>
@@ -2365,13 +2410,16 @@
         <v>0</v>
       </c>
       <c r="AI24" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ24" s="3">
         <v>100</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2474,216 +2522,225 @@
       <c r="AJ25" s="3">
         <v>0</v>
       </c>
+      <c r="AK25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>22200</v>
+      </c>
+      <c r="E26" s="3">
         <v>17100</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-49300</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>14400</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>8200</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>2200</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>32500</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>5600</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-1400</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-7900</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>13300</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-16500</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-100500</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-6600</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>100</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>25700</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-6400</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-4200</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-4400</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>500</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>15800</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-20100</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-1500</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>6400</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>-31400</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>4300</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>-1100</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>-18000</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>2800</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>-200</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>10900</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>400</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>3900</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>-1300</v>
       </c>
     </row>
-    <row r="27" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>21800</v>
+      </c>
+      <c r="E27" s="3">
         <v>16700</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-48600</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>14200</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>8000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>2100</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>32100</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>5400</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-1100</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-7800</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>13100</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-16800</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-98200</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-7000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-200</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>24600</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-6800</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-4600</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-4800</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-100</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>15300</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-19700</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-1800</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>5700</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>-31200</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>3900</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>-1400</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>-17900</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>2300</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>-600</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>10200</v>
       </c>
-      <c r="AH27" s="3">
-        <v>0</v>
-      </c>
       <c r="AI27" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ27" s="3">
         <v>3400</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>-1700</v>
       </c>
     </row>
-    <row r="28" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2786,8 +2843,11 @@
       <c r="AJ28" s="3">
         <v>0</v>
       </c>
+      <c r="AK28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2872,8 +2932,8 @@
       <c r="AD29" s="3">
         <v>0</v>
       </c>
-      <c r="AE29" s="3" t="s">
-        <v>8</v>
+      <c r="AE29" s="3">
+        <v>0</v>
       </c>
       <c r="AF29" s="3" t="s">
         <v>8</v>
@@ -2884,14 +2944,17 @@
       <c r="AH29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AI29" s="3">
-        <v>0</v>
-      </c>
-      <c r="AJ29" s="3" t="s">
+      <c r="AI29" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AJ29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK29" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="30" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2994,8 +3057,11 @@
       <c r="AJ30" s="3">
         <v>0</v>
       </c>
+      <c r="AK30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3098,67 +3164,70 @@
       <c r="AJ31" s="3">
         <v>0</v>
       </c>
+      <c r="AK31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>0</v>
+      </c>
+      <c r="E32" s="3">
         <v>-600</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-200</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-400</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>200</v>
       </c>
-      <c r="H32" s="3">
-        <v>0</v>
-      </c>
       <c r="I32" s="3">
+        <v>0</v>
+      </c>
+      <c r="J32" s="3">
         <v>100</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-200</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-400</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-100</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>200</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>100</v>
-      </c>
-      <c r="O32" s="3">
-        <v>-100</v>
       </c>
       <c r="P32" s="3">
         <v>-100</v>
       </c>
       <c r="Q32" s="3">
+        <v>-100</v>
+      </c>
+      <c r="R32" s="3">
         <v>-300</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>200</v>
       </c>
-      <c r="S32" s="3">
-        <v>0</v>
-      </c>
       <c r="T32" s="3">
         <v>0</v>
       </c>
       <c r="U32" s="3">
+        <v>0</v>
+      </c>
+      <c r="V32" s="3">
         <v>-400</v>
-      </c>
-      <c r="V32" s="3">
-        <v>100</v>
       </c>
       <c r="W32" s="3">
         <v>100</v>
@@ -3167,147 +3236,153 @@
         <v>100</v>
       </c>
       <c r="Y32" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="Z32" s="3">
         <v>200</v>
       </c>
       <c r="AA32" s="3">
+        <v>200</v>
+      </c>
+      <c r="AB32" s="3">
         <v>8300</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>300</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>-7700</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>-300</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>15200</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>100</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>-6300</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>-8700</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>-4000</v>
       </c>
-      <c r="AJ32" s="3">
+      <c r="AK32" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>21800</v>
+      </c>
+      <c r="E33" s="3">
         <v>16700</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-48600</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>14200</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>8000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>2100</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>32100</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>5400</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-1100</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-7800</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>13100</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-16800</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-98200</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-7000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-200</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>24600</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-6800</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-4600</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-4800</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-100</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>15300</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-19700</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-1800</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>5700</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>-31200</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>3900</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>-1400</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>-17900</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>2300</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>-600</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>10200</v>
       </c>
-      <c r="AH33" s="3">
-        <v>0</v>
-      </c>
       <c r="AI33" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ33" s="3">
         <v>3400</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>-1700</v>
       </c>
     </row>
-    <row r="34" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3410,221 +3485,230 @@
       <c r="AJ34" s="3">
         <v>0</v>
       </c>
+      <c r="AK34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>21800</v>
+      </c>
+      <c r="E35" s="3">
         <v>16700</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-48600</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>14200</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>8000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>2100</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>32100</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>5400</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-1100</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-7800</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>13100</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-16800</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-98200</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-7000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-200</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>24600</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-6800</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-4600</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-4800</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-100</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>15300</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-19700</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-1800</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>5700</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>-31200</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>3900</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>-1400</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>-17900</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>2300</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>-600</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>10200</v>
       </c>
-      <c r="AH35" s="3">
-        <v>0</v>
-      </c>
       <c r="AI35" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ35" s="3">
         <v>3400</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>-1700</v>
       </c>
     </row>
-    <row r="37" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:37" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E38" s="2">
         <v>45565</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45473</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45382</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45291</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45199</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45107</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45016</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44926</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44834</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44742</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44651</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44561</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44469</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44377</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44286</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44196</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44104</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44012</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43921</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43830</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43738</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43646</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43555</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43465</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43373</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43281</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43190</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43100</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43008</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>42916</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>42825</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>42735</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3661,8 +3745,9 @@
       <c r="AH39" s="3"/>
       <c r="AI39" s="3"/>
       <c r="AJ39" s="3"/>
+      <c r="AK39" s="3"/>
     </row>
-    <row r="40" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3699,139 +3784,143 @@
       <c r="AH40" s="3"/>
       <c r="AI40" s="3"/>
       <c r="AJ40" s="3"/>
+      <c r="AK40" s="3"/>
     </row>
-    <row r="41" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>128100</v>
+      </c>
+      <c r="E41" s="3">
         <v>117500</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>153800</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>83600</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>36400</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>52300</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>129300</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>43700</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>115800</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>88400</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>90800</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>74300</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>93200</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>99500</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>89900</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>228800</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>43600</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>129300</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>230000</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>343900</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>31300</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>40400</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>35800</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>28400</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>35400</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>30700</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>32400</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>28800</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>24100</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>32500</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>27600</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>22600</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>19900</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>28800</v>
       </c>
     </row>
-    <row r="42" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>10600</v>
+      </c>
+      <c r="E42" s="3">
         <v>10200</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>21800</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>25300</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>23100</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>37200</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>37000</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>26700</v>
       </c>
-      <c r="K42" s="3">
-        <v>0</v>
-      </c>
       <c r="L42" s="3">
         <v>0</v>
       </c>
@@ -3907,112 +3996,118 @@
       <c r="AJ42" s="3">
         <v>0</v>
       </c>
+      <c r="AK42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>125800</v>
+      </c>
+      <c r="E43" s="3">
         <v>113800</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>120000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>118100</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>113300</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>113100</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>109600</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>103500</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>101300</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>86600</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>76900</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>69100</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>68400</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>45900</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>46700</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>49100</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>57200</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>57100</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>61600</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>49900</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>55300</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>50000</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>52000</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>55400</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>58100</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>57100</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>53100</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>57200</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>58300</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>53300</v>
-      </c>
-      <c r="AG43" s="3">
-        <v>52300</v>
       </c>
       <c r="AH43" s="3">
         <v>52300</v>
       </c>
       <c r="AI43" s="3">
+        <v>52300</v>
+      </c>
+      <c r="AJ43" s="3">
         <v>53100</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AK43" s="3">
         <v>50400</v>
       </c>
     </row>
-    <row r="44" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -4037,8 +4132,8 @@
       <c r="J44" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K44" s="3">
-        <v>0</v>
+      <c r="K44" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="L44" s="3">
         <v>0</v>
@@ -4115,139 +4210,145 @@
       <c r="AJ44" s="3">
         <v>0</v>
       </c>
+      <c r="AK44" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="45" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>517800</v>
+      </c>
+      <c r="E45" s="3">
         <v>520700</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>285900</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>371500</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>94800</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>111800</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>93500</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>113500</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>127000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>142800</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>106000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>96300</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>84800</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>39200</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>39500</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>42900</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>13000</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>39300</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>38200</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>36300</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>7500</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>10100</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>10300</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>14100</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>12800</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>17400</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>14200</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>20300</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>16400</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>12800</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>10200</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>12800</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AJ45" s="3">
         <v>9700</v>
       </c>
-      <c r="AJ45" s="3">
+      <c r="AK45" s="3">
         <v>10800</v>
       </c>
     </row>
-    <row r="46" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>787500</v>
+      </c>
+      <c r="E46" s="3">
         <v>767800</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>586500</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>603800</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>272600</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>320300</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>375000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>296300</v>
       </c>
-      <c r="K46" s="3">
-        <v>0</v>
-      </c>
       <c r="L46" s="3">
         <v>0</v>
       </c>
@@ -4323,91 +4424,94 @@
       <c r="AJ46" s="3">
         <v>0</v>
       </c>
+      <c r="AK46" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="47" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>19500</v>
+      </c>
+      <c r="E47" s="3">
         <v>18800</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>10000</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>9600</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>9100</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>10200</v>
-      </c>
-      <c r="I47" s="3">
-        <v>10300</v>
       </c>
       <c r="J47" s="3">
         <v>10300</v>
       </c>
       <c r="K47" s="3">
+        <v>10300</v>
+      </c>
+      <c r="L47" s="3">
         <v>10400</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>10600</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>10400</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>136800</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>136900</v>
-      </c>
-      <c r="P47" s="3">
-        <v>138000</v>
       </c>
       <c r="Q47" s="3">
         <v>138000</v>
       </c>
       <c r="R47" s="3">
+        <v>138000</v>
+      </c>
+      <c r="S47" s="3">
         <v>13000</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>12800</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>13100</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>13200</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>12100</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>12600</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>12900</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>12700</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>13300</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>13500</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>13800</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>13900</v>
-      </c>
-      <c r="AD47" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AE47" s="3" t="s">
         <v>8</v>
@@ -4427,112 +4531,118 @@
       <c r="AJ47" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AK47" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="48" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>6046500</v>
+      </c>
+      <c r="E48" s="3">
         <v>6091000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>6098600</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>6305700</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>6358300</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>6397300</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>6426100</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>6508700</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>6571400</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>6621600</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>6617800</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>6676800</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>6707500</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>2308000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>2343700</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>2358900</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>2415900</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>2347400</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>2380500</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>2404000</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>2447400</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>2514100</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>2716800</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>2911300</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>2941200</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>3051700</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>3076800</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>3194200</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>3293300</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>3320300</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>3331800</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>3399700</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>3435400</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>3458300</v>
       </c>
     </row>
-    <row r="49" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -4557,12 +4667,12 @@
       <c r="J49" s="3">
         <v>0</v>
       </c>
-      <c r="K49" s="3" t="s">
+      <c r="K49" s="3">
+        <v>0</v>
+      </c>
+      <c r="L49" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L49" s="3">
-        <v>0</v>
-      </c>
       <c r="M49" s="3">
         <v>0</v>
       </c>
@@ -4612,31 +4722,34 @@
         <v>0</v>
       </c>
       <c r="AC49" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD49" s="3">
         <v>32300</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>39000</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>44000</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>47900</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>53000</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>59300</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>65500</v>
       </c>
-      <c r="AJ49" s="3">
+      <c r="AK49" s="3">
         <v>70000</v>
       </c>
     </row>
-    <row r="50" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4739,8 +4852,11 @@
       <c r="AJ50" s="3">
         <v>0</v>
       </c>
+      <c r="AK50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4843,8 +4959,11 @@
       <c r="AJ51" s="3">
         <v>0</v>
       </c>
+      <c r="AK51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -4869,86 +4988,89 @@
       <c r="J52" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K52" s="3">
+      <c r="K52" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L52" s="3">
         <v>416000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>450000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>483000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>520300</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>548600</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>78400</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>61400</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>62600</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>66100</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>71900</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>88300</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>91300</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>94600</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>86300</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>108700</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>180800</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>111100</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>115100</v>
-      </c>
-      <c r="AC52" s="3">
-        <v>79400</v>
       </c>
       <c r="AD52" s="3">
         <v>79400</v>
       </c>
       <c r="AE52" s="3">
+        <v>79400</v>
+      </c>
+      <c r="AF52" s="3">
         <v>76400</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>76600</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>75400</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>76700</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>72800</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AK52" s="3">
         <v>72700</v>
       </c>
     </row>
-    <row r="53" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5051,112 +5173,118 @@
       <c r="AJ53" s="3">
         <v>0</v>
       </c>
+      <c r="AK53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>7091800</v>
+      </c>
+      <c r="E54" s="3">
         <v>7129700</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>6958900</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>7204500</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>6944100</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>7052500</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>7165100</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>7196900</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>7342000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>7399900</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>7384900</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>7573700</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>7639600</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>2708900</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>2719200</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>2755300</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>2608500</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>2658100</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>2811800</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>2937400</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>2648900</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>2713900</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>2936300</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>3203200</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>3172000</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>3285900</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>3302200</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>3418900</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>3512500</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>3543400</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>3550300</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>3623500</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>3656400</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>3690900</v>
       </c>
     </row>
-    <row r="55" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5193,8 +5321,9 @@
       <c r="AH55" s="3"/>
       <c r="AI55" s="3"/>
       <c r="AJ55" s="3"/>
+      <c r="AK55" s="3"/>
     </row>
-    <row r="56" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5231,139 +5360,143 @@
       <c r="AH56" s="3"/>
       <c r="AI56" s="3"/>
       <c r="AJ56" s="3"/>
+      <c r="AK56" s="3"/>
     </row>
-    <row r="57" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>198700</v>
+      </c>
+      <c r="E57" s="3">
         <v>184000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>181800</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>162400</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>188000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>185700</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>164800</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>148100</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>207800</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>152000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>133800</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>124200</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>185000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>85700</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>74400</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>72100</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>77500</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>88600</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>85700</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>109400</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>69800</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>77500</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>66600</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>61900</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>85900</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>98500</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>101200</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>102900</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>78500</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>101600</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>88500</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>88800</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>80700</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AK57" s="3">
         <v>93400</v>
       </c>
     </row>
-    <row r="58" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>440400</v>
+      </c>
+      <c r="E58" s="3">
         <v>1300</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>122600</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>273500</v>
       </c>
-      <c r="G58" s="3">
-        <v>5100</v>
-      </c>
       <c r="H58" s="3">
+        <v>0</v>
+      </c>
+      <c r="I58" s="3">
         <v>1300</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>124200</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>125100</v>
       </c>
-      <c r="K58" s="3">
-        <v>0</v>
-      </c>
       <c r="L58" s="3">
         <v>0</v>
       </c>
@@ -5439,82 +5572,85 @@
       <c r="AJ58" s="3">
         <v>0</v>
       </c>
+      <c r="AK58" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="59" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>15100</v>
+      </c>
+      <c r="E59" s="3">
         <v>3800</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>3900</v>
       </c>
-      <c r="F59" s="3" t="s">
+      <c r="G59" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="G59" s="3">
-        <v>19300</v>
-      </c>
-      <c r="H59" s="3">
+      <c r="H59" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I59" s="3">
         <v>168000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>11400</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>14600</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>79300</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>78100</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>76000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>79200</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>70200</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>26200</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>26300</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>26400</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>26500</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>26600</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>26800</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>26900</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>27000</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>27100</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>27200</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>27300</v>
-      </c>
-      <c r="AA59" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AB59" s="3" t="s">
         <v>8</v>
@@ -5525,8 +5661,8 @@
       <c r="AD59" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AE59" s="3">
-        <v>0</v>
+      <c r="AE59" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AF59" s="3">
         <v>0</v>
@@ -5543,35 +5679,38 @@
       <c r="AJ59" s="3">
         <v>0</v>
       </c>
+      <c r="AK59" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="60" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>654300</v>
+      </c>
+      <c r="E60" s="3">
         <v>189100</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>308300</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>435900</v>
       </c>
-      <c r="G60" s="3">
-        <v>212400</v>
-      </c>
       <c r="H60" s="3">
+        <v>188000</v>
+      </c>
+      <c r="I60" s="3">
         <v>354900</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>300400</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>287800</v>
       </c>
-      <c r="K60" s="3">
-        <v>0</v>
-      </c>
       <c r="L60" s="3">
         <v>0</v>
       </c>
@@ -5647,138 +5786,144 @@
       <c r="AJ60" s="3">
         <v>0</v>
       </c>
+      <c r="AK60" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="61" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>2857500</v>
+      </c>
+      <c r="E61" s="3">
         <v>3311100</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>2969000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>2971700</v>
       </c>
-      <c r="G61" s="3">
-        <v>2903100</v>
-      </c>
       <c r="H61" s="3">
+        <v>2908200</v>
+      </c>
+      <c r="I61" s="3">
         <v>2949700</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>2895300</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>2927500</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>3010300</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>3012900</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>3001200</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>3179100</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>3150800</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>1289000</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>1289400</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>1315200</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>1170800</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>1196100</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>1346300</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>1446500</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>1146600</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>1198600</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>1376600</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>1602600</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>1543300</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>1578300</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>1565400</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>1650500</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>1699200</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>1681700</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>1675100</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>1726900</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>1731100</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AK61" s="3">
         <v>1732300</v>
       </c>
     </row>
-    <row r="62" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>135800</v>
+      </c>
+      <c r="E62" s="3">
         <v>151900</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>154400</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>164400</v>
       </c>
-      <c r="G62" s="3">
-        <v>149300</v>
-      </c>
       <c r="H62" s="3">
+        <v>168700</v>
+      </c>
+      <c r="I62" s="3">
         <v>12000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>176500</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>182900</v>
-      </c>
-      <c r="K62" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="L62" s="3" t="s">
         <v>8</v>
@@ -5789,8 +5934,8 @@
       <c r="N62" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O62" s="3">
-        <v>0</v>
+      <c r="O62" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="P62" s="3">
         <v>0</v>
@@ -5819,14 +5964,14 @@
       <c r="X62" s="3">
         <v>0</v>
       </c>
-      <c r="Y62" s="3" t="s">
+      <c r="Y62" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z62" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>2400</v>
-      </c>
-      <c r="AA62" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AB62" s="3" t="s">
         <v>8</v>
@@ -5837,8 +5982,8 @@
       <c r="AD62" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AE62" s="3">
-        <v>0</v>
+      <c r="AE62" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AF62" s="3">
         <v>0</v>
@@ -5855,8 +6000,11 @@
       <c r="AJ62" s="3">
         <v>0</v>
       </c>
+      <c r="AK62" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="63" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5959,8 +6107,11 @@
       <c r="AJ63" s="3">
         <v>0</v>
       </c>
+      <c r="AK63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6063,8 +6214,11 @@
       <c r="AJ64" s="3">
         <v>0</v>
       </c>
+      <c r="AK64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6167,112 +6321,118 @@
       <c r="AJ65" s="3">
         <v>0</v>
       </c>
+      <c r="AK65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>3679700</v>
+      </c>
+      <c r="E66" s="3">
         <v>3681500</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>3459300</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>3598100</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>3300200</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>3347800</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>3405900</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>3428400</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>3575500</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>3527100</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>3493700</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>3675100</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>3717500</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>1510000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>1505700</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>1523500</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>1377900</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>1416000</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>1563600</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>1684600</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>1359800</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>1411700</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>1583700</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>1816400</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>1759300</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>1807700</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>1802800</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>1893900</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>1947100</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>1958500</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>1940600</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>2004000</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>2012800</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>2046500</v>
       </c>
     </row>
-    <row r="67" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6309,8 +6469,9 @@
       <c r="AH67" s="3"/>
       <c r="AI67" s="3"/>
       <c r="AJ67" s="3"/>
+      <c r="AK67" s="3"/>
     </row>
-    <row r="68" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6413,8 +6574,11 @@
       <c r="AJ68" s="3">
         <v>0</v>
       </c>
+      <c r="AK68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6517,8 +6681,11 @@
       <c r="AJ69" s="3">
         <v>0</v>
       </c>
+      <c r="AK69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6621,8 +6788,11 @@
       <c r="AJ70" s="3">
         <v>0</v>
       </c>
+      <c r="AK70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6725,112 +6895,118 @@
       <c r="AJ71" s="3">
         <v>0</v>
       </c>
+      <c r="AK71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-1595300</v>
+      </c>
+      <c r="E72" s="3">
         <v>-1557800</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-1517400</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-1413800</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-1373100</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-1326200</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-1275600</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-1255000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-1207800</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-1105800</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-1052000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-1021300</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-962900</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-849500</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-827300</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-812700</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-824300</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-810800</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-801800</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-797000</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-770000</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-758600</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>-712200</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>-683700</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>-662700</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>-604900</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>-582200</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>-554300</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>-509800</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>-485600</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>-459700</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>-444600</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>-419300</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>-397400</v>
       </c>
     </row>
-    <row r="73" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6933,8 +7109,11 @@
       <c r="AJ73" s="3">
         <v>0</v>
       </c>
+      <c r="AK73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7037,8 +7216,11 @@
       <c r="AJ74" s="3">
         <v>0</v>
       </c>
+      <c r="AK74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -7141,112 +7323,118 @@
       <c r="AJ75" s="3">
         <v>0</v>
       </c>
+      <c r="AK75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>3312100</v>
+      </c>
+      <c r="E76" s="3">
         <v>3349400</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>3421600</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>3530800</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>3568100</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>3635300</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>3692800</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>3706000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>3766500</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>3872800</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>3891100</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>3898600</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>3922000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>1198800</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>1213500</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>1231900</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>1230700</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>1242100</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>1248200</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>1252800</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>1289000</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>1302200</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>1352700</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>1386800</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>1412700</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>1478200</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>1499400</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>1525000</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>1565400</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>1584900</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>1609700</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>1619500</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>1643600</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>1644400</v>
       </c>
     </row>
-    <row r="77" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7349,221 +7537,230 @@
       <c r="AJ77" s="3">
         <v>0</v>
       </c>
+      <c r="AK77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:37" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E80" s="2">
         <v>45565</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45473</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45382</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45291</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45199</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45107</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45016</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44926</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44834</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44742</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44651</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44561</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44469</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44377</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44286</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44196</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44104</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44012</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43921</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43830</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43738</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43646</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43555</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43465</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43373</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43281</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43190</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43100</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43008</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>42916</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>42825</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>42735</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>21800</v>
+      </c>
+      <c r="E81" s="3">
         <v>16700</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-48600</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>14200</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>8000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>2100</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>32100</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>5400</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-1100</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-7800</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>13100</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-16800</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-98200</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-7000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-200</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>24600</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-6800</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-4600</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-4800</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-100</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>15300</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-19700</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-1800</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>5700</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>-31200</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>3900</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>-1400</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>-17900</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>2300</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>-600</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>10200</v>
       </c>
-      <c r="AH81" s="3">
-        <v>0</v>
-      </c>
       <c r="AI81" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ81" s="3">
         <v>3400</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>-1700</v>
       </c>
     </row>
-    <row r="82" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7600,112 +7797,116 @@
       <c r="AH82" s="3"/>
       <c r="AI82" s="3"/>
       <c r="AJ82" s="3"/>
+      <c r="AK82" s="3"/>
     </row>
-    <row r="83" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>76300</v>
+      </c>
+      <c r="E83" s="3">
         <v>75900</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>77700</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>79600</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>78000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>79200</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>78300</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>79800</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>113700</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>116600</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>119300</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>123300</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>110600</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>30800</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>30500</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>31200</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>32300</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>34400</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>32000</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>32100</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>31400</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>32600</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>35600</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>35300</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>38000</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>37500</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>41300</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>39200</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>41400</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>43500</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>43400</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>46400</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>43700</v>
       </c>
-      <c r="AJ83" s="3">
+      <c r="AK83" s="3">
         <v>47700</v>
       </c>
     </row>
-    <row r="84" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7808,8 +8009,11 @@
       <c r="AJ84" s="3">
         <v>0</v>
       </c>
+      <c r="AK84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7912,8 +8116,11 @@
       <c r="AJ85" s="3">
         <v>0</v>
       </c>
+      <c r="AK85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -8016,8 +8223,11 @@
       <c r="AJ86" s="3">
         <v>0</v>
       </c>
+      <c r="AK86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -8120,8 +8330,11 @@
       <c r="AJ87" s="3">
         <v>0</v>
       </c>
+      <c r="AK87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8224,112 +8437,118 @@
       <c r="AJ88" s="3">
         <v>0</v>
       </c>
+      <c r="AK88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>111000</v>
+      </c>
+      <c r="E89" s="3">
         <v>112400</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>142100</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>53600</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>103500</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>110800</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>116800</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>63600</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>116900</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>108100</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>104700</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>49600</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-3500</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>36400</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>36100</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>31300</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>9800</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>35900</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>28000</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>21900</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>31800</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>36500</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>37300</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>32300</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>35400</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>37000</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>45800</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>36300</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>30800</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>42700</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>44900</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>36200</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>34200</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>39800</v>
       </c>
     </row>
-    <row r="90" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -8366,112 +8585,116 @@
       <c r="AH90" s="3"/>
       <c r="AI90" s="3"/>
       <c r="AJ90" s="3"/>
+      <c r="AK90" s="3"/>
     </row>
-    <row r="91" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-39000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-34800</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-38900</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-28200</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-43900</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-30900</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-28600</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-39100</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-52000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-47800</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-35000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-23800</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-20400</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-15700</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-13300</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-7900</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-7600</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-8200</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-9200</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-13200</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-15700</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-12400</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-13700</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-11500</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-12000</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-12700</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-16500</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-18100</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-10800</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-24800</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-11200</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-47700</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-26000</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AK91" s="3">
         <v>-24100</v>
       </c>
     </row>
-    <row r="92" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8574,8 +8797,11 @@
       <c r="AJ92" s="3">
         <v>0</v>
       </c>
+      <c r="AK92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8678,112 +8904,118 @@
       <c r="AJ93" s="3">
         <v>0</v>
       </c>
+      <c r="AK93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-29500</v>
+      </c>
+      <c r="E94" s="3">
         <v>-314900</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>134700</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-289300</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-26200</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-63500</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>49500</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-41500</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-31500</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-82300</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>130800</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-62200</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>18000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-9600</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-133300</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>33900</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-64900</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>4700</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-13500</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-7100</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>52800</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>166900</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>226600</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-29700</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>44700</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-14500</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>71800</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>46400</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-23200</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-16500</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>38100</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>1400</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-15600</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>-22200</v>
       </c>
     </row>
-    <row r="95" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8820,13 +9052,14 @@
       <c r="AH95" s="3"/>
       <c r="AI95" s="3"/>
       <c r="AJ95" s="3"/>
+      <c r="AK95" s="3"/>
     </row>
-    <row r="96" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>54900</v>
+        <v>57100</v>
       </c>
       <c r="E96" s="3">
         <v>54900</v>
@@ -8835,55 +9068,55 @@
         <v>54900</v>
       </c>
       <c r="G96" s="3">
-        <v>52700</v>
+        <v>54900</v>
       </c>
       <c r="H96" s="3">
         <v>52700</v>
       </c>
       <c r="I96" s="3">
-        <v>52600</v>
+        <v>52700</v>
       </c>
       <c r="J96" s="3">
         <v>52600</v>
       </c>
       <c r="K96" s="3">
+        <v>52600</v>
+      </c>
+      <c r="L96" s="3">
         <v>-48200</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>-46000</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>-43800</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>-41600</v>
-      </c>
-      <c r="O96" s="3">
-        <v>-15200</v>
       </c>
       <c r="P96" s="3">
         <v>-15200</v>
       </c>
       <c r="Q96" s="3">
+        <v>-15200</v>
+      </c>
+      <c r="R96" s="3">
         <v>-14400</v>
       </c>
-      <c r="R96" s="3">
+      <c r="S96" s="3">
         <v>-13000</v>
       </c>
-      <c r="S96" s="3">
+      <c r="T96" s="3">
         <v>-6700</v>
       </c>
-      <c r="T96" s="3">
+      <c r="U96" s="3">
         <v>-4400</v>
       </c>
-      <c r="U96" s="3">
+      <c r="V96" s="3">
         <v>-26700</v>
       </c>
-      <c r="V96" s="3">
+      <c r="W96" s="3">
         <v>-300</v>
-      </c>
-      <c r="W96" s="3">
-        <v>-26700</v>
       </c>
       <c r="X96" s="3">
         <v>-26700</v>
@@ -8892,10 +9125,10 @@
         <v>-26700</v>
       </c>
       <c r="Z96" s="3">
+        <v>-26700</v>
+      </c>
+      <c r="AA96" s="3">
         <v>-53300</v>
-      </c>
-      <c r="AA96" s="3">
-        <v>-26600</v>
       </c>
       <c r="AB96" s="3">
         <v>-26600</v>
@@ -8904,10 +9137,10 @@
         <v>-26600</v>
       </c>
       <c r="AD96" s="3">
+        <v>-26600</v>
+      </c>
+      <c r="AE96" s="3">
         <v>-26500</v>
-      </c>
-      <c r="AE96" s="3">
-        <v>-25300</v>
       </c>
       <c r="AF96" s="3">
         <v>-25300</v>
@@ -8919,13 +9152,16 @@
         <v>-25300</v>
       </c>
       <c r="AI96" s="3">
-        <v>-24000</v>
+        <v>-25300</v>
       </c>
       <c r="AJ96" s="3">
         <v>-24000</v>
       </c>
+      <c r="AK96" s="3">
+        <v>-24000</v>
+      </c>
     </row>
-    <row r="97" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -9028,8 +9264,11 @@
       <c r="AJ97" s="3">
         <v>0</v>
       </c>
+      <c r="AK97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -9132,8 +9371,11 @@
       <c r="AJ98" s="3">
         <v>0</v>
       </c>
+      <c r="AK98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -9236,112 +9478,118 @@
       <c r="AJ99" s="3">
         <v>0</v>
       </c>
+      <c r="AK99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-71200</v>
+      </c>
+      <c r="E100" s="3">
         <v>166800</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-206800</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>283300</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-94100</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-123900</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-84100</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-91400</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-59900</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-28400</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-218600</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-5600</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-18000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-17100</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-41200</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>120800</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-35600</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-155100</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-128300</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>298000</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-81800</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-212900</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-256400</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>3800</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-75600</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-24800</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-112800</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-76300</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-16800</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-19700</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-78700</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>-34200</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>-27600</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>-26600</v>
       </c>
     </row>
-    <row r="101" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -9366,8 +9614,8 @@
       <c r="J101" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K101" s="3">
-        <v>0</v>
+      <c r="K101" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="L101" s="3">
         <v>0</v>
@@ -9444,108 +9692,114 @@
       <c r="AJ101" s="3">
         <v>0</v>
       </c>
+      <c r="AK101" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="102" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>10300</v>
+      </c>
+      <c r="E102" s="3">
         <v>-35700</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>70000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>47500</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-16900</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-76600</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>82300</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-69300</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>25500</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-2600</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>17000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-18200</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-3400</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>9700</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-138500</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>185900</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-90700</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-114500</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-113800</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>312800</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>2800</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-9500</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>7600</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>6400</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>4500</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-2300</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>4800</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>6400</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>-8400</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>4800</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>4400</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>3300</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>-8900</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>-9100</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/KRG_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/KRG_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="183" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="187" uniqueCount="92">
   <si>
     <t>KRG</t>
   </si>
@@ -656,479 +656,492 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AK102"/>
+  <dimension ref="A5:AL102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="37" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="38" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="38" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="39" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:38" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E7" s="2">
         <v>45657</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45565</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45473</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45382</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45291</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45199</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45107</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45016</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44926</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44834</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44742</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44651</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44561</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44469</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44377</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44286</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44196</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44104</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44012</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43921</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43830</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43738</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43646</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43555</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43465</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43373</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43281</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43190</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43100</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43008</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>42916</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>42825</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>42735</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>221800</v>
+      </c>
+      <c r="E8" s="3">
         <v>214700</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>207300</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>212400</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>207400</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>200300</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>207200</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>208800</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>206800</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>204700</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>200300</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>202600</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>194400</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>163000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>71500</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>69500</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>69400</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>68400</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>65100</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>63300</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>69900</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>75200</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>74900</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>81500</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>83500</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>86900</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>85700</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>91700</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>89800</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>88900</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>87100</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>92600</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>90100</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>88900</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AL8" s="3">
         <v>89100</v>
       </c>
     </row>
-    <row r="9" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>57600</v>
+      </c>
+      <c r="E9" s="3">
         <v>54800</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>53000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>55100</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>54600</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>47900</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>54100</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>53900</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>54500</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>53800</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>51200</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>54000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>52800</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>47500</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>19100</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>18800</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>19700</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>19900</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>19700</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>17600</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>19700</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>20600</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>20700</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>21400</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>21600</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>23200</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>23300</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>23000</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>23200</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>23500</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>22700</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>23400</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>23300</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AK9" s="3">
         <v>23000</v>
       </c>
-      <c r="AK9" s="3">
+      <c r="AL9" s="3">
         <v>22600</v>
       </c>
     </row>
-    <row r="10" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>164200</v>
+      </c>
+      <c r="E10" s="3">
         <v>159900</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>154300</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>157400</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>152800</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>152400</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>153100</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>154800</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>152300</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>150900</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>149100</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>148600</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>141600</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>115500</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>52400</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>50700</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>49700</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>48500</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>45400</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>45700</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>50200</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>54600</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>54200</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>60100</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>61900</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>63700</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>62400</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>68700</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>66600</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>65400</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>64400</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>69200</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>66800</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AK10" s="3">
         <v>65900</v>
       </c>
-      <c r="AK10" s="3">
+      <c r="AL10" s="3">
         <v>66500</v>
       </c>
     </row>
-    <row r="11" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1166,8 +1179,9 @@
       <c r="AI11" s="3"/>
       <c r="AJ11" s="3"/>
       <c r="AK11" s="3"/>
+      <c r="AL11" s="3"/>
     </row>
-    <row r="12" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1273,8 +1287,11 @@
       <c r="AK12" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AL12" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="13" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1380,62 +1397,65 @@
       <c r="AK13" s="3">
         <v>0</v>
       </c>
+      <c r="AL13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>-4100</v>
+      </c>
+      <c r="E14" s="3">
         <v>-5400</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>-5000</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>63100</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>-5700</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>-500</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>5500</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>-28700</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>-400</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>-100</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>100</v>
       </c>
-      <c r="N14" s="3">
-        <v>0</v>
-      </c>
       <c r="O14" s="3">
+        <v>0</v>
+      </c>
+      <c r="P14" s="3">
         <v>900</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>76600</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>9200</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>800</v>
       </c>
-      <c r="S14" s="3" t="s">
+      <c r="T14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="T14" s="3">
-        <v>0</v>
-      </c>
       <c r="U14" s="3">
         <v>0</v>
       </c>
@@ -1446,32 +1466,32 @@
         <v>0</v>
       </c>
       <c r="X14" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y14" s="3">
         <v>2000</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="Z14" s="3">
         <v>15600</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AA14" s="3">
         <v>27700</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AB14" s="3">
         <v>4100</v>
       </c>
-      <c r="AB14" s="3">
+      <c r="AC14" s="3">
         <v>31500</v>
       </c>
-      <c r="AC14" s="3">
-        <v>0</v>
-      </c>
       <c r="AD14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE14" s="3">
         <v>14800</v>
       </c>
-      <c r="AE14" s="3">
+      <c r="AF14" s="3">
         <v>24100</v>
       </c>
-      <c r="AF14" s="3">
-        <v>0</v>
-      </c>
       <c r="AG14" s="3">
         <v>0</v>
       </c>
@@ -1479,123 +1499,129 @@
         <v>0</v>
       </c>
       <c r="AI14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ14" s="3">
         <v>7400</v>
       </c>
-      <c r="AJ14" s="3">
+      <c r="AK14" s="3">
         <v>2800</v>
       </c>
-      <c r="AK14" s="3" t="s">
+      <c r="AL14" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="15" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>98200</v>
+      </c>
+      <c r="E15" s="3">
         <v>97000</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>96700</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>99300</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>100400</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>102900</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>105900</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>109500</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>108100</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>112700</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>115800</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>119800</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>121500</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>109800</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>30200</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>29800</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>30600</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>31800</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>34000</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>31400</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>31500</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>30800</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="Z15" s="3">
         <v>32000</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AA15" s="3">
         <v>34700</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AB15" s="3">
         <v>34600</v>
       </c>
-      <c r="AB15" s="3">
+      <c r="AC15" s="3">
         <v>36300</v>
       </c>
-      <c r="AC15" s="3">
+      <c r="AD15" s="3">
         <v>36900</v>
       </c>
-      <c r="AD15" s="3">
+      <c r="AE15" s="3">
         <v>40500</v>
       </c>
-      <c r="AE15" s="3">
+      <c r="AF15" s="3">
         <v>38600</v>
       </c>
-      <c r="AF15" s="3">
+      <c r="AG15" s="3">
         <v>40800</v>
       </c>
-      <c r="AG15" s="3">
+      <c r="AH15" s="3">
         <v>42800</v>
       </c>
-      <c r="AH15" s="3">
+      <c r="AI15" s="3">
         <v>42700</v>
       </c>
-      <c r="AI15" s="3">
+      <c r="AJ15" s="3">
         <v>45800</v>
       </c>
-      <c r="AJ15" s="3">
+      <c r="AK15" s="3">
         <v>42900</v>
       </c>
-      <c r="AK15" s="3">
+      <c r="AL15" s="3">
         <v>45500</v>
       </c>
     </row>
-    <row r="16" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:38" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1630,222 +1656,229 @@
       <c r="AI16" s="3"/>
       <c r="AJ16" s="3"/>
       <c r="AK16" s="3"/>
+      <c r="AL16" s="3"/>
     </row>
-    <row r="17" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>168100</v>
+      </c>
+      <c r="E17" s="3">
         <v>165400</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>162900</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>167300</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>167800</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>165100</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>173900</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>177900</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>176000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>179400</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>182000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>163600</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>185400</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>240600</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>65500</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>57400</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>31400</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>62700</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>56900</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>54900</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>57100</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>47000</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>80700</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>66700</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>60500</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>92500</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>65000</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>83800</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>91800</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>54400</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>70900</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>71600</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>82000</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>71300</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>73200</v>
       </c>
     </row>
-    <row r="18" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>53700</v>
+      </c>
+      <c r="E18" s="3">
         <v>49300</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>44400</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>45100</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>39700</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>35200</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>33300</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>30900</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>30800</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>25300</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>18300</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>39000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>9000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-77600</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>6000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>12100</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>38000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>5700</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>8200</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>8400</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>12800</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>28200</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>-5800</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>14800</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>23000</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>-5600</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>20700</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>7900</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>-2000</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>34500</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>16200</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>21000</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>8100</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>17600</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3">
         <v>15900</v>
       </c>
     </row>
-    <row r="19" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1883,70 +1916,71 @@
       <c r="AI19" s="3"/>
       <c r="AJ19" s="3"/>
       <c r="AK19" s="3"/>
+      <c r="AL19" s="3"/>
     </row>
-    <row r="20" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>0</v>
+        <v>600</v>
       </c>
       <c r="E20" s="3">
+        <v>0</v>
+      </c>
+      <c r="F20" s="3">
         <v>600</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>200</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>400</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-200</v>
       </c>
-      <c r="I20" s="3">
-        <v>0</v>
-      </c>
       <c r="J20" s="3">
+        <v>0</v>
+      </c>
+      <c r="K20" s="3">
         <v>-100</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>200</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>400</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>100</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-200</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-100</v>
-      </c>
-      <c r="P20" s="3">
-        <v>100</v>
       </c>
       <c r="Q20" s="3">
         <v>100</v>
       </c>
       <c r="R20" s="3">
+        <v>100</v>
+      </c>
+      <c r="S20" s="3">
         <v>300</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-200</v>
       </c>
-      <c r="T20" s="3">
-        <v>0</v>
-      </c>
       <c r="U20" s="3">
         <v>0</v>
       </c>
       <c r="V20" s="3">
+        <v>0</v>
+      </c>
+      <c r="W20" s="3">
         <v>400</v>
-      </c>
-      <c r="W20" s="3">
-        <v>-100</v>
       </c>
       <c r="X20" s="3">
         <v>-100</v>
@@ -1955,242 +1989,248 @@
         <v>-100</v>
       </c>
       <c r="Z20" s="3">
-        <v>-200</v>
+        <v>-100</v>
       </c>
       <c r="AA20" s="3">
         <v>-200</v>
       </c>
       <c r="AB20" s="3">
+        <v>-200</v>
+      </c>
+      <c r="AC20" s="3">
         <v>-8300</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>-300</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>7700</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>300</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>-15200</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>-100</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>6300</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>8700</v>
       </c>
-      <c r="AJ20" s="3">
+      <c r="AK20" s="3">
         <v>4000</v>
       </c>
-      <c r="AK20" s="3">
+      <c r="AL20" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>151300</v>
+      </c>
+      <c r="E21" s="3">
         <v>146400</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>140400</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>144200</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>139600</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>138300</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>139200</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>140400</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>138600</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>139500</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>135000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>158200</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>132200</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>33100</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>37000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>42900</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>69000</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>38000</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>42600</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>40700</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>44800</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>59500</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>26800</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>50200</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>58100</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>24100</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>57900</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>57000</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>37500</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>60600</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>59600</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>70700</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>63200</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>65300</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AL21" s="3">
         <v>63500</v>
       </c>
     </row>
-    <row r="22" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>33000</v>
+      </c>
+      <c r="E22" s="3">
         <v>32700</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>31600</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>31000</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>30400</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>27200</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>25500</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>27200</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>25400</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>26800</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>26200</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>25700</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>25500</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>23100</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>12900</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>12300</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>12200</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>12300</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>12600</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>13300</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>12300</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>12400</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>14300</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>16100</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>16500</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>17600</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>16100</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>16700</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>16300</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>16500</v>
-      </c>
-      <c r="AG22" s="3">
-        <v>16400</v>
       </c>
       <c r="AH22" s="3">
         <v>16400</v>
@@ -2199,164 +2239,170 @@
         <v>16400</v>
       </c>
       <c r="AJ22" s="3">
+        <v>16400</v>
+      </c>
+      <c r="AK22" s="3">
         <v>17600</v>
       </c>
-      <c r="AK22" s="3">
+      <c r="AL22" s="3">
         <v>17100</v>
       </c>
     </row>
-    <row r="23" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>24300</v>
+      </c>
+      <c r="E23" s="3">
         <v>22000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>17100</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-49200</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>14600</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>8600</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>2200</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>32500</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>5500</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-1100</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-7900</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>13100</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-16600</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-100500</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-6700</v>
       </c>
-      <c r="R23" s="3">
-        <v>0</v>
-      </c>
       <c r="S23" s="3">
+        <v>0</v>
+      </c>
+      <c r="T23" s="3">
         <v>25600</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-6600</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-4400</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-4600</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>400</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>15700</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-20100</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>-1500</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>6300</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>-31600</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>4300</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>-1100</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>-18000</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>2800</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>-200</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>10900</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>400</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>4000</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>-1200</v>
       </c>
     </row>
-    <row r="24" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>0</v>
+      </c>
+      <c r="E24" s="3">
         <v>-200</v>
       </c>
-      <c r="E24" s="3">
-        <v>0</v>
-      </c>
       <c r="F24" s="3">
+        <v>0</v>
+      </c>
+      <c r="G24" s="3">
         <v>100</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>200</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>400</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>100</v>
       </c>
-      <c r="J24" s="3">
-        <v>0</v>
-      </c>
       <c r="K24" s="3">
         <v>0</v>
       </c>
       <c r="L24" s="3">
+        <v>0</v>
+      </c>
+      <c r="M24" s="3">
         <v>300</v>
       </c>
-      <c r="M24" s="3">
-        <v>0</v>
-      </c>
       <c r="N24" s="3">
+        <v>0</v>
+      </c>
+      <c r="O24" s="3">
         <v>-200</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>-100</v>
       </c>
-      <c r="P24" s="3">
-        <v>0</v>
-      </c>
       <c r="Q24" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="R24" s="3">
         <v>-100</v>
@@ -2365,7 +2411,7 @@
         <v>-100</v>
       </c>
       <c r="T24" s="3">
-        <v>-200</v>
+        <v>-100</v>
       </c>
       <c r="U24" s="3">
         <v>-200</v>
@@ -2374,16 +2420,16 @@
         <v>-200</v>
       </c>
       <c r="W24" s="3">
-        <v>-100</v>
+        <v>-200</v>
       </c>
       <c r="X24" s="3">
         <v>-100</v>
       </c>
       <c r="Y24" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="Z24" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="AA24" s="3">
         <v>-100</v>
@@ -2392,7 +2438,7 @@
         <v>-100</v>
       </c>
       <c r="AC24" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="AD24" s="3">
         <v>0</v>
@@ -2413,13 +2459,16 @@
         <v>0</v>
       </c>
       <c r="AJ24" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK24" s="3">
         <v>100</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AL24" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2525,222 +2574,231 @@
       <c r="AK25" s="3">
         <v>0</v>
       </c>
+      <c r="AL25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>24300</v>
+      </c>
+      <c r="E26" s="3">
         <v>22200</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>17100</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-49300</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>14400</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>8200</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>2200</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>32500</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>5600</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-1400</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-7900</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>13300</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-16500</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-100500</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-6600</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>100</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>25700</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-6400</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-4200</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-4400</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>500</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>15800</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-20100</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>-1500</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>6400</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>-31400</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>4300</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>-1100</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>-18000</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>2800</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>-200</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>10900</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>400</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>3900</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>-1300</v>
       </c>
     </row>
-    <row r="27" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>23700</v>
+      </c>
+      <c r="E27" s="3">
         <v>21800</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>16700</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-48600</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>14200</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>8000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>2100</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>32100</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>5400</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-1100</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-7800</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>13100</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-16800</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-98200</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-7000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-200</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>24600</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-6800</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-4600</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-4800</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-100</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>15300</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-19700</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>-1800</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>5700</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>-31200</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>3900</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>-1400</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>-17900</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>2300</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>-600</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>10200</v>
       </c>
-      <c r="AI27" s="3">
-        <v>0</v>
-      </c>
       <c r="AJ27" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK27" s="3">
         <v>3400</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>-1700</v>
       </c>
     </row>
-    <row r="28" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2846,8 +2904,11 @@
       <c r="AK28" s="3">
         <v>0</v>
       </c>
+      <c r="AL28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2935,8 +2996,8 @@
       <c r="AE29" s="3">
         <v>0</v>
       </c>
-      <c r="AF29" s="3" t="s">
-        <v>8</v>
+      <c r="AF29" s="3">
+        <v>0</v>
       </c>
       <c r="AG29" s="3" t="s">
         <v>8</v>
@@ -2947,14 +3008,17 @@
       <c r="AI29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AJ29" s="3">
-        <v>0</v>
-      </c>
-      <c r="AK29" s="3" t="s">
+      <c r="AJ29" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AK29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL29" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="30" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3060,8 +3124,11 @@
       <c r="AK30" s="3">
         <v>0</v>
       </c>
+      <c r="AL30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3167,70 +3234,73 @@
       <c r="AK31" s="3">
         <v>0</v>
       </c>
+      <c r="AL31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>0</v>
+        <v>-600</v>
       </c>
       <c r="E32" s="3">
+        <v>0</v>
+      </c>
+      <c r="F32" s="3">
         <v>-600</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-200</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-400</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>200</v>
       </c>
-      <c r="I32" s="3">
-        <v>0</v>
-      </c>
       <c r="J32" s="3">
+        <v>0</v>
+      </c>
+      <c r="K32" s="3">
         <v>100</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-200</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-400</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-100</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>200</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>100</v>
-      </c>
-      <c r="P32" s="3">
-        <v>-100</v>
       </c>
       <c r="Q32" s="3">
         <v>-100</v>
       </c>
       <c r="R32" s="3">
+        <v>-100</v>
+      </c>
+      <c r="S32" s="3">
         <v>-300</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>200</v>
       </c>
-      <c r="T32" s="3">
-        <v>0</v>
-      </c>
       <c r="U32" s="3">
         <v>0</v>
       </c>
       <c r="V32" s="3">
+        <v>0</v>
+      </c>
+      <c r="W32" s="3">
         <v>-400</v>
-      </c>
-      <c r="W32" s="3">
-        <v>100</v>
       </c>
       <c r="X32" s="3">
         <v>100</v>
@@ -3239,150 +3309,156 @@
         <v>100</v>
       </c>
       <c r="Z32" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="AA32" s="3">
         <v>200</v>
       </c>
       <c r="AB32" s="3">
+        <v>200</v>
+      </c>
+      <c r="AC32" s="3">
         <v>8300</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>300</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>-7700</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>-300</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>15200</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>100</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>-6300</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>-8700</v>
       </c>
-      <c r="AJ32" s="3">
+      <c r="AK32" s="3">
         <v>-4000</v>
       </c>
-      <c r="AK32" s="3">
+      <c r="AL32" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>23700</v>
+      </c>
+      <c r="E33" s="3">
         <v>21800</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>16700</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-48600</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>14200</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>8000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>2100</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>32100</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>5400</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-1100</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-7800</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>13100</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-16800</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-98200</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-7000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-200</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>24600</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-6800</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-4600</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-4800</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-100</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>15300</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-19700</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-1800</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>5700</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>-31200</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>3900</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>-1400</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>-17900</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>2300</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>-600</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>10200</v>
       </c>
-      <c r="AI33" s="3">
-        <v>0</v>
-      </c>
       <c r="AJ33" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK33" s="3">
         <v>3400</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>-1700</v>
       </c>
     </row>
-    <row r="34" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3488,227 +3564,236 @@
       <c r="AK34" s="3">
         <v>0</v>
       </c>
+      <c r="AL34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>23700</v>
+      </c>
+      <c r="E35" s="3">
         <v>21800</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>16700</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-48600</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>14200</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>8000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>2100</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>32100</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>5400</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-1100</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-7800</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>13100</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-16800</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-98200</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-7000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-200</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>24600</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-6800</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-4600</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-4800</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-100</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>15300</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-19700</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-1800</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>5700</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>-31200</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>3900</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>-1400</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>-17900</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>2300</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>-600</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>10200</v>
       </c>
-      <c r="AI35" s="3">
-        <v>0</v>
-      </c>
       <c r="AJ35" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK35" s="3">
         <v>3400</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>-1700</v>
       </c>
     </row>
-    <row r="37" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:38" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E38" s="2">
         <v>45657</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45565</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45473</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45382</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45291</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45199</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45107</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45016</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44926</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44834</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44742</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44651</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44561</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44469</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44377</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44286</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44196</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44104</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44012</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43921</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43830</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43738</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43646</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43555</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43465</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43373</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43281</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43190</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43100</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43008</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>42916</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>42825</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>42735</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3746,8 +3831,9 @@
       <c r="AI39" s="3"/>
       <c r="AJ39" s="3"/>
       <c r="AK39" s="3"/>
+      <c r="AL39" s="3"/>
     </row>
-    <row r="40" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3785,145 +3871,149 @@
       <c r="AI40" s="3"/>
       <c r="AJ40" s="3"/>
       <c r="AK40" s="3"/>
+      <c r="AL40" s="3"/>
     </row>
-    <row r="41" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>49100</v>
+      </c>
+      <c r="E41" s="3">
         <v>128100</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>117500</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>153800</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>83600</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>36400</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>52300</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>129300</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>43700</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>115800</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>88400</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>90800</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>74300</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>93200</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>99500</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>89900</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>228800</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>43600</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>129300</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>230000</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>343900</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>31300</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>40400</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>35800</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>28400</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>35400</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>30700</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>32400</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>28800</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>24100</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>32500</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>27600</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>22600</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>19900</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AL41" s="3">
         <v>28800</v>
       </c>
     </row>
-    <row r="42" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>7400</v>
+      </c>
+      <c r="E42" s="3">
         <v>10600</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>10200</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>21800</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>25300</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>23100</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>37200</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>37000</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>26700</v>
       </c>
-      <c r="L42" s="3">
-        <v>0</v>
-      </c>
       <c r="M42" s="3">
         <v>0</v>
       </c>
@@ -3999,115 +4089,121 @@
       <c r="AK42" s="3">
         <v>0</v>
       </c>
+      <c r="AL42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>124300</v>
+      </c>
+      <c r="E43" s="3">
         <v>125800</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>113800</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>120000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>118100</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>113300</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>113100</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>109600</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>103500</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>101300</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>86600</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>76900</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>69100</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>68400</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>45900</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>46700</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>49100</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>57200</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>57100</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>61600</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>49900</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>55300</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>50000</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>52000</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>55400</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>58100</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>57100</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>53100</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>57200</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>58300</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>53300</v>
-      </c>
-      <c r="AH43" s="3">
-        <v>52300</v>
       </c>
       <c r="AI43" s="3">
         <v>52300</v>
       </c>
       <c r="AJ43" s="3">
+        <v>52300</v>
+      </c>
+      <c r="AK43" s="3">
         <v>53100</v>
       </c>
-      <c r="AK43" s="3">
+      <c r="AL43" s="3">
         <v>50400</v>
       </c>
     </row>
-    <row r="44" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -4135,8 +4231,8 @@
       <c r="K44" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L44" s="3">
-        <v>0</v>
+      <c r="L44" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="M44" s="3">
         <v>0</v>
@@ -4213,145 +4309,151 @@
       <c r="AK44" s="3">
         <v>0</v>
       </c>
+      <c r="AL44" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="45" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>190000</v>
+      </c>
+      <c r="E45" s="3">
         <v>517800</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>520700</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>285900</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>371500</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>94800</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>111800</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>93500</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>113500</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>127000</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>142800</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>106000</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>96300</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>84800</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>39200</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>39500</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>42900</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>13000</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>39300</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>38200</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>36300</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>7500</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>10100</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>10300</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>14100</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>12800</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>17400</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>14200</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>20300</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>16400</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>12800</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>10200</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AJ45" s="3">
         <v>12800</v>
       </c>
-      <c r="AJ45" s="3">
+      <c r="AK45" s="3">
         <v>9700</v>
       </c>
-      <c r="AK45" s="3">
+      <c r="AL45" s="3">
         <v>10800</v>
       </c>
     </row>
-    <row r="46" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>376700</v>
+      </c>
+      <c r="E46" s="3">
         <v>787500</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>767800</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>586500</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>603800</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>272600</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>320300</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>375000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>296300</v>
       </c>
-      <c r="L46" s="3">
-        <v>0</v>
-      </c>
       <c r="M46" s="3">
         <v>0</v>
       </c>
@@ -4427,94 +4529,97 @@
       <c r="AK46" s="3">
         <v>0</v>
       </c>
+      <c r="AL46" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="47" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>20300</v>
+      </c>
+      <c r="E47" s="3">
         <v>19500</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>18800</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>10000</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>9600</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>9100</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>10200</v>
-      </c>
-      <c r="J47" s="3">
-        <v>10300</v>
       </c>
       <c r="K47" s="3">
         <v>10300</v>
       </c>
       <c r="L47" s="3">
+        <v>10300</v>
+      </c>
+      <c r="M47" s="3">
         <v>10400</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>10600</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>10400</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>136800</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>136900</v>
-      </c>
-      <c r="Q47" s="3">
-        <v>138000</v>
       </c>
       <c r="R47" s="3">
         <v>138000</v>
       </c>
       <c r="S47" s="3">
+        <v>138000</v>
+      </c>
+      <c r="T47" s="3">
         <v>13000</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>12800</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>13100</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>13200</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>12100</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>12600</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>12900</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>12700</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>13300</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>13500</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>13800</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>13900</v>
-      </c>
-      <c r="AE47" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AF47" s="3" t="s">
         <v>8</v>
@@ -4534,115 +4639,121 @@
       <c r="AK47" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AL47" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="48" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>6055300</v>
+      </c>
+      <c r="E48" s="3">
         <v>6046500</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>6091000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>6098600</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>6305700</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>6358300</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>6397300</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>6426100</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>6508700</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>6571400</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>6621600</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>6617800</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>6676800</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>6707500</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>2308000</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>2343700</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>2358900</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>2415900</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>2347400</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>2380500</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>2404000</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>2447400</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>2514100</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>2716800</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>2911300</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>2941200</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>3051700</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>3076800</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>3194200</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>3293300</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>3320300</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>3331800</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>3399700</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>3435400</v>
       </c>
-      <c r="AK48" s="3">
+      <c r="AL48" s="3">
         <v>3458300</v>
       </c>
     </row>
-    <row r="49" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -4670,12 +4781,12 @@
       <c r="K49" s="3">
         <v>0</v>
       </c>
-      <c r="L49" s="3" t="s">
+      <c r="L49" s="3">
+        <v>0</v>
+      </c>
+      <c r="M49" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M49" s="3">
-        <v>0</v>
-      </c>
       <c r="N49" s="3">
         <v>0</v>
       </c>
@@ -4725,31 +4836,34 @@
         <v>0</v>
       </c>
       <c r="AD49" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE49" s="3">
         <v>32300</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>39000</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>44000</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>47900</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>53000</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>59300</v>
       </c>
-      <c r="AJ49" s="3">
+      <c r="AK49" s="3">
         <v>65500</v>
       </c>
-      <c r="AK49" s="3">
+      <c r="AL49" s="3">
         <v>70000</v>
       </c>
     </row>
-    <row r="50" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4855,8 +4969,11 @@
       <c r="AK50" s="3">
         <v>0</v>
       </c>
+      <c r="AL50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4962,8 +5079,11 @@
       <c r="AK51" s="3">
         <v>0</v>
       </c>
+      <c r="AL51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -4991,86 +5111,89 @@
       <c r="K52" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L52" s="3">
+      <c r="L52" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M52" s="3">
         <v>416000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>450000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>483000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>520300</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>548600</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>78400</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>61400</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>62600</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>66100</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>71900</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>88300</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>91300</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>94600</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>86300</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>108700</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>180800</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>111100</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>115100</v>
-      </c>
-      <c r="AD52" s="3">
-        <v>79400</v>
       </c>
       <c r="AE52" s="3">
         <v>79400</v>
       </c>
       <c r="AF52" s="3">
+        <v>79400</v>
+      </c>
+      <c r="AG52" s="3">
         <v>76400</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>76600</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>75400</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>76700</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AK52" s="3">
         <v>72800</v>
       </c>
-      <c r="AK52" s="3">
+      <c r="AL52" s="3">
         <v>72700</v>
       </c>
     </row>
-    <row r="53" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5176,115 +5299,121 @@
       <c r="AK53" s="3">
         <v>0</v>
       </c>
+      <c r="AL53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>6682500</v>
+      </c>
+      <c r="E54" s="3">
         <v>7091800</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>7129700</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>6958900</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>7204500</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>6944100</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>7052500</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>7165100</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>7196900</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>7342000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>7399900</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>7384900</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>7573700</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>7639600</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>2708900</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>2719200</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>2755300</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>2608500</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>2658100</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>2811800</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>2937400</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>2648900</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>2713900</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>2936300</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>3203200</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>3172000</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>3285900</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>3302200</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>3418900</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>3512500</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>3543400</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>3550300</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>3623500</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>3656400</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AL54" s="3">
         <v>3690900</v>
       </c>
     </row>
-    <row r="55" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5322,8 +5451,9 @@
       <c r="AI55" s="3"/>
       <c r="AJ55" s="3"/>
       <c r="AK55" s="3"/>
+      <c r="AL55" s="3"/>
     </row>
-    <row r="56" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5361,145 +5491,149 @@
       <c r="AI56" s="3"/>
       <c r="AJ56" s="3"/>
       <c r="AK56" s="3"/>
+      <c r="AL56" s="3"/>
     </row>
-    <row r="57" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>158900</v>
+      </c>
+      <c r="E57" s="3">
         <v>198700</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>184000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>181800</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>162400</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>188000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>185700</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>164800</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>148100</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>207800</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>152000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>133800</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>124200</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>185000</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>85700</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>74400</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>72100</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>77500</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>88600</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>85700</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>109400</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>69800</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>77500</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>66600</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>61900</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>85900</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>98500</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>101200</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>102900</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>78500</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>101600</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>88500</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>88800</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AK57" s="3">
         <v>80700</v>
       </c>
-      <c r="AK57" s="3">
+      <c r="AL57" s="3">
         <v>93400</v>
       </c>
     </row>
-    <row r="58" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>83900</v>
+      </c>
+      <c r="E58" s="3">
         <v>440400</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>1300</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>122600</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>273500</v>
       </c>
-      <c r="H58" s="3">
-        <v>0</v>
-      </c>
       <c r="I58" s="3">
+        <v>0</v>
+      </c>
+      <c r="J58" s="3">
         <v>1300</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>124200</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>125100</v>
       </c>
-      <c r="L58" s="3">
-        <v>0</v>
-      </c>
       <c r="M58" s="3">
         <v>0</v>
       </c>
@@ -5575,85 +5709,88 @@
       <c r="AK58" s="3">
         <v>0</v>
       </c>
+      <c r="AL58" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="59" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>4200</v>
+      </c>
+      <c r="E59" s="3">
         <v>15100</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>3800</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>3900</v>
-      </c>
-      <c r="G59" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="H59" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="I59" s="3">
+      <c r="I59" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J59" s="3">
         <v>168000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>11400</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>14600</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>79300</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>78100</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>76000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>79200</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>70200</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>26200</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>26300</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>26400</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>26500</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>26600</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>26800</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>26900</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>27000</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>27100</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>27200</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>27300</v>
-      </c>
-      <c r="AB59" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AC59" s="3" t="s">
         <v>8</v>
@@ -5664,8 +5801,8 @@
       <c r="AE59" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AF59" s="3">
-        <v>0</v>
+      <c r="AF59" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AG59" s="3">
         <v>0</v>
@@ -5682,38 +5819,41 @@
       <c r="AK59" s="3">
         <v>0</v>
       </c>
+      <c r="AL59" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="60" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>247000</v>
+      </c>
+      <c r="E60" s="3">
         <v>654300</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>189100</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>308300</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>435900</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>188000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>354900</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>300400</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>287800</v>
       </c>
-      <c r="L60" s="3">
-        <v>0</v>
-      </c>
       <c r="M60" s="3">
         <v>0</v>
       </c>
@@ -5789,144 +5929,150 @@
       <c r="AK60" s="3">
         <v>0</v>
       </c>
+      <c r="AL60" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="61" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>2895200</v>
+      </c>
+      <c r="E61" s="3">
         <v>2857500</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>3311100</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>2969000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>2971700</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>2908200</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>2949700</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>2895300</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>2927500</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>3010300</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>3012900</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>3001200</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>3179100</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>3150800</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>1289000</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>1289400</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>1315200</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>1170800</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>1196100</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>1346300</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>1446500</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>1146600</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>1198600</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>1376600</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>1602600</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>1543300</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>1578300</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>1565400</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>1650500</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>1699200</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>1681700</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>1675100</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>1726900</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AK61" s="3">
         <v>1731100</v>
       </c>
-      <c r="AK61" s="3">
+      <c r="AL61" s="3">
         <v>1732300</v>
       </c>
     </row>
-    <row r="62" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>139800</v>
+      </c>
+      <c r="E62" s="3">
         <v>135800</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>151900</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>154400</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>164400</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>168700</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>12000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>176500</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>182900</v>
-      </c>
-      <c r="L62" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="M62" s="3" t="s">
         <v>8</v>
@@ -5937,8 +6083,8 @@
       <c r="O62" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P62" s="3">
-        <v>0</v>
+      <c r="P62" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="Q62" s="3">
         <v>0</v>
@@ -5967,14 +6113,14 @@
       <c r="Y62" s="3">
         <v>0</v>
       </c>
-      <c r="Z62" s="3" t="s">
+      <c r="Z62" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA62" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>2400</v>
-      </c>
-      <c r="AB62" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AC62" s="3" t="s">
         <v>8</v>
@@ -5985,8 +6131,8 @@
       <c r="AE62" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AF62" s="3">
-        <v>0</v>
+      <c r="AF62" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AG62" s="3">
         <v>0</v>
@@ -6003,8 +6149,11 @@
       <c r="AK62" s="3">
         <v>0</v>
       </c>
+      <c r="AL62" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="63" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6110,8 +6259,11 @@
       <c r="AK63" s="3">
         <v>0</v>
       </c>
+      <c r="AL63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6217,8 +6369,11 @@
       <c r="AK64" s="3">
         <v>0</v>
       </c>
+      <c r="AL64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6324,115 +6479,121 @@
       <c r="AK65" s="3">
         <v>0</v>
       </c>
+      <c r="AL65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>3311000</v>
+      </c>
+      <c r="E66" s="3">
         <v>3679700</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>3681500</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>3459300</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>3598100</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>3300200</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>3347800</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>3405900</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>3428400</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>3575500</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>3527100</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>3493700</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>3675100</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>3717500</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>1510000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>1505700</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>1523500</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>1377900</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>1416000</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>1563600</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>1684600</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>1359800</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>1411700</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>1583700</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>1816400</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>1759300</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>1807700</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>1802800</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>1893900</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>1947100</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>1958500</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>1940600</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>2004000</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>2012800</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AL66" s="3">
         <v>2046500</v>
       </c>
     </row>
-    <row r="67" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6470,8 +6631,9 @@
       <c r="AI67" s="3"/>
       <c r="AJ67" s="3"/>
       <c r="AK67" s="3"/>
+      <c r="AL67" s="3"/>
     </row>
-    <row r="68" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6577,8 +6739,11 @@
       <c r="AK68" s="3">
         <v>0</v>
       </c>
+      <c r="AL68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6684,8 +6849,11 @@
       <c r="AK69" s="3">
         <v>0</v>
       </c>
+      <c r="AL69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6791,8 +6959,11 @@
       <c r="AK70" s="3">
         <v>0</v>
       </c>
+      <c r="AL70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6898,115 +7069,121 @@
       <c r="AK71" s="3">
         <v>0</v>
       </c>
+      <c r="AL71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-1630900</v>
+      </c>
+      <c r="E72" s="3">
         <v>-1595300</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-1557800</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-1517400</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-1413800</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-1373100</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-1326200</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-1275600</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-1255000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-1207800</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-1105800</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-1052000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-1021300</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-962900</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-849500</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-827300</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-812700</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-824300</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-810800</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-801800</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-797000</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-770000</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>-758600</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>-712200</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>-683700</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>-662700</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>-604900</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>-582200</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>-554300</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>-509800</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>-485600</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>-459700</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>-444600</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>-419300</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AL72" s="3">
         <v>-397400</v>
       </c>
     </row>
-    <row r="73" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -7112,8 +7289,11 @@
       <c r="AK73" s="3">
         <v>0</v>
       </c>
+      <c r="AL73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7219,8 +7399,11 @@
       <c r="AK74" s="3">
         <v>0</v>
       </c>
+      <c r="AL74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -7326,115 +7509,121 @@
       <c r="AK75" s="3">
         <v>0</v>
       </c>
+      <c r="AL75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>3268000</v>
+      </c>
+      <c r="E76" s="3">
         <v>3312100</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>3349400</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>3421600</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>3530800</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>3568100</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>3635300</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>3692800</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>3706000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>3766500</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>3872800</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>3891100</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>3898600</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>3922000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>1198800</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>1213500</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>1231900</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>1230700</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>1242100</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>1248200</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>1252800</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>1289000</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>1302200</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>1352700</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>1386800</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>1412700</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>1478200</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>1499400</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>1525000</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>1565400</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>1584900</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>1609700</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>1619500</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>1643600</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3">
         <v>1644400</v>
       </c>
     </row>
-    <row r="77" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7540,227 +7729,236 @@
       <c r="AK77" s="3">
         <v>0</v>
       </c>
+      <c r="AL77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:38" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E80" s="2">
         <v>45657</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45565</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45473</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45382</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45291</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45199</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45107</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45016</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44926</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44834</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44742</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44651</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44561</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44469</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44377</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44286</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44196</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44104</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44012</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43921</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43830</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43738</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43646</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43555</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43465</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43373</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43281</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43190</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43100</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43008</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>42916</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>42825</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>42735</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>23700</v>
+      </c>
+      <c r="E81" s="3">
         <v>21800</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>16700</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-48600</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>14200</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>8000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>2100</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>32100</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>5400</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-1100</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-7800</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>13100</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-16800</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-98200</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-7000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-200</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>24600</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-6800</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-4600</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-4800</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-100</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>15300</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-19700</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-1800</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>5700</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>-31200</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>3900</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>-1400</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>-17900</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>2300</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>-600</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>10200</v>
       </c>
-      <c r="AI81" s="3">
-        <v>0</v>
-      </c>
       <c r="AJ81" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK81" s="3">
         <v>3400</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>-1700</v>
       </c>
     </row>
-    <row r="82" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7798,115 +7996,119 @@
       <c r="AI82" s="3"/>
       <c r="AJ82" s="3"/>
       <c r="AK82" s="3"/>
+      <c r="AL82" s="3"/>
     </row>
-    <row r="83" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>79100</v>
+      </c>
+      <c r="E83" s="3">
         <v>76300</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>75900</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>77700</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>79600</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>78000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>79200</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>78300</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>79800</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>113700</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>116600</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>119300</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>123300</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>110600</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>30800</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>30500</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>31200</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>32300</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>34400</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>32000</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>32100</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>31400</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>32600</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>35600</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>35300</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>38000</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>37500</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>41300</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>39200</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>41400</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>43500</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>43400</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>46400</v>
       </c>
-      <c r="AJ83" s="3">
+      <c r="AK83" s="3">
         <v>43700</v>
       </c>
-      <c r="AK83" s="3">
+      <c r="AL83" s="3">
         <v>47700</v>
       </c>
     </row>
-    <row r="84" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -8012,8 +8214,11 @@
       <c r="AK84" s="3">
         <v>0</v>
       </c>
+      <c r="AL84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -8119,8 +8324,11 @@
       <c r="AK85" s="3">
         <v>0</v>
       </c>
+      <c r="AL85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -8226,8 +8434,11 @@
       <c r="AK86" s="3">
         <v>0</v>
       </c>
+      <c r="AL86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -8333,8 +8544,11 @@
       <c r="AK87" s="3">
         <v>0</v>
       </c>
+      <c r="AL87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8440,115 +8654,121 @@
       <c r="AK88" s="3">
         <v>0</v>
       </c>
+      <c r="AL88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>74100</v>
+      </c>
+      <c r="E89" s="3">
         <v>111000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>112400</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>142100</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>53600</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>103500</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>110800</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>116800</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>63600</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>116900</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>108100</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>104700</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>49600</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-3500</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>36400</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>36100</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>31300</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>9800</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>35900</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>28000</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>21900</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>31800</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>36500</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>37300</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>32300</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>35400</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>37000</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>45800</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>36300</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>30800</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>42700</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>44900</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>36200</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>34200</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AL89" s="3">
         <v>39800</v>
       </c>
     </row>
-    <row r="90" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -8586,115 +8806,119 @@
       <c r="AI90" s="3"/>
       <c r="AJ90" s="3"/>
       <c r="AK90" s="3"/>
+      <c r="AL90" s="3"/>
     </row>
-    <row r="91" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-34400</v>
+      </c>
+      <c r="E91" s="3">
         <v>-39000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-34800</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-38900</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-28200</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-43900</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-30900</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-28600</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-39100</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-52000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-47800</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-35000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-23800</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-20400</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-15700</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-13300</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-7900</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-7600</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-8200</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-9200</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-13200</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-15700</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-12400</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-13700</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-11500</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-12000</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-12700</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-16500</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-18100</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-10800</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-24800</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-11200</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-47700</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AK91" s="3">
         <v>-26000</v>
       </c>
-      <c r="AK91" s="3">
+      <c r="AL91" s="3">
         <v>-24100</v>
       </c>
     </row>
-    <row r="92" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8800,8 +9024,11 @@
       <c r="AK92" s="3">
         <v>0</v>
       </c>
+      <c r="AL92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8907,115 +9134,121 @@
       <c r="AK93" s="3">
         <v>0</v>
       </c>
+      <c r="AL93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>227800</v>
+      </c>
+      <c r="E94" s="3">
         <v>-29500</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-314900</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>134700</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-289300</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-26200</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-63500</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>49500</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-41500</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-31500</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-82300</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>130800</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-62200</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>18000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-9600</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-133300</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>33900</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-64900</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>4700</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-13500</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-7100</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>52800</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>166900</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>226600</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-29700</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>44700</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-14500</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>71800</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>46400</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-23200</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-16500</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>38100</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>1400</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>-15600</v>
       </c>
-      <c r="AK94" s="3">
+      <c r="AL94" s="3">
         <v>-22200</v>
       </c>
     </row>
-    <row r="95" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -9053,16 +9286,17 @@
       <c r="AI95" s="3"/>
       <c r="AJ95" s="3"/>
       <c r="AK95" s="3"/>
+      <c r="AL95" s="3"/>
     </row>
-    <row r="96" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>59300</v>
+      </c>
+      <c r="E96" s="3">
         <v>57100</v>
-      </c>
-      <c r="E96" s="3">
-        <v>54900</v>
       </c>
       <c r="F96" s="3">
         <v>54900</v>
@@ -9071,55 +9305,55 @@
         <v>54900</v>
       </c>
       <c r="H96" s="3">
-        <v>52700</v>
+        <v>54900</v>
       </c>
       <c r="I96" s="3">
         <v>52700</v>
       </c>
       <c r="J96" s="3">
-        <v>52600</v>
+        <v>52700</v>
       </c>
       <c r="K96" s="3">
         <v>52600</v>
       </c>
       <c r="L96" s="3">
+        <v>52600</v>
+      </c>
+      <c r="M96" s="3">
         <v>-48200</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>-46000</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>-43800</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>-41600</v>
-      </c>
-      <c r="P96" s="3">
-        <v>-15200</v>
       </c>
       <c r="Q96" s="3">
         <v>-15200</v>
       </c>
       <c r="R96" s="3">
+        <v>-15200</v>
+      </c>
+      <c r="S96" s="3">
         <v>-14400</v>
       </c>
-      <c r="S96" s="3">
+      <c r="T96" s="3">
         <v>-13000</v>
       </c>
-      <c r="T96" s="3">
+      <c r="U96" s="3">
         <v>-6700</v>
       </c>
-      <c r="U96" s="3">
+      <c r="V96" s="3">
         <v>-4400</v>
       </c>
-      <c r="V96" s="3">
+      <c r="W96" s="3">
         <v>-26700</v>
       </c>
-      <c r="W96" s="3">
+      <c r="X96" s="3">
         <v>-300</v>
-      </c>
-      <c r="X96" s="3">
-        <v>-26700</v>
       </c>
       <c r="Y96" s="3">
         <v>-26700</v>
@@ -9128,10 +9362,10 @@
         <v>-26700</v>
       </c>
       <c r="AA96" s="3">
+        <v>-26700</v>
+      </c>
+      <c r="AB96" s="3">
         <v>-53300</v>
-      </c>
-      <c r="AB96" s="3">
-        <v>-26600</v>
       </c>
       <c r="AC96" s="3">
         <v>-26600</v>
@@ -9140,10 +9374,10 @@
         <v>-26600</v>
       </c>
       <c r="AE96" s="3">
+        <v>-26600</v>
+      </c>
+      <c r="AF96" s="3">
         <v>-26500</v>
-      </c>
-      <c r="AF96" s="3">
-        <v>-25300</v>
       </c>
       <c r="AG96" s="3">
         <v>-25300</v>
@@ -9155,13 +9389,16 @@
         <v>-25300</v>
       </c>
       <c r="AJ96" s="3">
-        <v>-24000</v>
+        <v>-25300</v>
       </c>
       <c r="AK96" s="3">
         <v>-24000</v>
       </c>
+      <c r="AL96" s="3">
+        <v>-24000</v>
+      </c>
     </row>
-    <row r="97" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -9267,8 +9504,11 @@
       <c r="AK97" s="3">
         <v>0</v>
       </c>
+      <c r="AL97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -9374,8 +9614,11 @@
       <c r="AK98" s="3">
         <v>0</v>
       </c>
+      <c r="AL98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -9481,115 +9724,121 @@
       <c r="AK99" s="3">
         <v>0</v>
       </c>
+      <c r="AL99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-380300</v>
+      </c>
+      <c r="E100" s="3">
         <v>-71200</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>166800</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-206800</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>283300</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-94100</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-123900</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-84100</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-91400</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-59900</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-28400</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-218600</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-5600</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-18000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-17100</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-41200</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>120800</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-35600</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-155100</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-128300</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>298000</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-81800</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-212900</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-256400</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>3800</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-75600</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-24800</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-112800</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-76300</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-16800</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-19700</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>-78700</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>-34200</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>-27600</v>
       </c>
-      <c r="AK100" s="3">
+      <c r="AL100" s="3">
         <v>-26600</v>
       </c>
     </row>
-    <row r="101" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -9617,8 +9866,8 @@
       <c r="K101" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L101" s="3">
-        <v>0</v>
+      <c r="L101" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="M101" s="3">
         <v>0</v>
@@ -9695,111 +9944,117 @@
       <c r="AK101" s="3">
         <v>0</v>
       </c>
+      <c r="AL101" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="102" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-78400</v>
+      </c>
+      <c r="E102" s="3">
         <v>10300</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-35700</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>70000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>47500</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-16900</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-76600</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>82300</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-69300</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>25500</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-2600</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>17000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-18200</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-3400</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>9700</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-138500</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>185900</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-90700</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-114500</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-113800</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>312800</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>2800</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-9500</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>7600</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>6400</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>4500</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-2300</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>4800</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>6400</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>-8400</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>4800</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>4400</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>3300</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>-8900</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AL102" s="3">
         <v>-9100</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/KRG_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/KRG_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="187" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="228" uniqueCount="92">
   <si>
     <t>KRG</t>
   </si>
@@ -656,492 +656,505 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AL102"/>
+  <dimension ref="A5:AM102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="38" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="39" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="35" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="39" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="40" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:39" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E7" s="2">
         <v>45747</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45657</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45565</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45473</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45382</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45291</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45199</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45107</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45016</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44926</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44834</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44742</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44651</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44561</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44469</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44377</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44286</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44196</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44104</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44012</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43921</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43830</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43738</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43646</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43555</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43465</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43373</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43281</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43190</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43100</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>43008</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>42916</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>42825</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>42735</v>
       </c>
-      <c r="AL7" s="2">
+      <c r="AM7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D8" s="3">
+      <c r="D8" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E8" s="3">
         <v>221800</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>214700</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>207300</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>212400</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>207400</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>200300</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>207200</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>208800</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>206800</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>204700</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>200300</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>202600</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>194400</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>163000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>71500</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>69500</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>69400</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>68400</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>65100</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>63300</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>69900</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>75200</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>74900</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>81500</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>83500</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>86900</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>85700</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>91700</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>89800</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>88900</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>87100</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>92600</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>90100</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AL8" s="3">
         <v>88900</v>
       </c>
-      <c r="AL8" s="3">
+      <c r="AM8" s="3">
         <v>89100</v>
       </c>
     </row>
-    <row r="9" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D9" s="3">
+      <c r="D9" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E9" s="3">
         <v>57600</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>54800</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>53000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>55100</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>54600</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>47900</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>54100</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>53900</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>54500</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>53800</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>51200</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>54000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>52800</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>47500</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>19100</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>18800</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>19700</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>19900</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>19700</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>17600</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>19700</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>20600</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>20700</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>21400</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>21600</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>23200</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>23300</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>23000</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>23200</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>23500</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>22700</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>23400</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AK9" s="3">
         <v>23300</v>
       </c>
-      <c r="AK9" s="3">
+      <c r="AL9" s="3">
         <v>23000</v>
       </c>
-      <c r="AL9" s="3">
+      <c r="AM9" s="3">
         <v>22600</v>
       </c>
     </row>
-    <row r="10" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="D10" s="3">
+      <c r="D10" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E10" s="3">
         <v>164200</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>159900</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>154300</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>157400</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>152800</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>152400</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>153100</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>154800</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>152300</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>150900</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>149100</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>148600</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>141600</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>115500</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>52400</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>50700</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>49700</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>48500</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>45400</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>45700</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>50200</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>54600</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>54200</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>60100</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>61900</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>63700</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>62400</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>68700</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>66600</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>65400</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>64400</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>69200</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AK10" s="3">
         <v>66800</v>
       </c>
-      <c r="AK10" s="3">
+      <c r="AL10" s="3">
         <v>65900</v>
       </c>
-      <c r="AL10" s="3">
+      <c r="AM10" s="3">
         <v>66500</v>
       </c>
     </row>
-    <row r="11" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1180,8 +1193,9 @@
       <c r="AJ11" s="3"/>
       <c r="AK11" s="3"/>
       <c r="AL11" s="3"/>
+      <c r="AM11" s="3"/>
     </row>
-    <row r="12" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1290,8 +1304,11 @@
       <c r="AL12" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AM12" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="13" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1400,64 +1417,67 @@
       <c r="AL13" s="3">
         <v>0</v>
       </c>
+      <c r="AM13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3">
+      <c r="D14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E14" s="3">
         <v>-4100</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>-5400</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>-5000</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>63100</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>-5700</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>-500</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>5500</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>-28700</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>-400</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>-100</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>100</v>
       </c>
-      <c r="O14" s="3">
-        <v>0</v>
-      </c>
       <c r="P14" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q14" s="3">
         <v>900</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>76600</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>9200</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>800</v>
       </c>
-      <c r="T14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="U14" s="3">
-        <v>0</v>
+      <c r="U14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="V14" s="3">
         <v>0</v>
@@ -1469,32 +1489,32 @@
         <v>0</v>
       </c>
       <c r="Y14" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z14" s="3">
         <v>2000</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AA14" s="3">
         <v>15600</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AB14" s="3">
         <v>27700</v>
       </c>
-      <c r="AB14" s="3">
+      <c r="AC14" s="3">
         <v>4100</v>
       </c>
-      <c r="AC14" s="3">
+      <c r="AD14" s="3">
         <v>31500</v>
       </c>
-      <c r="AD14" s="3">
-        <v>0</v>
-      </c>
       <c r="AE14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF14" s="3">
         <v>14800</v>
       </c>
-      <c r="AF14" s="3">
+      <c r="AG14" s="3">
         <v>24100</v>
       </c>
-      <c r="AG14" s="3">
-        <v>0</v>
-      </c>
       <c r="AH14" s="3">
         <v>0</v>
       </c>
@@ -1502,126 +1522,132 @@
         <v>0</v>
       </c>
       <c r="AJ14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK14" s="3">
         <v>7400</v>
       </c>
-      <c r="AK14" s="3">
+      <c r="AL14" s="3">
         <v>2800</v>
       </c>
-      <c r="AL14" s="3" t="s">
+      <c r="AM14" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="15" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>0</v>
+      </c>
+      <c r="E15" s="3">
         <v>98200</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>97000</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>96700</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>99300</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>100400</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>102900</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>105900</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>109500</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>108100</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>112700</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>115800</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>119800</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>121500</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>109800</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>30200</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>29800</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>30600</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>31800</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>34000</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>31400</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>31500</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="Z15" s="3">
         <v>30800</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AA15" s="3">
         <v>32000</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AB15" s="3">
         <v>34700</v>
       </c>
-      <c r="AB15" s="3">
+      <c r="AC15" s="3">
         <v>34600</v>
       </c>
-      <c r="AC15" s="3">
+      <c r="AD15" s="3">
         <v>36300</v>
       </c>
-      <c r="AD15" s="3">
+      <c r="AE15" s="3">
         <v>36900</v>
       </c>
-      <c r="AE15" s="3">
+      <c r="AF15" s="3">
         <v>40500</v>
       </c>
-      <c r="AF15" s="3">
+      <c r="AG15" s="3">
         <v>38600</v>
       </c>
-      <c r="AG15" s="3">
+      <c r="AH15" s="3">
         <v>40800</v>
       </c>
-      <c r="AH15" s="3">
+      <c r="AI15" s="3">
         <v>42800</v>
       </c>
-      <c r="AI15" s="3">
+      <c r="AJ15" s="3">
         <v>42700</v>
       </c>
-      <c r="AJ15" s="3">
+      <c r="AK15" s="3">
         <v>45800</v>
       </c>
-      <c r="AK15" s="3">
+      <c r="AL15" s="3">
         <v>42900</v>
       </c>
-      <c r="AL15" s="3">
+      <c r="AM15" s="3">
         <v>45500</v>
       </c>
     </row>
-    <row r="16" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:39" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1657,228 +1683,235 @@
       <c r="AJ16" s="3"/>
       <c r="AK16" s="3"/>
       <c r="AL16" s="3"/>
+      <c r="AM16" s="3"/>
     </row>
-    <row r="17" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="D17" s="3">
+      <c r="D17" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E17" s="3">
         <v>168100</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>165400</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>162900</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>167300</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>167800</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>165100</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>173900</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>177900</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>176000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>179400</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>182000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>163600</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>185400</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>240600</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>65500</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>57400</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>31400</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>62700</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>56900</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>54900</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>57100</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>47000</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>80700</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>66700</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>60500</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>92500</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>65000</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>83800</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>91800</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>54400</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>70900</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>71600</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>82000</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>71300</v>
       </c>
-      <c r="AL17" s="3">
+      <c r="AM17" s="3">
         <v>73200</v>
       </c>
     </row>
-    <row r="18" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D18" s="3">
+      <c r="D18" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E18" s="3">
         <v>53700</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>49300</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>44400</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>45100</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>39700</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>35200</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>33300</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>30900</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>30800</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>25300</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>18300</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>39000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>9000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-77600</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>6000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>12100</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>38000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>5700</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>8200</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>8400</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>12800</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>28200</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>-5800</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>14800</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>23000</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>-5600</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>20700</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>7900</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>-2000</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>34500</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>16200</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>21000</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>8100</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3">
         <v>17600</v>
       </c>
-      <c r="AL18" s="3">
+      <c r="AM18" s="3">
         <v>15900</v>
       </c>
     </row>
-    <row r="19" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1917,73 +1950,74 @@
       <c r="AJ19" s="3"/>
       <c r="AK19" s="3"/>
       <c r="AL19" s="3"/>
+      <c r="AM19" s="3"/>
     </row>
-    <row r="20" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D20" s="3">
+      <c r="D20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E20" s="3">
         <v>600</v>
       </c>
-      <c r="E20" s="3">
-        <v>0</v>
-      </c>
       <c r="F20" s="3">
+        <v>0</v>
+      </c>
+      <c r="G20" s="3">
         <v>600</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>200</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>400</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-200</v>
       </c>
-      <c r="J20" s="3">
-        <v>0</v>
-      </c>
       <c r="K20" s="3">
+        <v>0</v>
+      </c>
+      <c r="L20" s="3">
         <v>-100</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>200</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>400</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>100</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-200</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-100</v>
-      </c>
-      <c r="Q20" s="3">
-        <v>100</v>
       </c>
       <c r="R20" s="3">
         <v>100</v>
       </c>
       <c r="S20" s="3">
+        <v>100</v>
+      </c>
+      <c r="T20" s="3">
         <v>300</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-200</v>
       </c>
-      <c r="U20" s="3">
-        <v>0</v>
-      </c>
       <c r="V20" s="3">
         <v>0</v>
       </c>
       <c r="W20" s="3">
+        <v>0</v>
+      </c>
+      <c r="X20" s="3">
         <v>400</v>
-      </c>
-      <c r="X20" s="3">
-        <v>-100</v>
       </c>
       <c r="Y20" s="3">
         <v>-100</v>
@@ -1992,248 +2026,254 @@
         <v>-100</v>
       </c>
       <c r="AA20" s="3">
-        <v>-200</v>
+        <v>-100</v>
       </c>
       <c r="AB20" s="3">
         <v>-200</v>
       </c>
       <c r="AC20" s="3">
+        <v>-200</v>
+      </c>
+      <c r="AD20" s="3">
         <v>-8300</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>-300</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>7700</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>300</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>-15200</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>-100</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>6300</v>
       </c>
-      <c r="AJ20" s="3">
+      <c r="AK20" s="3">
         <v>8700</v>
       </c>
-      <c r="AK20" s="3">
+      <c r="AL20" s="3">
         <v>4000</v>
       </c>
-      <c r="AL20" s="3">
+      <c r="AM20" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>0</v>
+      </c>
+      <c r="E21" s="3">
         <v>151300</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>146400</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>140400</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>144200</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>139600</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>138300</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>139200</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>140400</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>138600</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>139500</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>135000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>158200</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>132200</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>33100</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>37000</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>42900</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>69000</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>38000</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>42600</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>40700</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>44800</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>59500</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>26800</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>50200</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>58100</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>24100</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>57900</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>57000</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>37500</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>60600</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>59600</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>70700</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>63200</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AL21" s="3">
         <v>65300</v>
       </c>
-      <c r="AL21" s="3">
+      <c r="AM21" s="3">
         <v>63500</v>
       </c>
     </row>
-    <row r="22" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D22" s="3">
+      <c r="D22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E22" s="3">
         <v>33000</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>32700</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>31600</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>31000</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>30400</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>27200</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>25500</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>27200</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>25400</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>26800</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>26200</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>25700</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>25500</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>23100</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>12900</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>12300</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>12200</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>12300</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>12600</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>13300</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>12300</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>12400</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>14300</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>16100</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>16500</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>17600</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>16100</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>16700</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>16300</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AH22" s="3">
         <v>16500</v>
-      </c>
-      <c r="AH22" s="3">
-        <v>16400</v>
       </c>
       <c r="AI22" s="3">
         <v>16400</v>
@@ -2242,170 +2282,176 @@
         <v>16400</v>
       </c>
       <c r="AK22" s="3">
+        <v>16400</v>
+      </c>
+      <c r="AL22" s="3">
         <v>17600</v>
       </c>
-      <c r="AL22" s="3">
+      <c r="AM22" s="3">
         <v>17100</v>
       </c>
     </row>
-    <row r="23" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="D23" s="3">
+      <c r="D23" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E23" s="3">
         <v>24300</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>22000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>17100</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-49200</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>14600</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>8600</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>2200</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>32500</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>5500</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-1100</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-7900</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>13100</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-16600</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-100500</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-6700</v>
       </c>
-      <c r="S23" s="3">
-        <v>0</v>
-      </c>
       <c r="T23" s="3">
+        <v>0</v>
+      </c>
+      <c r="U23" s="3">
         <v>25600</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-6600</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-4400</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-4600</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>400</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>15700</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>-20100</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>-1500</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>6300</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>-31600</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>4300</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>-1100</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>-18000</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>2800</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>-200</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>10900</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>400</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>4000</v>
       </c>
-      <c r="AL23" s="3">
+      <c r="AM23" s="3">
         <v>-1200</v>
       </c>
     </row>
-    <row r="24" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D24" s="3">
-        <v>0</v>
+      <c r="D24" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="E24" s="3">
+        <v>0</v>
+      </c>
+      <c r="F24" s="3">
         <v>-200</v>
       </c>
-      <c r="F24" s="3">
-        <v>0</v>
-      </c>
       <c r="G24" s="3">
+        <v>0</v>
+      </c>
+      <c r="H24" s="3">
         <v>100</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>200</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>400</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>100</v>
       </c>
-      <c r="K24" s="3">
-        <v>0</v>
-      </c>
       <c r="L24" s="3">
         <v>0</v>
       </c>
       <c r="M24" s="3">
+        <v>0</v>
+      </c>
+      <c r="N24" s="3">
         <v>300</v>
       </c>
-      <c r="N24" s="3">
-        <v>0</v>
-      </c>
       <c r="O24" s="3">
+        <v>0</v>
+      </c>
+      <c r="P24" s="3">
         <v>-200</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>-100</v>
       </c>
-      <c r="Q24" s="3">
-        <v>0</v>
-      </c>
       <c r="R24" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="S24" s="3">
         <v>-100</v>
@@ -2414,7 +2460,7 @@
         <v>-100</v>
       </c>
       <c r="U24" s="3">
-        <v>-200</v>
+        <v>-100</v>
       </c>
       <c r="V24" s="3">
         <v>-200</v>
@@ -2423,16 +2469,16 @@
         <v>-200</v>
       </c>
       <c r="X24" s="3">
-        <v>-100</v>
+        <v>-200</v>
       </c>
       <c r="Y24" s="3">
         <v>-100</v>
       </c>
       <c r="Z24" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="AA24" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="AB24" s="3">
         <v>-100</v>
@@ -2441,7 +2487,7 @@
         <v>-100</v>
       </c>
       <c r="AD24" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="AE24" s="3">
         <v>0</v>
@@ -2462,13 +2508,16 @@
         <v>0</v>
       </c>
       <c r="AK24" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL24" s="3">
         <v>100</v>
       </c>
-      <c r="AL24" s="3">
+      <c r="AM24" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2577,228 +2626,237 @@
       <c r="AL25" s="3">
         <v>0</v>
       </c>
+      <c r="AM25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="D26" s="3">
+      <c r="D26" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E26" s="3">
         <v>24300</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>22200</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>17100</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-49300</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>14400</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>8200</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>2200</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>32500</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>5600</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-1400</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-7900</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>13300</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-16500</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-100500</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-6600</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>100</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>25700</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-6400</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-4200</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-4400</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>500</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>15800</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>-20100</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>-1500</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>6400</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>-31400</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>4300</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>-1100</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>-18000</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>2800</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>-200</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>10900</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>400</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>3900</v>
       </c>
-      <c r="AL26" s="3">
+      <c r="AM26" s="3">
         <v>-1300</v>
       </c>
     </row>
-    <row r="27" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="D27" s="3">
+      <c r="D27" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E27" s="3">
         <v>23700</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>21800</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>16700</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-48600</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>14200</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>8000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>2100</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>32100</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>5400</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-1100</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-7800</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>13100</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-16800</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-98200</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-7000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-200</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>24600</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-6800</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-4600</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-4800</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-100</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>15300</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>-19700</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>-1800</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>5700</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>-31200</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>3900</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>-1400</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>-17900</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>2300</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>-600</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>10200</v>
       </c>
-      <c r="AJ27" s="3">
-        <v>0</v>
-      </c>
       <c r="AK27" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL27" s="3">
         <v>3400</v>
       </c>
-      <c r="AL27" s="3">
+      <c r="AM27" s="3">
         <v>-1700</v>
       </c>
     </row>
-    <row r="28" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2907,8 +2965,11 @@
       <c r="AL28" s="3">
         <v>0</v>
       </c>
+      <c r="AM28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2999,8 +3060,8 @@
       <c r="AF29" s="3">
         <v>0</v>
       </c>
-      <c r="AG29" s="3" t="s">
-        <v>8</v>
+      <c r="AG29" s="3">
+        <v>0</v>
       </c>
       <c r="AH29" s="3" t="s">
         <v>8</v>
@@ -3011,14 +3072,17 @@
       <c r="AJ29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AK29" s="3">
-        <v>0</v>
-      </c>
-      <c r="AL29" s="3" t="s">
+      <c r="AK29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AL29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM29" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="30" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3127,8 +3191,11 @@
       <c r="AL30" s="3">
         <v>0</v>
       </c>
+      <c r="AM30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3237,73 +3304,76 @@
       <c r="AL31" s="3">
         <v>0</v>
       </c>
+      <c r="AM31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D32" s="3">
+      <c r="D32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E32" s="3">
         <v>-600</v>
       </c>
-      <c r="E32" s="3">
-        <v>0</v>
-      </c>
       <c r="F32" s="3">
+        <v>0</v>
+      </c>
+      <c r="G32" s="3">
         <v>-600</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-200</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-400</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>200</v>
       </c>
-      <c r="J32" s="3">
-        <v>0</v>
-      </c>
       <c r="K32" s="3">
+        <v>0</v>
+      </c>
+      <c r="L32" s="3">
         <v>100</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-200</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-400</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-100</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>200</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>100</v>
-      </c>
-      <c r="Q32" s="3">
-        <v>-100</v>
       </c>
       <c r="R32" s="3">
         <v>-100</v>
       </c>
       <c r="S32" s="3">
+        <v>-100</v>
+      </c>
+      <c r="T32" s="3">
         <v>-300</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>200</v>
       </c>
-      <c r="U32" s="3">
-        <v>0</v>
-      </c>
       <c r="V32" s="3">
         <v>0</v>
       </c>
       <c r="W32" s="3">
+        <v>0</v>
+      </c>
+      <c r="X32" s="3">
         <v>-400</v>
-      </c>
-      <c r="X32" s="3">
-        <v>100</v>
       </c>
       <c r="Y32" s="3">
         <v>100</v>
@@ -3312,153 +3382,159 @@
         <v>100</v>
       </c>
       <c r="AA32" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="AB32" s="3">
         <v>200</v>
       </c>
       <c r="AC32" s="3">
+        <v>200</v>
+      </c>
+      <c r="AD32" s="3">
         <v>8300</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>300</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>-7700</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>-300</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>15200</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>100</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>-6300</v>
       </c>
-      <c r="AJ32" s="3">
+      <c r="AK32" s="3">
         <v>-8700</v>
       </c>
-      <c r="AK32" s="3">
+      <c r="AL32" s="3">
         <v>-4000</v>
       </c>
-      <c r="AL32" s="3">
+      <c r="AM32" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D33" s="3">
+      <c r="D33" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E33" s="3">
         <v>23700</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>21800</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>16700</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-48600</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>14200</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>8000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>2100</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>32100</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>5400</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-1100</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-7800</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>13100</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-16800</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-98200</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-7000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-200</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>24600</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-6800</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-4600</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-4800</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-100</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>15300</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-19700</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>-1800</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>5700</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>-31200</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>3900</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>-1400</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>-17900</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>2300</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>-600</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>10200</v>
       </c>
-      <c r="AJ33" s="3">
-        <v>0</v>
-      </c>
       <c r="AK33" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL33" s="3">
         <v>3400</v>
       </c>
-      <c r="AL33" s="3">
+      <c r="AM33" s="3">
         <v>-1700</v>
       </c>
     </row>
-    <row r="34" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3567,233 +3643,242 @@
       <c r="AL34" s="3">
         <v>0</v>
       </c>
+      <c r="AM34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="D35" s="3">
+      <c r="D35" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E35" s="3">
         <v>23700</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>21800</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>16700</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-48600</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>14200</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>8000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>2100</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>32100</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>5400</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-1100</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-7800</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>13100</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-16800</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-98200</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-7000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-200</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>24600</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-6800</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-4600</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-4800</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-100</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>15300</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-19700</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>-1800</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>5700</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>-31200</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>3900</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>-1400</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>-17900</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>2300</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>-600</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>10200</v>
       </c>
-      <c r="AJ35" s="3">
-        <v>0</v>
-      </c>
       <c r="AK35" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL35" s="3">
         <v>3400</v>
       </c>
-      <c r="AL35" s="3">
+      <c r="AM35" s="3">
         <v>-1700</v>
       </c>
     </row>
-    <row r="37" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:39" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E38" s="2">
         <v>45747</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45657</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45565</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45473</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45382</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45291</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45199</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45107</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45016</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44926</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44834</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44742</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44651</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44561</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44469</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44377</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44286</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44196</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44104</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44012</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43921</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43830</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43738</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43646</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43555</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43465</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43373</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43281</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43190</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43100</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>43008</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>42916</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>42825</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>42735</v>
       </c>
-      <c r="AL38" s="2">
+      <c r="AM38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3832,8 +3917,9 @@
       <c r="AJ39" s="3"/>
       <c r="AK39" s="3"/>
       <c r="AL39" s="3"/>
+      <c r="AM39" s="3"/>
     </row>
-    <row r="40" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3872,151 +3958,155 @@
       <c r="AJ40" s="3"/>
       <c r="AK40" s="3"/>
       <c r="AL40" s="3"/>
+      <c r="AM40" s="3"/>
     </row>
-    <row r="41" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="D41" s="3">
+      <c r="D41" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E41" s="3">
         <v>49100</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>128100</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>117500</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>153800</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>83600</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>36400</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>52300</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>129300</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>43700</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>115800</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>88400</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>90800</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>74300</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>93200</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>99500</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>89900</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>228800</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>43600</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>129300</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>230000</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>343900</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>31300</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>40400</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>35800</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>28400</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>35400</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>30700</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>32400</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>28800</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>24100</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>32500</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>27600</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>22600</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AL41" s="3">
         <v>19900</v>
       </c>
-      <c r="AL41" s="3">
+      <c r="AM41" s="3">
         <v>28800</v>
       </c>
     </row>
-    <row r="42" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>0</v>
+      </c>
+      <c r="E42" s="3">
         <v>7400</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>10600</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>10200</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>21800</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>25300</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>23100</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>37200</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>37000</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>26700</v>
       </c>
-      <c r="M42" s="3">
-        <v>0</v>
-      </c>
       <c r="N42" s="3">
         <v>0</v>
       </c>
@@ -4092,118 +4182,124 @@
       <c r="AL42" s="3">
         <v>0</v>
       </c>
+      <c r="AM42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="D43" s="3">
+      <c r="D43" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E43" s="3">
         <v>124300</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>125800</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>113800</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>120000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>118100</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>113300</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>113100</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>109600</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>103500</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>101300</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>86600</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>76900</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>69100</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>68400</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>45900</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>46700</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>49100</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>57200</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>57100</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>61600</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>49900</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>55300</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>50000</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>52000</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>55400</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>58100</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>57100</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>53100</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>57200</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>58300</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>53300</v>
-      </c>
-      <c r="AI43" s="3">
-        <v>52300</v>
       </c>
       <c r="AJ43" s="3">
         <v>52300</v>
       </c>
       <c r="AK43" s="3">
+        <v>52300</v>
+      </c>
+      <c r="AL43" s="3">
         <v>53100</v>
       </c>
-      <c r="AL43" s="3">
+      <c r="AM43" s="3">
         <v>50400</v>
       </c>
     </row>
-    <row r="44" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -4234,8 +4330,8 @@
       <c r="L44" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M44" s="3">
-        <v>0</v>
+      <c r="M44" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="N44" s="3">
         <v>0</v>
@@ -4312,151 +4408,157 @@
       <c r="AL44" s="3">
         <v>0</v>
       </c>
+      <c r="AM44" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="45" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D45" s="3">
+      <c r="D45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E45" s="3">
         <v>190000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>517800</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>520700</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>285900</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>371500</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>94800</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>111800</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>93500</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>113500</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>127000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>142800</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>106000</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>96300</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>84800</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>39200</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>39500</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>42900</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>13000</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>39300</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>38200</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>36300</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>7500</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>10100</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>10300</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>14100</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>12800</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>17400</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>14200</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>20300</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>16400</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>12800</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AJ45" s="3">
         <v>10200</v>
       </c>
-      <c r="AJ45" s="3">
+      <c r="AK45" s="3">
         <v>12800</v>
       </c>
-      <c r="AK45" s="3">
+      <c r="AL45" s="3">
         <v>9700</v>
       </c>
-      <c r="AL45" s="3">
+      <c r="AM45" s="3">
         <v>10800</v>
       </c>
     </row>
-    <row r="46" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="D46" s="3">
+      <c r="D46" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E46" s="3">
         <v>376700</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>787500</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>767800</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>586500</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>603800</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>272600</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>320300</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>375000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>296300</v>
       </c>
-      <c r="M46" s="3">
-        <v>0</v>
-      </c>
       <c r="N46" s="3">
         <v>0</v>
       </c>
@@ -4532,98 +4634,101 @@
       <c r="AL46" s="3">
         <v>0</v>
       </c>
+      <c r="AM46" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="47" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D47" s="3">
+      <c r="D47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E47" s="3">
         <v>20300</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>19500</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>18800</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>10000</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>9600</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>9100</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>10200</v>
-      </c>
-      <c r="K47" s="3">
-        <v>10300</v>
       </c>
       <c r="L47" s="3">
         <v>10300</v>
       </c>
       <c r="M47" s="3">
+        <v>10300</v>
+      </c>
+      <c r="N47" s="3">
         <v>10400</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>10600</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>10400</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>136800</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>136900</v>
-      </c>
-      <c r="R47" s="3">
-        <v>138000</v>
       </c>
       <c r="S47" s="3">
         <v>138000</v>
       </c>
       <c r="T47" s="3">
+        <v>138000</v>
+      </c>
+      <c r="U47" s="3">
         <v>13000</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>12800</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>13100</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>13200</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>12100</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>12600</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>12900</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>12700</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>13300</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>13500</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>13800</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>13900</v>
       </c>
-      <c r="AF47" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AG47" s="3" t="s">
         <v>8</v>
       </c>
@@ -4642,123 +4747,129 @@
       <c r="AL47" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AM47" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="48" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="D48" s="3">
+      <c r="D48" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E48" s="3">
         <v>6055300</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>6046500</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>6091000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>6098600</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>6305700</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>6358300</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>6397300</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>6426100</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>6508700</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>6571400</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>6621600</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>6617800</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>6676800</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>6707500</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>2308000</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>2343700</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>2358900</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>2415900</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>2347400</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>2380500</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>2404000</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>2447400</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>2514100</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>2716800</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>2911300</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>2941200</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>3051700</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>3076800</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>3194200</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>3293300</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>3320300</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>3331800</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>3399700</v>
       </c>
-      <c r="AK48" s="3">
+      <c r="AL48" s="3">
         <v>3435400</v>
       </c>
-      <c r="AL48" s="3">
+      <c r="AM48" s="3">
         <v>3458300</v>
       </c>
     </row>
-    <row r="49" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="D49" s="3">
-        <v>0</v>
+      <c r="D49" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="E49" s="3">
         <v>0</v>
@@ -4784,11 +4895,11 @@
       <c r="L49" s="3">
         <v>0</v>
       </c>
-      <c r="M49" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="N49" s="3">
-        <v>0</v>
+      <c r="M49" s="3">
+        <v>0</v>
+      </c>
+      <c r="N49" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="O49" s="3">
         <v>0</v>
@@ -4839,31 +4950,34 @@
         <v>0</v>
       </c>
       <c r="AE49" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF49" s="3">
         <v>32300</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>39000</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>44000</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>47900</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>53000</v>
       </c>
-      <c r="AJ49" s="3">
+      <c r="AK49" s="3">
         <v>59300</v>
       </c>
-      <c r="AK49" s="3">
+      <c r="AL49" s="3">
         <v>65500</v>
       </c>
-      <c r="AL49" s="3">
+      <c r="AM49" s="3">
         <v>70000</v>
       </c>
     </row>
-    <row r="50" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4972,8 +5086,11 @@
       <c r="AL50" s="3">
         <v>0</v>
       </c>
+      <c r="AM50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -5082,8 +5199,11 @@
       <c r="AL51" s="3">
         <v>0</v>
       </c>
+      <c r="AM51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -5114,86 +5234,89 @@
       <c r="L52" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M52" s="3">
+      <c r="M52" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N52" s="3">
         <v>416000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>450000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>483000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>520300</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>548600</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>78400</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>61400</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>62600</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>66100</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>71900</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>88300</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>91300</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>94600</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>86300</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>108700</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>180800</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>111100</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>115100</v>
-      </c>
-      <c r="AE52" s="3">
-        <v>79400</v>
       </c>
       <c r="AF52" s="3">
         <v>79400</v>
       </c>
       <c r="AG52" s="3">
+        <v>79400</v>
+      </c>
+      <c r="AH52" s="3">
         <v>76400</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>76600</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>75400</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AK52" s="3">
         <v>76700</v>
       </c>
-      <c r="AK52" s="3">
+      <c r="AL52" s="3">
         <v>72800</v>
       </c>
-      <c r="AL52" s="3">
+      <c r="AM52" s="3">
         <v>72700</v>
       </c>
     </row>
-    <row r="53" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5302,118 +5425,124 @@
       <c r="AL53" s="3">
         <v>0</v>
       </c>
+      <c r="AM53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="D54" s="3">
+      <c r="D54" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E54" s="3">
         <v>6682500</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>7091800</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>7129700</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>6958900</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>7204500</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>6944100</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>7052500</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>7165100</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>7196900</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>7342000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>7399900</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>7384900</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>7573700</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>7639600</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>2708900</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>2719200</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>2755300</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>2608500</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>2658100</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>2811800</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>2937400</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>2648900</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>2713900</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>2936300</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>3203200</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>3172000</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>3285900</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>3302200</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>3418900</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>3512500</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>3543400</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>3550300</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>3623500</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AL54" s="3">
         <v>3656400</v>
       </c>
-      <c r="AL54" s="3">
+      <c r="AM54" s="3">
         <v>3690900</v>
       </c>
     </row>
-    <row r="55" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5452,8 +5581,9 @@
       <c r="AJ55" s="3"/>
       <c r="AK55" s="3"/>
       <c r="AL55" s="3"/>
+      <c r="AM55" s="3"/>
     </row>
-    <row r="56" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5492,151 +5622,155 @@
       <c r="AJ56" s="3"/>
       <c r="AK56" s="3"/>
       <c r="AL56" s="3"/>
+      <c r="AM56" s="3"/>
     </row>
-    <row r="57" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="D57" s="3">
+      <c r="D57" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E57" s="3">
         <v>158900</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>198700</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>184000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>181800</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>162400</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>188000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>185700</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>164800</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>148100</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>207800</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>152000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>133800</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>124200</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>185000</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>85700</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>74400</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>72100</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>77500</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>88600</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>85700</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>109400</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>69800</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>77500</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>66600</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>61900</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>85900</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>98500</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>101200</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>102900</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>78500</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>101600</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>88500</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AK57" s="3">
         <v>88800</v>
       </c>
-      <c r="AK57" s="3">
+      <c r="AL57" s="3">
         <v>80700</v>
       </c>
-      <c r="AL57" s="3">
+      <c r="AM57" s="3">
         <v>93400</v>
       </c>
     </row>
-    <row r="58" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="D58" s="3">
+      <c r="D58" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E58" s="3">
         <v>83900</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>440400</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>1300</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>122600</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>273500</v>
       </c>
-      <c r="I58" s="3">
-        <v>0</v>
-      </c>
       <c r="J58" s="3">
+        <v>0</v>
+      </c>
+      <c r="K58" s="3">
         <v>1300</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>124200</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>125100</v>
       </c>
-      <c r="M58" s="3">
-        <v>0</v>
-      </c>
       <c r="N58" s="3">
         <v>0</v>
       </c>
@@ -5712,89 +5846,92 @@
       <c r="AL58" s="3">
         <v>0</v>
       </c>
+      <c r="AM58" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="59" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="D59" s="3">
+      <c r="D59" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E59" s="3">
         <v>4200</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>15100</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>3800</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>3900</v>
       </c>
-      <c r="H59" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="I59" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J59" s="3">
+      <c r="J59" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K59" s="3">
         <v>168000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>11400</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>14600</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>79300</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>78100</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>76000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>79200</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>70200</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>26200</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>26300</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>26400</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>26500</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>26600</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>26800</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>26900</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>27000</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>27100</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>27200</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>27300</v>
       </c>
-      <c r="AC59" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AD59" s="3" t="s">
         <v>8</v>
       </c>
@@ -5804,8 +5941,8 @@
       <c r="AF59" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AG59" s="3">
-        <v>0</v>
+      <c r="AG59" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AH59" s="3">
         <v>0</v>
@@ -5822,41 +5959,44 @@
       <c r="AL59" s="3">
         <v>0</v>
       </c>
+      <c r="AM59" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="60" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="D60" s="3">
+      <c r="D60" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E60" s="3">
         <v>247000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>654300</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>189100</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>308300</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>435900</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>188000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>354900</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>300400</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>287800</v>
       </c>
-      <c r="M60" s="3">
-        <v>0</v>
-      </c>
       <c r="N60" s="3">
         <v>0</v>
       </c>
@@ -5932,151 +6072,157 @@
       <c r="AL60" s="3">
         <v>0</v>
       </c>
+      <c r="AM60" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="61" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>0</v>
+      </c>
+      <c r="E61" s="3">
         <v>2895200</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>2857500</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>3311100</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>2969000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>2971700</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>2908200</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>2949700</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>2895300</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>2927500</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>3010300</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>3012900</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>3001200</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>3179100</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>3150800</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>1289000</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>1289400</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>1315200</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>1170800</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>1196100</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>1346300</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>1446500</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>1146600</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>1198600</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>1376600</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>1602600</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>1543300</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>1578300</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>1565400</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>1650500</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>1699200</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>1681700</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>1675100</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AK61" s="3">
         <v>1726900</v>
       </c>
-      <c r="AK61" s="3">
+      <c r="AL61" s="3">
         <v>1731100</v>
       </c>
-      <c r="AL61" s="3">
+      <c r="AM61" s="3">
         <v>1732300</v>
       </c>
     </row>
-    <row r="62" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="D62" s="3">
+      <c r="D62" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E62" s="3">
         <v>139800</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>135800</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>151900</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>154400</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>164400</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>168700</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>12000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>176500</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>182900</v>
       </c>
-      <c r="M62" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="N62" s="3" t="s">
         <v>8</v>
       </c>
@@ -6086,8 +6232,8 @@
       <c r="P62" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q62" s="3">
-        <v>0</v>
+      <c r="Q62" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="R62" s="3">
         <v>0</v>
@@ -6116,15 +6262,15 @@
       <c r="Z62" s="3">
         <v>0</v>
       </c>
-      <c r="AA62" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AB62" s="3">
+      <c r="AA62" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB62" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AC62" s="3">
         <v>2400</v>
       </c>
-      <c r="AC62" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AD62" s="3" t="s">
         <v>8</v>
       </c>
@@ -6134,8 +6280,8 @@
       <c r="AF62" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AG62" s="3">
-        <v>0</v>
+      <c r="AG62" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AH62" s="3">
         <v>0</v>
@@ -6152,8 +6298,11 @@
       <c r="AL62" s="3">
         <v>0</v>
       </c>
+      <c r="AM62" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="63" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6262,8 +6411,11 @@
       <c r="AL63" s="3">
         <v>0</v>
       </c>
+      <c r="AM63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6372,8 +6524,11 @@
       <c r="AL64" s="3">
         <v>0</v>
       </c>
+      <c r="AM64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6482,118 +6637,124 @@
       <c r="AL65" s="3">
         <v>0</v>
       </c>
+      <c r="AM65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="D66" s="3">
+      <c r="D66" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E66" s="3">
         <v>3311000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>3679700</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>3681500</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>3459300</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>3598100</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>3300200</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>3347800</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>3405900</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>3428400</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>3575500</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>3527100</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>3493700</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>3675100</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>3717500</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>1510000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>1505700</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>1523500</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>1377900</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>1416000</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>1563600</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>1684600</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>1359800</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>1411700</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>1583700</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>1816400</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>1759300</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>1807700</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>1802800</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>1893900</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>1947100</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>1958500</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>1940600</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>2004000</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AL66" s="3">
         <v>2012800</v>
       </c>
-      <c r="AL66" s="3">
+      <c r="AM66" s="3">
         <v>2046500</v>
       </c>
     </row>
-    <row r="67" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6632,8 +6793,9 @@
       <c r="AJ67" s="3"/>
       <c r="AK67" s="3"/>
       <c r="AL67" s="3"/>
+      <c r="AM67" s="3"/>
     </row>
-    <row r="68" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6742,8 +6904,11 @@
       <c r="AL68" s="3">
         <v>0</v>
       </c>
+      <c r="AM68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6852,8 +7017,11 @@
       <c r="AL69" s="3">
         <v>0</v>
       </c>
+      <c r="AM69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6962,8 +7130,11 @@
       <c r="AL70" s="3">
         <v>0</v>
       </c>
+      <c r="AM70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -7072,118 +7243,124 @@
       <c r="AL71" s="3">
         <v>0</v>
       </c>
+      <c r="AM71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="D72" s="3">
+      <c r="D72" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E72" s="3">
         <v>-1630900</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-1595300</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-1557800</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-1517400</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-1413800</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-1373100</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-1326200</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-1275600</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-1255000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-1207800</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-1105800</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-1052000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-1021300</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-962900</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-849500</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-827300</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-812700</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-824300</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-810800</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-801800</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-797000</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>-770000</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>-758600</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>-712200</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>-683700</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>-662700</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>-604900</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>-582200</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>-554300</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>-509800</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>-485600</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>-459700</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>-444600</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AL72" s="3">
         <v>-419300</v>
       </c>
-      <c r="AL72" s="3">
+      <c r="AM72" s="3">
         <v>-397400</v>
       </c>
     </row>
-    <row r="73" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -7292,8 +7469,11 @@
       <c r="AL73" s="3">
         <v>0</v>
       </c>
+      <c r="AM73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7402,8 +7582,11 @@
       <c r="AL74" s="3">
         <v>0</v>
       </c>
+      <c r="AM74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -7512,118 +7695,124 @@
       <c r="AL75" s="3">
         <v>0</v>
       </c>
+      <c r="AM75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="D76" s="3">
+      <c r="D76" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E76" s="3">
         <v>3268000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>3312100</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>3349400</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>3421600</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>3530800</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>3568100</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>3635300</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>3692800</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>3706000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>3766500</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>3872800</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>3891100</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>3898600</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>3922000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>1198800</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>1213500</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>1231900</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>1230700</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>1242100</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>1248200</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>1252800</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>1289000</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>1302200</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>1352700</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>1386800</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>1412700</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>1478200</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>1499400</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>1525000</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>1565400</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>1584900</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>1609700</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>1619500</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3">
         <v>1643600</v>
       </c>
-      <c r="AL76" s="3">
+      <c r="AM76" s="3">
         <v>1644400</v>
       </c>
     </row>
-    <row r="77" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7732,233 +7921,242 @@
       <c r="AL77" s="3">
         <v>0</v>
       </c>
+      <c r="AM77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:39" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E80" s="2">
         <v>45747</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45657</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45565</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45473</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45382</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45291</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45199</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45107</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45016</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44926</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44834</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44742</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44651</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44561</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44469</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44377</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44286</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44196</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44104</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44012</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43921</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43830</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43738</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43646</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43555</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43465</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43373</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43281</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43190</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43100</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>43008</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>42916</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>42825</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>42735</v>
       </c>
-      <c r="AL80" s="2">
+      <c r="AM80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D81" s="3">
+      <c r="D81" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E81" s="3">
         <v>23700</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>21800</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>16700</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-48600</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>14200</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>8000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>2100</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>32100</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>5400</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-1100</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-7800</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>13100</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-16800</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-98200</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-7000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-200</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>24600</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-6800</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-4600</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-4800</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-100</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>15300</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-19700</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>-1800</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>5700</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>-31200</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>3900</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>-1400</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>-17900</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>2300</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>-600</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>10200</v>
       </c>
-      <c r="AJ81" s="3">
-        <v>0</v>
-      </c>
       <c r="AK81" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL81" s="3">
         <v>3400</v>
       </c>
-      <c r="AL81" s="3">
+      <c r="AM81" s="3">
         <v>-1700</v>
       </c>
     </row>
-    <row r="82" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7997,118 +8195,122 @@
       <c r="AJ82" s="3"/>
       <c r="AK82" s="3"/>
       <c r="AL82" s="3"/>
+      <c r="AM82" s="3"/>
     </row>
-    <row r="83" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>77300</v>
+      </c>
+      <c r="E83" s="3">
         <v>79100</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>76300</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>75900</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>77700</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>79600</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>78000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>79200</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>78300</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>79800</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>113700</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>116600</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>119300</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>123300</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>110600</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>30800</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>30500</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>31200</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>32300</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>34400</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>32000</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>32100</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>31400</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>32600</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>35600</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>35300</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>38000</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>37500</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>41300</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>39200</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>41400</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>43500</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>43400</v>
       </c>
-      <c r="AJ83" s="3">
+      <c r="AK83" s="3">
         <v>46400</v>
       </c>
-      <c r="AK83" s="3">
+      <c r="AL83" s="3">
         <v>43700</v>
       </c>
-      <c r="AL83" s="3">
+      <c r="AM83" s="3">
         <v>47700</v>
       </c>
     </row>
-    <row r="84" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -8217,8 +8419,11 @@
       <c r="AL84" s="3">
         <v>0</v>
       </c>
+      <c r="AM84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -8327,8 +8532,11 @@
       <c r="AL85" s="3">
         <v>0</v>
       </c>
+      <c r="AM85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -8437,8 +8645,11 @@
       <c r="AL86" s="3">
         <v>0</v>
       </c>
+      <c r="AM86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -8547,8 +8758,11 @@
       <c r="AL87" s="3">
         <v>0</v>
       </c>
+      <c r="AM87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8657,118 +8871,124 @@
       <c r="AL88" s="3">
         <v>0</v>
       </c>
+      <c r="AM88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="D89" s="3">
+      <c r="D89" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E89" s="3">
         <v>74100</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>111000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>112400</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>142100</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>53600</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>103500</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>110800</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>116800</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>63600</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>116900</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>108100</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>104700</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>49600</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-3500</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>36400</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>36100</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>31300</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>9800</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>35900</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>28000</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>21900</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>31800</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>36500</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>37300</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>32300</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>35400</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>37000</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>45800</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>36300</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>30800</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>42700</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>44900</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>36200</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AL89" s="3">
         <v>34200</v>
       </c>
-      <c r="AL89" s="3">
+      <c r="AM89" s="3">
         <v>39800</v>
       </c>
     </row>
-    <row r="90" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -8807,118 +9027,122 @@
       <c r="AJ90" s="3"/>
       <c r="AK90" s="3"/>
       <c r="AL90" s="3"/>
+      <c r="AM90" s="3"/>
     </row>
-    <row r="91" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="D91" s="3">
+      <c r="D91" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E91" s="3">
         <v>-34400</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-39000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-34800</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-38900</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-28200</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-43900</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-30900</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-28600</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-39100</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-52000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-47800</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-35000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-23800</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-20400</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-15700</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-13300</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-7900</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-7600</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-8200</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-9200</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-13200</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-15700</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-12400</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-13700</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-11500</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-12000</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-12700</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-16500</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-18100</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-10800</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-24800</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-11200</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AK91" s="3">
         <v>-47700</v>
       </c>
-      <c r="AK91" s="3">
+      <c r="AL91" s="3">
         <v>-26000</v>
       </c>
-      <c r="AL91" s="3">
+      <c r="AM91" s="3">
         <v>-24100</v>
       </c>
     </row>
-    <row r="92" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -9027,8 +9251,11 @@
       <c r="AL92" s="3">
         <v>0</v>
       </c>
+      <c r="AM92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -9137,118 +9364,124 @@
       <c r="AL93" s="3">
         <v>0</v>
       </c>
+      <c r="AM93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="D94" s="3">
+      <c r="D94" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E94" s="3">
         <v>227800</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-29500</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-314900</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>134700</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-289300</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-26200</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-63500</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>49500</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-41500</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-31500</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-82300</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>130800</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-62200</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>18000</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-9600</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-133300</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>33900</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-64900</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>4700</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-13500</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-7100</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>52800</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>166900</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>226600</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-29700</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>44700</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-14500</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>71800</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>46400</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-23200</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-16500</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>38100</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>1400</v>
       </c>
-      <c r="AK94" s="3">
+      <c r="AL94" s="3">
         <v>-15600</v>
       </c>
-      <c r="AL94" s="3">
+      <c r="AM94" s="3">
         <v>-22200</v>
       </c>
     </row>
-    <row r="95" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -9287,19 +9520,20 @@
       <c r="AJ95" s="3"/>
       <c r="AK95" s="3"/>
       <c r="AL95" s="3"/>
+      <c r="AM95" s="3"/>
     </row>
-    <row r="96" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D96" s="3">
+      <c r="D96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E96" s="3">
         <v>59300</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>57100</v>
-      </c>
-      <c r="F96" s="3">
-        <v>54900</v>
       </c>
       <c r="G96" s="3">
         <v>54900</v>
@@ -9308,55 +9542,55 @@
         <v>54900</v>
       </c>
       <c r="I96" s="3">
-        <v>52700</v>
+        <v>54900</v>
       </c>
       <c r="J96" s="3">
         <v>52700</v>
       </c>
       <c r="K96" s="3">
-        <v>52600</v>
+        <v>52700</v>
       </c>
       <c r="L96" s="3">
         <v>52600</v>
       </c>
       <c r="M96" s="3">
+        <v>52600</v>
+      </c>
+      <c r="N96" s="3">
         <v>-48200</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>-46000</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>-43800</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>-41600</v>
-      </c>
-      <c r="Q96" s="3">
-        <v>-15200</v>
       </c>
       <c r="R96" s="3">
         <v>-15200</v>
       </c>
       <c r="S96" s="3">
+        <v>-15200</v>
+      </c>
+      <c r="T96" s="3">
         <v>-14400</v>
       </c>
-      <c r="T96" s="3">
+      <c r="U96" s="3">
         <v>-13000</v>
       </c>
-      <c r="U96" s="3">
+      <c r="V96" s="3">
         <v>-6700</v>
       </c>
-      <c r="V96" s="3">
+      <c r="W96" s="3">
         <v>-4400</v>
       </c>
-      <c r="W96" s="3">
+      <c r="X96" s="3">
         <v>-26700</v>
       </c>
-      <c r="X96" s="3">
+      <c r="Y96" s="3">
         <v>-300</v>
-      </c>
-      <c r="Y96" s="3">
-        <v>-26700</v>
       </c>
       <c r="Z96" s="3">
         <v>-26700</v>
@@ -9365,10 +9599,10 @@
         <v>-26700</v>
       </c>
       <c r="AB96" s="3">
+        <v>-26700</v>
+      </c>
+      <c r="AC96" s="3">
         <v>-53300</v>
-      </c>
-      <c r="AC96" s="3">
-        <v>-26600</v>
       </c>
       <c r="AD96" s="3">
         <v>-26600</v>
@@ -9377,10 +9611,10 @@
         <v>-26600</v>
       </c>
       <c r="AF96" s="3">
+        <v>-26600</v>
+      </c>
+      <c r="AG96" s="3">
         <v>-26500</v>
-      </c>
-      <c r="AG96" s="3">
-        <v>-25300</v>
       </c>
       <c r="AH96" s="3">
         <v>-25300</v>
@@ -9392,13 +9626,16 @@
         <v>-25300</v>
       </c>
       <c r="AK96" s="3">
-        <v>-24000</v>
+        <v>-25300</v>
       </c>
       <c r="AL96" s="3">
         <v>-24000</v>
       </c>
+      <c r="AM96" s="3">
+        <v>-24000</v>
+      </c>
     </row>
-    <row r="97" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -9507,8 +9744,11 @@
       <c r="AL97" s="3">
         <v>0</v>
       </c>
+      <c r="AM97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -9617,8 +9857,11 @@
       <c r="AL98" s="3">
         <v>0</v>
       </c>
+      <c r="AM98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -9727,118 +9970,124 @@
       <c r="AL99" s="3">
         <v>0</v>
       </c>
+      <c r="AM99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="D100" s="3">
+      <c r="D100" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E100" s="3">
         <v>-380300</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-71200</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>166800</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-206800</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>283300</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-94100</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-123900</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-84100</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-91400</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-59900</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-28400</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-218600</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-5600</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-18000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-17100</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-41200</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>120800</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-35600</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-155100</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-128300</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>298000</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-81800</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-212900</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-256400</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>3800</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-75600</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-24800</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-112800</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-76300</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-16800</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>-19700</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>-78700</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>-34200</v>
       </c>
-      <c r="AK100" s="3">
+      <c r="AL100" s="3">
         <v>-27600</v>
       </c>
-      <c r="AL100" s="3">
+      <c r="AM100" s="3">
         <v>-26600</v>
       </c>
     </row>
-    <row r="101" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -9869,8 +10118,8 @@
       <c r="L101" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M101" s="3">
-        <v>0</v>
+      <c r="M101" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="N101" s="3">
         <v>0</v>
@@ -9947,114 +10196,120 @@
       <c r="AL101" s="3">
         <v>0</v>
       </c>
+      <c r="AM101" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="102" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>0</v>
+      </c>
+      <c r="E102" s="3">
         <v>-78400</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>10300</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-35700</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>70000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>47500</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-16900</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-76600</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>82300</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-69300</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>25500</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-2600</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>17000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-18200</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-3400</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>9700</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-138500</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>185900</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-90700</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-114500</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-113800</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>312800</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>2800</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-9500</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>7600</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>6400</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>4500</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>-2300</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>4800</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>6400</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>-8400</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>4800</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>4400</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>3300</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AL102" s="3">
         <v>-8900</v>
       </c>
-      <c r="AL102" s="3">
+      <c r="AM102" s="3">
         <v>-9100</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/KRG_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/KRG_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="195" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="199" uniqueCount="92">
   <si>
     <t>KRG</t>
   </si>
@@ -656,402 +656,411 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AN102"/>
+  <dimension ref="A5:AO102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="36" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="37" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="38" max="38" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="39" max="40" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="41" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="37" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="38" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="39" max="39" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="40" max="41" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="42" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:41" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:41" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E7" s="2">
         <v>45930</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45838</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45747</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45657</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45565</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45473</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45382</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45291</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45199</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45107</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45016</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44926</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44834</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44742</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44651</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44561</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44469</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44377</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44286</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44196</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44104</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44012</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43921</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43830</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43738</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43646</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43555</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43465</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43373</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43281</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>43190</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>43100</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>43008</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>42916</v>
       </c>
-      <c r="AL7" s="2">
+      <c r="AM7" s="2">
         <v>42825</v>
       </c>
-      <c r="AM7" s="2">
+      <c r="AN7" s="2">
         <v>42735</v>
       </c>
-      <c r="AN7" s="2">
+      <c r="AO7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>204200</v>
+      </c>
+      <c r="E8" s="3">
         <v>205100</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>213400</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>221800</v>
       </c>
-      <c r="G8" s="3">
-        <v>214700</v>
-      </c>
       <c r="H8" s="3">
+        <v>212200</v>
+      </c>
+      <c r="I8" s="3">
         <v>207300</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>210600</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>207400</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>200300</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>207200</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>208800</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>206800</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>204700</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>200300</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>202600</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>194400</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>163000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>71500</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>69500</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>69400</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>68400</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>65100</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>63300</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>69900</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>75200</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>74900</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>81500</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>83500</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>86900</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>85700</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>91700</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>89800</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>88900</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>87100</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AL8" s="3">
         <v>92600</v>
       </c>
-      <c r="AL8" s="3">
+      <c r="AM8" s="3">
         <v>90100</v>
       </c>
-      <c r="AM8" s="3">
+      <c r="AN8" s="3">
         <v>88900</v>
       </c>
-      <c r="AN8" s="3">
+      <c r="AO8" s="3">
         <v>89100</v>
       </c>
     </row>
-    <row r="9" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>53300</v>
+      </c>
+      <c r="E9" s="3">
         <v>54200</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>55500</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>57600</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>54800</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>53000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>55100</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>54600</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>47900</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>54100</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>53900</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>54500</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>53800</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>51200</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>54000</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>52800</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>47500</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>19100</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>18800</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>19700</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>19900</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>19700</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>17600</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>19700</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>20600</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>20700</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>21400</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>21600</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>23200</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>23300</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>23000</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>23200</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>23500</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AK9" s="3">
         <v>22700</v>
       </c>
-      <c r="AK9" s="3">
+      <c r="AL9" s="3">
         <v>23400</v>
       </c>
-      <c r="AL9" s="3">
+      <c r="AM9" s="3">
         <v>23300</v>
       </c>
-      <c r="AM9" s="3">
+      <c r="AN9" s="3">
         <v>23000</v>
       </c>
-      <c r="AN9" s="3">
+      <c r="AO9" s="3">
         <v>22600</v>
       </c>
     </row>
-    <row r="10" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
@@ -1059,115 +1068,118 @@
         <v>150800</v>
       </c>
       <c r="E10" s="3">
+        <v>150800</v>
+      </c>
+      <c r="F10" s="3">
         <v>157900</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>164200</v>
       </c>
-      <c r="G10" s="3">
-        <v>159900</v>
-      </c>
       <c r="H10" s="3">
+        <v>157400</v>
+      </c>
+      <c r="I10" s="3">
         <v>154300</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>155500</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>152800</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>152400</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>153100</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>154800</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>152300</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>150900</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>149100</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>148600</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>141600</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>115500</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>52400</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>50700</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>49700</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>48500</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>45400</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>45700</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>50200</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>54600</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>54200</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>60100</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>61900</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>63700</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>62400</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>68700</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>66600</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>65400</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AK10" s="3">
         <v>64400</v>
       </c>
-      <c r="AK10" s="3">
+      <c r="AL10" s="3">
         <v>69200</v>
       </c>
-      <c r="AL10" s="3">
+      <c r="AM10" s="3">
         <v>66800</v>
       </c>
-      <c r="AM10" s="3">
+      <c r="AN10" s="3">
         <v>65900</v>
       </c>
-      <c r="AN10" s="3">
+      <c r="AO10" s="3">
         <v>66500</v>
       </c>
     </row>
-    <row r="11" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1208,8 +1220,9 @@
       <c r="AL11" s="3"/>
       <c r="AM11" s="3"/>
       <c r="AN11" s="3"/>
+      <c r="AO11" s="3"/>
     </row>
-    <row r="12" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1324,8 +1337,11 @@
       <c r="AN12" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AO12" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="13" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1440,71 +1456,74 @@
       <c r="AN13" s="3">
         <v>0</v>
       </c>
+      <c r="AO13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>-173400</v>
+      </c>
+      <c r="E14" s="3">
         <v>25800</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>-103500</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>-4100</v>
       </c>
-      <c r="G14" s="3">
-        <v>-5400</v>
-      </c>
       <c r="H14" s="3">
+        <v>-7900</v>
+      </c>
+      <c r="I14" s="3">
         <v>-5000</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>61300</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>-5700</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>-500</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>5500</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>-28700</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>-400</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>-100</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>100</v>
       </c>
-      <c r="Q14" s="3">
-        <v>0</v>
-      </c>
       <c r="R14" s="3">
+        <v>0</v>
+      </c>
+      <c r="S14" s="3">
         <v>900</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>76600</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>9200</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>800</v>
       </c>
-      <c r="V14" s="3" t="s">
+      <c r="W14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="W14" s="3">
-        <v>0</v>
-      </c>
       <c r="X14" s="3">
         <v>0</v>
       </c>
@@ -1515,32 +1534,32 @@
         <v>0</v>
       </c>
       <c r="AA14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB14" s="3">
         <v>2000</v>
       </c>
-      <c r="AB14" s="3">
+      <c r="AC14" s="3">
         <v>15600</v>
       </c>
-      <c r="AC14" s="3">
+      <c r="AD14" s="3">
         <v>27700</v>
       </c>
-      <c r="AD14" s="3">
+      <c r="AE14" s="3">
         <v>4100</v>
       </c>
-      <c r="AE14" s="3">
+      <c r="AF14" s="3">
         <v>31500</v>
       </c>
-      <c r="AF14" s="3">
-        <v>0</v>
-      </c>
       <c r="AG14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH14" s="3">
         <v>14800</v>
       </c>
-      <c r="AH14" s="3">
+      <c r="AI14" s="3">
         <v>24100</v>
       </c>
-      <c r="AI14" s="3">
-        <v>0</v>
-      </c>
       <c r="AJ14" s="3">
         <v>0</v>
       </c>
@@ -1548,132 +1567,138 @@
         <v>0</v>
       </c>
       <c r="AL14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM14" s="3">
         <v>7400</v>
       </c>
-      <c r="AM14" s="3">
+      <c r="AN14" s="3">
         <v>2800</v>
       </c>
-      <c r="AN14" s="3" t="s">
+      <c r="AO14" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="15" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>87800</v>
+      </c>
+      <c r="E15" s="3">
         <v>89400</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>97900</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>98200</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>97000</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>96700</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>99300</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>100400</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>102900</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>105900</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>109500</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>108100</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>112700</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>115800</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>119800</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>121500</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>109800</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>30200</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>29800</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>30600</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>31800</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>34000</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="Z15" s="3">
         <v>31400</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AA15" s="3">
         <v>31500</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AB15" s="3">
         <v>30800</v>
       </c>
-      <c r="AB15" s="3">
+      <c r="AC15" s="3">
         <v>32000</v>
       </c>
-      <c r="AC15" s="3">
+      <c r="AD15" s="3">
         <v>34700</v>
       </c>
-      <c r="AD15" s="3">
+      <c r="AE15" s="3">
         <v>34600</v>
       </c>
-      <c r="AE15" s="3">
+      <c r="AF15" s="3">
         <v>36300</v>
       </c>
-      <c r="AF15" s="3">
+      <c r="AG15" s="3">
         <v>36900</v>
       </c>
-      <c r="AG15" s="3">
+      <c r="AH15" s="3">
         <v>40500</v>
       </c>
-      <c r="AH15" s="3">
+      <c r="AI15" s="3">
         <v>38600</v>
       </c>
-      <c r="AI15" s="3">
+      <c r="AJ15" s="3">
         <v>40800</v>
       </c>
-      <c r="AJ15" s="3">
+      <c r="AK15" s="3">
         <v>42800</v>
       </c>
-      <c r="AK15" s="3">
+      <c r="AL15" s="3">
         <v>42700</v>
       </c>
-      <c r="AL15" s="3">
+      <c r="AM15" s="3">
         <v>45800</v>
       </c>
-      <c r="AM15" s="3">
+      <c r="AN15" s="3">
         <v>42900</v>
       </c>
-      <c r="AN15" s="3">
+      <c r="AO15" s="3">
         <v>45500</v>
       </c>
     </row>
-    <row r="16" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:41" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1711,240 +1736,247 @@
       <c r="AL16" s="3"/>
       <c r="AM16" s="3"/>
       <c r="AN16" s="3"/>
+      <c r="AO16" s="3"/>
     </row>
-    <row r="17" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>156700</v>
+      </c>
+      <c r="E17" s="3">
         <v>157800</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>166800</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>168100</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>165400</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>162900</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>167300</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>167800</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>165100</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>173900</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>177900</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>176000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>179400</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>182000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>163600</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>185400</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>240600</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>65500</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>57400</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>31400</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>62700</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>56900</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>54900</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>57100</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>47000</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>80700</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>66700</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>60500</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>92500</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>65000</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>83800</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>91800</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>54400</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>70900</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>71600</v>
       </c>
-      <c r="AL17" s="3">
+      <c r="AM17" s="3">
         <v>82000</v>
       </c>
-      <c r="AM17" s="3">
+      <c r="AN17" s="3">
         <v>71300</v>
       </c>
-      <c r="AN17" s="3">
+      <c r="AO17" s="3">
         <v>73200</v>
       </c>
     </row>
-    <row r="18" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>47400</v>
+      </c>
+      <c r="E18" s="3">
         <v>47300</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>46600</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>53700</v>
       </c>
-      <c r="G18" s="3">
-        <v>49300</v>
-      </c>
       <c r="H18" s="3">
+        <v>46800</v>
+      </c>
+      <c r="I18" s="3">
         <v>44400</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>43300</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>39700</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>35200</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>33300</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>30900</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>30800</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>25300</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>18300</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>39000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>9000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-77600</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>6000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>12100</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>38000</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>5700</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>8200</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>8400</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>12800</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>28200</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>-5800</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>14800</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>23000</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>-5600</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>20700</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>7900</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>-2000</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>34500</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>16200</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3">
         <v>21000</v>
       </c>
-      <c r="AL18" s="3">
+      <c r="AM18" s="3">
         <v>8100</v>
       </c>
-      <c r="AM18" s="3">
+      <c r="AN18" s="3">
         <v>17600</v>
       </c>
-      <c r="AN18" s="3">
+      <c r="AO18" s="3">
         <v>15900</v>
       </c>
     </row>
-    <row r="19" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1985,79 +2017,80 @@
       <c r="AL19" s="3"/>
       <c r="AM19" s="3"/>
       <c r="AN19" s="3"/>
+      <c r="AO19" s="3"/>
     </row>
-    <row r="20" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>3200</v>
+      </c>
+      <c r="E20" s="3">
         <v>4600</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>3200</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>600</v>
       </c>
-      <c r="G20" s="3">
-        <v>0</v>
-      </c>
       <c r="H20" s="3">
+        <v>0</v>
+      </c>
+      <c r="I20" s="3">
         <v>600</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>200</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>400</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-200</v>
       </c>
-      <c r="L20" s="3">
-        <v>0</v>
-      </c>
       <c r="M20" s="3">
+        <v>0</v>
+      </c>
+      <c r="N20" s="3">
         <v>-100</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>200</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>400</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>100</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-200</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-100</v>
-      </c>
-      <c r="S20" s="3">
-        <v>100</v>
       </c>
       <c r="T20" s="3">
         <v>100</v>
       </c>
       <c r="U20" s="3">
+        <v>100</v>
+      </c>
+      <c r="V20" s="3">
         <v>300</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-200</v>
       </c>
-      <c r="W20" s="3">
-        <v>0</v>
-      </c>
       <c r="X20" s="3">
         <v>0</v>
       </c>
       <c r="Y20" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z20" s="3">
         <v>400</v>
-      </c>
-      <c r="Z20" s="3">
-        <v>-100</v>
       </c>
       <c r="AA20" s="3">
         <v>-100</v>
@@ -2066,43 +2099,46 @@
         <v>-100</v>
       </c>
       <c r="AC20" s="3">
-        <v>-200</v>
+        <v>-100</v>
       </c>
       <c r="AD20" s="3">
         <v>-200</v>
       </c>
       <c r="AE20" s="3">
+        <v>-200</v>
+      </c>
+      <c r="AF20" s="3">
         <v>-8300</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>-300</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>7700</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>300</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>-15200</v>
       </c>
-      <c r="AJ20" s="3">
+      <c r="AK20" s="3">
         <v>-100</v>
       </c>
-      <c r="AK20" s="3">
+      <c r="AL20" s="3">
         <v>6300</v>
       </c>
-      <c r="AL20" s="3">
+      <c r="AM20" s="3">
         <v>8700</v>
       </c>
-      <c r="AM20" s="3">
+      <c r="AN20" s="3">
         <v>4000</v>
       </c>
-      <c r="AN20" s="3">
+      <c r="AO20" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -2110,216 +2146,219 @@
         <v>132000</v>
       </c>
       <c r="E21" s="3">
+        <v>132000</v>
+      </c>
+      <c r="F21" s="3">
         <v>141200</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>151300</v>
       </c>
-      <c r="G21" s="3">
-        <v>146400</v>
-      </c>
       <c r="H21" s="3">
+        <v>143900</v>
+      </c>
+      <c r="I21" s="3">
         <v>140400</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>142400</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>139600</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>138300</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>139200</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>140400</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>138600</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>139500</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>135000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>158200</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>132200</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>33100</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>37000</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>42900</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>69000</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>38000</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>42600</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>40700</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>44800</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>59500</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>26800</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>50200</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>58100</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>24100</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>57900</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>57000</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>37500</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>60600</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>59600</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AL21" s="3">
         <v>70700</v>
       </c>
-      <c r="AL21" s="3">
+      <c r="AM21" s="3">
         <v>63200</v>
       </c>
-      <c r="AM21" s="3">
+      <c r="AN21" s="3">
         <v>65300</v>
       </c>
-      <c r="AN21" s="3">
+      <c r="AO21" s="3">
         <v>63500</v>
       </c>
     </row>
-    <row r="22" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>32400</v>
+      </c>
+      <c r="E22" s="3">
         <v>33200</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>34100</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>33000</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>32700</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>31600</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>31000</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>30400</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>27200</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>25500</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>27200</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>25400</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>26800</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>26200</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>25700</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>25500</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>23100</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>12900</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>12300</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>12200</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>12300</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>12600</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>13300</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>12300</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>12400</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>14300</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>16100</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>16500</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>17600</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>16100</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AH22" s="3">
         <v>16700</v>
       </c>
-      <c r="AH22" s="3">
+      <c r="AI22" s="3">
         <v>16300</v>
       </c>
-      <c r="AI22" s="3">
+      <c r="AJ22" s="3">
         <v>16500</v>
-      </c>
-      <c r="AJ22" s="3">
-        <v>16400</v>
       </c>
       <c r="AK22" s="3">
         <v>16400</v>
@@ -2328,182 +2367,188 @@
         <v>16400</v>
       </c>
       <c r="AM22" s="3">
+        <v>16400</v>
+      </c>
+      <c r="AN22" s="3">
         <v>17600</v>
       </c>
-      <c r="AN22" s="3">
+      <c r="AO22" s="3">
         <v>17100</v>
       </c>
     </row>
-    <row r="23" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>185200</v>
+      </c>
+      <c r="E23" s="3">
         <v>-16300</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>112800</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>24300</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>22000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>17100</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-49200</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>14600</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>8600</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>2200</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>32500</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>5500</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-1100</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-7900</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>13100</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-16600</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-100500</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-6700</v>
       </c>
-      <c r="U23" s="3">
-        <v>0</v>
-      </c>
       <c r="V23" s="3">
+        <v>0</v>
+      </c>
+      <c r="W23" s="3">
         <v>25600</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-6600</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-4400</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-4600</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>400</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>15700</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>-20100</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>-1500</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>6300</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>-31600</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>4300</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>-1100</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>-18000</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>2800</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>-200</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>10900</v>
       </c>
-      <c r="AL23" s="3">
+      <c r="AM23" s="3">
         <v>400</v>
       </c>
-      <c r="AM23" s="3">
+      <c r="AN23" s="3">
         <v>4000</v>
       </c>
-      <c r="AN23" s="3">
+      <c r="AO23" s="3">
         <v>-1200</v>
       </c>
     </row>
-    <row r="24" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>200</v>
+      </c>
+      <c r="E24" s="3">
         <v>100</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>200</v>
       </c>
-      <c r="F24" s="3">
-        <v>0</v>
-      </c>
       <c r="G24" s="3">
+        <v>0</v>
+      </c>
+      <c r="H24" s="3">
         <v>-200</v>
       </c>
-      <c r="H24" s="3">
-        <v>0</v>
-      </c>
       <c r="I24" s="3">
+        <v>0</v>
+      </c>
+      <c r="J24" s="3">
         <v>100</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>200</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>400</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>100</v>
       </c>
-      <c r="M24" s="3">
-        <v>0</v>
-      </c>
       <c r="N24" s="3">
         <v>0</v>
       </c>
       <c r="O24" s="3">
+        <v>0</v>
+      </c>
+      <c r="P24" s="3">
         <v>300</v>
       </c>
-      <c r="P24" s="3">
-        <v>0</v>
-      </c>
       <c r="Q24" s="3">
+        <v>0</v>
+      </c>
+      <c r="R24" s="3">
         <v>-200</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>-100</v>
       </c>
-      <c r="S24" s="3">
-        <v>0</v>
-      </c>
       <c r="T24" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="U24" s="3">
         <v>-100</v>
@@ -2512,7 +2557,7 @@
         <v>-100</v>
       </c>
       <c r="W24" s="3">
-        <v>-200</v>
+        <v>-100</v>
       </c>
       <c r="X24" s="3">
         <v>-200</v>
@@ -2521,16 +2566,16 @@
         <v>-200</v>
       </c>
       <c r="Z24" s="3">
-        <v>-100</v>
+        <v>-200</v>
       </c>
       <c r="AA24" s="3">
         <v>-100</v>
       </c>
       <c r="AB24" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="AC24" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="AD24" s="3">
         <v>-100</v>
@@ -2539,7 +2584,7 @@
         <v>-100</v>
       </c>
       <c r="AF24" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="AG24" s="3">
         <v>0</v>
@@ -2560,13 +2605,16 @@
         <v>0</v>
       </c>
       <c r="AM24" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN24" s="3">
         <v>100</v>
       </c>
-      <c r="AN24" s="3">
+      <c r="AO24" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2681,240 +2729,249 @@
       <c r="AN25" s="3">
         <v>0</v>
       </c>
+      <c r="AO25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>185100</v>
+      </c>
+      <c r="E26" s="3">
         <v>-16400</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>112600</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>24300</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>22200</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>17100</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-49300</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>14400</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>8200</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>2200</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>32500</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>5600</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-1400</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-7900</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>13300</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-16500</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-100500</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-6600</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>100</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>25700</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-6400</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-4200</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-4400</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>500</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>15800</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>-20100</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>-1500</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>6400</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>-31400</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>4300</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>-1100</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>-18000</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>2800</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>-200</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>10900</v>
       </c>
-      <c r="AL26" s="3">
+      <c r="AM26" s="3">
         <v>400</v>
       </c>
-      <c r="AM26" s="3">
+      <c r="AN26" s="3">
         <v>3900</v>
       </c>
-      <c r="AN26" s="3">
+      <c r="AO26" s="3">
         <v>-1300</v>
       </c>
     </row>
-    <row r="27" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>180800</v>
+      </c>
+      <c r="E27" s="3">
         <v>-16200</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>110300</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>23700</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>21800</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>16700</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-48600</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>14200</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>8000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>2100</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>32100</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>5400</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-1100</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-7800</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>13100</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-16800</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-98200</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-7000</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-200</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>24600</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-6800</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-4600</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-4800</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>-100</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>15300</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>-19700</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>-1800</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>5700</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>-31200</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>3900</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>-1400</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>-17900</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>2300</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>-600</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>10200</v>
       </c>
-      <c r="AL27" s="3">
-        <v>0</v>
-      </c>
       <c r="AM27" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN27" s="3">
         <v>3400</v>
       </c>
-      <c r="AN27" s="3">
+      <c r="AO27" s="3">
         <v>-1700</v>
       </c>
     </row>
-    <row r="28" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -3029,8 +3086,11 @@
       <c r="AN28" s="3">
         <v>0</v>
       </c>
+      <c r="AO28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -3127,8 +3187,8 @@
       <c r="AH29" s="3">
         <v>0</v>
       </c>
-      <c r="AI29" s="3" t="s">
-        <v>8</v>
+      <c r="AI29" s="3">
+        <v>0</v>
       </c>
       <c r="AJ29" s="3" t="s">
         <v>8</v>
@@ -3139,14 +3199,17 @@
       <c r="AL29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AM29" s="3">
-        <v>0</v>
-      </c>
-      <c r="AN29" s="3" t="s">
+      <c r="AM29" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AN29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO29" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="30" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3261,8 +3324,11 @@
       <c r="AN30" s="3">
         <v>0</v>
       </c>
+      <c r="AO30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3377,79 +3443,82 @@
       <c r="AN31" s="3">
         <v>0</v>
       </c>
+      <c r="AO31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-3200</v>
+      </c>
+      <c r="E32" s="3">
         <v>-4600</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-3200</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-600</v>
       </c>
-      <c r="G32" s="3">
-        <v>0</v>
-      </c>
       <c r="H32" s="3">
+        <v>0</v>
+      </c>
+      <c r="I32" s="3">
         <v>-600</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-200</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-400</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>200</v>
       </c>
-      <c r="L32" s="3">
-        <v>0</v>
-      </c>
       <c r="M32" s="3">
+        <v>0</v>
+      </c>
+      <c r="N32" s="3">
         <v>100</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-200</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-400</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-100</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>200</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>100</v>
-      </c>
-      <c r="S32" s="3">
-        <v>-100</v>
       </c>
       <c r="T32" s="3">
         <v>-100</v>
       </c>
       <c r="U32" s="3">
+        <v>-100</v>
+      </c>
+      <c r="V32" s="3">
         <v>-300</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>200</v>
       </c>
-      <c r="W32" s="3">
-        <v>0</v>
-      </c>
       <c r="X32" s="3">
         <v>0</v>
       </c>
       <c r="Y32" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z32" s="3">
         <v>-400</v>
-      </c>
-      <c r="Z32" s="3">
-        <v>100</v>
       </c>
       <c r="AA32" s="3">
         <v>100</v>
@@ -3458,159 +3527,165 @@
         <v>100</v>
       </c>
       <c r="AC32" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="AD32" s="3">
         <v>200</v>
       </c>
       <c r="AE32" s="3">
+        <v>200</v>
+      </c>
+      <c r="AF32" s="3">
         <v>8300</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>300</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>-7700</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>-300</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>15200</v>
       </c>
-      <c r="AJ32" s="3">
+      <c r="AK32" s="3">
         <v>100</v>
       </c>
-      <c r="AK32" s="3">
+      <c r="AL32" s="3">
         <v>-6300</v>
       </c>
-      <c r="AL32" s="3">
+      <c r="AM32" s="3">
         <v>-8700</v>
       </c>
-      <c r="AM32" s="3">
+      <c r="AN32" s="3">
         <v>-4000</v>
       </c>
-      <c r="AN32" s="3">
+      <c r="AO32" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>180800</v>
+      </c>
+      <c r="E33" s="3">
         <v>-16200</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>110300</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>23700</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>21800</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>16700</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-48600</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>14200</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>8000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>2100</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>32100</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>5400</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-1100</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-7800</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>13100</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-16800</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-98200</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-7000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-200</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>24600</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-6800</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-4600</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-4800</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-100</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>15300</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>-19700</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>-1800</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>5700</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>-31200</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>3900</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>-1400</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>-17900</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>2300</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>-600</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>10200</v>
       </c>
-      <c r="AL33" s="3">
-        <v>0</v>
-      </c>
       <c r="AM33" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN33" s="3">
         <v>3400</v>
       </c>
-      <c r="AN33" s="3">
+      <c r="AO33" s="3">
         <v>-1700</v>
       </c>
     </row>
-    <row r="34" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3725,245 +3800,254 @@
       <c r="AN34" s="3">
         <v>0</v>
       </c>
+      <c r="AO34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>180800</v>
+      </c>
+      <c r="E35" s="3">
         <v>-16200</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>110300</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>23700</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>21800</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>16700</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-48600</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>14200</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>8000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>2100</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>32100</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>5400</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-1100</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-7800</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>13100</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-16800</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-98200</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-7000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-200</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>24600</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-6800</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-4600</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-4800</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-100</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>15300</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>-19700</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>-1800</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>5700</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>-31200</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>3900</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>-1400</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>-17900</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>2300</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>-600</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>10200</v>
       </c>
-      <c r="AL35" s="3">
-        <v>0</v>
-      </c>
       <c r="AM35" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN35" s="3">
         <v>3400</v>
       </c>
-      <c r="AN35" s="3">
+      <c r="AO35" s="3">
         <v>-1700</v>
       </c>
     </row>
-    <row r="37" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:41" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E38" s="2">
         <v>45930</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45838</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45747</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45657</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45565</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45473</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45382</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45291</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45199</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45107</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45016</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44926</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44834</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44742</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44651</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44561</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44469</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44377</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44286</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44196</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44104</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44012</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43921</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43830</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43738</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43646</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43555</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43465</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43373</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43281</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>43190</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>43100</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>43008</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>42916</v>
       </c>
-      <c r="AL38" s="2">
+      <c r="AM38" s="2">
         <v>42825</v>
       </c>
-      <c r="AM38" s="2">
+      <c r="AN38" s="2">
         <v>42735</v>
       </c>
-      <c r="AN38" s="2">
+      <c r="AO38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -4004,8 +4088,9 @@
       <c r="AL39" s="3"/>
       <c r="AM39" s="3"/>
       <c r="AN39" s="3"/>
+      <c r="AO39" s="3"/>
     </row>
-    <row r="40" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -4046,163 +4131,167 @@
       <c r="AL40" s="3"/>
       <c r="AM40" s="3"/>
       <c r="AN40" s="3"/>
+      <c r="AO40" s="3"/>
     </row>
-    <row r="41" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>36800</v>
+      </c>
+      <c r="E41" s="3">
         <v>68700</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>182000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>49100</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>128100</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>117500</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>153800</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>83600</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>36400</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>52300</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>129300</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>43700</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>115800</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>88400</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>90800</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>74300</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>93200</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>99500</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>89900</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>228800</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>43600</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>129300</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>230000</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>343900</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>31300</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>40400</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>35800</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>28400</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>35400</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>30700</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>32400</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>28800</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>24100</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>32500</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AL41" s="3">
         <v>27600</v>
       </c>
-      <c r="AL41" s="3">
+      <c r="AM41" s="3">
         <v>22600</v>
       </c>
-      <c r="AM41" s="3">
+      <c r="AN41" s="3">
         <v>19900</v>
       </c>
-      <c r="AN41" s="3">
+      <c r="AO41" s="3">
         <v>28800</v>
       </c>
     </row>
-    <row r="42" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>1500</v>
+      </c>
+      <c r="E42" s="3">
         <v>2500</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>4700</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>7400</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>10600</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>10200</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>21800</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>25300</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>23100</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>37200</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>37000</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>26700</v>
       </c>
-      <c r="O42" s="3">
-        <v>0</v>
-      </c>
       <c r="P42" s="3">
         <v>0</v>
       </c>
@@ -4278,124 +4367,130 @@
       <c r="AN42" s="3">
         <v>0</v>
       </c>
+      <c r="AO42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>127900</v>
+      </c>
+      <c r="E43" s="3">
         <v>129700</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>125300</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>124300</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>125800</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>113800</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>120000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>118100</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>113300</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>113100</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>109600</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>103500</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>101300</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>86600</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>76900</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>69100</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>68400</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>45900</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>46700</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>49100</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>57200</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>57100</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>61600</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>49900</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>55300</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>50000</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>52000</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>55400</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>58100</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>57100</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>53100</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>57200</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>58300</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AK43" s="3">
         <v>53300</v>
-      </c>
-      <c r="AK43" s="3">
-        <v>52300</v>
       </c>
       <c r="AL43" s="3">
         <v>52300</v>
       </c>
       <c r="AM43" s="3">
+        <v>52300</v>
+      </c>
+      <c r="AN43" s="3">
         <v>53100</v>
       </c>
-      <c r="AN43" s="3">
+      <c r="AO43" s="3">
         <v>50400</v>
       </c>
     </row>
-    <row r="44" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -4432,8 +4527,8 @@
       <c r="N44" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O44" s="3">
-        <v>0</v>
+      <c r="O44" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="P44" s="3">
         <v>0</v>
@@ -4510,163 +4605,169 @@
       <c r="AN44" s="3">
         <v>0</v>
       </c>
+      <c r="AO44" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="45" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>163500</v>
+      </c>
+      <c r="E45" s="3">
         <v>157800</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>179500</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>190000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>517800</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>520700</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>285900</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>371500</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>94800</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>111800</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>93500</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>113500</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>127000</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>142800</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>106000</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>96300</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>84800</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>39200</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>39500</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>42900</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>13000</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>39300</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>38200</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>36300</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>7500</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>10100</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>10300</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>14100</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>12800</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>17400</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>14200</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>20300</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AJ45" s="3">
         <v>16400</v>
       </c>
-      <c r="AJ45" s="3">
+      <c r="AK45" s="3">
         <v>12800</v>
       </c>
-      <c r="AK45" s="3">
+      <c r="AL45" s="3">
         <v>10200</v>
       </c>
-      <c r="AL45" s="3">
+      <c r="AM45" s="3">
         <v>12800</v>
       </c>
-      <c r="AM45" s="3">
+      <c r="AN45" s="3">
         <v>9700</v>
       </c>
-      <c r="AN45" s="3">
+      <c r="AO45" s="3">
         <v>10800</v>
       </c>
     </row>
-    <row r="46" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>771200</v>
+      </c>
+      <c r="E46" s="3">
         <v>382300</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>497100</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>376700</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>787500</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>767800</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>586500</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>603800</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>272600</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>320300</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>375000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>296300</v>
       </c>
-      <c r="O46" s="3">
-        <v>0</v>
-      </c>
       <c r="P46" s="3">
         <v>0</v>
       </c>
@@ -4742,103 +4843,106 @@
       <c r="AN46" s="3">
         <v>0</v>
       </c>
+      <c r="AO46" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="47" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>364400</v>
+      </c>
+      <c r="E47" s="3">
         <v>374900</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>390800</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>20300</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>19500</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>18800</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>10000</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>9600</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>9100</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>10200</v>
-      </c>
-      <c r="M47" s="3">
-        <v>10300</v>
       </c>
       <c r="N47" s="3">
         <v>10300</v>
       </c>
       <c r="O47" s="3">
+        <v>10300</v>
+      </c>
+      <c r="P47" s="3">
         <v>10400</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>10600</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>10400</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>136800</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>136900</v>
-      </c>
-      <c r="T47" s="3">
-        <v>138000</v>
       </c>
       <c r="U47" s="3">
         <v>138000</v>
       </c>
       <c r="V47" s="3">
+        <v>138000</v>
+      </c>
+      <c r="W47" s="3">
         <v>13000</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>12800</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>13100</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>13200</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>12100</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>12600</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>12900</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>12700</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>13300</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>13500</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>13800</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AH47" s="3">
         <v>13900</v>
-      </c>
-      <c r="AH47" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AI47" s="3" t="s">
         <v>8</v>
@@ -4858,124 +4962,130 @@
       <c r="AN47" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AO47" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="48" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>5347300</v>
+      </c>
+      <c r="E48" s="3">
         <v>5689600</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>5761700</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>6055300</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>6046500</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>6091000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>6098600</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>6305700</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>6358300</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>6397300</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>6426100</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>6508700</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>6571400</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>6621600</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>6617800</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>6676800</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>6707500</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>2308000</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>2343700</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>2358900</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>2415900</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>2347400</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>2380500</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>2404000</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>2447400</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>2514100</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>2716800</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>2911300</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>2941200</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>3051700</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>3076800</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>3194200</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>3293300</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>3320300</v>
       </c>
-      <c r="AK48" s="3">
+      <c r="AL48" s="3">
         <v>3331800</v>
       </c>
-      <c r="AL48" s="3">
+      <c r="AM48" s="3">
         <v>3399700</v>
       </c>
-      <c r="AM48" s="3">
+      <c r="AN48" s="3">
         <v>3435400</v>
       </c>
-      <c r="AN48" s="3">
+      <c r="AO48" s="3">
         <v>3458300</v>
       </c>
     </row>
-    <row r="49" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -5012,12 +5122,12 @@
       <c r="N49" s="3">
         <v>0</v>
       </c>
-      <c r="O49" s="3" t="s">
+      <c r="O49" s="3">
+        <v>0</v>
+      </c>
+      <c r="P49" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P49" s="3">
-        <v>0</v>
-      </c>
       <c r="Q49" s="3">
         <v>0</v>
       </c>
@@ -5067,31 +5177,34 @@
         <v>0</v>
       </c>
       <c r="AG49" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH49" s="3">
         <v>32300</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>39000</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>44000</v>
       </c>
-      <c r="AJ49" s="3">
+      <c r="AK49" s="3">
         <v>47900</v>
       </c>
-      <c r="AK49" s="3">
+      <c r="AL49" s="3">
         <v>53000</v>
       </c>
-      <c r="AL49" s="3">
+      <c r="AM49" s="3">
         <v>59300</v>
       </c>
-      <c r="AM49" s="3">
+      <c r="AN49" s="3">
         <v>65500</v>
       </c>
-      <c r="AN49" s="3">
+      <c r="AO49" s="3">
         <v>70000</v>
       </c>
     </row>
-    <row r="50" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -5206,8 +5319,11 @@
       <c r="AN50" s="3">
         <v>0</v>
       </c>
+      <c r="AO50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -5322,8 +5438,11 @@
       <c r="AN51" s="3">
         <v>0</v>
       </c>
+      <c r="AO51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -5360,86 +5479,89 @@
       <c r="N52" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O52" s="3">
+      <c r="O52" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P52" s="3">
         <v>416000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>450000</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>483000</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>520300</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>548600</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>78400</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>61400</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>62600</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>66100</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>71900</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>88300</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>91300</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>94600</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>86300</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>108700</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>180800</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>111100</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>115100</v>
-      </c>
-      <c r="AG52" s="3">
-        <v>79400</v>
       </c>
       <c r="AH52" s="3">
         <v>79400</v>
       </c>
       <c r="AI52" s="3">
+        <v>79400</v>
+      </c>
+      <c r="AJ52" s="3">
         <v>76400</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AK52" s="3">
         <v>76600</v>
       </c>
-      <c r="AK52" s="3">
+      <c r="AL52" s="3">
         <v>75400</v>
       </c>
-      <c r="AL52" s="3">
+      <c r="AM52" s="3">
         <v>76700</v>
       </c>
-      <c r="AM52" s="3">
+      <c r="AN52" s="3">
         <v>72800</v>
       </c>
-      <c r="AN52" s="3">
+      <c r="AO52" s="3">
         <v>72700</v>
       </c>
     </row>
-    <row r="53" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5554,124 +5676,130 @@
       <c r="AN53" s="3">
         <v>0</v>
       </c>
+      <c r="AO53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>6664500</v>
+      </c>
+      <c r="E54" s="3">
         <v>6647700</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>6858300</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>6682500</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>7091800</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>7129700</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>6958900</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>7204500</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>6944100</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>7052500</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>7165100</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>7196900</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>7342000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>7399900</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>7384900</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>7573700</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>7639600</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>2708900</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>2719200</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>2755300</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>2608500</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>2658100</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>2811800</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>2937400</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>2648900</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>2713900</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>2936300</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>3203200</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>3172000</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>3285900</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>3302200</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>3418900</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>3512500</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>3543400</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AL54" s="3">
         <v>3550300</v>
       </c>
-      <c r="AL54" s="3">
+      <c r="AM54" s="3">
         <v>3623500</v>
       </c>
-      <c r="AM54" s="3">
+      <c r="AN54" s="3">
         <v>3656400</v>
       </c>
-      <c r="AN54" s="3">
+      <c r="AO54" s="3">
         <v>3690900</v>
       </c>
     </row>
-    <row r="55" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5712,8 +5840,9 @@
       <c r="AL55" s="3"/>
       <c r="AM55" s="3"/>
       <c r="AN55" s="3"/>
+      <c r="AO55" s="3"/>
     </row>
-    <row r="56" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5754,163 +5883,167 @@
       <c r="AL56" s="3"/>
       <c r="AM56" s="3"/>
       <c r="AN56" s="3"/>
+      <c r="AO56" s="3"/>
     </row>
-    <row r="57" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>221100</v>
+      </c>
+      <c r="E57" s="3">
         <v>203100</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>179400</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>158900</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>198700</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>184000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>181800</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>162400</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>188000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>185700</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>164800</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>148100</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>207800</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>152000</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>133800</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>124200</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>185000</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>85700</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>74400</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>72100</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>77500</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>88600</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>85700</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>109400</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>69800</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>77500</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>66600</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>61900</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>85900</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>98500</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>101200</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>102900</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>78500</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AK57" s="3">
         <v>101600</v>
       </c>
-      <c r="AK57" s="3">
+      <c r="AL57" s="3">
         <v>88500</v>
       </c>
-      <c r="AL57" s="3">
+      <c r="AM57" s="3">
         <v>88800</v>
       </c>
-      <c r="AM57" s="3">
+      <c r="AN57" s="3">
         <v>80700</v>
       </c>
-      <c r="AN57" s="3">
+      <c r="AO57" s="3">
         <v>93400</v>
       </c>
     </row>
-    <row r="58" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>420400</v>
+      </c>
+      <c r="E58" s="3">
         <v>1300</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>82600</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>83900</v>
       </c>
-      <c r="G58" s="3">
-        <v>440400</v>
-      </c>
       <c r="H58" s="3">
+        <v>0</v>
+      </c>
+      <c r="I58" s="3">
         <v>1300</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>122600</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>273500</v>
       </c>
-      <c r="K58" s="3">
-        <v>0</v>
-      </c>
       <c r="L58" s="3">
+        <v>0</v>
+      </c>
+      <c r="M58" s="3">
         <v>1300</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>124200</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>125100</v>
       </c>
-      <c r="O58" s="3">
-        <v>0</v>
-      </c>
       <c r="P58" s="3">
         <v>0</v>
       </c>
@@ -5986,94 +6119,97 @@
       <c r="AN58" s="3">
         <v>0</v>
       </c>
+      <c r="AO58" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="59" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>11700</v>
+      </c>
+      <c r="E59" s="3">
         <v>4400</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>4900</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>4200</v>
       </c>
-      <c r="G59" s="3">
-        <v>15100</v>
-      </c>
       <c r="H59" s="3">
+        <v>500</v>
+      </c>
+      <c r="I59" s="3">
         <v>3800</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>3900</v>
-      </c>
-      <c r="J59" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="K59" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L59" s="3">
+      <c r="L59" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M59" s="3">
         <v>168000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>11400</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>14600</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>79300</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>78100</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>76000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>79200</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>70200</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>26200</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>26300</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>26400</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>26500</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>26600</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>26800</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>26900</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>27000</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>27100</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>27200</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>27300</v>
-      </c>
-      <c r="AE59" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AF59" s="3" t="s">
         <v>8</v>
@@ -6084,8 +6220,8 @@
       <c r="AH59" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AI59" s="3">
-        <v>0</v>
+      <c r="AI59" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AJ59" s="3">
         <v>0</v>
@@ -6102,47 +6238,50 @@
       <c r="AN59" s="3">
         <v>0</v>
       </c>
+      <c r="AO59" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="60" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>653200</v>
+      </c>
+      <c r="E60" s="3">
         <v>208800</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>267000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>247000</v>
       </c>
-      <c r="G60" s="3">
-        <v>654300</v>
-      </c>
       <c r="H60" s="3">
+        <v>199300</v>
+      </c>
+      <c r="I60" s="3">
         <v>189100</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>308300</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>435900</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>188000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>354900</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>300400</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>287800</v>
       </c>
-      <c r="O60" s="3">
-        <v>0</v>
-      </c>
       <c r="P60" s="3">
         <v>0</v>
       </c>
@@ -6218,162 +6357,168 @@
       <c r="AN60" s="3">
         <v>0</v>
       </c>
+      <c r="AO60" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="61" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>2670400</v>
+      </c>
+      <c r="E61" s="3">
         <v>3005500</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>3006900</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>2895200</v>
       </c>
-      <c r="G61" s="3">
-        <v>2857500</v>
-      </c>
       <c r="H61" s="3">
+        <v>3297900</v>
+      </c>
+      <c r="I61" s="3">
         <v>3311100</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>2969000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>2971700</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>2908200</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>2949700</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>2895300</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>2927500</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>3010300</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>3012900</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>3001200</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>3179100</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>3150800</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>1289000</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>1289400</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>1315200</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>1170800</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>1196100</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>1346300</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>1446500</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>1146600</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>1198600</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>1376600</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>1602600</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>1543300</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>1578300</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>1565400</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>1650500</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>1699200</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AK61" s="3">
         <v>1681700</v>
       </c>
-      <c r="AK61" s="3">
+      <c r="AL61" s="3">
         <v>1675100</v>
       </c>
-      <c r="AL61" s="3">
+      <c r="AM61" s="3">
         <v>1726900</v>
       </c>
-      <c r="AM61" s="3">
+      <c r="AN61" s="3">
         <v>1731100</v>
       </c>
-      <c r="AN61" s="3">
+      <c r="AO61" s="3">
         <v>1732300</v>
       </c>
     </row>
-    <row r="62" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>117700</v>
+      </c>
+      <c r="E62" s="3">
         <v>126800</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>130500</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>139800</v>
       </c>
-      <c r="G62" s="3">
-        <v>135800</v>
-      </c>
       <c r="H62" s="3">
+        <v>150400</v>
+      </c>
+      <c r="I62" s="3">
         <v>151900</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>154400</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>164400</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>168700</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>12000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>176500</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>182900</v>
-      </c>
-      <c r="O62" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="P62" s="3" t="s">
         <v>8</v>
@@ -6384,8 +6529,8 @@
       <c r="R62" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="S62" s="3">
-        <v>0</v>
+      <c r="S62" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="T62" s="3">
         <v>0</v>
@@ -6414,14 +6559,14 @@
       <c r="AB62" s="3">
         <v>0</v>
       </c>
-      <c r="AC62" s="3" t="s">
+      <c r="AC62" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD62" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>2400</v>
-      </c>
-      <c r="AE62" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AF62" s="3" t="s">
         <v>8</v>
@@ -6432,8 +6577,8 @@
       <c r="AH62" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AI62" s="3">
-        <v>0</v>
+      <c r="AI62" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AJ62" s="3">
         <v>0</v>
@@ -6450,8 +6595,11 @@
       <c r="AN62" s="3">
         <v>0</v>
       </c>
+      <c r="AO62" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="63" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6566,8 +6714,11 @@
       <c r="AN63" s="3">
         <v>0</v>
       </c>
+      <c r="AO63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6682,8 +6833,11 @@
       <c r="AN64" s="3">
         <v>0</v>
       </c>
+      <c r="AO64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6798,124 +6952,130 @@
       <c r="AN65" s="3">
         <v>0</v>
       </c>
+      <c r="AO65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>3472700</v>
+      </c>
+      <c r="E66" s="3">
         <v>3371700</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>3435800</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>3311000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>3679700</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>3681500</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>3459300</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>3598100</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>3300200</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>3347800</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>3405900</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>3428400</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>3575500</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>3527100</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>3493700</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>3675100</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>3717500</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>1510000</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>1505700</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>1523500</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>1377900</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>1416000</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>1563600</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>1684600</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>1359800</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>1411700</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>1583700</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>1816400</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>1759300</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>1807700</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>1802800</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>1893900</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>1947100</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>1958500</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AL66" s="3">
         <v>1940600</v>
       </c>
-      <c r="AL66" s="3">
+      <c r="AM66" s="3">
         <v>2004000</v>
       </c>
-      <c r="AM66" s="3">
+      <c r="AN66" s="3">
         <v>2012800</v>
       </c>
-      <c r="AN66" s="3">
+      <c r="AO66" s="3">
         <v>2046500</v>
       </c>
     </row>
-    <row r="67" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6956,8 +7116,9 @@
       <c r="AL67" s="3"/>
       <c r="AM67" s="3"/>
       <c r="AN67" s="3"/>
+      <c r="AO67" s="3"/>
     </row>
-    <row r="68" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -7072,8 +7233,11 @@
       <c r="AN68" s="3">
         <v>0</v>
       </c>
+      <c r="AO68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -7188,8 +7352,11 @@
       <c r="AN69" s="3">
         <v>0</v>
       </c>
+      <c r="AO69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -7304,8 +7471,11 @@
       <c r="AN70" s="3">
         <v>0</v>
       </c>
+      <c r="AO70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -7420,124 +7590,130 @@
       <c r="AN71" s="3">
         <v>0</v>
       </c>
+      <c r="AO71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-1563800</v>
+      </c>
+      <c r="E72" s="3">
         <v>-1654600</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-1579900</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-1630900</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-1595300</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-1557800</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-1517400</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-1413800</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-1373100</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-1326200</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-1275600</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-1255000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-1207800</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-1105800</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-1052000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-1021300</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-962900</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-849500</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-827300</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-812700</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-824300</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-810800</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>-801800</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>-797000</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>-770000</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>-758600</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>-712200</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>-683700</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>-662700</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>-604900</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>-582200</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>-554300</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>-509800</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>-485600</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AL72" s="3">
         <v>-459700</v>
       </c>
-      <c r="AL72" s="3">
+      <c r="AM72" s="3">
         <v>-444600</v>
       </c>
-      <c r="AM72" s="3">
+      <c r="AN72" s="3">
         <v>-419300</v>
       </c>
-      <c r="AN72" s="3">
+      <c r="AO72" s="3">
         <v>-397400</v>
       </c>
     </row>
-    <row r="73" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -7652,8 +7828,11 @@
       <c r="AN73" s="3">
         <v>0</v>
       </c>
+      <c r="AO73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7768,8 +7947,11 @@
       <c r="AN74" s="3">
         <v>0</v>
       </c>
+      <c r="AO74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -7884,124 +8066,130 @@
       <c r="AN75" s="3">
         <v>0</v>
       </c>
+      <c r="AO75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>3073600</v>
+      </c>
+      <c r="E76" s="3">
         <v>3172800</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>3317700</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>3268000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>3312100</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>3349400</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>3421600</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>3530800</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>3568100</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>3635300</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>3692800</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>3706000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>3766500</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>3872800</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>3891100</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>3898600</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>3922000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>1198800</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>1213500</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>1231900</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>1230700</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>1242100</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>1248200</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>1252800</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>1289000</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>1302200</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>1352700</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>1386800</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>1412700</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>1478200</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>1499400</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>1525000</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>1565400</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>1584900</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3">
         <v>1609700</v>
       </c>
-      <c r="AL76" s="3">
+      <c r="AM76" s="3">
         <v>1619500</v>
       </c>
-      <c r="AM76" s="3">
+      <c r="AN76" s="3">
         <v>1643600</v>
       </c>
-      <c r="AN76" s="3">
+      <c r="AO76" s="3">
         <v>1644400</v>
       </c>
     </row>
-    <row r="77" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -8116,245 +8304,254 @@
       <c r="AN77" s="3">
         <v>0</v>
       </c>
+      <c r="AO77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:41" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E80" s="2">
         <v>45930</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45838</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45747</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45657</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45565</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45473</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45382</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45291</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45199</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45107</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45016</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44926</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44834</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44742</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44651</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44561</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44469</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44377</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44286</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44196</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44104</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44012</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43921</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43830</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43738</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43646</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43555</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43465</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43373</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43281</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>43190</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>43100</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>43008</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>42916</v>
       </c>
-      <c r="AL80" s="2">
+      <c r="AM80" s="2">
         <v>42825</v>
       </c>
-      <c r="AM80" s="2">
+      <c r="AN80" s="2">
         <v>42735</v>
       </c>
-      <c r="AN80" s="2">
+      <c r="AO80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>180800</v>
+      </c>
+      <c r="E81" s="3">
         <v>-16200</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>110300</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>23700</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>21800</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>16700</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-48600</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>14200</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>8000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>2100</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>32100</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>5400</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-1100</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-7800</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>13100</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-16800</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-98200</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-7000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-200</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>24600</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-6800</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-4600</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-4800</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-100</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>15300</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>-19700</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>-1800</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>5700</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>-31200</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>3900</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>-1400</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>-17900</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>2300</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>-600</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>10200</v>
       </c>
-      <c r="AL81" s="3">
-        <v>0</v>
-      </c>
       <c r="AM81" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN81" s="3">
         <v>3400</v>
       </c>
-      <c r="AN81" s="3">
+      <c r="AO81" s="3">
         <v>-1700</v>
       </c>
     </row>
-    <row r="82" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -8395,124 +8592,128 @@
       <c r="AL82" s="3"/>
       <c r="AM82" s="3"/>
       <c r="AN82" s="3"/>
+      <c r="AO82" s="3"/>
     </row>
-    <row r="83" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>76200</v>
+      </c>
+      <c r="E83" s="3">
         <v>75700</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>77300</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>79100</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>76300</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>75900</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>77700</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>79600</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>78000</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>79200</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>78300</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>79800</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>113700</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>116600</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>119300</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>123300</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>110600</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>30800</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>30500</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>31200</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>32300</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>34400</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>32000</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>32100</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>31400</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>32600</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>35600</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>35300</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>38000</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>37500</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>41300</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>39200</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>41400</v>
       </c>
-      <c r="AJ83" s="3">
+      <c r="AK83" s="3">
         <v>43500</v>
       </c>
-      <c r="AK83" s="3">
+      <c r="AL83" s="3">
         <v>43400</v>
       </c>
-      <c r="AL83" s="3">
+      <c r="AM83" s="3">
         <v>46400</v>
       </c>
-      <c r="AM83" s="3">
+      <c r="AN83" s="3">
         <v>43700</v>
       </c>
-      <c r="AN83" s="3">
+      <c r="AO83" s="3">
         <v>47700</v>
       </c>
     </row>
-    <row r="84" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -8627,8 +8828,11 @@
       <c r="AN84" s="3">
         <v>0</v>
       </c>
+      <c r="AO84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -8743,8 +8947,11 @@
       <c r="AN85" s="3">
         <v>0</v>
       </c>
+      <c r="AO85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -8859,8 +9066,11 @@
       <c r="AN86" s="3">
         <v>0</v>
       </c>
+      <c r="AO86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -8975,8 +9185,11 @@
       <c r="AN87" s="3">
         <v>0</v>
       </c>
+      <c r="AO87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -9091,124 +9304,130 @@
       <c r="AN88" s="3">
         <v>0</v>
       </c>
+      <c r="AO88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>106600</v>
+      </c>
+      <c r="E89" s="3">
         <v>116200</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>132800</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>74100</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>111000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>112400</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>142100</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>53600</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>103500</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>110800</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>116800</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>63600</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>116900</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>108100</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>104700</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>49600</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-3500</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>36400</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>36100</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>31300</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>9800</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>35900</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>28000</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>21900</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>31800</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>36500</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>37300</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>32300</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>35400</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>37000</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>45800</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>36300</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>30800</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>42700</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AL89" s="3">
         <v>44900</v>
       </c>
-      <c r="AL89" s="3">
+      <c r="AM89" s="3">
         <v>36200</v>
       </c>
-      <c r="AM89" s="3">
+      <c r="AN89" s="3">
         <v>34200</v>
       </c>
-      <c r="AN89" s="3">
+      <c r="AO89" s="3">
         <v>39800</v>
       </c>
     </row>
-    <row r="90" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -9249,124 +9468,128 @@
       <c r="AL90" s="3"/>
       <c r="AM90" s="3"/>
       <c r="AN90" s="3"/>
+      <c r="AO90" s="3"/>
     </row>
-    <row r="91" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-38000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-30800</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-48900</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-34400</v>
       </c>
-      <c r="G91" s="3">
-        <v>-39000</v>
-      </c>
       <c r="H91" s="3">
+        <v>-33600</v>
+      </c>
+      <c r="I91" s="3">
         <v>-36900</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-41700</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-28200</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-43900</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-30900</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-28600</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-39100</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-52000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-47800</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-35000</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-23800</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-20400</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-15700</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-13300</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-7900</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-7600</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-8200</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-9200</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-13200</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-15700</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-12400</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-13700</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-11500</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-12000</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-12700</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-16500</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-18100</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-10800</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AK91" s="3">
         <v>-24800</v>
       </c>
-      <c r="AK91" s="3">
+      <c r="AL91" s="3">
         <v>-11200</v>
       </c>
-      <c r="AL91" s="3">
+      <c r="AM91" s="3">
         <v>-47700</v>
       </c>
-      <c r="AM91" s="3">
+      <c r="AN91" s="3">
         <v>-26000</v>
       </c>
-      <c r="AN91" s="3">
+      <c r="AO91" s="3">
         <v>-24100</v>
       </c>
     </row>
-    <row r="92" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -9481,8 +9704,11 @@
       <c r="AN92" s="3">
         <v>0</v>
       </c>
+      <c r="AO92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -9597,124 +9823,130 @@
       <c r="AN93" s="3">
         <v>0</v>
       </c>
+      <c r="AO93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>433700</v>
+      </c>
+      <c r="E94" s="3">
         <v>1800</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-49800</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>227800</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-29500</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-314900</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>134700</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-289300</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-26200</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-63500</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>49500</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-41500</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-31500</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-82300</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>130800</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-62200</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>18000</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-9600</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-133300</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>33900</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-64900</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>4700</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-13500</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-7100</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>52800</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>166900</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>226600</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-29700</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>44700</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-14500</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>71800</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>46400</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-23200</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>-16500</v>
       </c>
-      <c r="AK94" s="3">
+      <c r="AL94" s="3">
         <v>38100</v>
       </c>
-      <c r="AL94" s="3">
+      <c r="AM94" s="3">
         <v>1400</v>
       </c>
-      <c r="AM94" s="3">
+      <c r="AN94" s="3">
         <v>-15600</v>
       </c>
-      <c r="AN94" s="3">
+      <c r="AO94" s="3">
         <v>-22200</v>
       </c>
     </row>
-    <row r="95" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -9755,25 +9987,26 @@
       <c r="AL95" s="3"/>
       <c r="AM95" s="3"/>
       <c r="AN95" s="3"/>
+      <c r="AO95" s="3"/>
     </row>
-    <row r="96" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>59400</v>
+        <v>58500</v>
       </c>
       <c r="E96" s="3">
         <v>59400</v>
       </c>
       <c r="F96" s="3">
+        <v>59400</v>
+      </c>
+      <c r="G96" s="3">
         <v>59300</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>57100</v>
-      </c>
-      <c r="H96" s="3">
-        <v>54900</v>
       </c>
       <c r="I96" s="3">
         <v>54900</v>
@@ -9782,55 +10015,55 @@
         <v>54900</v>
       </c>
       <c r="K96" s="3">
-        <v>52700</v>
+        <v>54900</v>
       </c>
       <c r="L96" s="3">
         <v>52700</v>
       </c>
       <c r="M96" s="3">
-        <v>52600</v>
+        <v>52700</v>
       </c>
       <c r="N96" s="3">
         <v>52600</v>
       </c>
       <c r="O96" s="3">
+        <v>52600</v>
+      </c>
+      <c r="P96" s="3">
         <v>-48200</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>-46000</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="R96" s="3">
         <v>-43800</v>
       </c>
-      <c r="R96" s="3">
+      <c r="S96" s="3">
         <v>-41600</v>
-      </c>
-      <c r="S96" s="3">
-        <v>-15200</v>
       </c>
       <c r="T96" s="3">
         <v>-15200</v>
       </c>
       <c r="U96" s="3">
+        <v>-15200</v>
+      </c>
+      <c r="V96" s="3">
         <v>-14400</v>
       </c>
-      <c r="V96" s="3">
+      <c r="W96" s="3">
         <v>-13000</v>
       </c>
-      <c r="W96" s="3">
+      <c r="X96" s="3">
         <v>-6700</v>
       </c>
-      <c r="X96" s="3">
+      <c r="Y96" s="3">
         <v>-4400</v>
       </c>
-      <c r="Y96" s="3">
+      <c r="Z96" s="3">
         <v>-26700</v>
       </c>
-      <c r="Z96" s="3">
+      <c r="AA96" s="3">
         <v>-300</v>
-      </c>
-      <c r="AA96" s="3">
-        <v>-26700</v>
       </c>
       <c r="AB96" s="3">
         <v>-26700</v>
@@ -9839,10 +10072,10 @@
         <v>-26700</v>
       </c>
       <c r="AD96" s="3">
+        <v>-26700</v>
+      </c>
+      <c r="AE96" s="3">
         <v>-53300</v>
-      </c>
-      <c r="AE96" s="3">
-        <v>-26600</v>
       </c>
       <c r="AF96" s="3">
         <v>-26600</v>
@@ -9851,10 +10084,10 @@
         <v>-26600</v>
       </c>
       <c r="AH96" s="3">
+        <v>-26600</v>
+      </c>
+      <c r="AI96" s="3">
         <v>-26500</v>
-      </c>
-      <c r="AI96" s="3">
-        <v>-25300</v>
       </c>
       <c r="AJ96" s="3">
         <v>-25300</v>
@@ -9866,13 +10099,16 @@
         <v>-25300</v>
       </c>
       <c r="AM96" s="3">
-        <v>-24000</v>
+        <v>-25300</v>
       </c>
       <c r="AN96" s="3">
         <v>-24000</v>
       </c>
+      <c r="AO96" s="3">
+        <v>-24000</v>
+      </c>
     </row>
-    <row r="97" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -9987,8 +10223,11 @@
       <c r="AN97" s="3">
         <v>0</v>
       </c>
+      <c r="AO97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -10103,8 +10342,11 @@
       <c r="AN98" s="3">
         <v>0</v>
       </c>
+      <c r="AO98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -10219,124 +10461,130 @@
       <c r="AN99" s="3">
         <v>0</v>
       </c>
+      <c r="AO99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-154400</v>
+      </c>
+      <c r="E100" s="3">
         <v>-213300</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>49700</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-380300</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-71200</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>166800</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-206800</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>283300</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-94100</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-123900</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-84100</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-91400</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-59900</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-28400</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-218600</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-5600</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-18000</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-17100</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-41200</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>120800</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-35600</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-155100</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-128300</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>298000</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-81800</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-212900</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-256400</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>3800</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-75600</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-24800</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-112800</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>-76300</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>-16800</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>-19700</v>
       </c>
-      <c r="AK100" s="3">
+      <c r="AL100" s="3">
         <v>-78700</v>
       </c>
-      <c r="AL100" s="3">
+      <c r="AM100" s="3">
         <v>-34200</v>
       </c>
-      <c r="AM100" s="3">
+      <c r="AN100" s="3">
         <v>-27600</v>
       </c>
-      <c r="AN100" s="3">
+      <c r="AO100" s="3">
         <v>-26600</v>
       </c>
     </row>
-    <row r="101" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -10373,8 +10621,8 @@
       <c r="N101" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O101" s="3">
-        <v>0</v>
+      <c r="O101" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="P101" s="3">
         <v>0</v>
@@ -10451,120 +10699,126 @@
       <c r="AN101" s="3">
         <v>0</v>
       </c>
+      <c r="AO101" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="102" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>385900</v>
+      </c>
+      <c r="E102" s="3">
         <v>-95400</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>132700</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-78400</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>10300</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-35700</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>70000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>47500</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-16900</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-76600</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>82300</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-69300</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>25500</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-2600</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>17000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-18200</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-3400</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>9700</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-138500</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>185900</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-90700</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-114500</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-113800</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>312800</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>2800</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-9500</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>7600</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>6400</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>4500</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>-2300</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>4800</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>6400</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>-8400</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>4800</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AL102" s="3">
         <v>4400</v>
       </c>
-      <c r="AL102" s="3">
+      <c r="AM102" s="3">
         <v>3300</v>
       </c>
-      <c r="AM102" s="3">
+      <c r="AN102" s="3">
         <v>-8900</v>
       </c>
-      <c r="AN102" s="3">
+      <c r="AO102" s="3">
         <v>-9100</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/KRG_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/KRG_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="199" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="203" uniqueCount="92">
   <si>
     <t>KRG</t>
   </si>
@@ -656,530 +656,543 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AO102"/>
+  <dimension ref="A5:AP102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="37" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="38" max="38" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="39" max="39" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="40" max="41" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="42" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="38" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="39" max="39" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="40" max="40" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="41" max="42" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="43" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:42" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E7" s="2">
         <v>46022</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45930</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45838</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45747</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45657</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45565</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45473</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45382</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45291</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45199</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45107</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>45016</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44926</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44834</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44742</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44651</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44561</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44469</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44377</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44286</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44196</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44104</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>44012</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43921</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43830</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43738</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43646</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43555</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43465</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43373</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>43281</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>43190</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>43100</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>43008</v>
       </c>
-      <c r="AL7" s="2">
+      <c r="AM7" s="2">
         <v>42916</v>
       </c>
-      <c r="AM7" s="2">
+      <c r="AN7" s="2">
         <v>42825</v>
       </c>
-      <c r="AN7" s="2">
+      <c r="AO7" s="2">
         <v>42735</v>
       </c>
-      <c r="AO7" s="2">
+      <c r="AP7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>200700</v>
+      </c>
+      <c r="E8" s="3">
         <v>204200</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>205100</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>213400</v>
       </c>
-      <c r="G8" s="3">
-        <v>221800</v>
-      </c>
       <c r="H8" s="3">
+        <v>221100</v>
+      </c>
+      <c r="I8" s="3">
         <v>212200</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>207300</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>210600</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>207400</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>200300</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>207200</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>208800</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>206800</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>204700</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>200300</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>202600</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>194400</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>163000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>71500</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>69500</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>69400</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>68400</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>65100</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>63300</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>69900</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>75200</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>74900</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>81500</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>83500</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>86900</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>85700</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>91700</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>89800</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>88900</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AL8" s="3">
         <v>87100</v>
       </c>
-      <c r="AL8" s="3">
+      <c r="AM8" s="3">
         <v>92600</v>
       </c>
-      <c r="AM8" s="3">
+      <c r="AN8" s="3">
         <v>90100</v>
       </c>
-      <c r="AN8" s="3">
+      <c r="AO8" s="3">
         <v>88900</v>
       </c>
-      <c r="AO8" s="3">
+      <c r="AP8" s="3">
         <v>89100</v>
       </c>
     </row>
-    <row r="9" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>55900</v>
+      </c>
+      <c r="E9" s="3">
         <v>53300</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>54200</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>55500</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>57600</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>54800</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>53000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>55100</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>54600</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>47900</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>54100</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>53900</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>54500</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>53800</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>51200</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>54000</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>52800</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>47500</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>19100</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>18800</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>19700</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>19900</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>19700</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>17600</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>19700</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>20600</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>20700</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>21400</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>21600</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>23200</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>23300</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>23000</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>23200</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AK9" s="3">
         <v>23500</v>
       </c>
-      <c r="AK9" s="3">
+      <c r="AL9" s="3">
         <v>22700</v>
       </c>
-      <c r="AL9" s="3">
+      <c r="AM9" s="3">
         <v>23400</v>
       </c>
-      <c r="AM9" s="3">
+      <c r="AN9" s="3">
         <v>23300</v>
       </c>
-      <c r="AN9" s="3">
+      <c r="AO9" s="3">
         <v>23000</v>
       </c>
-      <c r="AO9" s="3">
+      <c r="AP9" s="3">
         <v>22600</v>
       </c>
     </row>
-    <row r="10" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>150800</v>
+        <v>144800</v>
       </c>
       <c r="E10" s="3">
         <v>150800</v>
       </c>
       <c r="F10" s="3">
+        <v>150800</v>
+      </c>
+      <c r="G10" s="3">
         <v>157900</v>
       </c>
-      <c r="G10" s="3">
-        <v>164200</v>
-      </c>
       <c r="H10" s="3">
+        <v>163500</v>
+      </c>
+      <c r="I10" s="3">
         <v>157400</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>154300</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>155500</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>152800</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>152400</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>153100</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>154800</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>152300</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>150900</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>149100</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>148600</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>141600</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>115500</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>52400</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>50700</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>49700</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>48500</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>45400</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>45700</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>50200</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>54600</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>54200</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>60100</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>61900</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>63700</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>62400</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>68700</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>66600</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AK10" s="3">
         <v>65400</v>
       </c>
-      <c r="AK10" s="3">
+      <c r="AL10" s="3">
         <v>64400</v>
       </c>
-      <c r="AL10" s="3">
+      <c r="AM10" s="3">
         <v>69200</v>
       </c>
-      <c r="AM10" s="3">
+      <c r="AN10" s="3">
         <v>66800</v>
       </c>
-      <c r="AN10" s="3">
+      <c r="AO10" s="3">
         <v>65900</v>
       </c>
-      <c r="AO10" s="3">
+      <c r="AP10" s="3">
         <v>66500</v>
       </c>
     </row>
-    <row r="11" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1221,8 +1234,9 @@
       <c r="AM11" s="3"/>
       <c r="AN11" s="3"/>
       <c r="AO11" s="3"/>
+      <c r="AP11" s="3"/>
     </row>
-    <row r="12" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1340,8 +1354,11 @@
       <c r="AO12" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AP12" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="13" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1459,74 +1476,77 @@
       <c r="AO13" s="3">
         <v>0</v>
       </c>
+      <c r="AP13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>2300</v>
+      </c>
+      <c r="E14" s="3">
         <v>-173400</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>25800</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>-103500</v>
       </c>
-      <c r="G14" s="3">
-        <v>-4100</v>
-      </c>
       <c r="H14" s="3">
+        <v>-4800</v>
+      </c>
+      <c r="I14" s="3">
         <v>-7900</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>-5000</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>61300</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>-5700</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>-500</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>5500</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>-28700</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>-400</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>-100</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>100</v>
       </c>
-      <c r="R14" s="3">
-        <v>0</v>
-      </c>
       <c r="S14" s="3">
+        <v>0</v>
+      </c>
+      <c r="T14" s="3">
         <v>900</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>76600</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>9200</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>800</v>
       </c>
-      <c r="W14" s="3" t="s">
+      <c r="X14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="X14" s="3">
-        <v>0</v>
-      </c>
       <c r="Y14" s="3">
         <v>0</v>
       </c>
@@ -1537,32 +1557,32 @@
         <v>0</v>
       </c>
       <c r="AB14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC14" s="3">
         <v>2000</v>
       </c>
-      <c r="AC14" s="3">
+      <c r="AD14" s="3">
         <v>15600</v>
       </c>
-      <c r="AD14" s="3">
+      <c r="AE14" s="3">
         <v>27700</v>
       </c>
-      <c r="AE14" s="3">
+      <c r="AF14" s="3">
         <v>4100</v>
       </c>
-      <c r="AF14" s="3">
+      <c r="AG14" s="3">
         <v>31500</v>
       </c>
-      <c r="AG14" s="3">
-        <v>0</v>
-      </c>
       <c r="AH14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI14" s="3">
         <v>14800</v>
       </c>
-      <c r="AI14" s="3">
+      <c r="AJ14" s="3">
         <v>24100</v>
       </c>
-      <c r="AJ14" s="3">
-        <v>0</v>
-      </c>
       <c r="AK14" s="3">
         <v>0</v>
       </c>
@@ -1570,135 +1590,141 @@
         <v>0</v>
       </c>
       <c r="AM14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN14" s="3">
         <v>7400</v>
       </c>
-      <c r="AN14" s="3">
+      <c r="AO14" s="3">
         <v>2800</v>
       </c>
-      <c r="AO14" s="3" t="s">
+      <c r="AP14" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="15" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>82500</v>
+      </c>
+      <c r="E15" s="3">
         <v>87800</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>89400</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>97900</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>98200</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>97000</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>96700</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>99300</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>100400</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>102900</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>105900</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>109500</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>108100</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>112700</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>115800</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>119800</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>121500</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>109800</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>30200</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>29800</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>30600</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>31800</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="Z15" s="3">
         <v>34000</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AA15" s="3">
         <v>31400</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AB15" s="3">
         <v>31500</v>
       </c>
-      <c r="AB15" s="3">
+      <c r="AC15" s="3">
         <v>30800</v>
       </c>
-      <c r="AC15" s="3">
+      <c r="AD15" s="3">
         <v>32000</v>
       </c>
-      <c r="AD15" s="3">
+      <c r="AE15" s="3">
         <v>34700</v>
       </c>
-      <c r="AE15" s="3">
+      <c r="AF15" s="3">
         <v>34600</v>
       </c>
-      <c r="AF15" s="3">
+      <c r="AG15" s="3">
         <v>36300</v>
       </c>
-      <c r="AG15" s="3">
+      <c r="AH15" s="3">
         <v>36900</v>
       </c>
-      <c r="AH15" s="3">
+      <c r="AI15" s="3">
         <v>40500</v>
       </c>
-      <c r="AI15" s="3">
+      <c r="AJ15" s="3">
         <v>38600</v>
       </c>
-      <c r="AJ15" s="3">
+      <c r="AK15" s="3">
         <v>40800</v>
       </c>
-      <c r="AK15" s="3">
+      <c r="AL15" s="3">
         <v>42800</v>
       </c>
-      <c r="AL15" s="3">
+      <c r="AM15" s="3">
         <v>42700</v>
       </c>
-      <c r="AM15" s="3">
+      <c r="AN15" s="3">
         <v>45800</v>
       </c>
-      <c r="AN15" s="3">
+      <c r="AO15" s="3">
         <v>42900</v>
       </c>
-      <c r="AO15" s="3">
+      <c r="AP15" s="3">
         <v>45500</v>
       </c>
     </row>
-    <row r="16" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:42" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1737,246 +1763,253 @@
       <c r="AM16" s="3"/>
       <c r="AN16" s="3"/>
       <c r="AO16" s="3"/>
+      <c r="AP16" s="3"/>
     </row>
-    <row r="17" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>152400</v>
+      </c>
+      <c r="E17" s="3">
         <v>156700</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>157800</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>166800</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>168100</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>165400</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>162900</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>167300</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>167800</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>165100</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>173900</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>177900</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>176000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>179400</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>182000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>163600</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>185400</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>240600</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>65500</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>57400</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>31400</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>62700</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>56900</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>54900</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>57100</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>47000</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>80700</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>66700</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>60500</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>92500</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>65000</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>83800</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>91800</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>54400</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>70900</v>
       </c>
-      <c r="AL17" s="3">
+      <c r="AM17" s="3">
         <v>71600</v>
       </c>
-      <c r="AM17" s="3">
+      <c r="AN17" s="3">
         <v>82000</v>
       </c>
-      <c r="AN17" s="3">
+      <c r="AO17" s="3">
         <v>71300</v>
       </c>
-      <c r="AO17" s="3">
+      <c r="AP17" s="3">
         <v>73200</v>
       </c>
     </row>
-    <row r="18" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>48300</v>
+      </c>
+      <c r="E18" s="3">
         <v>47400</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>47300</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>46600</v>
       </c>
-      <c r="G18" s="3">
-        <v>53700</v>
-      </c>
       <c r="H18" s="3">
+        <v>53000</v>
+      </c>
+      <c r="I18" s="3">
         <v>46800</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>44400</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>43300</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>39700</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>35200</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>33300</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>30900</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>30800</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>25300</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>18300</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>39000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>9000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-77600</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>6000</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>12100</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>38000</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>5700</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>8200</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>8400</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>12800</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>28200</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>-5800</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>14800</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>23000</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>-5600</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>20700</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>7900</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>-2000</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>34500</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3">
         <v>16200</v>
       </c>
-      <c r="AL18" s="3">
+      <c r="AM18" s="3">
         <v>21000</v>
       </c>
-      <c r="AM18" s="3">
+      <c r="AN18" s="3">
         <v>8100</v>
       </c>
-      <c r="AN18" s="3">
+      <c r="AO18" s="3">
         <v>17600</v>
       </c>
-      <c r="AO18" s="3">
+      <c r="AP18" s="3">
         <v>15900</v>
       </c>
     </row>
-    <row r="19" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -2018,82 +2051,83 @@
       <c r="AM19" s="3"/>
       <c r="AN19" s="3"/>
       <c r="AO19" s="3"/>
+      <c r="AP19" s="3"/>
     </row>
-    <row r="20" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>2200</v>
+      </c>
+      <c r="E20" s="3">
         <v>3200</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>4600</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>3200</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>600</v>
       </c>
-      <c r="H20" s="3">
-        <v>0</v>
-      </c>
       <c r="I20" s="3">
+        <v>0</v>
+      </c>
+      <c r="J20" s="3">
         <v>600</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>200</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>400</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-200</v>
       </c>
-      <c r="M20" s="3">
-        <v>0</v>
-      </c>
       <c r="N20" s="3">
+        <v>0</v>
+      </c>
+      <c r="O20" s="3">
         <v>-100</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>200</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>400</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>100</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-200</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-100</v>
-      </c>
-      <c r="T20" s="3">
-        <v>100</v>
       </c>
       <c r="U20" s="3">
         <v>100</v>
       </c>
       <c r="V20" s="3">
+        <v>100</v>
+      </c>
+      <c r="W20" s="3">
         <v>300</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-200</v>
       </c>
-      <c r="X20" s="3">
-        <v>0</v>
-      </c>
       <c r="Y20" s="3">
         <v>0</v>
       </c>
       <c r="Z20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA20" s="3">
         <v>400</v>
-      </c>
-      <c r="AA20" s="3">
-        <v>-100</v>
       </c>
       <c r="AB20" s="3">
         <v>-100</v>
@@ -2102,266 +2136,272 @@
         <v>-100</v>
       </c>
       <c r="AD20" s="3">
-        <v>-200</v>
+        <v>-100</v>
       </c>
       <c r="AE20" s="3">
         <v>-200</v>
       </c>
       <c r="AF20" s="3">
+        <v>-200</v>
+      </c>
+      <c r="AG20" s="3">
         <v>-8300</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>-300</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>7700</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>300</v>
       </c>
-      <c r="AJ20" s="3">
+      <c r="AK20" s="3">
         <v>-15200</v>
       </c>
-      <c r="AK20" s="3">
+      <c r="AL20" s="3">
         <v>-100</v>
       </c>
-      <c r="AL20" s="3">
+      <c r="AM20" s="3">
         <v>6300</v>
       </c>
-      <c r="AM20" s="3">
+      <c r="AN20" s="3">
         <v>8700</v>
       </c>
-      <c r="AN20" s="3">
+      <c r="AO20" s="3">
         <v>4000</v>
       </c>
-      <c r="AO20" s="3">
+      <c r="AP20" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>132000</v>
+        <v>128600</v>
       </c>
       <c r="E21" s="3">
         <v>132000</v>
       </c>
       <c r="F21" s="3">
+        <v>132000</v>
+      </c>
+      <c r="G21" s="3">
         <v>141200</v>
       </c>
-      <c r="G21" s="3">
-        <v>151300</v>
-      </c>
       <c r="H21" s="3">
+        <v>150600</v>
+      </c>
+      <c r="I21" s="3">
         <v>143900</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>140400</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>142400</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>139600</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>138300</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>139200</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>140400</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>138600</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>139500</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>135000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>158200</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>132200</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>33100</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>37000</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>42900</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>69000</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>38000</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>42600</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>40700</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>44800</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>59500</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>26800</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>50200</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>58100</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>24100</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>57900</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>57000</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>37500</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>60600</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AL21" s="3">
         <v>59600</v>
       </c>
-      <c r="AL21" s="3">
+      <c r="AM21" s="3">
         <v>70700</v>
       </c>
-      <c r="AM21" s="3">
+      <c r="AN21" s="3">
         <v>63200</v>
       </c>
-      <c r="AN21" s="3">
+      <c r="AO21" s="3">
         <v>65300</v>
       </c>
-      <c r="AO21" s="3">
+      <c r="AP21" s="3">
         <v>63500</v>
       </c>
     </row>
-    <row r="22" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>31700</v>
+      </c>
+      <c r="E22" s="3">
         <v>32400</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>33200</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>34100</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>33000</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>32700</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>31600</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>31000</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>30400</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>27200</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>25500</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>27200</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>25400</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>26800</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>26200</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>25700</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>25500</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>23100</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>12900</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>12300</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>12200</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>12300</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>12600</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>13300</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>12300</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>12400</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>14300</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>16100</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>16500</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>17600</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AH22" s="3">
         <v>16100</v>
       </c>
-      <c r="AH22" s="3">
+      <c r="AI22" s="3">
         <v>16700</v>
       </c>
-      <c r="AI22" s="3">
+      <c r="AJ22" s="3">
         <v>16300</v>
       </c>
-      <c r="AJ22" s="3">
+      <c r="AK22" s="3">
         <v>16500</v>
-      </c>
-      <c r="AK22" s="3">
-        <v>16400</v>
       </c>
       <c r="AL22" s="3">
         <v>16400</v>
@@ -2370,188 +2410,194 @@
         <v>16400</v>
       </c>
       <c r="AN22" s="3">
+        <v>16400</v>
+      </c>
+      <c r="AO22" s="3">
         <v>17600</v>
       </c>
-      <c r="AO22" s="3">
+      <c r="AP22" s="3">
         <v>17100</v>
       </c>
     </row>
-    <row r="23" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>12100</v>
+      </c>
+      <c r="E23" s="3">
         <v>185200</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-16300</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>112800</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>24300</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>22000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>17100</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-49200</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>14600</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>8600</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>2200</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>32500</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>5500</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-1100</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-7900</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>13100</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-16600</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-100500</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-6700</v>
       </c>
-      <c r="V23" s="3">
-        <v>0</v>
-      </c>
       <c r="W23" s="3">
+        <v>0</v>
+      </c>
+      <c r="X23" s="3">
         <v>25600</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-6600</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-4400</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>-4600</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>400</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>15700</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>-20100</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>-1500</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>6300</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>-31600</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>4300</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>-1100</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>-18000</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>2800</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>-200</v>
       </c>
-      <c r="AL23" s="3">
+      <c r="AM23" s="3">
         <v>10900</v>
       </c>
-      <c r="AM23" s="3">
+      <c r="AN23" s="3">
         <v>400</v>
       </c>
-      <c r="AN23" s="3">
+      <c r="AO23" s="3">
         <v>4000</v>
       </c>
-      <c r="AO23" s="3">
+      <c r="AP23" s="3">
         <v>-1200</v>
       </c>
     </row>
-    <row r="24" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>400</v>
+      </c>
+      <c r="E24" s="3">
         <v>200</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>100</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>200</v>
       </c>
-      <c r="G24" s="3">
-        <v>0</v>
-      </c>
       <c r="H24" s="3">
+        <v>0</v>
+      </c>
+      <c r="I24" s="3">
         <v>-200</v>
       </c>
-      <c r="I24" s="3">
-        <v>0</v>
-      </c>
       <c r="J24" s="3">
+        <v>0</v>
+      </c>
+      <c r="K24" s="3">
         <v>100</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>200</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>400</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>100</v>
       </c>
-      <c r="N24" s="3">
-        <v>0</v>
-      </c>
       <c r="O24" s="3">
         <v>0</v>
       </c>
       <c r="P24" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q24" s="3">
         <v>300</v>
       </c>
-      <c r="Q24" s="3">
-        <v>0</v>
-      </c>
       <c r="R24" s="3">
+        <v>0</v>
+      </c>
+      <c r="S24" s="3">
         <v>-200</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>-100</v>
       </c>
-      <c r="T24" s="3">
-        <v>0</v>
-      </c>
       <c r="U24" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="V24" s="3">
         <v>-100</v>
@@ -2560,7 +2606,7 @@
         <v>-100</v>
       </c>
       <c r="X24" s="3">
-        <v>-200</v>
+        <v>-100</v>
       </c>
       <c r="Y24" s="3">
         <v>-200</v>
@@ -2569,16 +2615,16 @@
         <v>-200</v>
       </c>
       <c r="AA24" s="3">
-        <v>-100</v>
+        <v>-200</v>
       </c>
       <c r="AB24" s="3">
         <v>-100</v>
       </c>
       <c r="AC24" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="AD24" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="AE24" s="3">
         <v>-100</v>
@@ -2587,7 +2633,7 @@
         <v>-100</v>
       </c>
       <c r="AG24" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="AH24" s="3">
         <v>0</v>
@@ -2608,13 +2654,16 @@
         <v>0</v>
       </c>
       <c r="AN24" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO24" s="3">
         <v>100</v>
       </c>
-      <c r="AO24" s="3">
+      <c r="AP24" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2732,246 +2781,255 @@
       <c r="AO25" s="3">
         <v>0</v>
       </c>
+      <c r="AP25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>11700</v>
+      </c>
+      <c r="E26" s="3">
         <v>185100</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-16400</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>112600</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>24300</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>22200</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>17100</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-49300</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>14400</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>8200</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>2200</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>32500</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>5600</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-1400</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-7900</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>13300</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-16500</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-100500</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-6600</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>100</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>25700</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-6400</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-4200</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>-4400</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>500</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>15800</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>-20100</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>-1500</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>6400</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>-31400</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>4300</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>-1100</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>-18000</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>2800</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>-200</v>
       </c>
-      <c r="AL26" s="3">
+      <c r="AM26" s="3">
         <v>10900</v>
       </c>
-      <c r="AM26" s="3">
+      <c r="AN26" s="3">
         <v>400</v>
       </c>
-      <c r="AN26" s="3">
+      <c r="AO26" s="3">
         <v>3900</v>
       </c>
-      <c r="AO26" s="3">
+      <c r="AP26" s="3">
         <v>-1300</v>
       </c>
     </row>
-    <row r="27" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>11400</v>
+      </c>
+      <c r="E27" s="3">
         <v>180800</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-16200</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>110300</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>23700</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>21800</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>16700</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-48600</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>14200</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>8000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>2100</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>32100</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>5400</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-1100</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-7800</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>13100</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-16800</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-98200</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-7000</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-200</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>24600</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-6800</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-4600</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>-4800</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>-100</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>15300</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>-19700</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>-1800</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>5700</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>-31200</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>3900</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>-1400</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>-17900</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>2300</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>-600</v>
       </c>
-      <c r="AL27" s="3">
+      <c r="AM27" s="3">
         <v>10200</v>
       </c>
-      <c r="AM27" s="3">
-        <v>0</v>
-      </c>
       <c r="AN27" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO27" s="3">
         <v>3400</v>
       </c>
-      <c r="AO27" s="3">
+      <c r="AP27" s="3">
         <v>-1700</v>
       </c>
     </row>
-    <row r="28" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -3089,8 +3147,11 @@
       <c r="AO28" s="3">
         <v>0</v>
       </c>
+      <c r="AP28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -3190,8 +3251,8 @@
       <c r="AI29" s="3">
         <v>0</v>
       </c>
-      <c r="AJ29" s="3" t="s">
-        <v>8</v>
+      <c r="AJ29" s="3">
+        <v>0</v>
       </c>
       <c r="AK29" s="3" t="s">
         <v>8</v>
@@ -3202,14 +3263,17 @@
       <c r="AM29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AN29" s="3">
-        <v>0</v>
-      </c>
-      <c r="AO29" s="3" t="s">
+      <c r="AN29" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AO29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP29" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="30" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3327,8 +3391,11 @@
       <c r="AO30" s="3">
         <v>0</v>
       </c>
+      <c r="AP30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3446,82 +3513,85 @@
       <c r="AO31" s="3">
         <v>0</v>
       </c>
+      <c r="AP31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-2200</v>
+      </c>
+      <c r="E32" s="3">
         <v>-3200</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-4600</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-3200</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-600</v>
       </c>
-      <c r="H32" s="3">
-        <v>0</v>
-      </c>
       <c r="I32" s="3">
+        <v>0</v>
+      </c>
+      <c r="J32" s="3">
         <v>-600</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-200</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-400</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>200</v>
       </c>
-      <c r="M32" s="3">
-        <v>0</v>
-      </c>
       <c r="N32" s="3">
+        <v>0</v>
+      </c>
+      <c r="O32" s="3">
         <v>100</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-200</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-400</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-100</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>200</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>100</v>
-      </c>
-      <c r="T32" s="3">
-        <v>-100</v>
       </c>
       <c r="U32" s="3">
         <v>-100</v>
       </c>
       <c r="V32" s="3">
+        <v>-100</v>
+      </c>
+      <c r="W32" s="3">
         <v>-300</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>200</v>
       </c>
-      <c r="X32" s="3">
-        <v>0</v>
-      </c>
       <c r="Y32" s="3">
         <v>0</v>
       </c>
       <c r="Z32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA32" s="3">
         <v>-400</v>
-      </c>
-      <c r="AA32" s="3">
-        <v>100</v>
       </c>
       <c r="AB32" s="3">
         <v>100</v>
@@ -3530,162 +3600,168 @@
         <v>100</v>
       </c>
       <c r="AD32" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="AE32" s="3">
         <v>200</v>
       </c>
       <c r="AF32" s="3">
+        <v>200</v>
+      </c>
+      <c r="AG32" s="3">
         <v>8300</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>300</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>-7700</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>-300</v>
       </c>
-      <c r="AJ32" s="3">
+      <c r="AK32" s="3">
         <v>15200</v>
       </c>
-      <c r="AK32" s="3">
+      <c r="AL32" s="3">
         <v>100</v>
       </c>
-      <c r="AL32" s="3">
+      <c r="AM32" s="3">
         <v>-6300</v>
       </c>
-      <c r="AM32" s="3">
+      <c r="AN32" s="3">
         <v>-8700</v>
       </c>
-      <c r="AN32" s="3">
+      <c r="AO32" s="3">
         <v>-4000</v>
       </c>
-      <c r="AO32" s="3">
+      <c r="AP32" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>11400</v>
+      </c>
+      <c r="E33" s="3">
         <v>180800</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-16200</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>110300</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>23700</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>21800</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>16700</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-48600</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>14200</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>8000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>2100</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>32100</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>5400</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-1100</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-7800</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>13100</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-16800</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-98200</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-7000</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-200</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>24600</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-6800</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-4600</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-4800</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>-100</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>15300</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>-19700</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>-1800</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>5700</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>-31200</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>3900</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>-1400</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>-17900</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>2300</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>-600</v>
       </c>
-      <c r="AL33" s="3">
+      <c r="AM33" s="3">
         <v>10200</v>
       </c>
-      <c r="AM33" s="3">
-        <v>0</v>
-      </c>
       <c r="AN33" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO33" s="3">
         <v>3400</v>
       </c>
-      <c r="AO33" s="3">
+      <c r="AP33" s="3">
         <v>-1700</v>
       </c>
     </row>
-    <row r="34" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3803,251 +3879,260 @@
       <c r="AO34" s="3">
         <v>0</v>
       </c>
+      <c r="AP34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>11400</v>
+      </c>
+      <c r="E35" s="3">
         <v>180800</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-16200</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>110300</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>23700</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>21800</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>16700</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-48600</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>14200</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>8000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>2100</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>32100</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>5400</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-1100</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-7800</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>13100</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-16800</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-98200</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-7000</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-200</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>24600</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-6800</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-4600</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-4800</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>-100</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>15300</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>-19700</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>-1800</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>5700</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>-31200</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>3900</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>-1400</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>-17900</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>2300</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>-600</v>
       </c>
-      <c r="AL35" s="3">
+      <c r="AM35" s="3">
         <v>10200</v>
       </c>
-      <c r="AM35" s="3">
-        <v>0</v>
-      </c>
       <c r="AN35" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO35" s="3">
         <v>3400</v>
       </c>
-      <c r="AO35" s="3">
+      <c r="AP35" s="3">
         <v>-1700</v>
       </c>
     </row>
-    <row r="37" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:42" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E38" s="2">
         <v>46022</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45930</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45838</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45747</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45657</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45565</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45473</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45382</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45291</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45199</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45107</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>45016</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44926</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44834</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44742</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44651</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44561</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44469</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44377</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44286</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44196</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44104</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>44012</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43921</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43830</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43738</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43646</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43555</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43465</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43373</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>43281</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>43190</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>43100</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>43008</v>
       </c>
-      <c r="AL38" s="2">
+      <c r="AM38" s="2">
         <v>42916</v>
       </c>
-      <c r="AM38" s="2">
+      <c r="AN38" s="2">
         <v>42825</v>
       </c>
-      <c r="AN38" s="2">
+      <c r="AO38" s="2">
         <v>42735</v>
       </c>
-      <c r="AO38" s="2">
+      <c r="AP38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -4089,8 +4174,9 @@
       <c r="AM39" s="3"/>
       <c r="AN39" s="3"/>
       <c r="AO39" s="3"/>
+      <c r="AP39" s="3"/>
     </row>
-    <row r="40" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -4132,169 +4218,173 @@
       <c r="AM40" s="3"/>
       <c r="AN40" s="3"/>
       <c r="AO40" s="3"/>
+      <c r="AP40" s="3"/>
     </row>
-    <row r="41" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>32500</v>
+      </c>
+      <c r="E41" s="3">
         <v>36800</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>68700</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>182000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>49100</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>128100</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>117500</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>153800</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>83600</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>36400</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>52300</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>129300</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>43700</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>115800</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>88400</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>90800</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>74300</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>93200</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>99500</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>89900</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>228800</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>43600</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>129300</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>230000</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>343900</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>31300</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>40400</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>35800</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>28400</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>35400</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>30700</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>32400</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>28800</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>24100</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AL41" s="3">
         <v>32500</v>
       </c>
-      <c r="AL41" s="3">
+      <c r="AM41" s="3">
         <v>27600</v>
       </c>
-      <c r="AM41" s="3">
+      <c r="AN41" s="3">
         <v>22600</v>
       </c>
-      <c r="AN41" s="3">
+      <c r="AO41" s="3">
         <v>19900</v>
       </c>
-      <c r="AO41" s="3">
+      <c r="AP41" s="3">
         <v>28800</v>
       </c>
     </row>
-    <row r="42" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>900</v>
+      </c>
+      <c r="E42" s="3">
         <v>1500</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>2500</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>4700</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>7400</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>10600</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>10200</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>21800</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>25300</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>23100</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>37200</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>37000</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>26700</v>
       </c>
-      <c r="P42" s="3">
-        <v>0</v>
-      </c>
       <c r="Q42" s="3">
         <v>0</v>
       </c>
@@ -4370,127 +4460,133 @@
       <c r="AO42" s="3">
         <v>0</v>
       </c>
+      <c r="AP42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>133300</v>
+      </c>
+      <c r="E43" s="3">
         <v>127900</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>129700</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>125300</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>124300</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>125800</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>113800</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>120000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>118100</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>113300</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>113100</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>109600</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>103500</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>101300</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>86600</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>76900</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>69100</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>68400</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>45900</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>46700</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>49100</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>57200</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>57100</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>61600</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>49900</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>55300</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>50000</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>52000</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>55400</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>58100</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>57100</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>53100</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>57200</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AK43" s="3">
         <v>58300</v>
       </c>
-      <c r="AK43" s="3">
+      <c r="AL43" s="3">
         <v>53300</v>
-      </c>
-      <c r="AL43" s="3">
-        <v>52300</v>
       </c>
       <c r="AM43" s="3">
         <v>52300</v>
       </c>
       <c r="AN43" s="3">
+        <v>52300</v>
+      </c>
+      <c r="AO43" s="3">
         <v>53100</v>
       </c>
-      <c r="AO43" s="3">
+      <c r="AP43" s="3">
         <v>50400</v>
       </c>
     </row>
-    <row r="44" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -4530,8 +4626,8 @@
       <c r="O44" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P44" s="3">
-        <v>0</v>
+      <c r="P44" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="Q44" s="3">
         <v>0</v>
@@ -4608,169 +4704,175 @@
       <c r="AO44" s="3">
         <v>0</v>
       </c>
+      <c r="AP44" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="45" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>151800</v>
+      </c>
+      <c r="E45" s="3">
         <v>163500</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>157800</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>179500</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>190000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>517800</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>520700</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>285900</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>371500</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>94800</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>111800</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>93500</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>113500</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>127000</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>142800</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>106000</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>96300</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>84800</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>39200</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>39500</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>42900</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>13000</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>39300</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>38200</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>36300</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>7500</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>10100</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>10300</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>14100</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>12800</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>17400</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>14200</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AJ45" s="3">
         <v>20300</v>
       </c>
-      <c r="AJ45" s="3">
+      <c r="AK45" s="3">
         <v>16400</v>
       </c>
-      <c r="AK45" s="3">
+      <c r="AL45" s="3">
         <v>12800</v>
       </c>
-      <c r="AL45" s="3">
+      <c r="AM45" s="3">
         <v>10200</v>
       </c>
-      <c r="AM45" s="3">
+      <c r="AN45" s="3">
         <v>12800</v>
       </c>
-      <c r="AN45" s="3">
+      <c r="AO45" s="3">
         <v>9700</v>
       </c>
-      <c r="AO45" s="3">
+      <c r="AP45" s="3">
         <v>10800</v>
       </c>
     </row>
-    <row r="46" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>509000</v>
+      </c>
+      <c r="E46" s="3">
         <v>771200</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>382300</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>497100</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>376700</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>787500</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>767800</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>586500</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>603800</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>272600</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>320300</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>375000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>296300</v>
       </c>
-      <c r="P46" s="3">
-        <v>0</v>
-      </c>
       <c r="Q46" s="3">
         <v>0</v>
       </c>
@@ -4846,106 +4948,109 @@
       <c r="AO46" s="3">
         <v>0</v>
       </c>
+      <c r="AP46" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="47" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>356600</v>
+      </c>
+      <c r="E47" s="3">
         <v>364400</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>374900</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>390800</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>20300</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>19500</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>18800</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>10000</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>9600</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>9100</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>10200</v>
-      </c>
-      <c r="N47" s="3">
-        <v>10300</v>
       </c>
       <c r="O47" s="3">
         <v>10300</v>
       </c>
       <c r="P47" s="3">
+        <v>10300</v>
+      </c>
+      <c r="Q47" s="3">
         <v>10400</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>10600</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>10400</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>136800</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>136900</v>
-      </c>
-      <c r="U47" s="3">
-        <v>138000</v>
       </c>
       <c r="V47" s="3">
         <v>138000</v>
       </c>
       <c r="W47" s="3">
+        <v>138000</v>
+      </c>
+      <c r="X47" s="3">
         <v>13000</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>12800</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>13100</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>13200</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>12100</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>12600</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>12900</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>12700</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>13300</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>13500</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AH47" s="3">
         <v>13800</v>
       </c>
-      <c r="AH47" s="3">
+      <c r="AI47" s="3">
         <v>13900</v>
-      </c>
-      <c r="AI47" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AJ47" s="3" t="s">
         <v>8</v>
@@ -4965,127 +5070,133 @@
       <c r="AO47" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AP47" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="48" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>5311900</v>
+      </c>
+      <c r="E48" s="3">
         <v>5347300</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>5689600</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>5761700</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>6055300</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>6046500</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>6091000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>6098600</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>6305700</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>6358300</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>6397300</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>6426100</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>6508700</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>6571400</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>6621600</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>6617800</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>6676800</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>6707500</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>2308000</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>2343700</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>2358900</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>2415900</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>2347400</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>2380500</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>2404000</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>2447400</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>2514100</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>2716800</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>2911300</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>2941200</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>3051700</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>3076800</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>3194200</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>3293300</v>
       </c>
-      <c r="AK48" s="3">
+      <c r="AL48" s="3">
         <v>3320300</v>
       </c>
-      <c r="AL48" s="3">
+      <c r="AM48" s="3">
         <v>3331800</v>
       </c>
-      <c r="AM48" s="3">
+      <c r="AN48" s="3">
         <v>3399700</v>
       </c>
-      <c r="AN48" s="3">
+      <c r="AO48" s="3">
         <v>3435400</v>
       </c>
-      <c r="AO48" s="3">
+      <c r="AP48" s="3">
         <v>3458300</v>
       </c>
     </row>
-    <row r="49" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -5125,12 +5236,12 @@
       <c r="O49" s="3">
         <v>0</v>
       </c>
-      <c r="P49" s="3" t="s">
+      <c r="P49" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q49" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q49" s="3">
-        <v>0</v>
-      </c>
       <c r="R49" s="3">
         <v>0</v>
       </c>
@@ -5180,31 +5291,34 @@
         <v>0</v>
       </c>
       <c r="AH49" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI49" s="3">
         <v>32300</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>39000</v>
       </c>
-      <c r="AJ49" s="3">
+      <c r="AK49" s="3">
         <v>44000</v>
       </c>
-      <c r="AK49" s="3">
+      <c r="AL49" s="3">
         <v>47900</v>
       </c>
-      <c r="AL49" s="3">
+      <c r="AM49" s="3">
         <v>53000</v>
       </c>
-      <c r="AM49" s="3">
+      <c r="AN49" s="3">
         <v>59300</v>
       </c>
-      <c r="AN49" s="3">
+      <c r="AO49" s="3">
         <v>65500</v>
       </c>
-      <c r="AO49" s="3">
+      <c r="AP49" s="3">
         <v>70000</v>
       </c>
     </row>
-    <row r="50" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -5322,8 +5436,11 @@
       <c r="AO50" s="3">
         <v>0</v>
       </c>
+      <c r="AP50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -5441,8 +5558,11 @@
       <c r="AO51" s="3">
         <v>0</v>
       </c>
+      <c r="AP51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -5482,86 +5602,89 @@
       <c r="O52" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P52" s="3">
+      <c r="P52" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q52" s="3">
         <v>416000</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>450000</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>483000</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>520300</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>548600</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>78400</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>61400</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>62600</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>66100</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>71900</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>88300</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>91300</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>94600</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>86300</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>108700</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>180800</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>111100</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>115100</v>
-      </c>
-      <c r="AH52" s="3">
-        <v>79400</v>
       </c>
       <c r="AI52" s="3">
         <v>79400</v>
       </c>
       <c r="AJ52" s="3">
+        <v>79400</v>
+      </c>
+      <c r="AK52" s="3">
         <v>76400</v>
       </c>
-      <c r="AK52" s="3">
+      <c r="AL52" s="3">
         <v>76600</v>
       </c>
-      <c r="AL52" s="3">
+      <c r="AM52" s="3">
         <v>75400</v>
       </c>
-      <c r="AM52" s="3">
+      <c r="AN52" s="3">
         <v>76700</v>
       </c>
-      <c r="AN52" s="3">
+      <c r="AO52" s="3">
         <v>72800</v>
       </c>
-      <c r="AO52" s="3">
+      <c r="AP52" s="3">
         <v>72700</v>
       </c>
     </row>
-    <row r="53" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5679,127 +5802,133 @@
       <c r="AO53" s="3">
         <v>0</v>
       </c>
+      <c r="AP53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>6350300</v>
+      </c>
+      <c r="E54" s="3">
         <v>6664500</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>6647700</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>6858300</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>6682500</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>7091800</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>7129700</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>6958900</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>7204500</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>6944100</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>7052500</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>7165100</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>7196900</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>7342000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>7399900</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>7384900</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>7573700</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>7639600</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>2708900</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>2719200</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>2755300</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>2608500</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>2658100</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>2811800</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>2937400</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>2648900</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>2713900</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>2936300</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>3203200</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>3172000</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>3285900</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>3302200</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>3418900</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>3512500</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AL54" s="3">
         <v>3543400</v>
       </c>
-      <c r="AL54" s="3">
+      <c r="AM54" s="3">
         <v>3550300</v>
       </c>
-      <c r="AM54" s="3">
+      <c r="AN54" s="3">
         <v>3623500</v>
       </c>
-      <c r="AN54" s="3">
+      <c r="AO54" s="3">
         <v>3656400</v>
       </c>
-      <c r="AO54" s="3">
+      <c r="AP54" s="3">
         <v>3690900</v>
       </c>
     </row>
-    <row r="55" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5841,8 +5970,9 @@
       <c r="AM55" s="3"/>
       <c r="AN55" s="3"/>
       <c r="AO55" s="3"/>
+      <c r="AP55" s="3"/>
     </row>
-    <row r="56" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5884,169 +6014,173 @@
       <c r="AM56" s="3"/>
       <c r="AN56" s="3"/>
       <c r="AO56" s="3"/>
+      <c r="AP56" s="3"/>
     </row>
-    <row r="57" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>156900</v>
+      </c>
+      <c r="E57" s="3">
         <v>221100</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>203100</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>179400</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>158900</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>198700</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>184000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>181800</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>162400</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>188000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>185700</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>164800</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>148100</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>207800</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>152000</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>133800</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>124200</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>185000</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>85700</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>74400</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>72100</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>77500</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>88600</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>85700</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>109400</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>69800</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>77500</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>66600</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>61900</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>85900</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>98500</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>101200</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>102900</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AK57" s="3">
         <v>78500</v>
       </c>
-      <c r="AK57" s="3">
+      <c r="AL57" s="3">
         <v>101600</v>
       </c>
-      <c r="AL57" s="3">
+      <c r="AM57" s="3">
         <v>88500</v>
       </c>
-      <c r="AM57" s="3">
+      <c r="AN57" s="3">
         <v>88800</v>
       </c>
-      <c r="AN57" s="3">
+      <c r="AO57" s="3">
         <v>80700</v>
       </c>
-      <c r="AO57" s="3">
+      <c r="AP57" s="3">
         <v>93400</v>
       </c>
     </row>
-    <row r="58" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>413800</v>
+      </c>
+      <c r="E58" s="3">
         <v>420400</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>1300</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>82600</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>83900</v>
       </c>
-      <c r="H58" s="3">
-        <v>0</v>
-      </c>
       <c r="I58" s="3">
+        <v>0</v>
+      </c>
+      <c r="J58" s="3">
         <v>1300</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>122600</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>273500</v>
       </c>
-      <c r="L58" s="3">
-        <v>0</v>
-      </c>
       <c r="M58" s="3">
+        <v>0</v>
+      </c>
+      <c r="N58" s="3">
         <v>1300</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>124200</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>125100</v>
       </c>
-      <c r="P58" s="3">
-        <v>0</v>
-      </c>
       <c r="Q58" s="3">
         <v>0</v>
       </c>
@@ -6122,97 +6256,100 @@
       <c r="AO58" s="3">
         <v>0</v>
       </c>
+      <c r="AP58" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="59" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>3800</v>
+      </c>
+      <c r="E59" s="3">
         <v>11700</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>4400</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>4900</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>4200</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>500</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>3800</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>3900</v>
-      </c>
-      <c r="K59" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="L59" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M59" s="3">
+      <c r="M59" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N59" s="3">
         <v>168000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>11400</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>14600</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>79300</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>78100</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>76000</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>79200</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>70200</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>26200</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>26300</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>26400</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>26500</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>26600</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>26800</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>26900</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>27000</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>27100</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>27200</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>27300</v>
-      </c>
-      <c r="AF59" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AG59" s="3" t="s">
         <v>8</v>
@@ -6223,8 +6360,8 @@
       <c r="AI59" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AJ59" s="3">
-        <v>0</v>
+      <c r="AJ59" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AK59" s="3">
         <v>0</v>
@@ -6241,50 +6378,53 @@
       <c r="AO59" s="3">
         <v>0</v>
       </c>
+      <c r="AP59" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="60" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>574500</v>
+      </c>
+      <c r="E60" s="3">
         <v>653200</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>208800</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>267000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>247000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>199300</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>189100</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>308300</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>435900</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>188000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>354900</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>300400</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>287800</v>
       </c>
-      <c r="P60" s="3">
-        <v>0</v>
-      </c>
       <c r="Q60" s="3">
         <v>0</v>
       </c>
@@ -6360,168 +6500,174 @@
       <c r="AO60" s="3">
         <v>0</v>
       </c>
+      <c r="AP60" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="61" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>2643300</v>
+      </c>
+      <c r="E61" s="3">
         <v>2670400</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>3005500</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>3006900</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>2895200</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>3297900</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>3311100</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>2969000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>2971700</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>2908200</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>2949700</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>2895300</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>2927500</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>3010300</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>3012900</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>3001200</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>3179100</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>3150800</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>1289000</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>1289400</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>1315200</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>1170800</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>1196100</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>1346300</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>1446500</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>1146600</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>1198600</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>1376600</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>1602600</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>1543300</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>1578300</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>1565400</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>1650500</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AK61" s="3">
         <v>1699200</v>
       </c>
-      <c r="AK61" s="3">
+      <c r="AL61" s="3">
         <v>1681700</v>
       </c>
-      <c r="AL61" s="3">
+      <c r="AM61" s="3">
         <v>1675100</v>
       </c>
-      <c r="AM61" s="3">
+      <c r="AN61" s="3">
         <v>1726900</v>
       </c>
-      <c r="AN61" s="3">
+      <c r="AO61" s="3">
         <v>1731100</v>
       </c>
-      <c r="AO61" s="3">
+      <c r="AP61" s="3">
         <v>1732300</v>
       </c>
     </row>
-    <row r="62" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>112300</v>
+      </c>
+      <c r="E62" s="3">
         <v>117700</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>126800</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>130500</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>139800</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>150400</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>151900</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>154400</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>164400</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>168700</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>12000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>176500</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>182900</v>
-      </c>
-      <c r="P62" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="Q62" s="3" t="s">
         <v>8</v>
@@ -6532,8 +6678,8 @@
       <c r="S62" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="T62" s="3">
-        <v>0</v>
+      <c r="T62" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="U62" s="3">
         <v>0</v>
@@ -6562,14 +6708,14 @@
       <c r="AC62" s="3">
         <v>0</v>
       </c>
-      <c r="AD62" s="3" t="s">
+      <c r="AD62" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE62" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>2400</v>
-      </c>
-      <c r="AF62" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AG62" s="3" t="s">
         <v>8</v>
@@ -6580,8 +6726,8 @@
       <c r="AI62" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AJ62" s="3">
-        <v>0</v>
+      <c r="AJ62" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AK62" s="3">
         <v>0</v>
@@ -6598,8 +6744,11 @@
       <c r="AO62" s="3">
         <v>0</v>
       </c>
+      <c r="AP62" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="63" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6717,8 +6866,11 @@
       <c r="AO63" s="3">
         <v>0</v>
       </c>
+      <c r="AP63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6836,8 +6988,11 @@
       <c r="AO64" s="3">
         <v>0</v>
       </c>
+      <c r="AP64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6955,127 +7110,133 @@
       <c r="AO65" s="3">
         <v>0</v>
       </c>
+      <c r="AP65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>3360700</v>
+      </c>
+      <c r="E66" s="3">
         <v>3472700</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>3371700</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>3435800</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>3311000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>3679700</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>3681500</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>3459300</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>3598100</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>3300200</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>3347800</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>3405900</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>3428400</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>3575500</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>3527100</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>3493700</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>3675100</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>3717500</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>1510000</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>1505700</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>1523500</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>1377900</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>1416000</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>1563600</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>1684600</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>1359800</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>1411700</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>1583700</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>1816400</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>1759300</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>1807700</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>1802800</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>1893900</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>1947100</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AL66" s="3">
         <v>1958500</v>
       </c>
-      <c r="AL66" s="3">
+      <c r="AM66" s="3">
         <v>1940600</v>
       </c>
-      <c r="AM66" s="3">
+      <c r="AN66" s="3">
         <v>2004000</v>
       </c>
-      <c r="AN66" s="3">
+      <c r="AO66" s="3">
         <v>2012800</v>
       </c>
-      <c r="AO66" s="3">
+      <c r="AP66" s="3">
         <v>2046500</v>
       </c>
     </row>
-    <row r="67" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -7117,8 +7278,9 @@
       <c r="AM67" s="3"/>
       <c r="AN67" s="3"/>
       <c r="AO67" s="3"/>
+      <c r="AP67" s="3"/>
     </row>
-    <row r="68" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -7236,8 +7398,11 @@
       <c r="AO68" s="3">
         <v>0</v>
       </c>
+      <c r="AP68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -7355,8 +7520,11 @@
       <c r="AO69" s="3">
         <v>0</v>
       </c>
+      <c r="AP69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -7474,8 +7642,11 @@
       <c r="AO70" s="3">
         <v>0</v>
       </c>
+      <c r="AP70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -7593,127 +7764,133 @@
       <c r="AO71" s="3">
         <v>0</v>
       </c>
+      <c r="AP71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-1611300</v>
+      </c>
+      <c r="E72" s="3">
         <v>-1563800</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-1654600</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-1579900</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-1630900</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-1595300</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-1557800</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-1517400</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-1413800</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-1373100</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-1326200</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-1275600</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-1255000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-1207800</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-1105800</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-1052000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-1021300</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-962900</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-849500</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-827300</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-812700</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-824300</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>-810800</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>-801800</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>-797000</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>-770000</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>-758600</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>-712200</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>-683700</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>-662700</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>-604900</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>-582200</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>-554300</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>-509800</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AL72" s="3">
         <v>-485600</v>
       </c>
-      <c r="AL72" s="3">
+      <c r="AM72" s="3">
         <v>-459700</v>
       </c>
-      <c r="AM72" s="3">
+      <c r="AN72" s="3">
         <v>-444600</v>
       </c>
-      <c r="AN72" s="3">
+      <c r="AO72" s="3">
         <v>-419300</v>
       </c>
-      <c r="AO72" s="3">
+      <c r="AP72" s="3">
         <v>-397400</v>
       </c>
     </row>
-    <row r="73" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -7831,8 +8008,11 @@
       <c r="AO73" s="3">
         <v>0</v>
       </c>
+      <c r="AP73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7950,8 +8130,11 @@
       <c r="AO74" s="3">
         <v>0</v>
       </c>
+      <c r="AP74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -8069,127 +8252,133 @@
       <c r="AO75" s="3">
         <v>0</v>
       </c>
+      <c r="AP75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>2857400</v>
+      </c>
+      <c r="E76" s="3">
         <v>3073600</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>3172800</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>3317700</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>3268000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>3312100</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>3349400</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>3421600</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>3530800</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>3568100</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>3635300</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>3692800</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>3706000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>3766500</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>3872800</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>3891100</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>3898600</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>3922000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>1198800</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>1213500</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>1231900</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>1230700</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>1242100</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>1248200</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>1252800</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>1289000</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>1302200</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>1352700</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>1386800</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>1412700</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>1478200</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>1499400</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>1525000</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>1565400</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3">
         <v>1584900</v>
       </c>
-      <c r="AL76" s="3">
+      <c r="AM76" s="3">
         <v>1609700</v>
       </c>
-      <c r="AM76" s="3">
+      <c r="AN76" s="3">
         <v>1619500</v>
       </c>
-      <c r="AN76" s="3">
+      <c r="AO76" s="3">
         <v>1643600</v>
       </c>
-      <c r="AO76" s="3">
+      <c r="AP76" s="3">
         <v>1644400</v>
       </c>
     </row>
-    <row r="77" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -8307,251 +8496,260 @@
       <c r="AO77" s="3">
         <v>0</v>
       </c>
+      <c r="AP77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:42" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E80" s="2">
         <v>46022</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45930</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45838</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45747</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45657</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45565</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45473</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45382</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45291</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45199</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45107</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>45016</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44926</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44834</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44742</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44651</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44561</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44469</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44377</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44286</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44196</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44104</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>44012</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43921</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43830</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43738</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43646</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43555</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43465</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43373</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>43281</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>43190</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>43100</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>43008</v>
       </c>
-      <c r="AL80" s="2">
+      <c r="AM80" s="2">
         <v>42916</v>
       </c>
-      <c r="AM80" s="2">
+      <c r="AN80" s="2">
         <v>42825</v>
       </c>
-      <c r="AN80" s="2">
+      <c r="AO80" s="2">
         <v>42735</v>
       </c>
-      <c r="AO80" s="2">
+      <c r="AP80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>11400</v>
+      </c>
+      <c r="E81" s="3">
         <v>180800</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-16200</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>110300</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>23700</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>21800</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>16700</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-48600</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>14200</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>8000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>2100</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>32100</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>5400</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-1100</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-7800</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>13100</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-16800</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-98200</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-7000</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-200</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>24600</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-6800</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-4600</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-4800</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>-100</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>15300</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>-19700</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>-1800</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>5700</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>-31200</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>3900</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>-1400</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>-17900</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>2300</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>-600</v>
       </c>
-      <c r="AL81" s="3">
+      <c r="AM81" s="3">
         <v>10200</v>
       </c>
-      <c r="AM81" s="3">
-        <v>0</v>
-      </c>
       <c r="AN81" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO81" s="3">
         <v>3400</v>
       </c>
-      <c r="AO81" s="3">
+      <c r="AP81" s="3">
         <v>-1700</v>
       </c>
     </row>
-    <row r="82" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -8593,127 +8791,131 @@
       <c r="AM82" s="3"/>
       <c r="AN82" s="3"/>
       <c r="AO82" s="3"/>
+      <c r="AP82" s="3"/>
     </row>
-    <row r="83" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>80200</v>
+      </c>
+      <c r="E83" s="3">
         <v>76200</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>75700</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>77300</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>79100</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>76300</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>75900</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>77700</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>79600</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>78000</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>79200</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>78300</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>79800</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>113700</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>116600</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>119300</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>123300</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>110600</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>30800</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>30500</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>31200</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>32300</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>34400</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>32000</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>32100</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>31400</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>32600</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>35600</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>35300</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>38000</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>37500</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>41300</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>39200</v>
       </c>
-      <c r="AJ83" s="3">
+      <c r="AK83" s="3">
         <v>41400</v>
       </c>
-      <c r="AK83" s="3">
+      <c r="AL83" s="3">
         <v>43500</v>
       </c>
-      <c r="AL83" s="3">
+      <c r="AM83" s="3">
         <v>43400</v>
       </c>
-      <c r="AM83" s="3">
+      <c r="AN83" s="3">
         <v>46400</v>
       </c>
-      <c r="AN83" s="3">
+      <c r="AO83" s="3">
         <v>43700</v>
       </c>
-      <c r="AO83" s="3">
+      <c r="AP83" s="3">
         <v>47700</v>
       </c>
     </row>
-    <row r="84" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -8831,8 +9033,11 @@
       <c r="AO84" s="3">
         <v>0</v>
       </c>
+      <c r="AP84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -8950,8 +9155,11 @@
       <c r="AO85" s="3">
         <v>0</v>
       </c>
+      <c r="AP85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -9069,8 +9277,11 @@
       <c r="AO86" s="3">
         <v>0</v>
       </c>
+      <c r="AP86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -9188,8 +9399,11 @@
       <c r="AO87" s="3">
         <v>0</v>
       </c>
+      <c r="AP87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -9307,127 +9521,133 @@
       <c r="AO88" s="3">
         <v>0</v>
       </c>
+      <c r="AP88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>49800</v>
+      </c>
+      <c r="E89" s="3">
         <v>106600</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>116200</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>132800</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>74100</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>111000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>112400</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>142100</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>53600</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>103500</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>110800</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>116800</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>63600</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>116900</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>108100</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>104700</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>49600</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-3500</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>36400</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>36100</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>31300</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>9800</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>35900</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>28000</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>21900</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>31800</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>36500</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>37300</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>32300</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>35400</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>37000</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>45800</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>36300</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>30800</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AL89" s="3">
         <v>42700</v>
       </c>
-      <c r="AL89" s="3">
+      <c r="AM89" s="3">
         <v>44900</v>
       </c>
-      <c r="AM89" s="3">
+      <c r="AN89" s="3">
         <v>36200</v>
       </c>
-      <c r="AN89" s="3">
+      <c r="AO89" s="3">
         <v>34200</v>
       </c>
-      <c r="AO89" s="3">
+      <c r="AP89" s="3">
         <v>39800</v>
       </c>
     </row>
-    <row r="90" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -9469,127 +9689,131 @@
       <c r="AM90" s="3"/>
       <c r="AN90" s="3"/>
       <c r="AO90" s="3"/>
+      <c r="AP90" s="3"/>
     </row>
-    <row r="91" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-32400</v>
+      </c>
+      <c r="E91" s="3">
         <v>-38000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-30800</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-48900</v>
       </c>
-      <c r="G91" s="3">
-        <v>-34400</v>
-      </c>
       <c r="H91" s="3">
+        <v>-42100</v>
+      </c>
+      <c r="I91" s="3">
         <v>-33600</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-36900</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-41700</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-28200</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-43900</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-30900</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-28600</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-39100</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-52000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-47800</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-35000</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-23800</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-20400</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-15700</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-13300</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-7900</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-7600</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-8200</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-9200</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-13200</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-15700</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-12400</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-13700</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-11500</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-12000</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-12700</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-16500</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-18100</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AK91" s="3">
         <v>-10800</v>
       </c>
-      <c r="AK91" s="3">
+      <c r="AL91" s="3">
         <v>-24800</v>
       </c>
-      <c r="AL91" s="3">
+      <c r="AM91" s="3">
         <v>-11200</v>
       </c>
-      <c r="AM91" s="3">
+      <c r="AN91" s="3">
         <v>-47700</v>
       </c>
-      <c r="AN91" s="3">
+      <c r="AO91" s="3">
         <v>-26000</v>
       </c>
-      <c r="AO91" s="3">
+      <c r="AP91" s="3">
         <v>-24100</v>
       </c>
     </row>
-    <row r="92" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -9707,8 +9931,11 @@
       <c r="AO92" s="3">
         <v>0</v>
       </c>
+      <c r="AP92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -9826,127 +10053,133 @@
       <c r="AO93" s="3">
         <v>0</v>
       </c>
+      <c r="AP93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-24500</v>
+      </c>
+      <c r="E94" s="3">
         <v>433700</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>1800</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-49800</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>227800</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-29500</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-314900</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>134700</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-289300</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-26200</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-63500</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>49500</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-41500</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-31500</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-82300</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>130800</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-62200</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>18000</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-9600</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-133300</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>33900</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-64900</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>4700</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-13500</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-7100</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>52800</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>166900</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>226600</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-29700</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>44700</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-14500</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>71800</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>46400</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>-23200</v>
       </c>
-      <c r="AK94" s="3">
+      <c r="AL94" s="3">
         <v>-16500</v>
       </c>
-      <c r="AL94" s="3">
+      <c r="AM94" s="3">
         <v>38100</v>
       </c>
-      <c r="AM94" s="3">
+      <c r="AN94" s="3">
         <v>1400</v>
       </c>
-      <c r="AN94" s="3">
+      <c r="AO94" s="3">
         <v>-15600</v>
       </c>
-      <c r="AO94" s="3">
+      <c r="AP94" s="3">
         <v>-22200</v>
       </c>
     </row>
-    <row r="95" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -9988,28 +10221,29 @@
       <c r="AM95" s="3"/>
       <c r="AN95" s="3"/>
       <c r="AO95" s="3"/>
+      <c r="AP95" s="3"/>
     </row>
-    <row r="96" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>90100</v>
+      </c>
+      <c r="E96" s="3">
         <v>58500</v>
-      </c>
-      <c r="E96" s="3">
-        <v>59400</v>
       </c>
       <c r="F96" s="3">
         <v>59400</v>
       </c>
       <c r="G96" s="3">
+        <v>59400</v>
+      </c>
+      <c r="H96" s="3">
         <v>59300</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>57100</v>
-      </c>
-      <c r="I96" s="3">
-        <v>54900</v>
       </c>
       <c r="J96" s="3">
         <v>54900</v>
@@ -10018,55 +10252,55 @@
         <v>54900</v>
       </c>
       <c r="L96" s="3">
-        <v>52700</v>
+        <v>54900</v>
       </c>
       <c r="M96" s="3">
         <v>52700</v>
       </c>
       <c r="N96" s="3">
-        <v>52600</v>
+        <v>52700</v>
       </c>
       <c r="O96" s="3">
         <v>52600</v>
       </c>
       <c r="P96" s="3">
+        <v>52600</v>
+      </c>
+      <c r="Q96" s="3">
         <v>-48200</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="R96" s="3">
         <v>-46000</v>
       </c>
-      <c r="R96" s="3">
+      <c r="S96" s="3">
         <v>-43800</v>
       </c>
-      <c r="S96" s="3">
+      <c r="T96" s="3">
         <v>-41600</v>
-      </c>
-      <c r="T96" s="3">
-        <v>-15200</v>
       </c>
       <c r="U96" s="3">
         <v>-15200</v>
       </c>
       <c r="V96" s="3">
+        <v>-15200</v>
+      </c>
+      <c r="W96" s="3">
         <v>-14400</v>
       </c>
-      <c r="W96" s="3">
+      <c r="X96" s="3">
         <v>-13000</v>
       </c>
-      <c r="X96" s="3">
+      <c r="Y96" s="3">
         <v>-6700</v>
       </c>
-      <c r="Y96" s="3">
+      <c r="Z96" s="3">
         <v>-4400</v>
       </c>
-      <c r="Z96" s="3">
+      <c r="AA96" s="3">
         <v>-26700</v>
       </c>
-      <c r="AA96" s="3">
+      <c r="AB96" s="3">
         <v>-300</v>
-      </c>
-      <c r="AB96" s="3">
-        <v>-26700</v>
       </c>
       <c r="AC96" s="3">
         <v>-26700</v>
@@ -10075,10 +10309,10 @@
         <v>-26700</v>
       </c>
       <c r="AE96" s="3">
+        <v>-26700</v>
+      </c>
+      <c r="AF96" s="3">
         <v>-53300</v>
-      </c>
-      <c r="AF96" s="3">
-        <v>-26600</v>
       </c>
       <c r="AG96" s="3">
         <v>-26600</v>
@@ -10087,10 +10321,10 @@
         <v>-26600</v>
       </c>
       <c r="AI96" s="3">
+        <v>-26600</v>
+      </c>
+      <c r="AJ96" s="3">
         <v>-26500</v>
-      </c>
-      <c r="AJ96" s="3">
-        <v>-25300</v>
       </c>
       <c r="AK96" s="3">
         <v>-25300</v>
@@ -10102,13 +10336,16 @@
         <v>-25300</v>
       </c>
       <c r="AN96" s="3">
-        <v>-24000</v>
+        <v>-25300</v>
       </c>
       <c r="AO96" s="3">
         <v>-24000</v>
       </c>
+      <c r="AP96" s="3">
+        <v>-24000</v>
+      </c>
     </row>
-    <row r="97" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -10226,8 +10463,11 @@
       <c r="AO97" s="3">
         <v>0</v>
       </c>
+      <c r="AP97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -10345,8 +10585,11 @@
       <c r="AO98" s="3">
         <v>0</v>
       </c>
+      <c r="AP98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -10464,127 +10707,133 @@
       <c r="AO99" s="3">
         <v>0</v>
       </c>
+      <c r="AP99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-280500</v>
+      </c>
+      <c r="E100" s="3">
         <v>-154400</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-213300</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>49700</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-380300</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-71200</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>166800</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-206800</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>283300</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-94100</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-123900</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-84100</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-91400</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-59900</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-28400</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-218600</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-5600</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-18000</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-17100</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-41200</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>120800</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-35600</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-155100</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-128300</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>298000</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-81800</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-212900</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-256400</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>3800</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-75600</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-24800</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>-112800</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>-76300</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>-16800</v>
       </c>
-      <c r="AK100" s="3">
+      <c r="AL100" s="3">
         <v>-19700</v>
       </c>
-      <c r="AL100" s="3">
+      <c r="AM100" s="3">
         <v>-78700</v>
       </c>
-      <c r="AM100" s="3">
+      <c r="AN100" s="3">
         <v>-34200</v>
       </c>
-      <c r="AN100" s="3">
+      <c r="AO100" s="3">
         <v>-27600</v>
       </c>
-      <c r="AO100" s="3">
+      <c r="AP100" s="3">
         <v>-26600</v>
       </c>
     </row>
-    <row r="101" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -10624,8 +10873,8 @@
       <c r="O101" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P101" s="3">
-        <v>0</v>
+      <c r="P101" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="Q101" s="3">
         <v>0</v>
@@ -10702,123 +10951,129 @@
       <c r="AO101" s="3">
         <v>0</v>
       </c>
+      <c r="AP101" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="102" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-255200</v>
+      </c>
+      <c r="E102" s="3">
         <v>385900</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-95400</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>132700</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-78400</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>10300</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-35700</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>70000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>47500</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-16900</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-76600</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>82300</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-69300</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>25500</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-2600</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>17000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-18200</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-3400</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>9700</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-138500</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>185900</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-90700</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-114500</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-113800</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>312800</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>2800</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-9500</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>7600</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>6400</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>4500</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>-2300</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>4800</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>6400</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>-8400</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AL102" s="3">
         <v>4800</v>
       </c>
-      <c r="AL102" s="3">
+      <c r="AM102" s="3">
         <v>4400</v>
       </c>
-      <c r="AM102" s="3">
+      <c r="AN102" s="3">
         <v>3300</v>
       </c>
-      <c r="AN102" s="3">
+      <c r="AO102" s="3">
         <v>-8900</v>
       </c>
-      <c r="AO102" s="3">
+      <c r="AP102" s="3">
         <v>-9100</v>
       </c>
     </row>
